--- a/GameDesign/Excel/Gacha.xlsx
+++ b/GameDesign/Excel/Gacha.xlsx
@@ -7,7 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="GachaTable" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="GachaItemTable" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="GachaInfoTable" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="GachaCharacterTable" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,10 +415,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A2:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1"/>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
@@ -425,12 +426,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>가챠 TID</t>
+          <t>아이템 가챠 TID</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>가챠 풀 ID</t>
+          <t>가챠 풀 ID (= GachaInfoTID)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -566,6 +567,11 @@
           <t>Ref</t>
         </is>
       </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>GachaInfoTable.GachaInfoTID</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>ItemTable.ItemTID</t>
@@ -575,7 +581,7 @@
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>GachaTID</t>
+          <t>GachaItemTID</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -733,6 +739,1131 @@
       <c r="G15" t="inlineStr">
         <is>
           <t>신화</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A2:G10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>//</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>가챠 풀 ID</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>풀 이름</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>비용 재화</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>단차(1회) 비용</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>10연차 비용</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>설명 (메모 — 로직 미사용)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>C&amp;S</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>eCurrencyType</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Default(Null)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>""</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>GachaInfoTID</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>CostCurrency</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>CostSingle</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>CostMulti</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>구슬 상자</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>500</v>
+      </c>
+      <c r="F9" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>아이템 풀(테스트용 구슬 6종)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>캐릭터 소환</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F10" t="n">
+        <v>10000</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>캐릭터 풀 30종</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A2:G39"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>//</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>캐릭터 가챠 TID</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>가챠 풀 ID (= GachaInfoTID)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>캐릭터 TID</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>지급 수량</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>확률가중치</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>설명 (메모 — 로직 미사용)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>C&amp;S</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Default(Null)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>""</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>GachaInfoTable.GachaInfoTID</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>CharacterTable.CharacterTID</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>GachaCharacterTID</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>GachaId</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>CharacterTID</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>2001</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1001</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>50</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Common 램볼</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>2002</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1007</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>50</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Common 밀개비</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>2003</v>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1008</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>50</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Common 물방개미</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>2004</v>
+      </c>
+      <c r="C13" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1009</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>50</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Common 두더삽</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>2005</v>
+      </c>
+      <c r="C14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1010</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>50</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Common 톱니쥐</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>2006</v>
+      </c>
+      <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1011</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" t="n">
+        <v>50</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Common 살쾡이</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>2007</v>
+      </c>
+      <c r="C16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1002</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" t="n">
+        <v>45</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Uncommon 치키피</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>2008</v>
+      </c>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1003</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="n">
+        <v>45</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Uncommon 펭구렛</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="n">
+        <v>2009</v>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1004</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="n">
+        <v>45</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Uncommon 캐티바</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="n">
+        <v>2010</v>
+      </c>
+      <c r="C19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1005</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" t="n">
+        <v>45</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Uncommon 리프몽</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="n">
+        <v>2011</v>
+      </c>
+      <c r="C20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1006</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" t="n">
+        <v>45</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Uncommon 폭스파크스</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="n">
+        <v>2012</v>
+      </c>
+      <c r="C21" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1012</v>
+      </c>
+      <c r="E21" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" t="n">
+        <v>45</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Uncommon 갈대오리</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="n">
+        <v>2013</v>
+      </c>
+      <c r="C22" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1013</v>
+      </c>
+      <c r="E22" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>45</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Uncommon 뿔사슴이</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="n">
+        <v>2014</v>
+      </c>
+      <c r="C23" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1014</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>45</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Uncommon 솔방울곰</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1015</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" t="n">
+        <v>30</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Rare 해달수</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>2016</v>
+      </c>
+      <c r="C25" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1016</v>
+      </c>
+      <c r="E25" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" t="n">
+        <v>30</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Rare 흙두꺼비</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="n">
+        <v>2017</v>
+      </c>
+      <c r="C26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1017</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" t="n">
+        <v>30</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Rare 광부오소리</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="n">
+        <v>2018</v>
+      </c>
+      <c r="C27" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1018</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" t="n">
+        <v>30</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Rare 도끼늑대</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="n">
+        <v>2019</v>
+      </c>
+      <c r="C28" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1019</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" t="n">
+        <v>30</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Rare 창날매</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="n">
+        <v>2020</v>
+      </c>
+      <c r="C29" t="n">
+        <v>2</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1020</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" t="n">
+        <v>30</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Rare 이삭토끼</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="n">
+        <v>2021</v>
+      </c>
+      <c r="C30" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1021</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" t="n">
+        <v>30</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Rare 산호게</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="n">
+        <v>2022</v>
+      </c>
+      <c r="C31" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1022</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" t="n">
+        <v>20</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Epic 화산도롱뇽</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C32" t="n">
+        <v>2</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1023</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" t="n">
+        <v>20</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Epic 파도고래</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="n">
+        <v>2024</v>
+      </c>
+      <c r="C33" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1024</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" t="n">
+        <v>20</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Epic 대지곰</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="n">
+        <v>2025</v>
+      </c>
+      <c r="C34" t="n">
+        <v>2</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1025</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" t="n">
+        <v>20</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Epic 강철사마귀</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1026</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" t="n">
+        <v>20</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Epic 거목정령</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="n">
+        <v>2027</v>
+      </c>
+      <c r="C36" t="n">
+        <v>2</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1027</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" t="n">
+        <v>9</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Legendary 황금기린</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" t="n">
+        <v>2028</v>
+      </c>
+      <c r="C37" t="n">
+        <v>2</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1028</v>
+      </c>
+      <c r="E37" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" t="n">
+        <v>9</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Legendary 심연이무기</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="n">
+        <v>2029</v>
+      </c>
+      <c r="C38" t="n">
+        <v>2</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1029</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" t="n">
+        <v>9</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Legendary 흑요석골렘</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="n">
+        <v>2030</v>
+      </c>
+      <c r="C39" t="n">
+        <v>2</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1030</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" t="n">
+        <v>3</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Mythic 별빛드래곤</t>
         </is>
       </c>
     </row>

--- a/GameDesign/Excel/Gacha.xlsx
+++ b/GameDesign/Excel/Gacha.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,16 +27,29 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -44,12 +57,44 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -124,6 +169,51 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>excel-table-creator</author>
+  </authors>
+  <commentList>
+    <comment ref="C2" authorId="0" shapeId="0">
+      <text>
+        <t>가챠 풀 ID (= GachaInfoTID)</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>excel-table-creator</author>
+  </authors>
+  <commentList>
+    <comment ref="E2" authorId="0" shapeId="0">
+      <text>
+        <t>단차(1회) 비용</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>excel-table-creator</author>
+  </authors>
+  <commentList>
+    <comment ref="C2" authorId="0" shapeId="0">
+      <text>
+        <t>가챠 풀 ID (= GachaInfoTID)</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -410,333 +500,362 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:G15"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+  </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>//</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>아이템 가챠 TID</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>가챠 풀 ID (= GachaInfoTID)</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>가챠 풀 ID</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>아이템 TID</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>지급 수량</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>확률가중치</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>설명 (메모 — 로직 미사용)</t>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>메모</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>C&amp;S</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>Min</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="3" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>Max</t>
         </is>
       </c>
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="3" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Default(Null)</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="B7" s="3" t="n"/>
+      <c r="C7" s="3" t="n"/>
+      <c r="D7" s="3" t="n"/>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="n"/>
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>""</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>Ref</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="B8" s="3" t="n"/>
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>GachaInfoTable.GachaInfoTID</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>ItemTable.ItemTID</t>
         </is>
       </c>
+      <c r="E8" s="3" t="n"/>
+      <c r="F8" s="3" t="n"/>
+      <c r="G8" s="3" t="n"/>
     </row>
     <row r="9">
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>GachaItemTID</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>GachaId</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>ItemTID</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>Weight</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" t="n">
+      <c r="B10" s="5" t="n">
         <v>1001</v>
       </c>
-      <c r="C10" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" t="n">
+      <c r="C10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="5" t="n">
         <v>100001</v>
       </c>
-      <c r="E10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" t="n">
+      <c r="E10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="5" t="n">
         <v>640</v>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>일반</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" t="n">
+      <c r="B11" s="5" t="n">
         <v>1002</v>
       </c>
-      <c r="C11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" t="n">
+      <c r="C11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="5" t="n">
         <v>100002</v>
       </c>
-      <c r="E11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" t="n">
+      <c r="E11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="5" t="n">
         <v>200</v>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>고급</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" t="n">
+      <c r="B12" s="5" t="n">
         <v>1003</v>
       </c>
-      <c r="C12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" t="n">
+      <c r="C12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="5" t="n">
         <v>100003</v>
       </c>
-      <c r="E12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" t="n">
+      <c r="E12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="5" t="n">
         <v>100</v>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>희귀</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" t="n">
+      <c r="B13" s="5" t="n">
         <v>1004</v>
       </c>
-      <c r="C13" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" t="n">
+      <c r="C13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="5" t="n">
         <v>100004</v>
       </c>
-      <c r="E13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" t="n">
+      <c r="E13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="5" t="n">
         <v>40</v>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>영웅</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" t="n">
+      <c r="B14" s="5" t="n">
         <v>1005</v>
       </c>
-      <c r="C14" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" t="n">
+      <c r="C14" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="5" t="n">
         <v>100005</v>
       </c>
-      <c r="E14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" t="n">
+      <c r="E14" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>전설</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" t="n">
+      <c r="B15" s="5" t="n">
         <v>1006</v>
       </c>
-      <c r="C15" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" t="n">
+      <c r="C15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="5" t="n">
         <v>100006</v>
       </c>
-      <c r="E15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" t="n">
+      <c r="E15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>신화</t>
         </is>
@@ -744,249 +863,266 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:G10"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>//</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>가챠 풀 ID</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>풀 이름</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>비용 재화</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>단차(1회) 비용</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>단차 비용</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>10연차 비용</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>설명 (메모 — 로직 미사용)</t>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>메모</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>C&amp;S</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>eCurrencyType</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>long</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>long</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>Min</t>
         </is>
       </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1</v>
-      </c>
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="3" t="n"/>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="3" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>Max</t>
         </is>
       </c>
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="3" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Default(Null)</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="B7" s="3" t="n"/>
+      <c r="C7" s="3" t="n"/>
+      <c r="D7" s="3" t="n"/>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="n"/>
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>""</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>GachaInfoTID</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>CostCurrency</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>CostSingle</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>CostMulti</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" t="inlineStr">
+      <c r="B9" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>구슬 상자</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" s="5" t="n">
         <v>500</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="5" t="n">
         <v>5000</v>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" s="6" t="inlineStr">
         <is>
           <t>아이템 풀(테스트용 구슬 6종)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" t="n">
-        <v>2</v>
-      </c>
-      <c r="C10" t="inlineStr">
+      <c r="B10" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>캐릭터 소환</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="6" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" s="5" t="n">
         <v>1000</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="5" t="n">
         <v>10000</v>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>캐릭터 풀 30종</t>
         </is>
@@ -994,874 +1130,895 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:G39"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>//</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>캐릭터 가챠 TID</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>가챠 풀 ID (= GachaInfoTID)</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>가챠 풀 ID</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>캐릭터 TID</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>지급 수량</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>확률가중치</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>설명 (메모 — 로직 미사용)</t>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>메모</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>C&amp;S</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>Min</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="3" t="n"/>
+      <c r="E5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="3" t="n"/>
+      <c r="G5" s="3" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>Max</t>
         </is>
       </c>
+      <c r="B6" s="3" t="n"/>
+      <c r="C6" s="3" t="n"/>
+      <c r="D6" s="3" t="n"/>
+      <c r="E6" s="3" t="n"/>
+      <c r="F6" s="3" t="n"/>
+      <c r="G6" s="3" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Default(Null)</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="B7" s="3" t="n"/>
+      <c r="C7" s="3" t="n"/>
+      <c r="D7" s="3" t="n"/>
+      <c r="E7" s="3" t="n"/>
+      <c r="F7" s="3" t="n"/>
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>""</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>Ref</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="B8" s="3" t="n"/>
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>GachaInfoTable.GachaInfoTID</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>CharacterTable.CharacterTID</t>
         </is>
       </c>
+      <c r="E8" s="3" t="n"/>
+      <c r="F8" s="3" t="n"/>
+      <c r="G8" s="3" t="n"/>
     </row>
     <row r="9">
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>GachaCharacterTID</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>GachaId</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>CharacterTID</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>Weight</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" t="n">
+      <c r="B10" s="5" t="n">
         <v>2001</v>
       </c>
-      <c r="C10" t="n">
-        <v>2</v>
-      </c>
-      <c r="D10" t="n">
+      <c r="C10" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" s="5" t="n">
         <v>1001</v>
       </c>
-      <c r="E10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" t="n">
+      <c r="E10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" s="6" t="inlineStr">
         <is>
           <t>Common 램볼</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" t="n">
+      <c r="B11" s="5" t="n">
         <v>2002</v>
       </c>
-      <c r="C11" t="n">
-        <v>2</v>
-      </c>
-      <c r="D11" t="n">
+      <c r="C11" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" s="5" t="n">
         <v>1007</v>
       </c>
-      <c r="E11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" t="n">
+      <c r="E11" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" s="6" t="inlineStr">
         <is>
           <t>Common 밀개비</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" t="n">
+      <c r="B12" s="5" t="n">
         <v>2003</v>
       </c>
-      <c r="C12" t="n">
-        <v>2</v>
-      </c>
-      <c r="D12" t="n">
+      <c r="C12" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" s="5" t="n">
         <v>1008</v>
       </c>
-      <c r="E12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" t="n">
+      <c r="E12" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" s="6" t="inlineStr">
         <is>
           <t>Common 물방개미</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" t="n">
+      <c r="B13" s="5" t="n">
         <v>2004</v>
       </c>
-      <c r="C13" t="n">
-        <v>2</v>
-      </c>
-      <c r="D13" t="n">
+      <c r="C13" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" s="5" t="n">
         <v>1009</v>
       </c>
-      <c r="E13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" t="n">
+      <c r="E13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G13" s="6" t="inlineStr">
         <is>
           <t>Common 두더삽</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" t="n">
+      <c r="B14" s="5" t="n">
         <v>2005</v>
       </c>
-      <c r="C14" t="n">
-        <v>2</v>
-      </c>
-      <c r="D14" t="n">
+      <c r="C14" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" s="5" t="n">
         <v>1010</v>
       </c>
-      <c r="E14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" t="n">
+      <c r="E14" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G14" s="6" t="inlineStr">
         <is>
           <t>Common 톱니쥐</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" t="n">
+      <c r="B15" s="5" t="n">
         <v>2006</v>
       </c>
-      <c r="C15" t="n">
-        <v>2</v>
-      </c>
-      <c r="D15" t="n">
+      <c r="C15" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" s="5" t="n">
         <v>1011</v>
       </c>
-      <c r="E15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" t="n">
+      <c r="E15" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G15" s="6" t="inlineStr">
         <is>
           <t>Common 살쾡이</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" t="n">
+      <c r="B16" s="5" t="n">
         <v>2007</v>
       </c>
-      <c r="C16" t="n">
-        <v>2</v>
-      </c>
-      <c r="D16" t="n">
+      <c r="C16" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" s="5" t="n">
         <v>1002</v>
       </c>
-      <c r="E16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" t="n">
+      <c r="E16" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="5" t="n">
         <v>45</v>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G16" s="6" t="inlineStr">
         <is>
           <t>Uncommon 치키피</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" t="n">
+      <c r="B17" s="5" t="n">
         <v>2008</v>
       </c>
-      <c r="C17" t="n">
-        <v>2</v>
-      </c>
-      <c r="D17" t="n">
+      <c r="C17" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" s="5" t="n">
         <v>1003</v>
       </c>
-      <c r="E17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F17" t="n">
+      <c r="E17" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="5" t="n">
         <v>45</v>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G17" s="6" t="inlineStr">
         <is>
           <t>Uncommon 펭구렛</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" t="n">
+      <c r="B18" s="5" t="n">
         <v>2009</v>
       </c>
-      <c r="C18" t="n">
-        <v>2</v>
-      </c>
-      <c r="D18" t="n">
+      <c r="C18" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" s="5" t="n">
         <v>1004</v>
       </c>
-      <c r="E18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" t="n">
+      <c r="E18" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="5" t="n">
         <v>45</v>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G18" s="6" t="inlineStr">
         <is>
           <t>Uncommon 캐티바</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" t="n">
+      <c r="B19" s="5" t="n">
         <v>2010</v>
       </c>
-      <c r="C19" t="n">
-        <v>2</v>
-      </c>
-      <c r="D19" t="n">
+      <c r="C19" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" s="5" t="n">
         <v>1005</v>
       </c>
-      <c r="E19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" t="n">
+      <c r="E19" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="5" t="n">
         <v>45</v>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G19" s="6" t="inlineStr">
         <is>
           <t>Uncommon 리프몽</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" t="n">
+      <c r="B20" s="5" t="n">
         <v>2011</v>
       </c>
-      <c r="C20" t="n">
-        <v>2</v>
-      </c>
-      <c r="D20" t="n">
+      <c r="C20" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" s="5" t="n">
         <v>1006</v>
       </c>
-      <c r="E20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" t="n">
+      <c r="E20" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="5" t="n">
         <v>45</v>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G20" s="6" t="inlineStr">
         <is>
           <t>Uncommon 폭스파크스</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" t="n">
+      <c r="B21" s="5" t="n">
         <v>2012</v>
       </c>
-      <c r="C21" t="n">
-        <v>2</v>
-      </c>
-      <c r="D21" t="n">
+      <c r="C21" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" s="5" t="n">
         <v>1012</v>
       </c>
-      <c r="E21" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" t="n">
+      <c r="E21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="5" t="n">
         <v>45</v>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G21" s="6" t="inlineStr">
         <is>
           <t>Uncommon 갈대오리</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" t="n">
+      <c r="B22" s="5" t="n">
         <v>2013</v>
       </c>
-      <c r="C22" t="n">
-        <v>2</v>
-      </c>
-      <c r="D22" t="n">
+      <c r="C22" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" s="5" t="n">
         <v>1013</v>
       </c>
-      <c r="E22" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" t="n">
+      <c r="E22" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="5" t="n">
         <v>45</v>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G22" s="6" t="inlineStr">
         <is>
           <t>Uncommon 뿔사슴이</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" t="n">
+      <c r="B23" s="5" t="n">
         <v>2014</v>
       </c>
-      <c r="C23" t="n">
-        <v>2</v>
-      </c>
-      <c r="D23" t="n">
+      <c r="C23" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" s="5" t="n">
         <v>1014</v>
       </c>
-      <c r="E23" t="n">
-        <v>1</v>
-      </c>
-      <c r="F23" t="n">
+      <c r="E23" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="5" t="n">
         <v>45</v>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G23" s="6" t="inlineStr">
         <is>
           <t>Uncommon 솔방울곰</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" t="n">
+      <c r="B24" s="5" t="n">
         <v>2015</v>
       </c>
-      <c r="C24" t="n">
-        <v>2</v>
-      </c>
-      <c r="D24" t="n">
+      <c r="C24" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" s="5" t="n">
         <v>1015</v>
       </c>
-      <c r="E24" t="n">
-        <v>1</v>
-      </c>
-      <c r="F24" t="n">
+      <c r="E24" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G24" s="6" t="inlineStr">
         <is>
           <t>Rare 해달수</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="B25" t="n">
+      <c r="B25" s="5" t="n">
         <v>2016</v>
       </c>
-      <c r="C25" t="n">
-        <v>2</v>
-      </c>
-      <c r="D25" t="n">
+      <c r="C25" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" s="5" t="n">
         <v>1016</v>
       </c>
-      <c r="E25" t="n">
-        <v>1</v>
-      </c>
-      <c r="F25" t="n">
+      <c r="E25" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G25" s="6" t="inlineStr">
         <is>
           <t>Rare 흙두꺼비</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" t="n">
+      <c r="B26" s="5" t="n">
         <v>2017</v>
       </c>
-      <c r="C26" t="n">
-        <v>2</v>
-      </c>
-      <c r="D26" t="n">
+      <c r="C26" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" s="5" t="n">
         <v>1017</v>
       </c>
-      <c r="E26" t="n">
-        <v>1</v>
-      </c>
-      <c r="F26" t="n">
+      <c r="E26" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G26" s="6" t="inlineStr">
         <is>
           <t>Rare 광부오소리</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" t="n">
+      <c r="B27" s="5" t="n">
         <v>2018</v>
       </c>
-      <c r="C27" t="n">
-        <v>2</v>
-      </c>
-      <c r="D27" t="n">
+      <c r="C27" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" s="5" t="n">
         <v>1018</v>
       </c>
-      <c r="E27" t="n">
-        <v>1</v>
-      </c>
-      <c r="F27" t="n">
+      <c r="E27" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G27" s="6" t="inlineStr">
         <is>
           <t>Rare 도끼늑대</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="B28" t="n">
+      <c r="B28" s="5" t="n">
         <v>2019</v>
       </c>
-      <c r="C28" t="n">
-        <v>2</v>
-      </c>
-      <c r="D28" t="n">
+      <c r="C28" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" s="5" t="n">
         <v>1019</v>
       </c>
-      <c r="E28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F28" t="n">
+      <c r="E28" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G28" s="6" t="inlineStr">
         <is>
           <t>Rare 창날매</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="B29" t="n">
+      <c r="B29" s="5" t="n">
         <v>2020</v>
       </c>
-      <c r="C29" t="n">
-        <v>2</v>
-      </c>
-      <c r="D29" t="n">
+      <c r="C29" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D29" s="5" t="n">
         <v>1020</v>
       </c>
-      <c r="E29" t="n">
-        <v>1</v>
-      </c>
-      <c r="F29" t="n">
+      <c r="E29" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G29" s="6" t="inlineStr">
         <is>
           <t>Rare 이삭토끼</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" t="n">
+      <c r="B30" s="5" t="n">
         <v>2021</v>
       </c>
-      <c r="C30" t="n">
-        <v>2</v>
-      </c>
-      <c r="D30" t="n">
+      <c r="C30" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" s="5" t="n">
         <v>1021</v>
       </c>
-      <c r="E30" t="n">
-        <v>1</v>
-      </c>
-      <c r="F30" t="n">
+      <c r="E30" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" s="5" t="n">
         <v>30</v>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G30" s="6" t="inlineStr">
         <is>
           <t>Rare 산호게</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="B31" t="n">
+      <c r="B31" s="5" t="n">
         <v>2022</v>
       </c>
-      <c r="C31" t="n">
-        <v>2</v>
-      </c>
-      <c r="D31" t="n">
+      <c r="C31" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" s="5" t="n">
         <v>1022</v>
       </c>
-      <c r="E31" t="n">
-        <v>1</v>
-      </c>
-      <c r="F31" t="n">
+      <c r="E31" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G31" s="6" t="inlineStr">
         <is>
           <t>Epic 화산도롱뇽</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="B32" t="n">
+      <c r="B32" s="5" t="n">
         <v>2023</v>
       </c>
-      <c r="C32" t="n">
-        <v>2</v>
-      </c>
-      <c r="D32" t="n">
+      <c r="C32" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D32" s="5" t="n">
         <v>1023</v>
       </c>
-      <c r="E32" t="n">
-        <v>1</v>
-      </c>
-      <c r="F32" t="n">
+      <c r="E32" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G32" s="6" t="inlineStr">
         <is>
           <t>Epic 파도고래</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="B33" t="n">
+      <c r="B33" s="5" t="n">
         <v>2024</v>
       </c>
-      <c r="C33" t="n">
-        <v>2</v>
-      </c>
-      <c r="D33" t="n">
+      <c r="C33" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" s="5" t="n">
         <v>1024</v>
       </c>
-      <c r="E33" t="n">
-        <v>1</v>
-      </c>
-      <c r="F33" t="n">
+      <c r="E33" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G33" s="6" t="inlineStr">
         <is>
           <t>Epic 대지곰</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="B34" t="n">
+      <c r="B34" s="5" t="n">
         <v>2025</v>
       </c>
-      <c r="C34" t="n">
-        <v>2</v>
-      </c>
-      <c r="D34" t="n">
+      <c r="C34" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D34" s="5" t="n">
         <v>1025</v>
       </c>
-      <c r="E34" t="n">
-        <v>1</v>
-      </c>
-      <c r="F34" t="n">
+      <c r="E34" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G34" s="6" t="inlineStr">
         <is>
           <t>Epic 강철사마귀</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="B35" t="n">
+      <c r="B35" s="5" t="n">
         <v>2026</v>
       </c>
-      <c r="C35" t="n">
-        <v>2</v>
-      </c>
-      <c r="D35" t="n">
+      <c r="C35" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D35" s="5" t="n">
         <v>1026</v>
       </c>
-      <c r="E35" t="n">
-        <v>1</v>
-      </c>
-      <c r="F35" t="n">
+      <c r="E35" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G35" s="6" t="inlineStr">
         <is>
           <t>Epic 거목정령</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="B36" t="n">
+      <c r="B36" s="5" t="n">
         <v>2027</v>
       </c>
-      <c r="C36" t="n">
-        <v>2</v>
-      </c>
-      <c r="D36" t="n">
+      <c r="C36" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D36" s="5" t="n">
         <v>1027</v>
       </c>
-      <c r="E36" t="n">
-        <v>1</v>
-      </c>
-      <c r="F36" t="n">
+      <c r="E36" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G36" s="6" t="inlineStr">
         <is>
           <t>Legendary 황금기린</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="B37" t="n">
+      <c r="B37" s="5" t="n">
         <v>2028</v>
       </c>
-      <c r="C37" t="n">
-        <v>2</v>
-      </c>
-      <c r="D37" t="n">
+      <c r="C37" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D37" s="5" t="n">
         <v>1028</v>
       </c>
-      <c r="E37" t="n">
-        <v>1</v>
-      </c>
-      <c r="F37" t="n">
+      <c r="E37" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G37" s="6" t="inlineStr">
         <is>
           <t>Legendary 심연이무기</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="B38" t="n">
+      <c r="B38" s="5" t="n">
         <v>2029</v>
       </c>
-      <c r="C38" t="n">
-        <v>2</v>
-      </c>
-      <c r="D38" t="n">
+      <c r="C38" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D38" s="5" t="n">
         <v>1029</v>
       </c>
-      <c r="E38" t="n">
-        <v>1</v>
-      </c>
-      <c r="F38" t="n">
+      <c r="E38" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G38" s="6" t="inlineStr">
         <is>
           <t>Legendary 흑요석골렘</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="B39" t="n">
+      <c r="B39" s="5" t="n">
         <v>2030</v>
       </c>
-      <c r="C39" t="n">
-        <v>2</v>
-      </c>
-      <c r="D39" t="n">
+      <c r="C39" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D39" s="5" t="n">
         <v>1030</v>
       </c>
-      <c r="E39" t="n">
-        <v>1</v>
-      </c>
-      <c r="F39" t="n">
+      <c r="E39" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="G39" s="6" t="inlineStr">
         <is>
           <t>Mythic 별빛드래곤</t>
         </is>
@@ -1869,5 +2026,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing r:id="anysvml"/>
 </worksheet>
 </file>
--- a/GameDesign/Excel/Gacha.xlsx
+++ b/GameDesign/Excel/Gacha.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,8 +35,23 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -48,8 +63,13 @@
         <fgColor theme="9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF79646"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -71,11 +91,12 @@
         <color indexed="64"/>
       </bottom>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -94,6 +115,28 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -517,345 +560,360 @@
     <col width="13" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1"/>
+    <row r="1">
+      <c r="A1" s="13" t="n"/>
+      <c r="B1" s="13" t="n"/>
+      <c r="C1" s="13" t="n"/>
+      <c r="D1" s="13" t="n"/>
+      <c r="E1" s="13" t="n"/>
+      <c r="F1" s="13" t="n"/>
+      <c r="G1" s="13" t="n"/>
+    </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>//</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>아이템 가챠 TID</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>가챠 풀 ID</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>아이템 TID</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="8" t="inlineStr">
         <is>
           <t>지급 수량</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="8" t="inlineStr">
         <is>
           <t>확률가중치</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="8" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>C&amp;S</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="9" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="9" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="9" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="9" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="9" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="9" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="9" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="9" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="9" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Min</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="3" t="n"/>
-      <c r="G5" s="3" t="n"/>
+      <c r="B5" s="9" t="n"/>
+      <c r="C5" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="9" t="n"/>
+      <c r="E5" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="9" t="n"/>
+      <c r="G5" s="9" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>Max</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n"/>
-      <c r="C6" s="3" t="n"/>
-      <c r="D6" s="3" t="n"/>
-      <c r="E6" s="3" t="n"/>
-      <c r="F6" s="3" t="n"/>
-      <c r="G6" s="3" t="n"/>
+      <c r="B6" s="9" t="n"/>
+      <c r="C6" s="9" t="n"/>
+      <c r="D6" s="9" t="n"/>
+      <c r="E6" s="9" t="n"/>
+      <c r="F6" s="9" t="n"/>
+      <c r="G6" s="9" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>Default(Null)</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n"/>
-      <c r="C7" s="3" t="n"/>
-      <c r="D7" s="3" t="n"/>
-      <c r="E7" s="3" t="n"/>
-      <c r="F7" s="3" t="n"/>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="B7" s="9" t="n"/>
+      <c r="C7" s="9" t="n"/>
+      <c r="D7" s="9" t="n"/>
+      <c r="E7" s="9" t="n"/>
+      <c r="F7" s="9" t="n"/>
+      <c r="G7" s="9" t="inlineStr">
         <is>
           <t>""</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>Ref</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n"/>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="B8" s="9" t="n"/>
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>GachaInfoTable.GachaInfoTID</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="9" t="inlineStr">
         <is>
           <t>ItemTable.ItemTID</t>
         </is>
       </c>
-      <c r="E8" s="3" t="n"/>
-      <c r="F8" s="3" t="n"/>
-      <c r="G8" s="3" t="n"/>
+      <c r="E8" s="9" t="n"/>
+      <c r="F8" s="9" t="n"/>
+      <c r="G8" s="9" t="n"/>
     </row>
     <row r="9">
-      <c r="B9" s="4" t="inlineStr">
+      <c r="A9" s="13" t="n"/>
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>GachaItemTID</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>GachaId</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="10" t="inlineStr">
         <is>
           <t>ItemTID</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" s="10" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F9" s="10" t="inlineStr">
         <is>
           <t>Weight</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="10" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="5" t="n">
+      <c r="A10" s="13" t="n"/>
+      <c r="B10" s="11" t="n">
         <v>1001</v>
       </c>
-      <c r="C10" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" s="5" t="n">
+      <c r="C10" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="11" t="n">
         <v>100001</v>
       </c>
-      <c r="E10" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="5" t="n">
+      <c r="E10" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="11" t="n">
         <v>640</v>
       </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="G10" s="12" t="inlineStr">
         <is>
           <t>일반</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="5" t="n">
+      <c r="A11" s="13" t="n"/>
+      <c r="B11" s="11" t="n">
         <v>1002</v>
       </c>
-      <c r="C11" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D11" s="5" t="n">
+      <c r="C11" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="11" t="n">
         <v>100002</v>
       </c>
-      <c r="E11" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" s="5" t="n">
+      <c r="E11" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="11" t="n">
         <v>200</v>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G11" s="12" t="inlineStr">
         <is>
           <t>고급</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="5" t="n">
+      <c r="A12" s="13" t="n"/>
+      <c r="B12" s="11" t="n">
         <v>1003</v>
       </c>
-      <c r="C12" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D12" s="5" t="n">
+      <c r="C12" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" s="11" t="n">
         <v>100003</v>
       </c>
-      <c r="E12" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" s="5" t="n">
+      <c r="E12" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="11" t="n">
         <v>100</v>
       </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="G12" s="12" t="inlineStr">
         <is>
           <t>희귀</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="5" t="n">
+      <c r="A13" s="13" t="n"/>
+      <c r="B13" s="11" t="n">
         <v>1004</v>
       </c>
-      <c r="C13" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D13" s="5" t="n">
+      <c r="C13" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="11" t="n">
         <v>100004</v>
       </c>
-      <c r="E13" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" s="5" t="n">
+      <c r="E13" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="11" t="n">
         <v>40</v>
       </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="G13" s="12" t="inlineStr">
         <is>
           <t>영웅</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="5" t="n">
+      <c r="A14" s="13" t="n"/>
+      <c r="B14" s="11" t="n">
         <v>1005</v>
       </c>
-      <c r="C14" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" s="5" t="n">
+      <c r="C14" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="11" t="n">
         <v>100005</v>
       </c>
-      <c r="E14" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" s="5" t="n">
+      <c r="E14" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="G14" s="12" t="inlineStr">
         <is>
           <t>전설</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="5" t="n">
+      <c r="A15" s="13" t="n"/>
+      <c r="B15" s="11" t="n">
         <v>1006</v>
       </c>
-      <c r="C15" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D15" s="5" t="n">
+      <c r="C15" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="11" t="n">
         <v>100006</v>
       </c>
-      <c r="E15" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" s="5" t="n">
+      <c r="E15" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="11" t="n">
         <v>5</v>
       </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="G15" s="12" t="inlineStr">
         <is>
           <t>신화</t>
         </is>
@@ -885,244 +943,255 @@
     <col width="30" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1"/>
+    <row r="1">
+      <c r="A1" s="13" t="n"/>
+      <c r="B1" s="13" t="n"/>
+      <c r="C1" s="13" t="n"/>
+      <c r="D1" s="13" t="n"/>
+      <c r="E1" s="13" t="n"/>
+      <c r="F1" s="13" t="n"/>
+      <c r="G1" s="13" t="n"/>
+    </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>//</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>가챠 풀 ID</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>풀 이름</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>비용 재화</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="8" t="inlineStr">
         <is>
           <t>단차 비용</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="8" t="inlineStr">
         <is>
           <t>10연차 비용</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="8" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>C&amp;S</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="9" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="9" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="9" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="9" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="9" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="9" t="inlineStr">
         <is>
           <t>eCurrencyType</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="9" t="inlineStr">
         <is>
           <t>long</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="9" t="inlineStr">
         <is>
           <t>long</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="9" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Min</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="3" t="n"/>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" s="3" t="n"/>
+      <c r="B5" s="9" t="n"/>
+      <c r="C5" s="9" t="n"/>
+      <c r="D5" s="9" t="n"/>
+      <c r="E5" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="9" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>Max</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n"/>
-      <c r="C6" s="3" t="n"/>
-      <c r="D6" s="3" t="n"/>
-      <c r="E6" s="3" t="n"/>
-      <c r="F6" s="3" t="n"/>
-      <c r="G6" s="3" t="n"/>
+      <c r="B6" s="9" t="n"/>
+      <c r="C6" s="9" t="n"/>
+      <c r="D6" s="9" t="n"/>
+      <c r="E6" s="9" t="n"/>
+      <c r="F6" s="9" t="n"/>
+      <c r="G6" s="9" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>Default(Null)</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n"/>
-      <c r="C7" s="3" t="n"/>
-      <c r="D7" s="3" t="n"/>
-      <c r="E7" s="3" t="n"/>
-      <c r="F7" s="3" t="n"/>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="B7" s="9" t="n"/>
+      <c r="C7" s="9" t="n"/>
+      <c r="D7" s="9" t="n"/>
+      <c r="E7" s="9" t="n"/>
+      <c r="F7" s="9" t="n"/>
+      <c r="G7" s="9" t="inlineStr">
         <is>
           <t>""</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="4" t="inlineStr">
+      <c r="A8" s="13" t="n"/>
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>GachaInfoTID</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>CostCurrency</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="10" t="inlineStr">
         <is>
           <t>CostSingle</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="F8" s="10" t="inlineStr">
         <is>
           <t>CostMulti</t>
         </is>
       </c>
-      <c r="G8" s="4" t="inlineStr">
+      <c r="G8" s="10" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="A9" s="13" t="n"/>
+      <c r="B9" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
         <is>
           <t>구슬 상자</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="12" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="E9" s="5" t="n">
+      <c r="E9" s="11" t="n">
         <v>500</v>
       </c>
-      <c r="F9" s="5" t="n">
+      <c r="F9" s="11" t="n">
         <v>5000</v>
       </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="G9" s="12" t="inlineStr">
         <is>
           <t>아이템 풀(테스트용 구슬 6종)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="A10" s="13" t="n"/>
+      <c r="B10" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
         <is>
           <t>캐릭터 소환</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" s="12" t="inlineStr">
         <is>
           <t>Gold</t>
         </is>
       </c>
-      <c r="E10" s="5" t="n">
+      <c r="E10" s="11" t="n">
         <v>1000</v>
       </c>
-      <c r="F10" s="5" t="n">
+      <c r="F10" s="11" t="n">
         <v>10000</v>
       </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="G10" s="12" t="inlineStr">
         <is>
           <t>캐릭터 풀 30종</t>
         </is>
@@ -1152,873 +1221,912 @@
     <col width="22" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1"/>
+    <row r="1">
+      <c r="A1" s="13" t="n"/>
+      <c r="B1" s="13" t="n"/>
+      <c r="C1" s="13" t="n"/>
+      <c r="D1" s="13" t="n"/>
+      <c r="E1" s="13" t="n"/>
+      <c r="F1" s="13" t="n"/>
+      <c r="G1" s="13" t="n"/>
+    </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>//</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="8" t="inlineStr">
         <is>
           <t>캐릭터 가챠 TID</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="8" t="inlineStr">
         <is>
           <t>가챠 풀 ID</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="8" t="inlineStr">
         <is>
           <t>캐릭터 TID</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="8" t="inlineStr">
         <is>
           <t>지급 수량</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="8" t="inlineStr">
         <is>
           <t>확률가중치</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="8" t="inlineStr">
         <is>
           <t>메모</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="14" t="inlineStr">
         <is>
           <t>C&amp;S</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="C3" s="9" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="9" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="9" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="9" t="inlineStr">
         <is>
           <t>a</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" s="14" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="9" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="9" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="9" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="9" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="9" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" s="14" t="inlineStr">
         <is>
           <t>Min</t>
         </is>
       </c>
-      <c r="B5" s="3" t="n"/>
-      <c r="C5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="3" t="n"/>
-      <c r="G5" s="3" t="n"/>
+      <c r="B5" s="9" t="n"/>
+      <c r="C5" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="9" t="n"/>
+      <c r="E5" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="9" t="n"/>
+      <c r="G5" s="9" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>Max</t>
         </is>
       </c>
-      <c r="B6" s="3" t="n"/>
-      <c r="C6" s="3" t="n"/>
-      <c r="D6" s="3" t="n"/>
-      <c r="E6" s="3" t="n"/>
-      <c r="F6" s="3" t="n"/>
-      <c r="G6" s="3" t="n"/>
+      <c r="B6" s="9" t="n"/>
+      <c r="C6" s="9" t="n"/>
+      <c r="D6" s="9" t="n"/>
+      <c r="E6" s="9" t="n"/>
+      <c r="F6" s="9" t="n"/>
+      <c r="G6" s="9" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" s="14" t="inlineStr">
         <is>
           <t>Default(Null)</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n"/>
-      <c r="C7" s="3" t="n"/>
-      <c r="D7" s="3" t="n"/>
-      <c r="E7" s="3" t="n"/>
-      <c r="F7" s="3" t="n"/>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="B7" s="9" t="n"/>
+      <c r="C7" s="9" t="n"/>
+      <c r="D7" s="9" t="n"/>
+      <c r="E7" s="9" t="n"/>
+      <c r="F7" s="9" t="n"/>
+      <c r="G7" s="9" t="inlineStr">
         <is>
           <t>""</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>Ref</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n"/>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="B8" s="9" t="n"/>
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>GachaInfoTable.GachaInfoTID</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D8" s="9" t="inlineStr">
         <is>
           <t>CharacterTable.CharacterTID</t>
         </is>
       </c>
-      <c r="E8" s="3" t="n"/>
-      <c r="F8" s="3" t="n"/>
-      <c r="G8" s="3" t="n"/>
+      <c r="E8" s="9" t="n"/>
+      <c r="F8" s="9" t="n"/>
+      <c r="G8" s="9" t="n"/>
     </row>
     <row r="9">
-      <c r="B9" s="4" t="inlineStr">
+      <c r="A9" s="13" t="n"/>
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>GachaCharacterTID</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>GachaId</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D9" s="10" t="inlineStr">
         <is>
           <t>CharacterTID</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E9" s="10" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="F9" s="10" t="inlineStr">
         <is>
           <t>Weight</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="G9" s="10" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="5" t="n">
+      <c r="A10" s="13" t="n"/>
+      <c r="B10" s="11" t="n">
         <v>2001</v>
       </c>
-      <c r="C10" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D10" s="5" t="n">
+      <c r="C10" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D10" s="11" t="n">
         <v>1001</v>
       </c>
-      <c r="E10" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="5" t="n">
+      <c r="E10" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="11" t="n">
         <v>50</v>
       </c>
-      <c r="G10" s="6" t="inlineStr">
+      <c r="G10" s="12" t="inlineStr">
         <is>
           <t>Common 램볼</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="5" t="n">
+      <c r="A11" s="13" t="n"/>
+      <c r="B11" s="11" t="n">
         <v>2002</v>
       </c>
-      <c r="C11" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D11" s="5" t="n">
+      <c r="C11" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" s="11" t="n">
         <v>1007</v>
       </c>
-      <c r="E11" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" s="5" t="n">
+      <c r="E11" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="11" t="n">
         <v>50</v>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="G11" s="12" t="inlineStr">
         <is>
           <t>Common 밀개비</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="5" t="n">
+      <c r="A12" s="13" t="n"/>
+      <c r="B12" s="11" t="n">
         <v>2003</v>
       </c>
-      <c r="C12" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D12" s="5" t="n">
+      <c r="C12" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" s="11" t="n">
         <v>1008</v>
       </c>
-      <c r="E12" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" s="5" t="n">
+      <c r="E12" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="11" t="n">
         <v>50</v>
       </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="G12" s="12" t="inlineStr">
         <is>
           <t>Common 물방개미</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="5" t="n">
+      <c r="A13" s="13" t="n"/>
+      <c r="B13" s="11" t="n">
         <v>2004</v>
       </c>
-      <c r="C13" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D13" s="5" t="n">
+      <c r="C13" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D13" s="11" t="n">
         <v>1009</v>
       </c>
-      <c r="E13" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" s="5" t="n">
+      <c r="E13" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="11" t="n">
         <v>50</v>
       </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="G13" s="12" t="inlineStr">
         <is>
           <t>Common 두더삽</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="5" t="n">
+      <c r="A14" s="13" t="n"/>
+      <c r="B14" s="11" t="n">
         <v>2005</v>
       </c>
-      <c r="C14" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D14" s="5" t="n">
+      <c r="C14" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" s="11" t="n">
         <v>1010</v>
       </c>
-      <c r="E14" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" s="5" t="n">
+      <c r="E14" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="11" t="n">
         <v>50</v>
       </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="G14" s="12" t="inlineStr">
         <is>
           <t>Common 톱니쥐</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="5" t="n">
+      <c r="A15" s="13" t="n"/>
+      <c r="B15" s="11" t="n">
         <v>2006</v>
       </c>
-      <c r="C15" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D15" s="5" t="n">
+      <c r="C15" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" s="11" t="n">
         <v>1011</v>
       </c>
-      <c r="E15" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" s="5" t="n">
+      <c r="E15" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="11" t="n">
         <v>50</v>
       </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="G15" s="12" t="inlineStr">
         <is>
           <t>Common 살쾡이</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="5" t="n">
+      <c r="A16" s="13" t="n"/>
+      <c r="B16" s="11" t="n">
         <v>2007</v>
       </c>
-      <c r="C16" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D16" s="5" t="n">
+      <c r="C16" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" s="11" t="n">
         <v>1002</v>
       </c>
-      <c r="E16" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" s="5" t="n">
+      <c r="E16" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="11" t="n">
         <v>45</v>
       </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="G16" s="12" t="inlineStr">
         <is>
           <t>Uncommon 치키피</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="5" t="n">
+      <c r="A17" s="13" t="n"/>
+      <c r="B17" s="11" t="n">
         <v>2008</v>
       </c>
-      <c r="C17" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D17" s="5" t="n">
+      <c r="C17" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" s="11" t="n">
         <v>1003</v>
       </c>
-      <c r="E17" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F17" s="5" t="n">
+      <c r="E17" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="11" t="n">
         <v>45</v>
       </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="G17" s="12" t="inlineStr">
         <is>
           <t>Uncommon 펭구렛</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="5" t="n">
+      <c r="A18" s="13" t="n"/>
+      <c r="B18" s="11" t="n">
         <v>2009</v>
       </c>
-      <c r="C18" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D18" s="5" t="n">
+      <c r="C18" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" s="11" t="n">
         <v>1004</v>
       </c>
-      <c r="E18" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" s="5" t="n">
+      <c r="E18" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="11" t="n">
         <v>45</v>
       </c>
-      <c r="G18" s="6" t="inlineStr">
+      <c r="G18" s="12" t="inlineStr">
         <is>
           <t>Uncommon 캐티바</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="5" t="n">
+      <c r="A19" s="13" t="n"/>
+      <c r="B19" s="11" t="n">
         <v>2010</v>
       </c>
-      <c r="C19" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D19" s="5" t="n">
+      <c r="C19" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" s="11" t="n">
         <v>1005</v>
       </c>
-      <c r="E19" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" s="5" t="n">
+      <c r="E19" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="11" t="n">
         <v>45</v>
       </c>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="G19" s="12" t="inlineStr">
         <is>
           <t>Uncommon 리프몽</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="5" t="n">
+      <c r="A20" s="13" t="n"/>
+      <c r="B20" s="11" t="n">
         <v>2011</v>
       </c>
-      <c r="C20" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D20" s="5" t="n">
+      <c r="C20" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" s="11" t="n">
         <v>1006</v>
       </c>
-      <c r="E20" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" s="5" t="n">
+      <c r="E20" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="11" t="n">
         <v>45</v>
       </c>
-      <c r="G20" s="6" t="inlineStr">
+      <c r="G20" s="12" t="inlineStr">
         <is>
           <t>Uncommon 폭스파크스</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="5" t="n">
+      <c r="A21" s="13" t="n"/>
+      <c r="B21" s="11" t="n">
         <v>2012</v>
       </c>
-      <c r="C21" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D21" s="5" t="n">
+      <c r="C21" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" s="11" t="n">
         <v>1012</v>
       </c>
-      <c r="E21" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" s="5" t="n">
+      <c r="E21" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="11" t="n">
         <v>45</v>
       </c>
-      <c r="G21" s="6" t="inlineStr">
+      <c r="G21" s="12" t="inlineStr">
         <is>
           <t>Uncommon 갈대오리</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="5" t="n">
+      <c r="A22" s="13" t="n"/>
+      <c r="B22" s="11" t="n">
         <v>2013</v>
       </c>
-      <c r="C22" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D22" s="5" t="n">
+      <c r="C22" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" s="11" t="n">
         <v>1013</v>
       </c>
-      <c r="E22" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" s="5" t="n">
+      <c r="E22" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="11" t="n">
         <v>45</v>
       </c>
-      <c r="G22" s="6" t="inlineStr">
+      <c r="G22" s="12" t="inlineStr">
         <is>
           <t>Uncommon 뿔사슴이</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="5" t="n">
+      <c r="A23" s="13" t="n"/>
+      <c r="B23" s="11" t="n">
         <v>2014</v>
       </c>
-      <c r="C23" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D23" s="5" t="n">
+      <c r="C23" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" s="11" t="n">
         <v>1014</v>
       </c>
-      <c r="E23" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F23" s="5" t="n">
+      <c r="E23" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="11" t="n">
         <v>45</v>
       </c>
-      <c r="G23" s="6" t="inlineStr">
+      <c r="G23" s="12" t="inlineStr">
         <is>
           <t>Uncommon 솔방울곰</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="5" t="n">
+      <c r="A24" s="13" t="n"/>
+      <c r="B24" s="11" t="n">
         <v>2015</v>
       </c>
-      <c r="C24" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D24" s="5" t="n">
+      <c r="C24" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" s="11" t="n">
         <v>1015</v>
       </c>
-      <c r="E24" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F24" s="5" t="n">
+      <c r="E24" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="G24" s="6" t="inlineStr">
+      <c r="G24" s="12" t="inlineStr">
         <is>
           <t>Rare 해달수</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="5" t="n">
+      <c r="A25" s="13" t="n"/>
+      <c r="B25" s="11" t="n">
         <v>2016</v>
       </c>
-      <c r="C25" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D25" s="5" t="n">
+      <c r="C25" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D25" s="11" t="n">
         <v>1016</v>
       </c>
-      <c r="E25" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F25" s="5" t="n">
+      <c r="E25" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="G25" s="6" t="inlineStr">
+      <c r="G25" s="12" t="inlineStr">
         <is>
           <t>Rare 흙두꺼비</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="5" t="n">
+      <c r="A26" s="13" t="n"/>
+      <c r="B26" s="11" t="n">
         <v>2017</v>
       </c>
-      <c r="C26" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D26" s="5" t="n">
+      <c r="C26" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D26" s="11" t="n">
         <v>1017</v>
       </c>
-      <c r="E26" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F26" s="5" t="n">
+      <c r="E26" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="G26" s="6" t="inlineStr">
+      <c r="G26" s="12" t="inlineStr">
         <is>
           <t>Rare 광부오소리</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="5" t="n">
+      <c r="A27" s="13" t="n"/>
+      <c r="B27" s="11" t="n">
         <v>2018</v>
       </c>
-      <c r="C27" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D27" s="5" t="n">
+      <c r="C27" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" s="11" t="n">
         <v>1018</v>
       </c>
-      <c r="E27" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F27" s="5" t="n">
+      <c r="E27" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="G27" s="6" t="inlineStr">
+      <c r="G27" s="12" t="inlineStr">
         <is>
           <t>Rare 도끼늑대</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="5" t="n">
+      <c r="A28" s="13" t="n"/>
+      <c r="B28" s="11" t="n">
         <v>2019</v>
       </c>
-      <c r="C28" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D28" s="5" t="n">
+      <c r="C28" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D28" s="11" t="n">
         <v>1019</v>
       </c>
-      <c r="E28" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F28" s="5" t="n">
+      <c r="E28" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="G28" s="6" t="inlineStr">
+      <c r="G28" s="12" t="inlineStr">
         <is>
           <t>Rare 창날매</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="5" t="n">
+      <c r="A29" s="13" t="n"/>
+      <c r="B29" s="11" t="n">
         <v>2020</v>
       </c>
-      <c r="C29" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D29" s="5" t="n">
+      <c r="C29" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D29" s="11" t="n">
         <v>1020</v>
       </c>
-      <c r="E29" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F29" s="5" t="n">
+      <c r="E29" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="G29" s="6" t="inlineStr">
+      <c r="G29" s="12" t="inlineStr">
         <is>
           <t>Rare 이삭토끼</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="5" t="n">
+      <c r="A30" s="13" t="n"/>
+      <c r="B30" s="11" t="n">
         <v>2021</v>
       </c>
-      <c r="C30" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D30" s="5" t="n">
+      <c r="C30" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D30" s="11" t="n">
         <v>1021</v>
       </c>
-      <c r="E30" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F30" s="5" t="n">
+      <c r="E30" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="G30" s="6" t="inlineStr">
+      <c r="G30" s="12" t="inlineStr">
         <is>
           <t>Rare 산호게</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="5" t="n">
+      <c r="A31" s="13" t="n"/>
+      <c r="B31" s="11" t="n">
         <v>2022</v>
       </c>
-      <c r="C31" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D31" s="5" t="n">
+      <c r="C31" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" s="11" t="n">
         <v>1022</v>
       </c>
-      <c r="E31" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F31" s="5" t="n">
+      <c r="E31" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="G31" s="6" t="inlineStr">
+      <c r="G31" s="12" t="inlineStr">
         <is>
           <t>Epic 화산도롱뇽</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="5" t="n">
+      <c r="A32" s="13" t="n"/>
+      <c r="B32" s="11" t="n">
         <v>2023</v>
       </c>
-      <c r="C32" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D32" s="5" t="n">
+      <c r="C32" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D32" s="11" t="n">
         <v>1023</v>
       </c>
-      <c r="E32" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F32" s="5" t="n">
+      <c r="E32" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="G32" s="6" t="inlineStr">
+      <c r="G32" s="12" t="inlineStr">
         <is>
           <t>Epic 파도고래</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="5" t="n">
+      <c r="A33" s="13" t="n"/>
+      <c r="B33" s="11" t="n">
         <v>2024</v>
       </c>
-      <c r="C33" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D33" s="5" t="n">
+      <c r="C33" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" s="11" t="n">
         <v>1024</v>
       </c>
-      <c r="E33" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F33" s="5" t="n">
+      <c r="E33" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="G33" s="6" t="inlineStr">
+      <c r="G33" s="12" t="inlineStr">
         <is>
           <t>Epic 대지곰</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="5" t="n">
+      <c r="A34" s="13" t="n"/>
+      <c r="B34" s="11" t="n">
         <v>2025</v>
       </c>
-      <c r="C34" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D34" s="5" t="n">
+      <c r="C34" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D34" s="11" t="n">
         <v>1025</v>
       </c>
-      <c r="E34" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F34" s="5" t="n">
+      <c r="E34" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="G34" s="6" t="inlineStr">
+      <c r="G34" s="12" t="inlineStr">
         <is>
           <t>Epic 강철사마귀</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="5" t="n">
+      <c r="A35" s="13" t="n"/>
+      <c r="B35" s="11" t="n">
         <v>2026</v>
       </c>
-      <c r="C35" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D35" s="5" t="n">
+      <c r="C35" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D35" s="11" t="n">
         <v>1026</v>
       </c>
-      <c r="E35" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F35" s="5" t="n">
+      <c r="E35" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="G35" s="6" t="inlineStr">
+      <c r="G35" s="12" t="inlineStr">
         <is>
           <t>Epic 거목정령</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="5" t="n">
+      <c r="A36" s="13" t="n"/>
+      <c r="B36" s="11" t="n">
         <v>2027</v>
       </c>
-      <c r="C36" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D36" s="5" t="n">
+      <c r="C36" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D36" s="11" t="n">
         <v>1027</v>
       </c>
-      <c r="E36" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F36" s="5" t="n">
+      <c r="E36" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="G36" s="6" t="inlineStr">
+      <c r="G36" s="12" t="inlineStr">
         <is>
           <t>Legendary 황금기린</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="5" t="n">
+      <c r="A37" s="13" t="n"/>
+      <c r="B37" s="11" t="n">
         <v>2028</v>
       </c>
-      <c r="C37" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D37" s="5" t="n">
+      <c r="C37" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D37" s="11" t="n">
         <v>1028</v>
       </c>
-      <c r="E37" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F37" s="5" t="n">
+      <c r="E37" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="G37" s="6" t="inlineStr">
+      <c r="G37" s="12" t="inlineStr">
         <is>
           <t>Legendary 심연이무기</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="5" t="n">
+      <c r="A38" s="13" t="n"/>
+      <c r="B38" s="11" t="n">
         <v>2029</v>
       </c>
-      <c r="C38" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D38" s="5" t="n">
+      <c r="C38" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D38" s="11" t="n">
         <v>1029</v>
       </c>
-      <c r="E38" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F38" s="5" t="n">
+      <c r="E38" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" s="11" t="n">
         <v>9</v>
       </c>
-      <c r="G38" s="6" t="inlineStr">
+      <c r="G38" s="12" t="inlineStr">
         <is>
           <t>Legendary 흑요석골렘</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="5" t="n">
+      <c r="A39" s="13" t="n"/>
+      <c r="B39" s="11" t="n">
         <v>2030</v>
       </c>
-      <c r="C39" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D39" s="5" t="n">
+      <c r="C39" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D39" s="11" t="n">
         <v>1030</v>
       </c>
-      <c r="E39" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="F39" s="5" t="n">
+      <c r="E39" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="G39" s="6" t="inlineStr">
+      <c r="G39" s="12" t="inlineStr">
         <is>
           <t>Mythic 별빛드래곤</t>
         </is>

--- a/GameDesign/Excel/Gacha.xlsx
+++ b/GameDesign/Excel/Gacha.xlsx
@@ -10,6 +10,7 @@
     <sheet name="GachaItemTable" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="GachaInfoTable" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="GachaCharacterTable" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="GachaEquipTable" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -245,6 +246,21 @@
 </file>
 
 <file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>excel-table-creator</author>
+  </authors>
+  <commentList>
+    <comment ref="C2" authorId="0" shapeId="0">
+      <text>
+        <t>가챠 풀 ID (= GachaInfoTID)</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment4.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>excel-table-creator</author>
@@ -931,7 +947,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1194,6 +1210,87 @@
       <c r="G10" s="12" t="inlineStr">
         <is>
           <t>캐릭터 풀 30종</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="n"/>
+      <c r="B11" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>무기 뽑기</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="n">
+        <v>500</v>
+      </c>
+      <c r="F11" s="11" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G11" s="12" t="inlineStr">
+        <is>
+          <t>무기 31종</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="n"/>
+      <c r="B12" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>장신구 뽑기</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="E12" s="11" t="n">
+        <v>300</v>
+      </c>
+      <c r="F12" s="11" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G12" s="12" t="inlineStr">
+        <is>
+          <t>장신구 7종</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="n"/>
+      <c r="B13" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>보석 뽑기</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="n">
+        <v>200</v>
+      </c>
+      <c r="F13" s="11" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G13" s="12" t="inlineStr">
+        <is>
+          <t>보석 31종</t>
         </is>
       </c>
     </row>
@@ -2136,4 +2233,1836 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing r:id="anysvml"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G78"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="25" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="13" t="n"/>
+      <c r="B1" s="13" t="n"/>
+      <c r="C1" s="13" t="n"/>
+      <c r="D1" s="13" t="n"/>
+      <c r="E1" s="13" t="n"/>
+      <c r="F1" s="13" t="n"/>
+      <c r="G1" s="13" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>//</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>장비 가챠 TID</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>가챠 풀 ID</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>장비 TID</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>지급 수량</t>
+        </is>
+      </c>
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>확률가중치</t>
+        </is>
+      </c>
+      <c r="G2" s="8" t="inlineStr">
+        <is>
+          <t>메모</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>C&amp;S</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="G3" s="9" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="n"/>
+      <c r="C5" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="9" t="n"/>
+      <c r="E5" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="9" t="n"/>
+      <c r="G5" s="9" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="n"/>
+      <c r="C6" s="9" t="n"/>
+      <c r="D6" s="9" t="n"/>
+      <c r="E6" s="9" t="n"/>
+      <c r="F6" s="9" t="n"/>
+      <c r="G6" s="9" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>Default(Null)</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="n"/>
+      <c r="C7" s="9" t="n"/>
+      <c r="D7" s="9" t="n"/>
+      <c r="E7" s="9" t="n"/>
+      <c r="F7" s="9" t="n"/>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>""</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="n"/>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>GachaInfoTable.GachaInfoTID</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>EquipTable.EquipTID</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="n"/>
+      <c r="F8" s="9" t="n"/>
+      <c r="G8" s="9" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="n"/>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>GachaEquipTID</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>GachaId</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>EquipTID</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="n"/>
+      <c r="B10" s="11" t="n">
+        <v>3001</v>
+      </c>
+      <c r="C10" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" s="11" t="n">
+        <v>1001</v>
+      </c>
+      <c r="E10" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="11" t="n">
+        <v>640</v>
+      </c>
+      <c r="G10" s="12" t="inlineStr">
+        <is>
+          <t>Common 목검</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="n"/>
+      <c r="B11" s="11" t="n">
+        <v>3002</v>
+      </c>
+      <c r="C11" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" s="11" t="n">
+        <v>1101</v>
+      </c>
+      <c r="E11" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="11" t="n">
+        <v>640</v>
+      </c>
+      <c r="G11" s="12" t="inlineStr">
+        <is>
+          <t>Common 나무 호미</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="n"/>
+      <c r="B12" s="11" t="n">
+        <v>3003</v>
+      </c>
+      <c r="C12" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" s="11" t="n">
+        <v>1201</v>
+      </c>
+      <c r="E12" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="11" t="n">
+        <v>640</v>
+      </c>
+      <c r="G12" s="12" t="inlineStr">
+        <is>
+          <t>Common 대나무 낚싯대</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="n"/>
+      <c r="B13" s="11" t="n">
+        <v>3004</v>
+      </c>
+      <c r="C13" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" s="11" t="n">
+        <v>1301</v>
+      </c>
+      <c r="E13" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="11" t="n">
+        <v>640</v>
+      </c>
+      <c r="G13" s="12" t="inlineStr">
+        <is>
+          <t>Common 돌 곡괭이</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="n"/>
+      <c r="B14" s="11" t="n">
+        <v>3005</v>
+      </c>
+      <c r="C14" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" s="11" t="n">
+        <v>1401</v>
+      </c>
+      <c r="E14" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="11" t="n">
+        <v>640</v>
+      </c>
+      <c r="G14" s="12" t="inlineStr">
+        <is>
+          <t>Common 손도끼</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="n"/>
+      <c r="B15" s="11" t="n">
+        <v>3006</v>
+      </c>
+      <c r="C15" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" s="11" t="n">
+        <v>1501</v>
+      </c>
+      <c r="E15" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>640</v>
+      </c>
+      <c r="G15" s="12" t="inlineStr">
+        <is>
+          <t>Common 사냥용 활</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="n"/>
+      <c r="B16" s="11" t="n">
+        <v>3007</v>
+      </c>
+      <c r="C16" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" s="11" t="n">
+        <v>1002</v>
+      </c>
+      <c r="E16" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="11" t="n">
+        <v>200</v>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon 낚싯대</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="n"/>
+      <c r="B17" s="11" t="n">
+        <v>3008</v>
+      </c>
+      <c r="C17" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" s="11" t="n">
+        <v>1102</v>
+      </c>
+      <c r="E17" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="11" t="n">
+        <v>200</v>
+      </c>
+      <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon 무쇠 호미</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="n"/>
+      <c r="B18" s="11" t="n">
+        <v>3009</v>
+      </c>
+      <c r="C18" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" s="11" t="n">
+        <v>1302</v>
+      </c>
+      <c r="E18" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="11" t="n">
+        <v>200</v>
+      </c>
+      <c r="G18" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon 무쇠 곡괭이</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="n"/>
+      <c r="B19" s="11" t="n">
+        <v>3010</v>
+      </c>
+      <c r="C19" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D19" s="11" t="n">
+        <v>1402</v>
+      </c>
+      <c r="E19" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="11" t="n">
+        <v>200</v>
+      </c>
+      <c r="G19" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon 무쇠 도끼</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="n"/>
+      <c r="B20" s="11" t="n">
+        <v>3011</v>
+      </c>
+      <c r="C20" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" s="11" t="n">
+        <v>1502</v>
+      </c>
+      <c r="E20" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="11" t="n">
+        <v>200</v>
+      </c>
+      <c r="G20" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon 참나무 활</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="n"/>
+      <c r="B21" s="11" t="n">
+        <v>3012</v>
+      </c>
+      <c r="C21" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D21" s="11" t="n">
+        <v>1103</v>
+      </c>
+      <c r="E21" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="G21" s="12" t="inlineStr">
+        <is>
+          <t>Rare 강철 낫</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="n"/>
+      <c r="B22" s="11" t="n">
+        <v>3013</v>
+      </c>
+      <c r="C22" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" s="11" t="n">
+        <v>1203</v>
+      </c>
+      <c r="E22" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="G22" s="12" t="inlineStr">
+        <is>
+          <t>Rare 은사 낚싯대</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="n"/>
+      <c r="B23" s="11" t="n">
+        <v>3014</v>
+      </c>
+      <c r="C23" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D23" s="11" t="n">
+        <v>1303</v>
+      </c>
+      <c r="E23" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="G23" s="12" t="inlineStr">
+        <is>
+          <t>Rare 강철 곡괭이</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="n"/>
+      <c r="B24" s="11" t="n">
+        <v>3015</v>
+      </c>
+      <c r="C24" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D24" s="11" t="n">
+        <v>1403</v>
+      </c>
+      <c r="E24" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="G24" s="12" t="inlineStr">
+        <is>
+          <t>Rare 양날 도끼</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="n"/>
+      <c r="B25" s="11" t="n">
+        <v>3016</v>
+      </c>
+      <c r="C25" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" s="11" t="n">
+        <v>1503</v>
+      </c>
+      <c r="E25" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="G25" s="12" t="inlineStr">
+        <is>
+          <t>Rare 강철 석궁</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="13" t="n"/>
+      <c r="B26" s="11" t="n">
+        <v>3017</v>
+      </c>
+      <c r="C26" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" s="11" t="n">
+        <v>1104</v>
+      </c>
+      <c r="E26" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="G26" s="12" t="inlineStr">
+        <is>
+          <t>Epic 은빛 쟁기</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="13" t="n"/>
+      <c r="B27" s="11" t="n">
+        <v>3018</v>
+      </c>
+      <c r="C27" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D27" s="11" t="n">
+        <v>1204</v>
+      </c>
+      <c r="E27" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="G27" s="12" t="inlineStr">
+        <is>
+          <t>Epic 심해 작살</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="n"/>
+      <c r="B28" s="11" t="n">
+        <v>3019</v>
+      </c>
+      <c r="C28" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" s="11" t="n">
+        <v>1304</v>
+      </c>
+      <c r="E28" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="G28" s="12" t="inlineStr">
+        <is>
+          <t>Epic 흑요석 곡괭이</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="13" t="n"/>
+      <c r="B29" s="11" t="n">
+        <v>3020</v>
+      </c>
+      <c r="C29" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D29" s="11" t="n">
+        <v>1404</v>
+      </c>
+      <c r="E29" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="G29" s="12" t="inlineStr">
+        <is>
+          <t>Epic 백년목 도끼</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="13" t="n"/>
+      <c r="B30" s="11" t="n">
+        <v>3021</v>
+      </c>
+      <c r="C30" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D30" s="11" t="n">
+        <v>1504</v>
+      </c>
+      <c r="E30" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="G30" s="12" t="inlineStr">
+        <is>
+          <t>Epic 은빛 장궁</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="13" t="n"/>
+      <c r="B31" s="11" t="n">
+        <v>3022</v>
+      </c>
+      <c r="C31" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D31" s="11" t="n">
+        <v>1105</v>
+      </c>
+      <c r="E31" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="G31" s="12" t="inlineStr">
+        <is>
+          <t>Legendary 풍년의 괭이</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="13" t="n"/>
+      <c r="B32" s="11" t="n">
+        <v>3023</v>
+      </c>
+      <c r="C32" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D32" s="11" t="n">
+        <v>1205</v>
+      </c>
+      <c r="E32" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F32" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="G32" s="12" t="inlineStr">
+        <is>
+          <t>Legendary 용린 낚싯대</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="13" t="n"/>
+      <c r="B33" s="11" t="n">
+        <v>3024</v>
+      </c>
+      <c r="C33" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D33" s="11" t="n">
+        <v>1305</v>
+      </c>
+      <c r="E33" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="G33" s="12" t="inlineStr">
+        <is>
+          <t>Legendary 미스릴 곡괭이</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="13" t="n"/>
+      <c r="B34" s="11" t="n">
+        <v>3025</v>
+      </c>
+      <c r="C34" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D34" s="11" t="n">
+        <v>1405</v>
+      </c>
+      <c r="E34" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="G34" s="12" t="inlineStr">
+        <is>
+          <t>Legendary 서리강철 도끼</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="13" t="n"/>
+      <c r="B35" s="11" t="n">
+        <v>3026</v>
+      </c>
+      <c r="C35" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D35" s="11" t="n">
+        <v>1505</v>
+      </c>
+      <c r="E35" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F35" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="G35" s="12" t="inlineStr">
+        <is>
+          <t>Legendary 폭풍의 장궁</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="13" t="n"/>
+      <c r="B36" s="11" t="n">
+        <v>3027</v>
+      </c>
+      <c r="C36" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D36" s="11" t="n">
+        <v>1106</v>
+      </c>
+      <c r="E36" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="G36" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 대지모의 호미</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="13" t="n"/>
+      <c r="B37" s="11" t="n">
+        <v>3028</v>
+      </c>
+      <c r="C37" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D37" s="11" t="n">
+        <v>1206</v>
+      </c>
+      <c r="E37" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F37" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="G37" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 해신의 삼지창</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="13" t="n"/>
+      <c r="B38" s="11" t="n">
+        <v>3029</v>
+      </c>
+      <c r="C38" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D38" s="11" t="n">
+        <v>1306</v>
+      </c>
+      <c r="E38" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="G38" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 산신의 곡괭이</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="13" t="n"/>
+      <c r="B39" s="11" t="n">
+        <v>3030</v>
+      </c>
+      <c r="C39" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D39" s="11" t="n">
+        <v>1406</v>
+      </c>
+      <c r="E39" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="G39" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 세계수의 도끼</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="13" t="n"/>
+      <c r="B40" s="11" t="n">
+        <v>3031</v>
+      </c>
+      <c r="C40" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D40" s="11" t="n">
+        <v>1506</v>
+      </c>
+      <c r="E40" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="G40" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 월신의 활</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="13" t="n"/>
+      <c r="B41" s="11" t="n">
+        <v>4001</v>
+      </c>
+      <c r="C41" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D41" s="11" t="n">
+        <v>2001</v>
+      </c>
+      <c r="E41" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" s="11" t="n">
+        <v>640</v>
+      </c>
+      <c r="G41" s="12" t="inlineStr">
+        <is>
+          <t>Common 구리 반지</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="13" t="n"/>
+      <c r="B42" s="11" t="n">
+        <v>4002</v>
+      </c>
+      <c r="C42" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D42" s="11" t="n">
+        <v>2003</v>
+      </c>
+      <c r="E42" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" s="11" t="n">
+        <v>200</v>
+      </c>
+      <c r="G42" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon 은 목걸이</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="13" t="n"/>
+      <c r="B43" s="11" t="n">
+        <v>4003</v>
+      </c>
+      <c r="C43" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D43" s="11" t="n">
+        <v>2002</v>
+      </c>
+      <c r="E43" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="G43" s="12" t="inlineStr">
+        <is>
+          <t>Rare 어부의 목걸이</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="13" t="n"/>
+      <c r="B44" s="11" t="n">
+        <v>4004</v>
+      </c>
+      <c r="C44" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D44" s="11" t="n">
+        <v>2004</v>
+      </c>
+      <c r="E44" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="G44" s="12" t="inlineStr">
+        <is>
+          <t>Rare 노동자의 팔찌</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="13" t="n"/>
+      <c r="B45" s="11" t="n">
+        <v>4005</v>
+      </c>
+      <c r="C45" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D45" s="11" t="n">
+        <v>2005</v>
+      </c>
+      <c r="E45" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="G45" s="12" t="inlineStr">
+        <is>
+          <t>Epic 장인의 인장</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="13" t="n"/>
+      <c r="B46" s="11" t="n">
+        <v>4006</v>
+      </c>
+      <c r="C46" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D46" s="11" t="n">
+        <v>2006</v>
+      </c>
+      <c r="E46" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="G46" s="12" t="inlineStr">
+        <is>
+          <t>Legendary 대장인의 훈장</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="13" t="n"/>
+      <c r="B47" s="11" t="n">
+        <v>4007</v>
+      </c>
+      <c r="C47" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D47" s="11" t="n">
+        <v>2007</v>
+      </c>
+      <c r="E47" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="G47" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 창세의 고리</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="13" t="n"/>
+      <c r="B48" s="11" t="n">
+        <v>5001</v>
+      </c>
+      <c r="C48" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D48" s="11" t="n">
+        <v>3001</v>
+      </c>
+      <c r="E48" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" s="11" t="n">
+        <v>640</v>
+      </c>
+      <c r="G48" s="12" t="inlineStr">
+        <is>
+          <t>Common 원석</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="13" t="n"/>
+      <c r="B49" s="11" t="n">
+        <v>5002</v>
+      </c>
+      <c r="C49" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D49" s="11" t="n">
+        <v>3101</v>
+      </c>
+      <c r="E49" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" s="11" t="n">
+        <v>640</v>
+      </c>
+      <c r="G49" s="12" t="inlineStr">
+        <is>
+          <t>Common 풍년석</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="13" t="n"/>
+      <c r="B50" s="11" t="n">
+        <v>5003</v>
+      </c>
+      <c r="C50" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D50" s="11" t="n">
+        <v>3201</v>
+      </c>
+      <c r="E50" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" s="11" t="n">
+        <v>640</v>
+      </c>
+      <c r="G50" s="12" t="inlineStr">
+        <is>
+          <t>Common 물방울석</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="13" t="n"/>
+      <c r="B51" s="11" t="n">
+        <v>5004</v>
+      </c>
+      <c r="C51" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D51" s="11" t="n">
+        <v>3301</v>
+      </c>
+      <c r="E51" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" s="11" t="n">
+        <v>640</v>
+      </c>
+      <c r="G51" s="12" t="inlineStr">
+        <is>
+          <t>Common 철광석 조각</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="13" t="n"/>
+      <c r="B52" s="11" t="n">
+        <v>5005</v>
+      </c>
+      <c r="C52" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D52" s="11" t="n">
+        <v>3401</v>
+      </c>
+      <c r="E52" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F52" s="11" t="n">
+        <v>640</v>
+      </c>
+      <c r="G52" s="12" t="inlineStr">
+        <is>
+          <t>Common 나무옹이석</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="13" t="n"/>
+      <c r="B53" s="11" t="n">
+        <v>5006</v>
+      </c>
+      <c r="C53" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D53" s="11" t="n">
+        <v>3501</v>
+      </c>
+      <c r="E53" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" s="11" t="n">
+        <v>640</v>
+      </c>
+      <c r="G53" s="12" t="inlineStr">
+        <is>
+          <t>Common 짐승 이빨석</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="13" t="n"/>
+      <c r="B54" s="11" t="n">
+        <v>5007</v>
+      </c>
+      <c r="C54" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D54" s="11" t="n">
+        <v>3102</v>
+      </c>
+      <c r="E54" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" s="11" t="n">
+        <v>200</v>
+      </c>
+      <c r="G54" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon 새싹 수정</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="13" t="n"/>
+      <c r="B55" s="11" t="n">
+        <v>5008</v>
+      </c>
+      <c r="C55" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D55" s="11" t="n">
+        <v>3202</v>
+      </c>
+      <c r="E55" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F55" s="11" t="n">
+        <v>200</v>
+      </c>
+      <c r="G55" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon 조류 수정</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="13" t="n"/>
+      <c r="B56" s="11" t="n">
+        <v>5009</v>
+      </c>
+      <c r="C56" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D56" s="11" t="n">
+        <v>3302</v>
+      </c>
+      <c r="E56" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F56" s="11" t="n">
+        <v>200</v>
+      </c>
+      <c r="G56" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon 광맥 수정</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="13" t="n"/>
+      <c r="B57" s="11" t="n">
+        <v>5010</v>
+      </c>
+      <c r="C57" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D57" s="11" t="n">
+        <v>3402</v>
+      </c>
+      <c r="E57" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F57" s="11" t="n">
+        <v>200</v>
+      </c>
+      <c r="G57" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon 수액 호박</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="13" t="n"/>
+      <c r="B58" s="11" t="n">
+        <v>5011</v>
+      </c>
+      <c r="C58" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D58" s="11" t="n">
+        <v>3502</v>
+      </c>
+      <c r="E58" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F58" s="11" t="n">
+        <v>200</v>
+      </c>
+      <c r="G58" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon 추적자의 수정</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="13" t="n"/>
+      <c r="B59" s="11" t="n">
+        <v>5012</v>
+      </c>
+      <c r="C59" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D59" s="11" t="n">
+        <v>3103</v>
+      </c>
+      <c r="E59" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F59" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="G59" s="12" t="inlineStr">
+        <is>
+          <t>Rare 곡창의 비취</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="13" t="n"/>
+      <c r="B60" s="11" t="n">
+        <v>5013</v>
+      </c>
+      <c r="C60" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D60" s="11" t="n">
+        <v>3203</v>
+      </c>
+      <c r="E60" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F60" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="G60" s="12" t="inlineStr">
+        <is>
+          <t>Rare 심해의 청옥</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="13" t="n"/>
+      <c r="B61" s="11" t="n">
+        <v>5014</v>
+      </c>
+      <c r="C61" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D61" s="11" t="n">
+        <v>3303</v>
+      </c>
+      <c r="E61" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F61" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="G61" s="12" t="inlineStr">
+        <is>
+          <t>Rare 지맥의 흑옥</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="13" t="n"/>
+      <c r="B62" s="11" t="n">
+        <v>5015</v>
+      </c>
+      <c r="C62" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D62" s="11" t="n">
+        <v>3403</v>
+      </c>
+      <c r="E62" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F62" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="G62" s="12" t="inlineStr">
+        <is>
+          <t>Rare 고목의 녹옥</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="13" t="n"/>
+      <c r="B63" s="11" t="n">
+        <v>5016</v>
+      </c>
+      <c r="C63" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D63" s="11" t="n">
+        <v>3503</v>
+      </c>
+      <c r="E63" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F63" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="G63" s="12" t="inlineStr">
+        <is>
+          <t>Rare 맹수의 홍옥</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="13" t="n"/>
+      <c r="B64" s="11" t="n">
+        <v>5017</v>
+      </c>
+      <c r="C64" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D64" s="11" t="n">
+        <v>3104</v>
+      </c>
+      <c r="E64" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F64" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="G64" s="12" t="inlineStr">
+        <is>
+          <t>Epic 황금 이삭석</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="13" t="n"/>
+      <c r="B65" s="11" t="n">
+        <v>5018</v>
+      </c>
+      <c r="C65" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D65" s="11" t="n">
+        <v>3204</v>
+      </c>
+      <c r="E65" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F65" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="G65" s="12" t="inlineStr">
+        <is>
+          <t>Epic 산호 진주</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="13" t="n"/>
+      <c r="B66" s="11" t="n">
+        <v>5019</v>
+      </c>
+      <c r="C66" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D66" s="11" t="n">
+        <v>3304</v>
+      </c>
+      <c r="E66" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F66" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="G66" s="12" t="inlineStr">
+        <is>
+          <t>Epic 용암 결정</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="13" t="n"/>
+      <c r="B67" s="11" t="n">
+        <v>5020</v>
+      </c>
+      <c r="C67" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D67" s="11" t="n">
+        <v>3404</v>
+      </c>
+      <c r="E67" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F67" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="G67" s="12" t="inlineStr">
+        <is>
+          <t>Epic 백년목 결정</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="13" t="n"/>
+      <c r="B68" s="11" t="n">
+        <v>5021</v>
+      </c>
+      <c r="C68" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D68" s="11" t="n">
+        <v>3504</v>
+      </c>
+      <c r="E68" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F68" s="11" t="n">
+        <v>40</v>
+      </c>
+      <c r="G68" s="12" t="inlineStr">
+        <is>
+          <t>Epic 사냥꾼의 별</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="13" t="n"/>
+      <c r="B69" s="11" t="n">
+        <v>5022</v>
+      </c>
+      <c r="C69" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D69" s="11" t="n">
+        <v>3105</v>
+      </c>
+      <c r="E69" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F69" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="G69" s="12" t="inlineStr">
+        <is>
+          <t>Legendary 대지의 심장</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="13" t="n"/>
+      <c r="B70" s="11" t="n">
+        <v>5023</v>
+      </c>
+      <c r="C70" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D70" s="11" t="n">
+        <v>3205</v>
+      </c>
+      <c r="E70" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F70" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="G70" s="12" t="inlineStr">
+        <is>
+          <t>Legendary 바다의 심장</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="13" t="n"/>
+      <c r="B71" s="11" t="n">
+        <v>5024</v>
+      </c>
+      <c r="C71" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D71" s="11" t="n">
+        <v>3305</v>
+      </c>
+      <c r="E71" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F71" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="G71" s="12" t="inlineStr">
+        <is>
+          <t>Legendary 대지핵 결정</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="13" t="n"/>
+      <c r="B72" s="11" t="n">
+        <v>5025</v>
+      </c>
+      <c r="C72" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D72" s="11" t="n">
+        <v>3405</v>
+      </c>
+      <c r="E72" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F72" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="G72" s="12" t="inlineStr">
+        <is>
+          <t>Legendary 숲의 심장</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="13" t="n"/>
+      <c r="B73" s="11" t="n">
+        <v>5026</v>
+      </c>
+      <c r="C73" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D73" s="11" t="n">
+        <v>3505</v>
+      </c>
+      <c r="E73" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F73" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="G73" s="12" t="inlineStr">
+        <is>
+          <t>Legendary 야수의 심장</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="13" t="n"/>
+      <c r="B74" s="11" t="n">
+        <v>5027</v>
+      </c>
+      <c r="C74" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D74" s="11" t="n">
+        <v>3106</v>
+      </c>
+      <c r="E74" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F74" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="G74" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 풍요의 성석</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="13" t="n"/>
+      <c r="B75" s="11" t="n">
+        <v>5028</v>
+      </c>
+      <c r="C75" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D75" s="11" t="n">
+        <v>3206</v>
+      </c>
+      <c r="E75" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F75" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="G75" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 해원의 성석</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="13" t="n"/>
+      <c r="B76" s="11" t="n">
+        <v>5029</v>
+      </c>
+      <c r="C76" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D76" s="11" t="n">
+        <v>3306</v>
+      </c>
+      <c r="E76" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F76" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="G76" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 광신의 성석</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="13" t="n"/>
+      <c r="B77" s="11" t="n">
+        <v>5030</v>
+      </c>
+      <c r="C77" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D77" s="11" t="n">
+        <v>3406</v>
+      </c>
+      <c r="E77" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F77" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="G77" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 세계수 성석</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="13" t="n"/>
+      <c r="B78" s="11" t="n">
+        <v>5031</v>
+      </c>
+      <c r="C78" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="D78" s="11" t="n">
+        <v>3506</v>
+      </c>
+      <c r="E78" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F78" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="G78" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 월광 성석</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing r:id="anysvml"/>
+</worksheet>
 </file>
--- a/GameDesign/Excel/Gacha.xlsx
+++ b/GameDesign/Excel/Gacha.xlsx
@@ -11,6 +11,7 @@
     <sheet name="GachaInfoTable" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="GachaCharacterTable" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="GachaEquipTable" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="GachaGoldTable" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -261,6 +262,21 @@
 </file>
 
 <file path=xl/comments/comment4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>excel-table-creator</author>
+  </authors>
+  <commentList>
+    <comment ref="C2" authorId="0" shapeId="0">
+      <text>
+        <t>가챠 풀 ID (= GachaInfoTID)</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment5.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>excel-table-creator</author>
@@ -564,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -573,7 +589,7 @@
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -932,6 +948,420 @@
       <c r="G15" s="12" t="inlineStr">
         <is>
           <t>신화</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="n"/>
+      <c r="B16" s="11" t="n">
+        <v>6001</v>
+      </c>
+      <c r="C16" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="D16" s="11" t="n">
+        <v>10001</v>
+      </c>
+      <c r="E16" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="F16" s="11" t="n">
+        <v>80</v>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>자원 붕어 x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="n"/>
+      <c r="B17" s="11" t="n">
+        <v>6002</v>
+      </c>
+      <c r="C17" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="D17" s="11" t="n">
+        <v>20001</v>
+      </c>
+      <c r="E17" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="F17" s="11" t="n">
+        <v>80</v>
+      </c>
+      <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>자원 밀 x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="n"/>
+      <c r="B18" s="11" t="n">
+        <v>6003</v>
+      </c>
+      <c r="C18" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="D18" s="11" t="n">
+        <v>30001</v>
+      </c>
+      <c r="E18" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="F18" s="11" t="n">
+        <v>80</v>
+      </c>
+      <c r="G18" s="12" t="inlineStr">
+        <is>
+          <t>자원 잡목 x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="n"/>
+      <c r="B19" s="11" t="n">
+        <v>6004</v>
+      </c>
+      <c r="C19" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="D19" s="11" t="n">
+        <v>40001</v>
+      </c>
+      <c r="E19" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="F19" s="11" t="n">
+        <v>80</v>
+      </c>
+      <c r="G19" s="12" t="inlineStr">
+        <is>
+          <t>자원 돌덩어리 x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="n"/>
+      <c r="B20" s="11" t="n">
+        <v>6005</v>
+      </c>
+      <c r="C20" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="D20" s="11" t="n">
+        <v>50001</v>
+      </c>
+      <c r="E20" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="F20" s="11" t="n">
+        <v>80</v>
+      </c>
+      <c r="G20" s="12" t="inlineStr">
+        <is>
+          <t>자원 질긴 고기 x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="n"/>
+      <c r="B21" s="11" t="n">
+        <v>6006</v>
+      </c>
+      <c r="C21" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="D21" s="11" t="n">
+        <v>100010</v>
+      </c>
+      <c r="E21" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="G21" s="12" t="inlineStr">
+        <is>
+          <t>상자 전용 낡은 보물 지도</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="n"/>
+      <c r="B22" s="11" t="n">
+        <v>7001</v>
+      </c>
+      <c r="C22" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="D22" s="11" t="n">
+        <v>10002</v>
+      </c>
+      <c r="E22" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F22" s="11" t="n">
+        <v>80</v>
+      </c>
+      <c r="G22" s="12" t="inlineStr">
+        <is>
+          <t>자원 잉어 x3</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="n"/>
+      <c r="B23" s="11" t="n">
+        <v>7002</v>
+      </c>
+      <c r="C23" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="D23" s="11" t="n">
+        <v>20002</v>
+      </c>
+      <c r="E23" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F23" s="11" t="n">
+        <v>80</v>
+      </c>
+      <c r="G23" s="12" t="inlineStr">
+        <is>
+          <t>자원 감자 x3</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="n"/>
+      <c r="B24" s="11" t="n">
+        <v>7003</v>
+      </c>
+      <c r="C24" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="D24" s="11" t="n">
+        <v>30002</v>
+      </c>
+      <c r="E24" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F24" s="11" t="n">
+        <v>80</v>
+      </c>
+      <c r="G24" s="12" t="inlineStr">
+        <is>
+          <t>자원 소나무 목재 x3</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="n"/>
+      <c r="B25" s="11" t="n">
+        <v>7004</v>
+      </c>
+      <c r="C25" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="D25" s="11" t="n">
+        <v>40002</v>
+      </c>
+      <c r="E25" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F25" s="11" t="n">
+        <v>80</v>
+      </c>
+      <c r="G25" s="12" t="inlineStr">
+        <is>
+          <t>자원 구리 광석 x3</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="13" t="n"/>
+      <c r="B26" s="11" t="n">
+        <v>7005</v>
+      </c>
+      <c r="C26" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="D26" s="11" t="n">
+        <v>50002</v>
+      </c>
+      <c r="E26" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F26" s="11" t="n">
+        <v>80</v>
+      </c>
+      <c r="G26" s="12" t="inlineStr">
+        <is>
+          <t>자원 토끼 가죽 x3</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="13" t="n"/>
+      <c r="B27" s="11" t="n">
+        <v>7006</v>
+      </c>
+      <c r="C27" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="D27" s="11" t="n">
+        <v>100011</v>
+      </c>
+      <c r="E27" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="G27" s="12" t="inlineStr">
+        <is>
+          <t>상자 전용 은빛 나침반</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="n"/>
+      <c r="B28" s="11" t="n">
+        <v>8001</v>
+      </c>
+      <c r="C28" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="D28" s="11" t="n">
+        <v>10003</v>
+      </c>
+      <c r="E28" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F28" s="11" t="n">
+        <v>80</v>
+      </c>
+      <c r="G28" s="12" t="inlineStr">
+        <is>
+          <t>자원 월척 붕어 x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="13" t="n"/>
+      <c r="B29" s="11" t="n">
+        <v>8002</v>
+      </c>
+      <c r="C29" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="D29" s="11" t="n">
+        <v>20003</v>
+      </c>
+      <c r="E29" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F29" s="11" t="n">
+        <v>80</v>
+      </c>
+      <c r="G29" s="12" t="inlineStr">
+        <is>
+          <t>자원 옥수수 x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="13" t="n"/>
+      <c r="B30" s="11" t="n">
+        <v>8003</v>
+      </c>
+      <c r="C30" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="D30" s="11" t="n">
+        <v>30003</v>
+      </c>
+      <c r="E30" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F30" s="11" t="n">
+        <v>80</v>
+      </c>
+      <c r="G30" s="12" t="inlineStr">
+        <is>
+          <t>자원 참나무 목재 x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="13" t="n"/>
+      <c r="B31" s="11" t="n">
+        <v>8004</v>
+      </c>
+      <c r="C31" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="D31" s="11" t="n">
+        <v>40003</v>
+      </c>
+      <c r="E31" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F31" s="11" t="n">
+        <v>80</v>
+      </c>
+      <c r="G31" s="12" t="inlineStr">
+        <is>
+          <t>자원 은광석 x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="13" t="n"/>
+      <c r="B32" s="11" t="n">
+        <v>8005</v>
+      </c>
+      <c r="C32" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="D32" s="11" t="n">
+        <v>50003</v>
+      </c>
+      <c r="E32" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F32" s="11" t="n">
+        <v>80</v>
+      </c>
+      <c r="G32" s="12" t="inlineStr">
+        <is>
+          <t>자원 늑대 가죽 x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="13" t="n"/>
+      <c r="B33" s="11" t="n">
+        <v>8006</v>
+      </c>
+      <c r="C33" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="D33" s="11" t="n">
+        <v>100012</v>
+      </c>
+      <c r="E33" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F33" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="G33" s="12" t="inlineStr">
+        <is>
+          <t>상자 전용 황금 열쇠</t>
         </is>
       </c>
     </row>
@@ -947,7 +1377,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -956,7 +1386,7 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="33" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1089,10 +1519,10 @@
       <c r="C5" s="9" t="n"/>
       <c r="D5" s="9" t="n"/>
       <c r="E5" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" s="9" t="n"/>
     </row>
@@ -1291,6 +1721,87 @@
       <c r="G13" s="12" t="inlineStr">
         <is>
           <t>보석 31종</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="n"/>
+      <c r="B14" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="C14" s="12" t="inlineStr">
+        <is>
+          <t>나무 상자</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="12" t="inlineStr">
+        <is>
+          <t>상자 전용 — 골드로 뽑을 수 없다</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="n"/>
+      <c r="B15" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="C15" s="12" t="inlineStr">
+        <is>
+          <t>은 상자</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E15" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="12" t="inlineStr">
+        <is>
+          <t>상자 전용 — 골드로 뽑을 수 없다</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="n"/>
+      <c r="B16" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="C16" s="12" t="inlineStr">
+        <is>
+          <t>황금 상자</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E16" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>상자 전용 — 골드로 뽑을 수 없다</t>
         </is>
       </c>
     </row>
@@ -2241,7 +2752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G78"/>
+  <dimension ref="A1:G92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -4061,6 +4572,709 @@
         </is>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" s="13" t="n"/>
+      <c r="B79" s="11" t="n">
+        <v>6101</v>
+      </c>
+      <c r="C79" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="D79" s="11" t="n">
+        <v>1001</v>
+      </c>
+      <c r="E79" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F79" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="G79" s="12" t="inlineStr">
+        <is>
+          <t>장비</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="13" t="n"/>
+      <c r="B80" s="11" t="n">
+        <v>6102</v>
+      </c>
+      <c r="C80" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="D80" s="11" t="n">
+        <v>2001</v>
+      </c>
+      <c r="E80" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F80" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="G80" s="12" t="inlineStr">
+        <is>
+          <t>장비</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="13" t="n"/>
+      <c r="B81" s="11" t="n">
+        <v>6103</v>
+      </c>
+      <c r="C81" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="D81" s="11" t="n">
+        <v>3001</v>
+      </c>
+      <c r="E81" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F81" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="G81" s="12" t="inlineStr">
+        <is>
+          <t>장비</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="13" t="n"/>
+      <c r="B82" s="11" t="n">
+        <v>7101</v>
+      </c>
+      <c r="C82" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="D82" s="11" t="n">
+        <v>1102</v>
+      </c>
+      <c r="E82" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F82" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="G82" s="12" t="inlineStr">
+        <is>
+          <t>장비</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="13" t="n"/>
+      <c r="B83" s="11" t="n">
+        <v>7102</v>
+      </c>
+      <c r="C83" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="D83" s="11" t="n">
+        <v>1302</v>
+      </c>
+      <c r="E83" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F83" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="G83" s="12" t="inlineStr">
+        <is>
+          <t>장비</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="13" t="n"/>
+      <c r="B84" s="11" t="n">
+        <v>7103</v>
+      </c>
+      <c r="C84" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="D84" s="11" t="n">
+        <v>1402</v>
+      </c>
+      <c r="E84" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F84" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="G84" s="12" t="inlineStr">
+        <is>
+          <t>장비</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="13" t="n"/>
+      <c r="B85" s="11" t="n">
+        <v>7104</v>
+      </c>
+      <c r="C85" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="D85" s="11" t="n">
+        <v>1502</v>
+      </c>
+      <c r="E85" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F85" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="G85" s="12" t="inlineStr">
+        <is>
+          <t>장비</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="13" t="n"/>
+      <c r="B86" s="11" t="n">
+        <v>7105</v>
+      </c>
+      <c r="C86" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="D86" s="11" t="n">
+        <v>2003</v>
+      </c>
+      <c r="E86" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F86" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="G86" s="12" t="inlineStr">
+        <is>
+          <t>장비</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="13" t="n"/>
+      <c r="B87" s="11" t="n">
+        <v>8101</v>
+      </c>
+      <c r="C87" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="D87" s="11" t="n">
+        <v>1103</v>
+      </c>
+      <c r="E87" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F87" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="G87" s="12" t="inlineStr">
+        <is>
+          <t>장비</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="13" t="n"/>
+      <c r="B88" s="11" t="n">
+        <v>8102</v>
+      </c>
+      <c r="C88" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="D88" s="11" t="n">
+        <v>1203</v>
+      </c>
+      <c r="E88" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F88" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="G88" s="12" t="inlineStr">
+        <is>
+          <t>장비</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="13" t="n"/>
+      <c r="B89" s="11" t="n">
+        <v>8103</v>
+      </c>
+      <c r="C89" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="D89" s="11" t="n">
+        <v>1303</v>
+      </c>
+      <c r="E89" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F89" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="G89" s="12" t="inlineStr">
+        <is>
+          <t>장비</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="13" t="n"/>
+      <c r="B90" s="11" t="n">
+        <v>8104</v>
+      </c>
+      <c r="C90" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="D90" s="11" t="n">
+        <v>1403</v>
+      </c>
+      <c r="E90" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F90" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="G90" s="12" t="inlineStr">
+        <is>
+          <t>장비</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="13" t="n"/>
+      <c r="B91" s="11" t="n">
+        <v>8105</v>
+      </c>
+      <c r="C91" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="D91" s="11" t="n">
+        <v>1503</v>
+      </c>
+      <c r="E91" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F91" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="G91" s="12" t="inlineStr">
+        <is>
+          <t>장비</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="13" t="n"/>
+      <c r="B92" s="11" t="n">
+        <v>8106</v>
+      </c>
+      <c r="C92" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="D92" s="11" t="n">
+        <v>2004</v>
+      </c>
+      <c r="E92" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F92" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="G92" s="12" t="inlineStr">
+        <is>
+          <t>장비</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="13" t="n"/>
+      <c r="B1" s="13" t="n"/>
+      <c r="C1" s="13" t="n"/>
+      <c r="D1" s="13" t="n"/>
+      <c r="E1" s="13" t="n"/>
+      <c r="F1" s="13" t="n"/>
+      <c r="G1" s="13" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>//</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>골드 가챠 TID</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>가챠 풀 ID</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>최소 골드</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>최대 골드</t>
+        </is>
+      </c>
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>확률가중치</t>
+        </is>
+      </c>
+      <c r="G2" s="8" t="inlineStr">
+        <is>
+          <t>메모</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>C&amp;S</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="G3" s="9" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="n"/>
+      <c r="C5" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="9" t="n"/>
+      <c r="G5" s="9" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="n"/>
+      <c r="C6" s="9" t="n"/>
+      <c r="D6" s="9" t="n"/>
+      <c r="E6" s="9" t="n"/>
+      <c r="F6" s="9" t="n"/>
+      <c r="G6" s="9" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>Default(Null)</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="n"/>
+      <c r="C7" s="9" t="n"/>
+      <c r="D7" s="9" t="n"/>
+      <c r="E7" s="9" t="n"/>
+      <c r="F7" s="9" t="n"/>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>""</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="n"/>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>GachaInfoTable.GachaInfoTID</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="n"/>
+      <c r="E8" s="9" t="n"/>
+      <c r="F8" s="9" t="n"/>
+      <c r="G8" s="9" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="n"/>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>GachaGoldTID</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>GachaId</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>MinAmount</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>MaxAmount</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="n"/>
+      <c r="B10" s="11" t="n">
+        <v>6201</v>
+      </c>
+      <c r="C10" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="D10" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E10" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="F10" s="11" t="n">
+        <v>300</v>
+      </c>
+      <c r="G10" s="12" t="inlineStr">
+        <is>
+          <t>골드 50~100</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="n"/>
+      <c r="B11" s="11" t="n">
+        <v>6202</v>
+      </c>
+      <c r="C11" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="D11" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="E11" s="11" t="n">
+        <v>300</v>
+      </c>
+      <c r="F11" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="G11" s="12" t="inlineStr">
+        <is>
+          <t>골드 100~300</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="n"/>
+      <c r="B12" s="11" t="n">
+        <v>7201</v>
+      </c>
+      <c r="C12" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="D12" s="11" t="n">
+        <v>300</v>
+      </c>
+      <c r="E12" s="11" t="n">
+        <v>600</v>
+      </c>
+      <c r="F12" s="11" t="n">
+        <v>300</v>
+      </c>
+      <c r="G12" s="12" t="inlineStr">
+        <is>
+          <t>골드 300~600</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="n"/>
+      <c r="B13" s="11" t="n">
+        <v>7202</v>
+      </c>
+      <c r="C13" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="D13" s="11" t="n">
+        <v>600</v>
+      </c>
+      <c r="E13" s="11" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F13" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="G13" s="12" t="inlineStr">
+        <is>
+          <t>골드 600~1500</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="n"/>
+      <c r="B14" s="11" t="n">
+        <v>8201</v>
+      </c>
+      <c r="C14" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="D14" s="11" t="n">
+        <v>1500</v>
+      </c>
+      <c r="E14" s="11" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F14" s="11" t="n">
+        <v>300</v>
+      </c>
+      <c r="G14" s="12" t="inlineStr">
+        <is>
+          <t>골드 1500~3000</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="n"/>
+      <c r="B15" s="11" t="n">
+        <v>8202</v>
+      </c>
+      <c r="C15" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="D15" s="11" t="n">
+        <v>3000</v>
+      </c>
+      <c r="E15" s="11" t="n">
+        <v>8000</v>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="G15" s="12" t="inlineStr">
+        <is>
+          <t>골드 3000~8000</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing r:id="anysvml"/>

--- a/GameDesign/Excel/Gacha.xlsx
+++ b/GameDesign/Excel/Gacha.xlsx
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1092,59 +1092,59 @@
     <row r="22">
       <c r="A22" s="13" t="n"/>
       <c r="B22" s="11" t="n">
-        <v>7001</v>
+        <v>6007</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>10002</v>
+        <v>100013</v>
       </c>
       <c r="E22" s="11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
-          <t>자원 잉어 x3</t>
+          <t>인챈트 원석</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="13" t="n"/>
       <c r="B23" s="11" t="n">
-        <v>7002</v>
+        <v>6008</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>20002</v>
+        <v>100016</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
-          <t>자원 감자 x3</t>
+          <t>인챈트 확장석</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="13" t="n"/>
       <c r="B24" s="11" t="n">
-        <v>7003</v>
+        <v>7001</v>
       </c>
       <c r="C24" s="11" t="n">
         <v>7</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>30002</v>
+        <v>10002</v>
       </c>
       <c r="E24" s="11" t="n">
         <v>3</v>
@@ -1154,20 +1154,20 @@
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
-          <t>자원 소나무 목재 x3</t>
+          <t>자원 잉어 x3</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="13" t="n"/>
       <c r="B25" s="11" t="n">
-        <v>7004</v>
+        <v>7002</v>
       </c>
       <c r="C25" s="11" t="n">
         <v>7</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>40002</v>
+        <v>20002</v>
       </c>
       <c r="E25" s="11" t="n">
         <v>3</v>
@@ -1177,20 +1177,20 @@
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
-          <t>자원 구리 광석 x3</t>
+          <t>자원 감자 x3</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="13" t="n"/>
       <c r="B26" s="11" t="n">
-        <v>7005</v>
+        <v>7003</v>
       </c>
       <c r="C26" s="11" t="n">
         <v>7</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>50002</v>
+        <v>30002</v>
       </c>
       <c r="E26" s="11" t="n">
         <v>3</v>
@@ -1200,168 +1200,352 @@
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
-          <t>자원 토끼 가죽 x3</t>
+          <t>자원 소나무 목재 x3</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="13" t="n"/>
       <c r="B27" s="11" t="n">
-        <v>7006</v>
+        <v>7004</v>
       </c>
       <c r="C27" s="11" t="n">
         <v>7</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>100011</v>
+        <v>40002</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
-          <t>상자 전용 은빛 나침반</t>
+          <t>자원 구리 광석 x3</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="13" t="n"/>
       <c r="B28" s="11" t="n">
-        <v>8001</v>
+        <v>7005</v>
       </c>
       <c r="C28" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>10003</v>
+        <v>50002</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F28" s="11" t="n">
         <v>80</v>
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
-          <t>자원 월척 붕어 x2</t>
+          <t>자원 토끼 가죽 x3</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="13" t="n"/>
       <c r="B29" s="11" t="n">
-        <v>8002</v>
+        <v>7006</v>
       </c>
       <c r="C29" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>20003</v>
+        <v>100011</v>
       </c>
       <c r="E29" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
-          <t>자원 옥수수 x2</t>
+          <t>상자 전용 은빛 나침반</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="13" t="n"/>
       <c r="B30" s="11" t="n">
-        <v>8003</v>
+        <v>7007</v>
       </c>
       <c r="C30" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>30003</v>
+        <v>100013</v>
       </c>
       <c r="E30" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
-          <t>자원 참나무 목재 x2</t>
+          <t>인챈트 원석</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="13" t="n"/>
       <c r="B31" s="11" t="n">
-        <v>8004</v>
+        <v>7008</v>
       </c>
       <c r="C31" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>40003</v>
+        <v>100015</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
-          <t>자원 은광석 x2</t>
+          <t>인챈트 큐브</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="13" t="n"/>
       <c r="B32" s="11" t="n">
-        <v>8005</v>
+        <v>7009</v>
       </c>
       <c r="C32" s="11" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>50003</v>
+        <v>100016</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="G32" s="12" t="inlineStr">
         <is>
-          <t>자원 늑대 가죽 x2</t>
+          <t>인챈트 확장석</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="13" t="n"/>
       <c r="B33" s="11" t="n">
-        <v>8006</v>
+        <v>8001</v>
       </c>
       <c r="C33" s="11" t="n">
         <v>8</v>
       </c>
       <c r="D33" s="11" t="n">
+        <v>10003</v>
+      </c>
+      <c r="E33" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F33" s="11" t="n">
+        <v>80</v>
+      </c>
+      <c r="G33" s="12" t="inlineStr">
+        <is>
+          <t>자원 월척 붕어 x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="13" t="n"/>
+      <c r="B34" s="11" t="n">
+        <v>8002</v>
+      </c>
+      <c r="C34" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="D34" s="11" t="n">
+        <v>20003</v>
+      </c>
+      <c r="E34" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F34" s="11" t="n">
+        <v>80</v>
+      </c>
+      <c r="G34" s="12" t="inlineStr">
+        <is>
+          <t>자원 옥수수 x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="13" t="n"/>
+      <c r="B35" s="11" t="n">
+        <v>8003</v>
+      </c>
+      <c r="C35" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="D35" s="11" t="n">
+        <v>30003</v>
+      </c>
+      <c r="E35" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F35" s="11" t="n">
+        <v>80</v>
+      </c>
+      <c r="G35" s="12" t="inlineStr">
+        <is>
+          <t>자원 참나무 목재 x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="13" t="n"/>
+      <c r="B36" s="11" t="n">
+        <v>8004</v>
+      </c>
+      <c r="C36" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="D36" s="11" t="n">
+        <v>40003</v>
+      </c>
+      <c r="E36" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F36" s="11" t="n">
+        <v>80</v>
+      </c>
+      <c r="G36" s="12" t="inlineStr">
+        <is>
+          <t>자원 은광석 x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="13" t="n"/>
+      <c r="B37" s="11" t="n">
+        <v>8005</v>
+      </c>
+      <c r="C37" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="D37" s="11" t="n">
+        <v>50003</v>
+      </c>
+      <c r="E37" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F37" s="11" t="n">
+        <v>80</v>
+      </c>
+      <c r="G37" s="12" t="inlineStr">
+        <is>
+          <t>자원 늑대 가죽 x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="13" t="n"/>
+      <c r="B38" s="11" t="n">
+        <v>8006</v>
+      </c>
+      <c r="C38" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="D38" s="11" t="n">
         <v>100012</v>
       </c>
-      <c r="E33" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F33" s="11" t="n">
+      <c r="E38" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F38" s="11" t="n">
         <v>20</v>
       </c>
-      <c r="G33" s="12" t="inlineStr">
+      <c r="G38" s="12" t="inlineStr">
         <is>
           <t>상자 전용 황금 열쇠</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="13" t="n"/>
+      <c r="B39" s="11" t="n">
+        <v>8007</v>
+      </c>
+      <c r="C39" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="D39" s="11" t="n">
+        <v>100015</v>
+      </c>
+      <c r="E39" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F39" s="11" t="n">
+        <v>80</v>
+      </c>
+      <c r="G39" s="12" t="inlineStr">
+        <is>
+          <t>인챈트 큐브</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="13" t="n"/>
+      <c r="B40" s="11" t="n">
+        <v>8008</v>
+      </c>
+      <c r="C40" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="D40" s="11" t="n">
+        <v>100014</v>
+      </c>
+      <c r="E40" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="G40" s="12" t="inlineStr">
+        <is>
+          <t>정제된 인챈트 원석</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="13" t="n"/>
+      <c r="B41" s="11" t="n">
+        <v>8009</v>
+      </c>
+      <c r="C41" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="D41" s="11" t="n">
+        <v>100017</v>
+      </c>
+      <c r="E41" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="G41" s="12" t="inlineStr">
+        <is>
+          <t>정제된 인챈트 확장석</t>
         </is>
       </c>
     </row>

--- a/GameDesign/Excel/Gacha.xlsx
+++ b/GameDesign/Excel/Gacha.xlsx
@@ -575,12 +575,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -1092,13 +1092,13 @@
     <row r="22">
       <c r="A22" s="13" t="n"/>
       <c r="B22" s="11" t="n">
-        <v>6007</v>
+        <v>6009</v>
       </c>
       <c r="C22" s="11" t="n">
         <v>6</v>
       </c>
       <c r="D22" s="11" t="n">
-        <v>100013</v>
+        <v>100015</v>
       </c>
       <c r="E22" s="11" t="n">
         <v>1</v>
@@ -1108,43 +1108,43 @@
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
-          <t>인챈트 원석</t>
+          <t>인챈트 큐브</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="13" t="n"/>
       <c r="B23" s="11" t="n">
-        <v>6008</v>
+        <v>7001</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>100016</v>
+        <v>10002</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
-          <t>인챈트 확장석</t>
+          <t>자원 잉어 x3</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="13" t="n"/>
       <c r="B24" s="11" t="n">
-        <v>7001</v>
+        <v>7002</v>
       </c>
       <c r="C24" s="11" t="n">
         <v>7</v>
       </c>
       <c r="D24" s="11" t="n">
-        <v>10002</v>
+        <v>20002</v>
       </c>
       <c r="E24" s="11" t="n">
         <v>3</v>
@@ -1154,20 +1154,20 @@
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
-          <t>자원 잉어 x3</t>
+          <t>자원 감자 x3</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="13" t="n"/>
       <c r="B25" s="11" t="n">
-        <v>7002</v>
+        <v>7003</v>
       </c>
       <c r="C25" s="11" t="n">
         <v>7</v>
       </c>
       <c r="D25" s="11" t="n">
-        <v>20002</v>
+        <v>30002</v>
       </c>
       <c r="E25" s="11" t="n">
         <v>3</v>
@@ -1177,20 +1177,20 @@
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
-          <t>자원 감자 x3</t>
+          <t>자원 소나무 목재 x3</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="13" t="n"/>
       <c r="B26" s="11" t="n">
-        <v>7003</v>
+        <v>7004</v>
       </c>
       <c r="C26" s="11" t="n">
         <v>7</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>30002</v>
+        <v>40002</v>
       </c>
       <c r="E26" s="11" t="n">
         <v>3</v>
@@ -1200,20 +1200,20 @@
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
-          <t>자원 소나무 목재 x3</t>
+          <t>자원 구리 광석 x3</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="13" t="n"/>
       <c r="B27" s="11" t="n">
-        <v>7004</v>
+        <v>7005</v>
       </c>
       <c r="C27" s="11" t="n">
         <v>7</v>
       </c>
       <c r="D27" s="11" t="n">
-        <v>40002</v>
+        <v>50002</v>
       </c>
       <c r="E27" s="11" t="n">
         <v>3</v>
@@ -1223,135 +1223,135 @@
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
-          <t>자원 구리 광석 x3</t>
+          <t>자원 토끼 가죽 x3</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="13" t="n"/>
       <c r="B28" s="11" t="n">
-        <v>7005</v>
+        <v>7006</v>
       </c>
       <c r="C28" s="11" t="n">
         <v>7</v>
       </c>
       <c r="D28" s="11" t="n">
-        <v>50002</v>
+        <v>100011</v>
       </c>
       <c r="E28" s="11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
-          <t>자원 토끼 가죽 x3</t>
+          <t>상자 전용 은빛 나침반</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="13" t="n"/>
       <c r="B29" s="11" t="n">
-        <v>7006</v>
+        <v>7008</v>
       </c>
       <c r="C29" s="11" t="n">
         <v>7</v>
       </c>
       <c r="D29" s="11" t="n">
-        <v>100011</v>
+        <v>100015</v>
       </c>
       <c r="E29" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
-          <t>상자 전용 은빛 나침반</t>
+          <t>인챈트 큐브</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="13" t="n"/>
       <c r="B30" s="11" t="n">
-        <v>7007</v>
+        <v>7010</v>
       </c>
       <c r="C30" s="11" t="n">
         <v>7</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>100013</v>
+        <v>100018</v>
       </c>
       <c r="E30" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
-          <t>인챈트 원석</t>
+          <t>상급 인챈트 큐브</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="13" t="n"/>
       <c r="B31" s="11" t="n">
-        <v>7008</v>
+        <v>8001</v>
       </c>
       <c r="C31" s="11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D31" s="11" t="n">
-        <v>100015</v>
+        <v>10003</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
-          <t>인챈트 큐브</t>
+          <t>자원 월척 붕어 x2</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="13" t="n"/>
       <c r="B32" s="11" t="n">
-        <v>7009</v>
+        <v>8002</v>
       </c>
       <c r="C32" s="11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D32" s="11" t="n">
-        <v>100016</v>
+        <v>20003</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="G32" s="12" t="inlineStr">
         <is>
-          <t>인챈트 확장석</t>
+          <t>자원 옥수수 x2</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="13" t="n"/>
       <c r="B33" s="11" t="n">
-        <v>8001</v>
+        <v>8003</v>
       </c>
       <c r="C33" s="11" t="n">
         <v>8</v>
       </c>
       <c r="D33" s="11" t="n">
-        <v>10003</v>
+        <v>30003</v>
       </c>
       <c r="E33" s="11" t="n">
         <v>2</v>
@@ -1361,20 +1361,20 @@
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
-          <t>자원 월척 붕어 x2</t>
+          <t>자원 참나무 목재 x2</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="13" t="n"/>
       <c r="B34" s="11" t="n">
-        <v>8002</v>
+        <v>8004</v>
       </c>
       <c r="C34" s="11" t="n">
         <v>8</v>
       </c>
       <c r="D34" s="11" t="n">
-        <v>20003</v>
+        <v>40003</v>
       </c>
       <c r="E34" s="11" t="n">
         <v>2</v>
@@ -1384,20 +1384,20 @@
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
-          <t>자원 옥수수 x2</t>
+          <t>자원 은광석 x2</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="13" t="n"/>
       <c r="B35" s="11" t="n">
-        <v>8003</v>
+        <v>8005</v>
       </c>
       <c r="C35" s="11" t="n">
         <v>8</v>
       </c>
       <c r="D35" s="11" t="n">
-        <v>30003</v>
+        <v>50003</v>
       </c>
       <c r="E35" s="11" t="n">
         <v>2</v>
@@ -1407,156 +1407,87 @@
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
-          <t>자원 참나무 목재 x2</t>
+          <t>자원 늑대 가죽 x2</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="13" t="n"/>
       <c r="B36" s="11" t="n">
-        <v>8004</v>
+        <v>8006</v>
       </c>
       <c r="C36" s="11" t="n">
         <v>8</v>
       </c>
       <c r="D36" s="11" t="n">
-        <v>40003</v>
+        <v>100012</v>
       </c>
       <c r="E36" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="G36" s="12" t="inlineStr">
         <is>
-          <t>자원 은광석 x2</t>
+          <t>상자 전용 황금 열쇠</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="13" t="n"/>
       <c r="B37" s="11" t="n">
-        <v>8005</v>
+        <v>8007</v>
       </c>
       <c r="C37" s="11" t="n">
         <v>8</v>
       </c>
       <c r="D37" s="11" t="n">
-        <v>50003</v>
+        <v>100015</v>
       </c>
       <c r="E37" s="11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F37" s="11" t="n">
         <v>80</v>
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
-          <t>자원 늑대 가죽 x2</t>
+          <t>인챈트 큐브</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="13" t="n"/>
       <c r="B38" s="11" t="n">
-        <v>8006</v>
+        <v>8010</v>
       </c>
       <c r="C38" s="11" t="n">
         <v>8</v>
       </c>
       <c r="D38" s="11" t="n">
-        <v>100012</v>
+        <v>100018</v>
       </c>
       <c r="E38" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="G38" s="12" t="inlineStr">
         <is>
-          <t>상자 전용 황금 열쇠</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="13" t="n"/>
-      <c r="B39" s="11" t="n">
-        <v>8007</v>
-      </c>
-      <c r="C39" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="D39" s="11" t="n">
-        <v>100015</v>
-      </c>
-      <c r="E39" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F39" s="11" t="n">
-        <v>80</v>
-      </c>
-      <c r="G39" s="12" t="inlineStr">
-        <is>
-          <t>인챈트 큐브</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="13" t="n"/>
-      <c r="B40" s="11" t="n">
-        <v>8008</v>
-      </c>
-      <c r="C40" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="D40" s="11" t="n">
-        <v>100014</v>
-      </c>
-      <c r="E40" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F40" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="G40" s="12" t="inlineStr">
-        <is>
-          <t>정제된 인챈트 원석</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="13" t="n"/>
-      <c r="B41" s="11" t="n">
-        <v>8009</v>
-      </c>
-      <c r="C41" s="11" t="n">
-        <v>8</v>
-      </c>
-      <c r="D41" s="11" t="n">
-        <v>100017</v>
-      </c>
-      <c r="E41" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F41" s="11" t="n">
-        <v>15</v>
-      </c>
-      <c r="G41" s="12" t="inlineStr">
-        <is>
-          <t>정제된 인챈트 확장석</t>
+          <t>상급 인챈트 큐브</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing r:id="anysvml"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -1991,12 +1922,12 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing r:id="anysvml"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -2926,12 +2857,12 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing r:id="anysvml"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -5080,12 +5011,12 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing r:id="anysvml"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -5461,6 +5392,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing r:id="anysvml"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
--- a/GameDesign/Excel/Gacha.xlsx
+++ b/GameDesign/Excel/Gacha.xlsx
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -954,125 +954,125 @@
     <row r="16">
       <c r="A16" s="13" t="n"/>
       <c r="B16" s="11" t="n">
-        <v>6001</v>
+        <v>9001</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D16" s="11" t="n">
         <v>10001</v>
       </c>
       <c r="E16" s="11" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>80</v>
+        <v>800</v>
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
-          <t>자원 붕어 x5</t>
+          <t>자원 붕어 x27</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="13" t="n"/>
       <c r="B17" s="11" t="n">
-        <v>6002</v>
+        <v>9002</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D17" s="11" t="n">
         <v>20001</v>
       </c>
       <c r="E17" s="11" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>80</v>
+        <v>800</v>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
-          <t>자원 밀 x5</t>
+          <t>자원 밀 x27</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="13" t="n"/>
       <c r="B18" s="11" t="n">
-        <v>6003</v>
+        <v>9003</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D18" s="11" t="n">
         <v>30001</v>
       </c>
       <c r="E18" s="11" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>80</v>
+        <v>800</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
-          <t>자원 잡목 x5</t>
+          <t>자원 잡목 x27</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="13" t="n"/>
       <c r="B19" s="11" t="n">
-        <v>6004</v>
+        <v>9004</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D19" s="11" t="n">
         <v>40001</v>
       </c>
       <c r="E19" s="11" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>80</v>
+        <v>800</v>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
-          <t>자원 돌덩어리 x5</t>
+          <t>자원 돌덩어리 x27</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="13" t="n"/>
       <c r="B20" s="11" t="n">
-        <v>6005</v>
+        <v>9005</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D20" s="11" t="n">
         <v>50001</v>
       </c>
       <c r="E20" s="11" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>80</v>
+        <v>800</v>
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
-          <t>자원 질긴 고기 x5</t>
+          <t>자원 질긴 고기 x27</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="13" t="n"/>
       <c r="B21" s="11" t="n">
-        <v>6006</v>
+        <v>9006</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D21" s="11" t="n">
         <v>100010</v>
@@ -1081,7 +1081,7 @@
         <v>1</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
@@ -1092,10 +1092,10 @@
     <row r="22">
       <c r="A22" s="13" t="n"/>
       <c r="B22" s="11" t="n">
-        <v>6009</v>
+        <v>9007</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D22" s="11" t="n">
         <v>100015</v>
@@ -1104,136 +1104,136 @@
         <v>1</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>40</v>
+        <v>400</v>
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
-          <t>인챈트 큐브</t>
+          <t>인챈트 큐브 x1</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="13" t="n"/>
       <c r="B23" s="11" t="n">
-        <v>7001</v>
+        <v>10001</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D23" s="11" t="n">
         <v>10002</v>
       </c>
       <c r="E23" s="11" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>80</v>
+        <v>800</v>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
-          <t>자원 잉어 x3</t>
+          <t>자원 잉어 x33</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="13" t="n"/>
       <c r="B24" s="11" t="n">
-        <v>7002</v>
+        <v>10002</v>
       </c>
       <c r="C24" s="11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D24" s="11" t="n">
         <v>20002</v>
       </c>
       <c r="E24" s="11" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>80</v>
+        <v>800</v>
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
-          <t>자원 감자 x3</t>
+          <t>자원 감자 x33</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="13" t="n"/>
       <c r="B25" s="11" t="n">
-        <v>7003</v>
+        <v>10003</v>
       </c>
       <c r="C25" s="11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D25" s="11" t="n">
         <v>30002</v>
       </c>
       <c r="E25" s="11" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>80</v>
+        <v>800</v>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
-          <t>자원 소나무 목재 x3</t>
+          <t>자원 소나무 목재 x33</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="13" t="n"/>
       <c r="B26" s="11" t="n">
-        <v>7004</v>
+        <v>10004</v>
       </c>
       <c r="C26" s="11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D26" s="11" t="n">
         <v>40002</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>80</v>
+        <v>800</v>
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
-          <t>자원 구리 광석 x3</t>
+          <t>자원 구리 광석 x33</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="13" t="n"/>
       <c r="B27" s="11" t="n">
-        <v>7005</v>
+        <v>10005</v>
       </c>
       <c r="C27" s="11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D27" s="11" t="n">
         <v>50002</v>
       </c>
       <c r="E27" s="11" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>80</v>
+        <v>800</v>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
-          <t>자원 토끼 가죽 x3</t>
+          <t>자원 토끼 가죽 x33</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="13" t="n"/>
       <c r="B28" s="11" t="n">
-        <v>7006</v>
+        <v>10006</v>
       </c>
       <c r="C28" s="11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D28" s="11" t="n">
         <v>100011</v>
@@ -1242,7 +1242,7 @@
         <v>1</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
@@ -1253,10 +1253,10 @@
     <row r="29">
       <c r="A29" s="13" t="n"/>
       <c r="B29" s="11" t="n">
-        <v>7008</v>
+        <v>10007</v>
       </c>
       <c r="C29" s="11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D29" s="11" t="n">
         <v>100015</v>
@@ -1265,21 +1265,21 @@
         <v>1</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>40</v>
+        <v>400</v>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
-          <t>인챈트 큐브</t>
+          <t>인챈트 큐브 x1</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="13" t="n"/>
       <c r="B30" s="11" t="n">
-        <v>7010</v>
+        <v>10008</v>
       </c>
       <c r="C30" s="11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D30" s="11" t="n">
         <v>100018</v>
@@ -1288,136 +1288,136 @@
         <v>1</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
-          <t>상급 인챈트 큐브</t>
+          <t>상급 인챈트 큐브 x1</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="13" t="n"/>
       <c r="B31" s="11" t="n">
-        <v>8001</v>
+        <v>11001</v>
       </c>
       <c r="C31" s="11" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D31" s="11" t="n">
         <v>10003</v>
       </c>
       <c r="E31" s="11" t="n">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>80</v>
+        <v>800</v>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
-          <t>자원 월척 붕어 x2</t>
+          <t>자원 월척 붕어 x45</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="13" t="n"/>
       <c r="B32" s="11" t="n">
-        <v>8002</v>
+        <v>11002</v>
       </c>
       <c r="C32" s="11" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D32" s="11" t="n">
         <v>20003</v>
       </c>
       <c r="E32" s="11" t="n">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>80</v>
+        <v>800</v>
       </c>
       <c r="G32" s="12" t="inlineStr">
         <is>
-          <t>자원 옥수수 x2</t>
+          <t>자원 옥수수 x45</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="13" t="n"/>
       <c r="B33" s="11" t="n">
-        <v>8003</v>
+        <v>11003</v>
       </c>
       <c r="C33" s="11" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D33" s="11" t="n">
         <v>30003</v>
       </c>
       <c r="E33" s="11" t="n">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>80</v>
+        <v>800</v>
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
-          <t>자원 참나무 목재 x2</t>
+          <t>자원 참나무 목재 x45</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="13" t="n"/>
       <c r="B34" s="11" t="n">
-        <v>8004</v>
+        <v>11004</v>
       </c>
       <c r="C34" s="11" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D34" s="11" t="n">
         <v>40003</v>
       </c>
       <c r="E34" s="11" t="n">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>80</v>
+        <v>800</v>
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
-          <t>자원 은광석 x2</t>
+          <t>자원 은광석 x45</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="13" t="n"/>
       <c r="B35" s="11" t="n">
-        <v>8005</v>
+        <v>11005</v>
       </c>
       <c r="C35" s="11" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D35" s="11" t="n">
         <v>50003</v>
       </c>
       <c r="E35" s="11" t="n">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>80</v>
+        <v>800</v>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
-          <t>자원 늑대 가죽 x2</t>
+          <t>자원 늑대 가죽 x45</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="13" t="n"/>
       <c r="B36" s="11" t="n">
-        <v>8006</v>
+        <v>11006</v>
       </c>
       <c r="C36" s="11" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D36" s="11" t="n">
         <v>100012</v>
@@ -1426,7 +1426,7 @@
         <v>1</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>20</v>
+        <v>200</v>
       </c>
       <c r="G36" s="12" t="inlineStr">
         <is>
@@ -1437,10 +1437,10 @@
     <row r="37">
       <c r="A37" s="13" t="n"/>
       <c r="B37" s="11" t="n">
-        <v>8007</v>
+        <v>11007</v>
       </c>
       <c r="C37" s="11" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D37" s="11" t="n">
         <v>100015</v>
@@ -1449,21 +1449,21 @@
         <v>1</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>80</v>
+        <v>800</v>
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
-          <t>인챈트 큐브</t>
+          <t>인챈트 큐브 x1</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="13" t="n"/>
       <c r="B38" s="11" t="n">
-        <v>8010</v>
+        <v>11008</v>
       </c>
       <c r="C38" s="11" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D38" s="11" t="n">
         <v>100018</v>
@@ -1472,11 +1472,2127 @@
         <v>1</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>40</v>
+        <v>400</v>
       </c>
       <c r="G38" s="12" t="inlineStr">
         <is>
-          <t>상급 인챈트 큐브</t>
+          <t>상급 인챈트 큐브 x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="13" t="n"/>
+      <c r="B39" s="11" t="n">
+        <v>12001</v>
+      </c>
+      <c r="C39" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="D39" s="11" t="n">
+        <v>10011</v>
+      </c>
+      <c r="E39" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="F39" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="G39" s="12" t="inlineStr">
+        <is>
+          <t>자원 피라미 x27</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="13" t="n"/>
+      <c r="B40" s="11" t="n">
+        <v>12002</v>
+      </c>
+      <c r="C40" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="D40" s="11" t="n">
+        <v>20011</v>
+      </c>
+      <c r="E40" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="F40" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="G40" s="12" t="inlineStr">
+        <is>
+          <t>자원 보리 x27</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="13" t="n"/>
+      <c r="B41" s="11" t="n">
+        <v>12003</v>
+      </c>
+      <c r="C41" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="D41" s="11" t="n">
+        <v>30011</v>
+      </c>
+      <c r="E41" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="F41" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="G41" s="12" t="inlineStr">
+        <is>
+          <t>자원 잔가지 x27</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="13" t="n"/>
+      <c r="B42" s="11" t="n">
+        <v>12004</v>
+      </c>
+      <c r="C42" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="D42" s="11" t="n">
+        <v>40011</v>
+      </c>
+      <c r="E42" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="F42" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="G42" s="12" t="inlineStr">
+        <is>
+          <t>자원 석회암 x27</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="13" t="n"/>
+      <c r="B43" s="11" t="n">
+        <v>12005</v>
+      </c>
+      <c r="C43" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="D43" s="11" t="n">
+        <v>50011</v>
+      </c>
+      <c r="E43" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="F43" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="G43" s="12" t="inlineStr">
+        <is>
+          <t>자원 여우 가죽 x27</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="13" t="n"/>
+      <c r="B44" s="11" t="n">
+        <v>12006</v>
+      </c>
+      <c r="C44" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="D44" s="11" t="n">
+        <v>100010</v>
+      </c>
+      <c r="E44" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" s="11" t="n">
+        <v>200</v>
+      </c>
+      <c r="G44" s="12" t="inlineStr">
+        <is>
+          <t>상자 전용 낡은 보물 지도</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="13" t="n"/>
+      <c r="B45" s="11" t="n">
+        <v>12007</v>
+      </c>
+      <c r="C45" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="D45" s="11" t="n">
+        <v>100015</v>
+      </c>
+      <c r="E45" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F45" s="11" t="n">
+        <v>400</v>
+      </c>
+      <c r="G45" s="12" t="inlineStr">
+        <is>
+          <t>인챈트 큐브 x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="13" t="n"/>
+      <c r="B46" s="11" t="n">
+        <v>13001</v>
+      </c>
+      <c r="C46" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="D46" s="11" t="n">
+        <v>10012</v>
+      </c>
+      <c r="E46" s="11" t="n">
+        <v>33</v>
+      </c>
+      <c r="F46" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="G46" s="12" t="inlineStr">
+        <is>
+          <t>자원 메기 x33</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="13" t="n"/>
+      <c r="B47" s="11" t="n">
+        <v>13002</v>
+      </c>
+      <c r="C47" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="D47" s="11" t="n">
+        <v>20012</v>
+      </c>
+      <c r="E47" s="11" t="n">
+        <v>33</v>
+      </c>
+      <c r="F47" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="G47" s="12" t="inlineStr">
+        <is>
+          <t>자원 고구마 x33</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="13" t="n"/>
+      <c r="B48" s="11" t="n">
+        <v>13003</v>
+      </c>
+      <c r="C48" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="D48" s="11" t="n">
+        <v>30012</v>
+      </c>
+      <c r="E48" s="11" t="n">
+        <v>33</v>
+      </c>
+      <c r="F48" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="G48" s="12" t="inlineStr">
+        <is>
+          <t>자원 삼나무 목재 x33</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="13" t="n"/>
+      <c r="B49" s="11" t="n">
+        <v>13004</v>
+      </c>
+      <c r="C49" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="D49" s="11" t="n">
+        <v>40012</v>
+      </c>
+      <c r="E49" s="11" t="n">
+        <v>33</v>
+      </c>
+      <c r="F49" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="G49" s="12" t="inlineStr">
+        <is>
+          <t>자원 주석 광석 x33</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="13" t="n"/>
+      <c r="B50" s="11" t="n">
+        <v>13005</v>
+      </c>
+      <c r="C50" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="D50" s="11" t="n">
+        <v>50012</v>
+      </c>
+      <c r="E50" s="11" t="n">
+        <v>33</v>
+      </c>
+      <c r="F50" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="G50" s="12" t="inlineStr">
+        <is>
+          <t>자원 멧돼지 엄니 x33</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="13" t="n"/>
+      <c r="B51" s="11" t="n">
+        <v>13006</v>
+      </c>
+      <c r="C51" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="D51" s="11" t="n">
+        <v>100011</v>
+      </c>
+      <c r="E51" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" s="11" t="n">
+        <v>200</v>
+      </c>
+      <c r="G51" s="12" t="inlineStr">
+        <is>
+          <t>상자 전용 은빛 나침반</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="13" t="n"/>
+      <c r="B52" s="11" t="n">
+        <v>13007</v>
+      </c>
+      <c r="C52" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="D52" s="11" t="n">
+        <v>100015</v>
+      </c>
+      <c r="E52" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F52" s="11" t="n">
+        <v>400</v>
+      </c>
+      <c r="G52" s="12" t="inlineStr">
+        <is>
+          <t>인챈트 큐브 x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="13" t="n"/>
+      <c r="B53" s="11" t="n">
+        <v>13008</v>
+      </c>
+      <c r="C53" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="D53" s="11" t="n">
+        <v>100018</v>
+      </c>
+      <c r="E53" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F53" s="11" t="n">
+        <v>200</v>
+      </c>
+      <c r="G53" s="12" t="inlineStr">
+        <is>
+          <t>상급 인챈트 큐브 x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="13" t="n"/>
+      <c r="B54" s="11" t="n">
+        <v>14001</v>
+      </c>
+      <c r="C54" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="D54" s="11" t="n">
+        <v>10013</v>
+      </c>
+      <c r="E54" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="F54" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="G54" s="12" t="inlineStr">
+        <is>
+          <t>자원 가물치 x45</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="13" t="n"/>
+      <c r="B55" s="11" t="n">
+        <v>14002</v>
+      </c>
+      <c r="C55" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="D55" s="11" t="n">
+        <v>20013</v>
+      </c>
+      <c r="E55" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="F55" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="G55" s="12" t="inlineStr">
+        <is>
+          <t>자원 호박 x45</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="13" t="n"/>
+      <c r="B56" s="11" t="n">
+        <v>14003</v>
+      </c>
+      <c r="C56" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="D56" s="11" t="n">
+        <v>30013</v>
+      </c>
+      <c r="E56" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="F56" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="G56" s="12" t="inlineStr">
+        <is>
+          <t>자원 편백나무 목재 x45</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="13" t="n"/>
+      <c r="B57" s="11" t="n">
+        <v>14004</v>
+      </c>
+      <c r="C57" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="D57" s="11" t="n">
+        <v>40013</v>
+      </c>
+      <c r="E57" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="F57" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="G57" s="12" t="inlineStr">
+        <is>
+          <t>자원 철광석 x45</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="13" t="n"/>
+      <c r="B58" s="11" t="n">
+        <v>14005</v>
+      </c>
+      <c r="C58" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="D58" s="11" t="n">
+        <v>50013</v>
+      </c>
+      <c r="E58" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="F58" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="G58" s="12" t="inlineStr">
+        <is>
+          <t>자원 사슴뿔 x45</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="13" t="n"/>
+      <c r="B59" s="11" t="n">
+        <v>14006</v>
+      </c>
+      <c r="C59" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="D59" s="11" t="n">
+        <v>100012</v>
+      </c>
+      <c r="E59" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F59" s="11" t="n">
+        <v>200</v>
+      </c>
+      <c r="G59" s="12" t="inlineStr">
+        <is>
+          <t>상자 전용 황금 열쇠</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="13" t="n"/>
+      <c r="B60" s="11" t="n">
+        <v>14007</v>
+      </c>
+      <c r="C60" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="D60" s="11" t="n">
+        <v>100015</v>
+      </c>
+      <c r="E60" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F60" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="G60" s="12" t="inlineStr">
+        <is>
+          <t>인챈트 큐브 x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="13" t="n"/>
+      <c r="B61" s="11" t="n">
+        <v>14008</v>
+      </c>
+      <c r="C61" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="D61" s="11" t="n">
+        <v>100018</v>
+      </c>
+      <c r="E61" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F61" s="11" t="n">
+        <v>400</v>
+      </c>
+      <c r="G61" s="12" t="inlineStr">
+        <is>
+          <t>상급 인챈트 큐브 x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="13" t="n"/>
+      <c r="B62" s="11" t="n">
+        <v>15001</v>
+      </c>
+      <c r="C62" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="D62" s="11" t="n">
+        <v>10021</v>
+      </c>
+      <c r="E62" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="F62" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="G62" s="12" t="inlineStr">
+        <is>
+          <t>자원 모래무지 x27</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="13" t="n"/>
+      <c r="B63" s="11" t="n">
+        <v>15002</v>
+      </c>
+      <c r="C63" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="D63" s="11" t="n">
+        <v>20021</v>
+      </c>
+      <c r="E63" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="F63" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="G63" s="12" t="inlineStr">
+        <is>
+          <t>자원 벼 x27</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="13" t="n"/>
+      <c r="B64" s="11" t="n">
+        <v>15003</v>
+      </c>
+      <c r="C64" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="D64" s="11" t="n">
+        <v>30021</v>
+      </c>
+      <c r="E64" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="F64" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="G64" s="12" t="inlineStr">
+        <is>
+          <t>자원 도토리 가지 x27</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="13" t="n"/>
+      <c r="B65" s="11" t="n">
+        <v>15004</v>
+      </c>
+      <c r="C65" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="D65" s="11" t="n">
+        <v>40021</v>
+      </c>
+      <c r="E65" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="F65" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="G65" s="12" t="inlineStr">
+        <is>
+          <t>자원 현무암 x27</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="13" t="n"/>
+      <c r="B66" s="11" t="n">
+        <v>15005</v>
+      </c>
+      <c r="C66" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="D66" s="11" t="n">
+        <v>50021</v>
+      </c>
+      <c r="E66" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="F66" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="G66" s="12" t="inlineStr">
+        <is>
+          <t>자원 표범 가죽 x27</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="13" t="n"/>
+      <c r="B67" s="11" t="n">
+        <v>15006</v>
+      </c>
+      <c r="C67" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="D67" s="11" t="n">
+        <v>100010</v>
+      </c>
+      <c r="E67" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F67" s="11" t="n">
+        <v>200</v>
+      </c>
+      <c r="G67" s="12" t="inlineStr">
+        <is>
+          <t>상자 전용 낡은 보물 지도</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="13" t="n"/>
+      <c r="B68" s="11" t="n">
+        <v>15007</v>
+      </c>
+      <c r="C68" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="D68" s="11" t="n">
+        <v>100015</v>
+      </c>
+      <c r="E68" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F68" s="11" t="n">
+        <v>400</v>
+      </c>
+      <c r="G68" s="12" t="inlineStr">
+        <is>
+          <t>인챈트 큐브 x3</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="13" t="n"/>
+      <c r="B69" s="11" t="n">
+        <v>16001</v>
+      </c>
+      <c r="C69" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="D69" s="11" t="n">
+        <v>10022</v>
+      </c>
+      <c r="E69" s="11" t="n">
+        <v>33</v>
+      </c>
+      <c r="F69" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="G69" s="12" t="inlineStr">
+        <is>
+          <t>자원 쏘가리 x33</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="13" t="n"/>
+      <c r="B70" s="11" t="n">
+        <v>16002</v>
+      </c>
+      <c r="C70" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="D70" s="11" t="n">
+        <v>20022</v>
+      </c>
+      <c r="E70" s="11" t="n">
+        <v>33</v>
+      </c>
+      <c r="F70" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="G70" s="12" t="inlineStr">
+        <is>
+          <t>자원 콩 x33</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="13" t="n"/>
+      <c r="B71" s="11" t="n">
+        <v>16003</v>
+      </c>
+      <c r="C71" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="D71" s="11" t="n">
+        <v>30022</v>
+      </c>
+      <c r="E71" s="11" t="n">
+        <v>33</v>
+      </c>
+      <c r="F71" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="G71" s="12" t="inlineStr">
+        <is>
+          <t>자원 너도밤나무 목재 x33</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="13" t="n"/>
+      <c r="B72" s="11" t="n">
+        <v>16004</v>
+      </c>
+      <c r="C72" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="D72" s="11" t="n">
+        <v>40022</v>
+      </c>
+      <c r="E72" s="11" t="n">
+        <v>33</v>
+      </c>
+      <c r="F72" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="G72" s="12" t="inlineStr">
+        <is>
+          <t>자원 아연 광석 x33</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="13" t="n"/>
+      <c r="B73" s="11" t="n">
+        <v>16005</v>
+      </c>
+      <c r="C73" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="D73" s="11" t="n">
+        <v>50022</v>
+      </c>
+      <c r="E73" s="11" t="n">
+        <v>33</v>
+      </c>
+      <c r="F73" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="G73" s="12" t="inlineStr">
+        <is>
+          <t>자원 큰뿔 사슴뿔 x33</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="13" t="n"/>
+      <c r="B74" s="11" t="n">
+        <v>16006</v>
+      </c>
+      <c r="C74" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="D74" s="11" t="n">
+        <v>100011</v>
+      </c>
+      <c r="E74" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F74" s="11" t="n">
+        <v>200</v>
+      </c>
+      <c r="G74" s="12" t="inlineStr">
+        <is>
+          <t>상자 전용 은빛 나침반</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="13" t="n"/>
+      <c r="B75" s="11" t="n">
+        <v>16007</v>
+      </c>
+      <c r="C75" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="D75" s="11" t="n">
+        <v>100015</v>
+      </c>
+      <c r="E75" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F75" s="11" t="n">
+        <v>400</v>
+      </c>
+      <c r="G75" s="12" t="inlineStr">
+        <is>
+          <t>인챈트 큐브 x3</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="13" t="n"/>
+      <c r="B76" s="11" t="n">
+        <v>16008</v>
+      </c>
+      <c r="C76" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="D76" s="11" t="n">
+        <v>100018</v>
+      </c>
+      <c r="E76" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F76" s="11" t="n">
+        <v>200</v>
+      </c>
+      <c r="G76" s="12" t="inlineStr">
+        <is>
+          <t>상급 인챈트 큐브 x3</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="13" t="n"/>
+      <c r="B77" s="11" t="n">
+        <v>17001</v>
+      </c>
+      <c r="C77" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="D77" s="11" t="n">
+        <v>10023</v>
+      </c>
+      <c r="E77" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="F77" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="G77" s="12" t="inlineStr">
+        <is>
+          <t>자원 황금 잉어 x45</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="13" t="n"/>
+      <c r="B78" s="11" t="n">
+        <v>17002</v>
+      </c>
+      <c r="C78" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="D78" s="11" t="n">
+        <v>20023</v>
+      </c>
+      <c r="E78" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="F78" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="G78" s="12" t="inlineStr">
+        <is>
+          <t>자원 딸기 x45</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="13" t="n"/>
+      <c r="B79" s="11" t="n">
+        <v>17003</v>
+      </c>
+      <c r="C79" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="D79" s="11" t="n">
+        <v>30023</v>
+      </c>
+      <c r="E79" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="F79" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="G79" s="12" t="inlineStr">
+        <is>
+          <t>자원 단풍나무 목재 x45</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="13" t="n"/>
+      <c r="B80" s="11" t="n">
+        <v>17004</v>
+      </c>
+      <c r="C80" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="D80" s="11" t="n">
+        <v>40023</v>
+      </c>
+      <c r="E80" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="F80" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="G80" s="12" t="inlineStr">
+        <is>
+          <t>자원 미스릴 광석 x45</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="13" t="n"/>
+      <c r="B81" s="11" t="n">
+        <v>17005</v>
+      </c>
+      <c r="C81" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="D81" s="11" t="n">
+        <v>50023</v>
+      </c>
+      <c r="E81" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="F81" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="G81" s="12" t="inlineStr">
+        <is>
+          <t>자원 곰의 이빨 x45</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="13" t="n"/>
+      <c r="B82" s="11" t="n">
+        <v>17006</v>
+      </c>
+      <c r="C82" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="D82" s="11" t="n">
+        <v>100012</v>
+      </c>
+      <c r="E82" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F82" s="11" t="n">
+        <v>200</v>
+      </c>
+      <c r="G82" s="12" t="inlineStr">
+        <is>
+          <t>상자 전용 황금 열쇠</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="13" t="n"/>
+      <c r="B83" s="11" t="n">
+        <v>17007</v>
+      </c>
+      <c r="C83" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="D83" s="11" t="n">
+        <v>100015</v>
+      </c>
+      <c r="E83" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F83" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="G83" s="12" t="inlineStr">
+        <is>
+          <t>인챈트 큐브 x3</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="13" t="n"/>
+      <c r="B84" s="11" t="n">
+        <v>17008</v>
+      </c>
+      <c r="C84" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="D84" s="11" t="n">
+        <v>100018</v>
+      </c>
+      <c r="E84" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F84" s="11" t="n">
+        <v>400</v>
+      </c>
+      <c r="G84" s="12" t="inlineStr">
+        <is>
+          <t>상급 인챈트 큐브 x3</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="13" t="n"/>
+      <c r="B85" s="11" t="n">
+        <v>18001</v>
+      </c>
+      <c r="C85" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="D85" s="11" t="n">
+        <v>10031</v>
+      </c>
+      <c r="E85" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="F85" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="G85" s="12" t="inlineStr">
+        <is>
+          <t>자원 빙어 x27</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="13" t="n"/>
+      <c r="B86" s="11" t="n">
+        <v>18002</v>
+      </c>
+      <c r="C86" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="D86" s="11" t="n">
+        <v>20031</v>
+      </c>
+      <c r="E86" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="F86" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="G86" s="12" t="inlineStr">
+        <is>
+          <t>자원 목화 x27</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="13" t="n"/>
+      <c r="B87" s="11" t="n">
+        <v>18003</v>
+      </c>
+      <c r="C87" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="D87" s="11" t="n">
+        <v>30031</v>
+      </c>
+      <c r="E87" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="F87" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="G87" s="12" t="inlineStr">
+        <is>
+          <t>자원 그을린 통나무 x27</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="13" t="n"/>
+      <c r="B88" s="11" t="n">
+        <v>18004</v>
+      </c>
+      <c r="C88" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="D88" s="11" t="n">
+        <v>40031</v>
+      </c>
+      <c r="E88" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="F88" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="G88" s="12" t="inlineStr">
+        <is>
+          <t>자원 수정 파편 x27</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="13" t="n"/>
+      <c r="B89" s="11" t="n">
+        <v>18005</v>
+      </c>
+      <c r="C89" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="D89" s="11" t="n">
+        <v>50031</v>
+      </c>
+      <c r="E89" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="F89" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="G89" s="12" t="inlineStr">
+        <is>
+          <t>자원 설표 가죽 x27</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="13" t="n"/>
+      <c r="B90" s="11" t="n">
+        <v>18006</v>
+      </c>
+      <c r="C90" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="D90" s="11" t="n">
+        <v>100010</v>
+      </c>
+      <c r="E90" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F90" s="11" t="n">
+        <v>200</v>
+      </c>
+      <c r="G90" s="12" t="inlineStr">
+        <is>
+          <t>상자 전용 낡은 보물 지도</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="13" t="n"/>
+      <c r="B91" s="11" t="n">
+        <v>18007</v>
+      </c>
+      <c r="C91" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="D91" s="11" t="n">
+        <v>100015</v>
+      </c>
+      <c r="E91" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="F91" s="11" t="n">
+        <v>400</v>
+      </c>
+      <c r="G91" s="12" t="inlineStr">
+        <is>
+          <t>인챈트 큐브 x4</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="13" t="n"/>
+      <c r="B92" s="11" t="n">
+        <v>19001</v>
+      </c>
+      <c r="C92" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="D92" s="11" t="n">
+        <v>10032</v>
+      </c>
+      <c r="E92" s="11" t="n">
+        <v>33</v>
+      </c>
+      <c r="F92" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="G92" s="12" t="inlineStr">
+        <is>
+          <t>자원 송어 x33</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="13" t="n"/>
+      <c r="B93" s="11" t="n">
+        <v>19002</v>
+      </c>
+      <c r="C93" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="D93" s="11" t="n">
+        <v>20032</v>
+      </c>
+      <c r="E93" s="11" t="n">
+        <v>33</v>
+      </c>
+      <c r="F93" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="G93" s="12" t="inlineStr">
+        <is>
+          <t>자원 사탕수수 x33</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="13" t="n"/>
+      <c r="B94" s="11" t="n">
+        <v>19003</v>
+      </c>
+      <c r="C94" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="D94" s="11" t="n">
+        <v>30032</v>
+      </c>
+      <c r="E94" s="11" t="n">
+        <v>33</v>
+      </c>
+      <c r="F94" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="G94" s="12" t="inlineStr">
+        <is>
+          <t>자원 흑참나무 목재 x33</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="13" t="n"/>
+      <c r="B95" s="11" t="n">
+        <v>19004</v>
+      </c>
+      <c r="C95" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="D95" s="11" t="n">
+        <v>40032</v>
+      </c>
+      <c r="E95" s="11" t="n">
+        <v>33</v>
+      </c>
+      <c r="F95" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="G95" s="12" t="inlineStr">
+        <is>
+          <t>자원 코발트 광석 x33</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="13" t="n"/>
+      <c r="B96" s="11" t="n">
+        <v>19005</v>
+      </c>
+      <c r="C96" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="D96" s="11" t="n">
+        <v>50032</v>
+      </c>
+      <c r="E96" s="11" t="n">
+        <v>33</v>
+      </c>
+      <c r="F96" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="G96" s="12" t="inlineStr">
+        <is>
+          <t>자원 얼음늑대 송곳니 x33</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="13" t="n"/>
+      <c r="B97" s="11" t="n">
+        <v>19006</v>
+      </c>
+      <c r="C97" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="D97" s="11" t="n">
+        <v>100011</v>
+      </c>
+      <c r="E97" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F97" s="11" t="n">
+        <v>200</v>
+      </c>
+      <c r="G97" s="12" t="inlineStr">
+        <is>
+          <t>상자 전용 은빛 나침반</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="13" t="n"/>
+      <c r="B98" s="11" t="n">
+        <v>19007</v>
+      </c>
+      <c r="C98" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="D98" s="11" t="n">
+        <v>100015</v>
+      </c>
+      <c r="E98" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="F98" s="11" t="n">
+        <v>400</v>
+      </c>
+      <c r="G98" s="12" t="inlineStr">
+        <is>
+          <t>인챈트 큐브 x4</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="13" t="n"/>
+      <c r="B99" s="11" t="n">
+        <v>19008</v>
+      </c>
+      <c r="C99" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="D99" s="11" t="n">
+        <v>100018</v>
+      </c>
+      <c r="E99" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="F99" s="11" t="n">
+        <v>200</v>
+      </c>
+      <c r="G99" s="12" t="inlineStr">
+        <is>
+          <t>상급 인챈트 큐브 x4</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="13" t="n"/>
+      <c r="B100" s="11" t="n">
+        <v>20001</v>
+      </c>
+      <c r="C100" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="D100" s="11" t="n">
+        <v>10033</v>
+      </c>
+      <c r="E100" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="F100" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="G100" s="12" t="inlineStr">
+        <is>
+          <t>자원 무지개 송어 x45</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="13" t="n"/>
+      <c r="B101" s="11" t="n">
+        <v>20002</v>
+      </c>
+      <c r="C101" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="D101" s="11" t="n">
+        <v>20033</v>
+      </c>
+      <c r="E101" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="F101" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="G101" s="12" t="inlineStr">
+        <is>
+          <t>자원 커피 열매 x45</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="13" t="n"/>
+      <c r="B102" s="11" t="n">
+        <v>20003</v>
+      </c>
+      <c r="C102" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="D102" s="11" t="n">
+        <v>30033</v>
+      </c>
+      <c r="E102" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="F102" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="G102" s="12" t="inlineStr">
+        <is>
+          <t>자원 자단 목재 x45</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="13" t="n"/>
+      <c r="B103" s="11" t="n">
+        <v>20004</v>
+      </c>
+      <c r="C103" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="D103" s="11" t="n">
+        <v>40033</v>
+      </c>
+      <c r="E103" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="F103" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="G103" s="12" t="inlineStr">
+        <is>
+          <t>자원 오리하르콘 광석 x45</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="13" t="n"/>
+      <c r="B104" s="11" t="n">
+        <v>20005</v>
+      </c>
+      <c r="C104" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="D104" s="11" t="n">
+        <v>50033</v>
+      </c>
+      <c r="E104" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="F104" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="G104" s="12" t="inlineStr">
+        <is>
+          <t>자원 서리곰 모피 x45</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="13" t="n"/>
+      <c r="B105" s="11" t="n">
+        <v>20006</v>
+      </c>
+      <c r="C105" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="D105" s="11" t="n">
+        <v>100012</v>
+      </c>
+      <c r="E105" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F105" s="11" t="n">
+        <v>200</v>
+      </c>
+      <c r="G105" s="12" t="inlineStr">
+        <is>
+          <t>상자 전용 황금 열쇠</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="13" t="n"/>
+      <c r="B106" s="11" t="n">
+        <v>20007</v>
+      </c>
+      <c r="C106" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="D106" s="11" t="n">
+        <v>100015</v>
+      </c>
+      <c r="E106" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="F106" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="G106" s="12" t="inlineStr">
+        <is>
+          <t>인챈트 큐브 x4</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="13" t="n"/>
+      <c r="B107" s="11" t="n">
+        <v>20008</v>
+      </c>
+      <c r="C107" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="D107" s="11" t="n">
+        <v>100018</v>
+      </c>
+      <c r="E107" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="F107" s="11" t="n">
+        <v>400</v>
+      </c>
+      <c r="G107" s="12" t="inlineStr">
+        <is>
+          <t>상급 인챈트 큐브 x4</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="13" t="n"/>
+      <c r="B108" s="11" t="n">
+        <v>21001</v>
+      </c>
+      <c r="C108" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="D108" s="11" t="n">
+        <v>10041</v>
+      </c>
+      <c r="E108" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="F108" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="G108" s="12" t="inlineStr">
+        <is>
+          <t>자원 심해 새우 x27</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="13" t="n"/>
+      <c r="B109" s="11" t="n">
+        <v>21002</v>
+      </c>
+      <c r="C109" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="D109" s="11" t="n">
+        <v>20041</v>
+      </c>
+      <c r="E109" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="F109" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="G109" s="12" t="inlineStr">
+        <is>
+          <t>자원 정화된 흙 x27</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="13" t="n"/>
+      <c r="B110" s="11" t="n">
+        <v>21003</v>
+      </c>
+      <c r="C110" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="D110" s="11" t="n">
+        <v>30041</v>
+      </c>
+      <c r="E110" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="F110" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="G110" s="12" t="inlineStr">
+        <is>
+          <t>자원 세계수 껍질 x27</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="13" t="n"/>
+      <c r="B111" s="11" t="n">
+        <v>21004</v>
+      </c>
+      <c r="C111" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="D111" s="11" t="n">
+        <v>40041</v>
+      </c>
+      <c r="E111" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="F111" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="G111" s="12" t="inlineStr">
+        <is>
+          <t>자원 심연의 파편 x27</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="13" t="n"/>
+      <c r="B112" s="11" t="n">
+        <v>21005</v>
+      </c>
+      <c r="C112" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="D112" s="11" t="n">
+        <v>50041</v>
+      </c>
+      <c r="E112" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="F112" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="G112" s="12" t="inlineStr">
+        <is>
+          <t>자원 마수의 가죽 x27</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="13" t="n"/>
+      <c r="B113" s="11" t="n">
+        <v>21006</v>
+      </c>
+      <c r="C113" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="D113" s="11" t="n">
+        <v>100010</v>
+      </c>
+      <c r="E113" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F113" s="11" t="n">
+        <v>200</v>
+      </c>
+      <c r="G113" s="12" t="inlineStr">
+        <is>
+          <t>상자 전용 낡은 보물 지도</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="13" t="n"/>
+      <c r="B114" s="11" t="n">
+        <v>21007</v>
+      </c>
+      <c r="C114" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="D114" s="11" t="n">
+        <v>100015</v>
+      </c>
+      <c r="E114" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="F114" s="11" t="n">
+        <v>400</v>
+      </c>
+      <c r="G114" s="12" t="inlineStr">
+        <is>
+          <t>인챈트 큐브 x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="13" t="n"/>
+      <c r="B115" s="11" t="n">
+        <v>22001</v>
+      </c>
+      <c r="C115" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="D115" s="11" t="n">
+        <v>10042</v>
+      </c>
+      <c r="E115" s="11" t="n">
+        <v>33</v>
+      </c>
+      <c r="F115" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="G115" s="12" t="inlineStr">
+        <is>
+          <t>자원 아귀 x33</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="13" t="n"/>
+      <c r="B116" s="11" t="n">
+        <v>22002</v>
+      </c>
+      <c r="C116" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="D116" s="11" t="n">
+        <v>20042</v>
+      </c>
+      <c r="E116" s="11" t="n">
+        <v>33</v>
+      </c>
+      <c r="F116" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="G116" s="12" t="inlineStr">
+        <is>
+          <t>자원 성스러운 이삭 x33</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="13" t="n"/>
+      <c r="B117" s="11" t="n">
+        <v>22003</v>
+      </c>
+      <c r="C117" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="D117" s="11" t="n">
+        <v>30042</v>
+      </c>
+      <c r="E117" s="11" t="n">
+        <v>33</v>
+      </c>
+      <c r="F117" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="G117" s="12" t="inlineStr">
+        <is>
+          <t>자원 빛나는 수액 x33</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="13" t="n"/>
+      <c r="B118" s="11" t="n">
+        <v>22004</v>
+      </c>
+      <c r="C118" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="D118" s="11" t="n">
+        <v>40042</v>
+      </c>
+      <c r="E118" s="11" t="n">
+        <v>33</v>
+      </c>
+      <c r="F118" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="G118" s="12" t="inlineStr">
+        <is>
+          <t>자원 암흑 광석 x33</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="13" t="n"/>
+      <c r="B119" s="11" t="n">
+        <v>22005</v>
+      </c>
+      <c r="C119" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="D119" s="11" t="n">
+        <v>50042</v>
+      </c>
+      <c r="E119" s="11" t="n">
+        <v>33</v>
+      </c>
+      <c r="F119" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="G119" s="12" t="inlineStr">
+        <is>
+          <t>자원 마물의 뿔 x33</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="13" t="n"/>
+      <c r="B120" s="11" t="n">
+        <v>22006</v>
+      </c>
+      <c r="C120" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="D120" s="11" t="n">
+        <v>100011</v>
+      </c>
+      <c r="E120" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F120" s="11" t="n">
+        <v>200</v>
+      </c>
+      <c r="G120" s="12" t="inlineStr">
+        <is>
+          <t>상자 전용 은빛 나침반</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="13" t="n"/>
+      <c r="B121" s="11" t="n">
+        <v>22007</v>
+      </c>
+      <c r="C121" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="D121" s="11" t="n">
+        <v>100015</v>
+      </c>
+      <c r="E121" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="F121" s="11" t="n">
+        <v>400</v>
+      </c>
+      <c r="G121" s="12" t="inlineStr">
+        <is>
+          <t>인챈트 큐브 x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="13" t="n"/>
+      <c r="B122" s="11" t="n">
+        <v>22008</v>
+      </c>
+      <c r="C122" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="D122" s="11" t="n">
+        <v>100018</v>
+      </c>
+      <c r="E122" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="F122" s="11" t="n">
+        <v>200</v>
+      </c>
+      <c r="G122" s="12" t="inlineStr">
+        <is>
+          <t>상급 인챈트 큐브 x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="13" t="n"/>
+      <c r="B123" s="11" t="n">
+        <v>23001</v>
+      </c>
+      <c r="C123" s="11" t="n">
+        <v>23</v>
+      </c>
+      <c r="D123" s="11" t="n">
+        <v>10043</v>
+      </c>
+      <c r="E123" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="F123" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="G123" s="12" t="inlineStr">
+        <is>
+          <t>자원 심해 등불고기 x45</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="13" t="n"/>
+      <c r="B124" s="11" t="n">
+        <v>23002</v>
+      </c>
+      <c r="C124" s="11" t="n">
+        <v>23</v>
+      </c>
+      <c r="D124" s="11" t="n">
+        <v>20043</v>
+      </c>
+      <c r="E124" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="F124" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="G124" s="12" t="inlineStr">
+        <is>
+          <t>자원 영약초 x45</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="13" t="n"/>
+      <c r="B125" s="11" t="n">
+        <v>23003</v>
+      </c>
+      <c r="C125" s="11" t="n">
+        <v>23</v>
+      </c>
+      <c r="D125" s="11" t="n">
+        <v>30043</v>
+      </c>
+      <c r="E125" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="F125" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="G125" s="12" t="inlineStr">
+        <is>
+          <t>자원 신목 목재 x45</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="13" t="n"/>
+      <c r="B126" s="11" t="n">
+        <v>23004</v>
+      </c>
+      <c r="C126" s="11" t="n">
+        <v>23</v>
+      </c>
+      <c r="D126" s="11" t="n">
+        <v>40043</v>
+      </c>
+      <c r="E126" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="F126" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="G126" s="12" t="inlineStr">
+        <is>
+          <t>자원 아다만트 광석 x45</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="13" t="n"/>
+      <c r="B127" s="11" t="n">
+        <v>23005</v>
+      </c>
+      <c r="C127" s="11" t="n">
+        <v>23</v>
+      </c>
+      <c r="D127" s="11" t="n">
+        <v>50043</v>
+      </c>
+      <c r="E127" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="F127" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="G127" s="12" t="inlineStr">
+        <is>
+          <t>자원 흉수의 송곳니 x45</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="13" t="n"/>
+      <c r="B128" s="11" t="n">
+        <v>23006</v>
+      </c>
+      <c r="C128" s="11" t="n">
+        <v>23</v>
+      </c>
+      <c r="D128" s="11" t="n">
+        <v>100012</v>
+      </c>
+      <c r="E128" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F128" s="11" t="n">
+        <v>200</v>
+      </c>
+      <c r="G128" s="12" t="inlineStr">
+        <is>
+          <t>상자 전용 황금 열쇠</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="13" t="n"/>
+      <c r="B129" s="11" t="n">
+        <v>23007</v>
+      </c>
+      <c r="C129" s="11" t="n">
+        <v>23</v>
+      </c>
+      <c r="D129" s="11" t="n">
+        <v>100015</v>
+      </c>
+      <c r="E129" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="F129" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="G129" s="12" t="inlineStr">
+        <is>
+          <t>인챈트 큐브 x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="13" t="n"/>
+      <c r="B130" s="11" t="n">
+        <v>23008</v>
+      </c>
+      <c r="C130" s="11" t="n">
+        <v>23</v>
+      </c>
+      <c r="D130" s="11" t="n">
+        <v>100018</v>
+      </c>
+      <c r="E130" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="F130" s="11" t="n">
+        <v>400</v>
+      </c>
+      <c r="G130" s="12" t="inlineStr">
+        <is>
+          <t>상급 인챈트 큐브 x5</t>
         </is>
       </c>
     </row>
@@ -1492,12 +3608,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
@@ -1842,11 +3958,11 @@
     <row r="14">
       <c r="A14" s="13" t="n"/>
       <c r="B14" s="11" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>나무 상자</t>
+          <t>나무 상자 Lv1</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
@@ -1869,11 +3985,11 @@
     <row r="15">
       <c r="A15" s="13" t="n"/>
       <c r="B15" s="11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>은 상자</t>
+          <t>은 상자 Lv1</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
@@ -1896,11 +4012,11 @@
     <row r="16">
       <c r="A16" s="13" t="n"/>
       <c r="B16" s="11" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>황금 상자</t>
+          <t>황금 상자 Lv1</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
@@ -1915,6 +4031,330 @@
         <v>0</v>
       </c>
       <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>상자 전용 — 골드로 뽑을 수 없다</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="n"/>
+      <c r="B17" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>나무 상자 Lv2</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E17" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>상자 전용 — 골드로 뽑을 수 없다</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="n"/>
+      <c r="B18" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>은 상자 Lv2</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E18" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="12" t="inlineStr">
+        <is>
+          <t>상자 전용 — 골드로 뽑을 수 없다</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="n"/>
+      <c r="B19" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>황금 상자 Lv2</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E19" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="12" t="inlineStr">
+        <is>
+          <t>상자 전용 — 골드로 뽑을 수 없다</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="n"/>
+      <c r="B20" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="C20" s="12" t="inlineStr">
+        <is>
+          <t>나무 상자 Lv3</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="12" t="inlineStr">
+        <is>
+          <t>상자 전용 — 골드로 뽑을 수 없다</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="n"/>
+      <c r="B21" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>은 상자 Lv3</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="12" t="inlineStr">
+        <is>
+          <t>상자 전용 — 골드로 뽑을 수 없다</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="n"/>
+      <c r="B22" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>황금 상자 Lv3</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E22" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="12" t="inlineStr">
+        <is>
+          <t>상자 전용 — 골드로 뽑을 수 없다</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="n"/>
+      <c r="B23" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="C23" s="12" t="inlineStr">
+        <is>
+          <t>나무 상자 Lv4</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E23" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="12" t="inlineStr">
+        <is>
+          <t>상자 전용 — 골드로 뽑을 수 없다</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="n"/>
+      <c r="B24" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="C24" s="12" t="inlineStr">
+        <is>
+          <t>은 상자 Lv4</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E24" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="12" t="inlineStr">
+        <is>
+          <t>상자 전용 — 골드로 뽑을 수 없다</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="n"/>
+      <c r="B25" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C25" s="12" t="inlineStr">
+        <is>
+          <t>황금 상자 Lv4</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E25" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="12" t="inlineStr">
+        <is>
+          <t>상자 전용 — 골드로 뽑을 수 없다</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="13" t="n"/>
+      <c r="B26" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>나무 상자 Lv5</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E26" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="12" t="inlineStr">
+        <is>
+          <t>상자 전용 — 골드로 뽑을 수 없다</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="13" t="n"/>
+      <c r="B27" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>은 상자 Lv5</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="12" t="inlineStr">
+        <is>
+          <t>상자 전용 — 골드로 뽑을 수 없다</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="n"/>
+      <c r="B28" s="11" t="n">
+        <v>23</v>
+      </c>
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>황금 상자 Lv5</t>
+        </is>
+      </c>
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E28" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="12" t="inlineStr">
         <is>
           <t>상자 전용 — 골드로 뽑을 수 없다</t>
         </is>
@@ -2867,7 +5307,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:G248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -4690,10 +7130,10 @@
     <row r="79">
       <c r="A79" s="13" t="n"/>
       <c r="B79" s="11" t="n">
-        <v>6101</v>
+        <v>9101</v>
       </c>
       <c r="C79" s="11" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D79" s="11" t="n">
         <v>1001</v>
@@ -4702,21 +7142,21 @@
         <v>1</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>30</v>
+        <v>69</v>
       </c>
       <c r="G79" s="12" t="inlineStr">
         <is>
-          <t>장비</t>
+          <t>Common 목검</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="13" t="n"/>
       <c r="B80" s="11" t="n">
-        <v>6102</v>
+        <v>9102</v>
       </c>
       <c r="C80" s="11" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D80" s="11" t="n">
         <v>2001</v>
@@ -4725,21 +7165,21 @@
         <v>1</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>30</v>
+        <v>69</v>
       </c>
       <c r="G80" s="12" t="inlineStr">
         <is>
-          <t>장비</t>
+          <t>Common 구리 반지</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="13" t="n"/>
       <c r="B81" s="11" t="n">
-        <v>6103</v>
+        <v>9103</v>
       </c>
       <c r="C81" s="11" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D81" s="11" t="n">
         <v>3001</v>
@@ -4748,264 +7188,3852 @@
         <v>1</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>30</v>
+        <v>69</v>
       </c>
       <c r="G81" s="12" t="inlineStr">
         <is>
-          <t>장비</t>
+          <t>Common 원석</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="13" t="n"/>
       <c r="B82" s="11" t="n">
-        <v>7101</v>
+        <v>9104</v>
       </c>
       <c r="C82" s="11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D82" s="11" t="n">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="E82" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>18</v>
+        <v>69</v>
       </c>
       <c r="G82" s="12" t="inlineStr">
         <is>
-          <t>장비</t>
+          <t>Common 나무 호미</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="13" t="n"/>
       <c r="B83" s="11" t="n">
-        <v>7102</v>
+        <v>9105</v>
       </c>
       <c r="C83" s="11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D83" s="11" t="n">
-        <v>1302</v>
+        <v>1201</v>
       </c>
       <c r="E83" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>18</v>
+        <v>69</v>
       </c>
       <c r="G83" s="12" t="inlineStr">
         <is>
-          <t>장비</t>
+          <t>Common 대나무 낚싯대</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="13" t="n"/>
       <c r="B84" s="11" t="n">
-        <v>7103</v>
+        <v>9106</v>
       </c>
       <c r="C84" s="11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D84" s="11" t="n">
-        <v>1402</v>
+        <v>1301</v>
       </c>
       <c r="E84" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>18</v>
+        <v>69</v>
       </c>
       <c r="G84" s="12" t="inlineStr">
         <is>
-          <t>장비</t>
+          <t>Common 돌 곡괭이</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="13" t="n"/>
       <c r="B85" s="11" t="n">
-        <v>7104</v>
+        <v>9107</v>
       </c>
       <c r="C85" s="11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D85" s="11" t="n">
-        <v>1502</v>
+        <v>1401</v>
       </c>
       <c r="E85" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>18</v>
+        <v>69</v>
       </c>
       <c r="G85" s="12" t="inlineStr">
         <is>
-          <t>장비</t>
+          <t>Common 손도끼</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="13" t="n"/>
       <c r="B86" s="11" t="n">
-        <v>7105</v>
+        <v>9108</v>
       </c>
       <c r="C86" s="11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D86" s="11" t="n">
-        <v>2003</v>
+        <v>1501</v>
       </c>
       <c r="E86" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>18</v>
+        <v>69</v>
       </c>
       <c r="G86" s="12" t="inlineStr">
         <is>
-          <t>장비</t>
+          <t>Common 사냥용 활</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="13" t="n"/>
       <c r="B87" s="11" t="n">
-        <v>8101</v>
+        <v>9109</v>
       </c>
       <c r="C87" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D87" s="11" t="n">
-        <v>1103</v>
+        <v>3101</v>
       </c>
       <c r="E87" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>15</v>
+        <v>69</v>
       </c>
       <c r="G87" s="12" t="inlineStr">
         <is>
-          <t>장비</t>
+          <t>Common 풍년석</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="13" t="n"/>
       <c r="B88" s="11" t="n">
-        <v>8102</v>
+        <v>9110</v>
       </c>
       <c r="C88" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D88" s="11" t="n">
-        <v>1203</v>
+        <v>3201</v>
       </c>
       <c r="E88" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>15</v>
+        <v>69</v>
       </c>
       <c r="G88" s="12" t="inlineStr">
         <is>
-          <t>장비</t>
+          <t>Common 물방울석</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="13" t="n"/>
       <c r="B89" s="11" t="n">
-        <v>8103</v>
+        <v>9111</v>
       </c>
       <c r="C89" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D89" s="11" t="n">
-        <v>1303</v>
+        <v>3301</v>
       </c>
       <c r="E89" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>15</v>
+        <v>69</v>
       </c>
       <c r="G89" s="12" t="inlineStr">
         <is>
-          <t>장비</t>
+          <t>Common 철광석 조각</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="13" t="n"/>
       <c r="B90" s="11" t="n">
-        <v>8104</v>
+        <v>9112</v>
       </c>
       <c r="C90" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D90" s="11" t="n">
-        <v>1403</v>
+        <v>3401</v>
       </c>
       <c r="E90" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>15</v>
+        <v>69</v>
       </c>
       <c r="G90" s="12" t="inlineStr">
         <is>
-          <t>장비</t>
+          <t>Common 나무옹이석</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="13" t="n"/>
       <c r="B91" s="11" t="n">
-        <v>8105</v>
+        <v>9113</v>
       </c>
       <c r="C91" s="11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D91" s="11" t="n">
-        <v>1503</v>
+        <v>3501</v>
       </c>
       <c r="E91" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>15</v>
+        <v>69</v>
       </c>
       <c r="G91" s="12" t="inlineStr">
         <is>
-          <t>장비</t>
+          <t>Common 짐승 이빨석</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="13" t="n"/>
       <c r="B92" s="11" t="n">
-        <v>8106</v>
+        <v>10101</v>
       </c>
       <c r="C92" s="11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D92" s="11" t="n">
+        <v>1002</v>
+      </c>
+      <c r="E92" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F92" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G92" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon 낚싯대</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="13" t="n"/>
+      <c r="B93" s="11" t="n">
+        <v>10102</v>
+      </c>
+      <c r="C93" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="D93" s="11" t="n">
+        <v>1102</v>
+      </c>
+      <c r="E93" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F93" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G93" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon 무쇠 호미</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="13" t="n"/>
+      <c r="B94" s="11" t="n">
+        <v>10103</v>
+      </c>
+      <c r="C94" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="D94" s="11" t="n">
+        <v>1302</v>
+      </c>
+      <c r="E94" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F94" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G94" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon 무쇠 곡괭이</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="13" t="n"/>
+      <c r="B95" s="11" t="n">
+        <v>10104</v>
+      </c>
+      <c r="C95" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="D95" s="11" t="n">
+        <v>1402</v>
+      </c>
+      <c r="E95" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F95" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G95" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon 무쇠 도끼</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="13" t="n"/>
+      <c r="B96" s="11" t="n">
+        <v>10105</v>
+      </c>
+      <c r="C96" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="D96" s="11" t="n">
+        <v>1502</v>
+      </c>
+      <c r="E96" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F96" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G96" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon 참나무 활</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="13" t="n"/>
+      <c r="B97" s="11" t="n">
+        <v>10106</v>
+      </c>
+      <c r="C97" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="D97" s="11" t="n">
+        <v>2003</v>
+      </c>
+      <c r="E97" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F97" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G97" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon 은 목걸이</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="13" t="n"/>
+      <c r="B98" s="11" t="n">
+        <v>10107</v>
+      </c>
+      <c r="C98" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="D98" s="11" t="n">
+        <v>3102</v>
+      </c>
+      <c r="E98" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F98" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G98" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon 새싹 수정</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="13" t="n"/>
+      <c r="B99" s="11" t="n">
+        <v>10108</v>
+      </c>
+      <c r="C99" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="D99" s="11" t="n">
+        <v>3202</v>
+      </c>
+      <c r="E99" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F99" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G99" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon 조류 수정</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="13" t="n"/>
+      <c r="B100" s="11" t="n">
+        <v>10109</v>
+      </c>
+      <c r="C100" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="D100" s="11" t="n">
+        <v>3302</v>
+      </c>
+      <c r="E100" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F100" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G100" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon 광맥 수정</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="13" t="n"/>
+      <c r="B101" s="11" t="n">
+        <v>10110</v>
+      </c>
+      <c r="C101" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="D101" s="11" t="n">
+        <v>3402</v>
+      </c>
+      <c r="E101" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F101" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G101" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon 수액 호박</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="13" t="n"/>
+      <c r="B102" s="11" t="n">
+        <v>10111</v>
+      </c>
+      <c r="C102" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="D102" s="11" t="n">
+        <v>3502</v>
+      </c>
+      <c r="E102" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F102" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G102" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon 추적자의 수정</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="13" t="n"/>
+      <c r="B103" s="11" t="n">
+        <v>11101</v>
+      </c>
+      <c r="C103" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="D103" s="11" t="n">
+        <v>2002</v>
+      </c>
+      <c r="E103" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F103" s="11" t="n">
+        <v>75</v>
+      </c>
+      <c r="G103" s="12" t="inlineStr">
+        <is>
+          <t>Rare 어부의 목걸이</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="13" t="n"/>
+      <c r="B104" s="11" t="n">
+        <v>11102</v>
+      </c>
+      <c r="C104" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="D104" s="11" t="n">
+        <v>1103</v>
+      </c>
+      <c r="E104" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F104" s="11" t="n">
+        <v>75</v>
+      </c>
+      <c r="G104" s="12" t="inlineStr">
+        <is>
+          <t>Rare 강철 낫</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="13" t="n"/>
+      <c r="B105" s="11" t="n">
+        <v>11103</v>
+      </c>
+      <c r="C105" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="D105" s="11" t="n">
+        <v>1203</v>
+      </c>
+      <c r="E105" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F105" s="11" t="n">
+        <v>75</v>
+      </c>
+      <c r="G105" s="12" t="inlineStr">
+        <is>
+          <t>Rare 은사 낚싯대</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="13" t="n"/>
+      <c r="B106" s="11" t="n">
+        <v>11104</v>
+      </c>
+      <c r="C106" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="D106" s="11" t="n">
+        <v>1303</v>
+      </c>
+      <c r="E106" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F106" s="11" t="n">
+        <v>75</v>
+      </c>
+      <c r="G106" s="12" t="inlineStr">
+        <is>
+          <t>Rare 강철 곡괭이</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="13" t="n"/>
+      <c r="B107" s="11" t="n">
+        <v>11105</v>
+      </c>
+      <c r="C107" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="D107" s="11" t="n">
+        <v>1403</v>
+      </c>
+      <c r="E107" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F107" s="11" t="n">
+        <v>75</v>
+      </c>
+      <c r="G107" s="12" t="inlineStr">
+        <is>
+          <t>Rare 양날 도끼</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="13" t="n"/>
+      <c r="B108" s="11" t="n">
+        <v>11106</v>
+      </c>
+      <c r="C108" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="D108" s="11" t="n">
+        <v>1503</v>
+      </c>
+      <c r="E108" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F108" s="11" t="n">
+        <v>75</v>
+      </c>
+      <c r="G108" s="12" t="inlineStr">
+        <is>
+          <t>Rare 강철 석궁</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="13" t="n"/>
+      <c r="B109" s="11" t="n">
+        <v>11107</v>
+      </c>
+      <c r="C109" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="D109" s="11" t="n">
         <v>2004</v>
       </c>
-      <c r="E92" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F92" s="11" t="n">
+      <c r="E109" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F109" s="11" t="n">
+        <v>75</v>
+      </c>
+      <c r="G109" s="12" t="inlineStr">
+        <is>
+          <t>Rare 노동자의 팔찌</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="13" t="n"/>
+      <c r="B110" s="11" t="n">
+        <v>11108</v>
+      </c>
+      <c r="C110" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="D110" s="11" t="n">
+        <v>3103</v>
+      </c>
+      <c r="E110" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F110" s="11" t="n">
+        <v>75</v>
+      </c>
+      <c r="G110" s="12" t="inlineStr">
+        <is>
+          <t>Rare 곡창의 비취</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="13" t="n"/>
+      <c r="B111" s="11" t="n">
+        <v>11109</v>
+      </c>
+      <c r="C111" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="D111" s="11" t="n">
+        <v>3203</v>
+      </c>
+      <c r="E111" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F111" s="11" t="n">
+        <v>75</v>
+      </c>
+      <c r="G111" s="12" t="inlineStr">
+        <is>
+          <t>Rare 심해의 청옥</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="13" t="n"/>
+      <c r="B112" s="11" t="n">
+        <v>11110</v>
+      </c>
+      <c r="C112" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="D112" s="11" t="n">
+        <v>3303</v>
+      </c>
+      <c r="E112" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F112" s="11" t="n">
+        <v>75</v>
+      </c>
+      <c r="G112" s="12" t="inlineStr">
+        <is>
+          <t>Rare 지맥의 흑옥</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="13" t="n"/>
+      <c r="B113" s="11" t="n">
+        <v>11111</v>
+      </c>
+      <c r="C113" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="D113" s="11" t="n">
+        <v>3403</v>
+      </c>
+      <c r="E113" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F113" s="11" t="n">
+        <v>75</v>
+      </c>
+      <c r="G113" s="12" t="inlineStr">
+        <is>
+          <t>Rare 고목의 녹옥</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="13" t="n"/>
+      <c r="B114" s="11" t="n">
+        <v>11112</v>
+      </c>
+      <c r="C114" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="D114" s="11" t="n">
+        <v>3503</v>
+      </c>
+      <c r="E114" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F114" s="11" t="n">
+        <v>75</v>
+      </c>
+      <c r="G114" s="12" t="inlineStr">
+        <is>
+          <t>Rare 맹수의 홍옥</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="13" t="n"/>
+      <c r="B115" s="11" t="n">
+        <v>12101</v>
+      </c>
+      <c r="C115" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="D115" s="11" t="n">
+        <v>1002</v>
+      </c>
+      <c r="E115" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F115" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G115" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon 낚싯대</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="13" t="n"/>
+      <c r="B116" s="11" t="n">
+        <v>12102</v>
+      </c>
+      <c r="C116" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="D116" s="11" t="n">
+        <v>1102</v>
+      </c>
+      <c r="E116" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F116" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G116" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon 무쇠 호미</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="13" t="n"/>
+      <c r="B117" s="11" t="n">
+        <v>12103</v>
+      </c>
+      <c r="C117" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="D117" s="11" t="n">
+        <v>1302</v>
+      </c>
+      <c r="E117" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F117" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G117" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon 무쇠 곡괭이</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="13" t="n"/>
+      <c r="B118" s="11" t="n">
+        <v>12104</v>
+      </c>
+      <c r="C118" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="D118" s="11" t="n">
+        <v>1402</v>
+      </c>
+      <c r="E118" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F118" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G118" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon 무쇠 도끼</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="13" t="n"/>
+      <c r="B119" s="11" t="n">
+        <v>12105</v>
+      </c>
+      <c r="C119" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="D119" s="11" t="n">
+        <v>1502</v>
+      </c>
+      <c r="E119" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F119" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G119" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon 참나무 활</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="13" t="n"/>
+      <c r="B120" s="11" t="n">
+        <v>12106</v>
+      </c>
+      <c r="C120" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="D120" s="11" t="n">
+        <v>2003</v>
+      </c>
+      <c r="E120" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F120" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G120" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon 은 목걸이</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="13" t="n"/>
+      <c r="B121" s="11" t="n">
+        <v>12107</v>
+      </c>
+      <c r="C121" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="D121" s="11" t="n">
+        <v>3102</v>
+      </c>
+      <c r="E121" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F121" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G121" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon 새싹 수정</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="13" t="n"/>
+      <c r="B122" s="11" t="n">
+        <v>12108</v>
+      </c>
+      <c r="C122" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="D122" s="11" t="n">
+        <v>3202</v>
+      </c>
+      <c r="E122" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F122" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G122" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon 조류 수정</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="13" t="n"/>
+      <c r="B123" s="11" t="n">
+        <v>12109</v>
+      </c>
+      <c r="C123" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="D123" s="11" t="n">
+        <v>3302</v>
+      </c>
+      <c r="E123" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F123" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G123" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon 광맥 수정</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="13" t="n"/>
+      <c r="B124" s="11" t="n">
+        <v>12110</v>
+      </c>
+      <c r="C124" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="D124" s="11" t="n">
+        <v>3402</v>
+      </c>
+      <c r="E124" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F124" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G124" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon 수액 호박</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="13" t="n"/>
+      <c r="B125" s="11" t="n">
+        <v>12111</v>
+      </c>
+      <c r="C125" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="D125" s="11" t="n">
+        <v>3502</v>
+      </c>
+      <c r="E125" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F125" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G125" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon 추적자의 수정</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="13" t="n"/>
+      <c r="B126" s="11" t="n">
+        <v>13101</v>
+      </c>
+      <c r="C126" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="D126" s="11" t="n">
+        <v>2002</v>
+      </c>
+      <c r="E126" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F126" s="11" t="n">
+        <v>75</v>
+      </c>
+      <c r="G126" s="12" t="inlineStr">
+        <is>
+          <t>Rare 어부의 목걸이</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="13" t="n"/>
+      <c r="B127" s="11" t="n">
+        <v>13102</v>
+      </c>
+      <c r="C127" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="D127" s="11" t="n">
+        <v>1103</v>
+      </c>
+      <c r="E127" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F127" s="11" t="n">
+        <v>75</v>
+      </c>
+      <c r="G127" s="12" t="inlineStr">
+        <is>
+          <t>Rare 강철 낫</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="13" t="n"/>
+      <c r="B128" s="11" t="n">
+        <v>13103</v>
+      </c>
+      <c r="C128" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="D128" s="11" t="n">
+        <v>1203</v>
+      </c>
+      <c r="E128" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F128" s="11" t="n">
+        <v>75</v>
+      </c>
+      <c r="G128" s="12" t="inlineStr">
+        <is>
+          <t>Rare 은사 낚싯대</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="13" t="n"/>
+      <c r="B129" s="11" t="n">
+        <v>13104</v>
+      </c>
+      <c r="C129" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="D129" s="11" t="n">
+        <v>1303</v>
+      </c>
+      <c r="E129" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F129" s="11" t="n">
+        <v>75</v>
+      </c>
+      <c r="G129" s="12" t="inlineStr">
+        <is>
+          <t>Rare 강철 곡괭이</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="13" t="n"/>
+      <c r="B130" s="11" t="n">
+        <v>13105</v>
+      </c>
+      <c r="C130" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="D130" s="11" t="n">
+        <v>1403</v>
+      </c>
+      <c r="E130" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F130" s="11" t="n">
+        <v>75</v>
+      </c>
+      <c r="G130" s="12" t="inlineStr">
+        <is>
+          <t>Rare 양날 도끼</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="13" t="n"/>
+      <c r="B131" s="11" t="n">
+        <v>13106</v>
+      </c>
+      <c r="C131" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="D131" s="11" t="n">
+        <v>1503</v>
+      </c>
+      <c r="E131" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F131" s="11" t="n">
+        <v>75</v>
+      </c>
+      <c r="G131" s="12" t="inlineStr">
+        <is>
+          <t>Rare 강철 석궁</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="13" t="n"/>
+      <c r="B132" s="11" t="n">
+        <v>13107</v>
+      </c>
+      <c r="C132" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="D132" s="11" t="n">
+        <v>2004</v>
+      </c>
+      <c r="E132" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F132" s="11" t="n">
+        <v>75</v>
+      </c>
+      <c r="G132" s="12" t="inlineStr">
+        <is>
+          <t>Rare 노동자의 팔찌</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="13" t="n"/>
+      <c r="B133" s="11" t="n">
+        <v>13108</v>
+      </c>
+      <c r="C133" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="D133" s="11" t="n">
+        <v>3103</v>
+      </c>
+      <c r="E133" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F133" s="11" t="n">
+        <v>75</v>
+      </c>
+      <c r="G133" s="12" t="inlineStr">
+        <is>
+          <t>Rare 곡창의 비취</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="13" t="n"/>
+      <c r="B134" s="11" t="n">
+        <v>13109</v>
+      </c>
+      <c r="C134" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="D134" s="11" t="n">
+        <v>3203</v>
+      </c>
+      <c r="E134" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F134" s="11" t="n">
+        <v>75</v>
+      </c>
+      <c r="G134" s="12" t="inlineStr">
+        <is>
+          <t>Rare 심해의 청옥</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="13" t="n"/>
+      <c r="B135" s="11" t="n">
+        <v>13110</v>
+      </c>
+      <c r="C135" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="D135" s="11" t="n">
+        <v>3303</v>
+      </c>
+      <c r="E135" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F135" s="11" t="n">
+        <v>75</v>
+      </c>
+      <c r="G135" s="12" t="inlineStr">
+        <is>
+          <t>Rare 지맥의 흑옥</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="13" t="n"/>
+      <c r="B136" s="11" t="n">
+        <v>13111</v>
+      </c>
+      <c r="C136" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="D136" s="11" t="n">
+        <v>3403</v>
+      </c>
+      <c r="E136" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F136" s="11" t="n">
+        <v>75</v>
+      </c>
+      <c r="G136" s="12" t="inlineStr">
+        <is>
+          <t>Rare 고목의 녹옥</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="13" t="n"/>
+      <c r="B137" s="11" t="n">
+        <v>13112</v>
+      </c>
+      <c r="C137" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="D137" s="11" t="n">
+        <v>3503</v>
+      </c>
+      <c r="E137" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F137" s="11" t="n">
+        <v>75</v>
+      </c>
+      <c r="G137" s="12" t="inlineStr">
+        <is>
+          <t>Rare 맹수의 홍옥</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="13" t="n"/>
+      <c r="B138" s="11" t="n">
+        <v>14101</v>
+      </c>
+      <c r="C138" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="D138" s="11" t="n">
+        <v>1104</v>
+      </c>
+      <c r="E138" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F138" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G138" s="12" t="inlineStr">
+        <is>
+          <t>Epic 은빛 쟁기</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="13" t="n"/>
+      <c r="B139" s="11" t="n">
+        <v>14102</v>
+      </c>
+      <c r="C139" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="D139" s="11" t="n">
+        <v>1204</v>
+      </c>
+      <c r="E139" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F139" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G139" s="12" t="inlineStr">
+        <is>
+          <t>Epic 심해 작살</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="13" t="n"/>
+      <c r="B140" s="11" t="n">
+        <v>14103</v>
+      </c>
+      <c r="C140" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="D140" s="11" t="n">
+        <v>1304</v>
+      </c>
+      <c r="E140" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F140" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G140" s="12" t="inlineStr">
+        <is>
+          <t>Epic 흑요석 곡괭이</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="13" t="n"/>
+      <c r="B141" s="11" t="n">
+        <v>14104</v>
+      </c>
+      <c r="C141" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="D141" s="11" t="n">
+        <v>1404</v>
+      </c>
+      <c r="E141" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F141" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G141" s="12" t="inlineStr">
+        <is>
+          <t>Epic 백년목 도끼</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="13" t="n"/>
+      <c r="B142" s="11" t="n">
+        <v>14105</v>
+      </c>
+      <c r="C142" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="D142" s="11" t="n">
+        <v>1504</v>
+      </c>
+      <c r="E142" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F142" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G142" s="12" t="inlineStr">
+        <is>
+          <t>Epic 은빛 장궁</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="13" t="n"/>
+      <c r="B143" s="11" t="n">
+        <v>14106</v>
+      </c>
+      <c r="C143" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="D143" s="11" t="n">
+        <v>2005</v>
+      </c>
+      <c r="E143" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F143" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G143" s="12" t="inlineStr">
+        <is>
+          <t>Epic 장인의 인장</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="13" t="n"/>
+      <c r="B144" s="11" t="n">
+        <v>14107</v>
+      </c>
+      <c r="C144" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="D144" s="11" t="n">
+        <v>3104</v>
+      </c>
+      <c r="E144" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F144" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G144" s="12" t="inlineStr">
+        <is>
+          <t>Epic 황금 이삭석</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="13" t="n"/>
+      <c r="B145" s="11" t="n">
+        <v>14108</v>
+      </c>
+      <c r="C145" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="D145" s="11" t="n">
+        <v>3204</v>
+      </c>
+      <c r="E145" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F145" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G145" s="12" t="inlineStr">
+        <is>
+          <t>Epic 산호 진주</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="13" t="n"/>
+      <c r="B146" s="11" t="n">
+        <v>14109</v>
+      </c>
+      <c r="C146" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="D146" s="11" t="n">
+        <v>3304</v>
+      </c>
+      <c r="E146" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F146" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G146" s="12" t="inlineStr">
+        <is>
+          <t>Epic 용암 결정</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="13" t="n"/>
+      <c r="B147" s="11" t="n">
+        <v>14110</v>
+      </c>
+      <c r="C147" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="D147" s="11" t="n">
+        <v>3404</v>
+      </c>
+      <c r="E147" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F147" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G147" s="12" t="inlineStr">
+        <is>
+          <t>Epic 백년목 결정</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="13" t="n"/>
+      <c r="B148" s="11" t="n">
+        <v>14111</v>
+      </c>
+      <c r="C148" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="D148" s="11" t="n">
+        <v>3504</v>
+      </c>
+      <c r="E148" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F148" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G148" s="12" t="inlineStr">
+        <is>
+          <t>Epic 사냥꾼의 별</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="13" t="n"/>
+      <c r="B149" s="11" t="n">
+        <v>15101</v>
+      </c>
+      <c r="C149" s="11" t="n">
         <v>15</v>
       </c>
-      <c r="G92" s="12" t="inlineStr">
-        <is>
-          <t>장비</t>
+      <c r="D149" s="11" t="n">
+        <v>2002</v>
+      </c>
+      <c r="E149" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F149" s="11" t="n">
+        <v>75</v>
+      </c>
+      <c r="G149" s="12" t="inlineStr">
+        <is>
+          <t>Rare 어부의 목걸이</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="13" t="n"/>
+      <c r="B150" s="11" t="n">
+        <v>15102</v>
+      </c>
+      <c r="C150" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="D150" s="11" t="n">
+        <v>1103</v>
+      </c>
+      <c r="E150" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F150" s="11" t="n">
+        <v>75</v>
+      </c>
+      <c r="G150" s="12" t="inlineStr">
+        <is>
+          <t>Rare 강철 낫</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="13" t="n"/>
+      <c r="B151" s="11" t="n">
+        <v>15103</v>
+      </c>
+      <c r="C151" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="D151" s="11" t="n">
+        <v>1203</v>
+      </c>
+      <c r="E151" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F151" s="11" t="n">
+        <v>75</v>
+      </c>
+      <c r="G151" s="12" t="inlineStr">
+        <is>
+          <t>Rare 은사 낚싯대</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="13" t="n"/>
+      <c r="B152" s="11" t="n">
+        <v>15104</v>
+      </c>
+      <c r="C152" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="D152" s="11" t="n">
+        <v>1303</v>
+      </c>
+      <c r="E152" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F152" s="11" t="n">
+        <v>75</v>
+      </c>
+      <c r="G152" s="12" t="inlineStr">
+        <is>
+          <t>Rare 강철 곡괭이</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="13" t="n"/>
+      <c r="B153" s="11" t="n">
+        <v>15105</v>
+      </c>
+      <c r="C153" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="D153" s="11" t="n">
+        <v>1403</v>
+      </c>
+      <c r="E153" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F153" s="11" t="n">
+        <v>75</v>
+      </c>
+      <c r="G153" s="12" t="inlineStr">
+        <is>
+          <t>Rare 양날 도끼</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="13" t="n"/>
+      <c r="B154" s="11" t="n">
+        <v>15106</v>
+      </c>
+      <c r="C154" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="D154" s="11" t="n">
+        <v>1503</v>
+      </c>
+      <c r="E154" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F154" s="11" t="n">
+        <v>75</v>
+      </c>
+      <c r="G154" s="12" t="inlineStr">
+        <is>
+          <t>Rare 강철 석궁</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="13" t="n"/>
+      <c r="B155" s="11" t="n">
+        <v>15107</v>
+      </c>
+      <c r="C155" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="D155" s="11" t="n">
+        <v>2004</v>
+      </c>
+      <c r="E155" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F155" s="11" t="n">
+        <v>75</v>
+      </c>
+      <c r="G155" s="12" t="inlineStr">
+        <is>
+          <t>Rare 노동자의 팔찌</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="13" t="n"/>
+      <c r="B156" s="11" t="n">
+        <v>15108</v>
+      </c>
+      <c r="C156" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="D156" s="11" t="n">
+        <v>3103</v>
+      </c>
+      <c r="E156" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F156" s="11" t="n">
+        <v>75</v>
+      </c>
+      <c r="G156" s="12" t="inlineStr">
+        <is>
+          <t>Rare 곡창의 비취</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="13" t="n"/>
+      <c r="B157" s="11" t="n">
+        <v>15109</v>
+      </c>
+      <c r="C157" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="D157" s="11" t="n">
+        <v>3203</v>
+      </c>
+      <c r="E157" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F157" s="11" t="n">
+        <v>75</v>
+      </c>
+      <c r="G157" s="12" t="inlineStr">
+        <is>
+          <t>Rare 심해의 청옥</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="13" t="n"/>
+      <c r="B158" s="11" t="n">
+        <v>15110</v>
+      </c>
+      <c r="C158" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="D158" s="11" t="n">
+        <v>3303</v>
+      </c>
+      <c r="E158" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F158" s="11" t="n">
+        <v>75</v>
+      </c>
+      <c r="G158" s="12" t="inlineStr">
+        <is>
+          <t>Rare 지맥의 흑옥</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="13" t="n"/>
+      <c r="B159" s="11" t="n">
+        <v>15111</v>
+      </c>
+      <c r="C159" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="D159" s="11" t="n">
+        <v>3403</v>
+      </c>
+      <c r="E159" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F159" s="11" t="n">
+        <v>75</v>
+      </c>
+      <c r="G159" s="12" t="inlineStr">
+        <is>
+          <t>Rare 고목의 녹옥</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="13" t="n"/>
+      <c r="B160" s="11" t="n">
+        <v>15112</v>
+      </c>
+      <c r="C160" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="D160" s="11" t="n">
+        <v>3503</v>
+      </c>
+      <c r="E160" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F160" s="11" t="n">
+        <v>75</v>
+      </c>
+      <c r="G160" s="12" t="inlineStr">
+        <is>
+          <t>Rare 맹수의 홍옥</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="13" t="n"/>
+      <c r="B161" s="11" t="n">
+        <v>16101</v>
+      </c>
+      <c r="C161" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="D161" s="11" t="n">
+        <v>1104</v>
+      </c>
+      <c r="E161" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F161" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G161" s="12" t="inlineStr">
+        <is>
+          <t>Epic 은빛 쟁기</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="13" t="n"/>
+      <c r="B162" s="11" t="n">
+        <v>16102</v>
+      </c>
+      <c r="C162" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="D162" s="11" t="n">
+        <v>1204</v>
+      </c>
+      <c r="E162" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F162" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G162" s="12" t="inlineStr">
+        <is>
+          <t>Epic 심해 작살</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="13" t="n"/>
+      <c r="B163" s="11" t="n">
+        <v>16103</v>
+      </c>
+      <c r="C163" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="D163" s="11" t="n">
+        <v>1304</v>
+      </c>
+      <c r="E163" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F163" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G163" s="12" t="inlineStr">
+        <is>
+          <t>Epic 흑요석 곡괭이</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="13" t="n"/>
+      <c r="B164" s="11" t="n">
+        <v>16104</v>
+      </c>
+      <c r="C164" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="D164" s="11" t="n">
+        <v>1404</v>
+      </c>
+      <c r="E164" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F164" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G164" s="12" t="inlineStr">
+        <is>
+          <t>Epic 백년목 도끼</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="13" t="n"/>
+      <c r="B165" s="11" t="n">
+        <v>16105</v>
+      </c>
+      <c r="C165" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="D165" s="11" t="n">
+        <v>1504</v>
+      </c>
+      <c r="E165" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F165" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G165" s="12" t="inlineStr">
+        <is>
+          <t>Epic 은빛 장궁</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="13" t="n"/>
+      <c r="B166" s="11" t="n">
+        <v>16106</v>
+      </c>
+      <c r="C166" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="D166" s="11" t="n">
+        <v>2005</v>
+      </c>
+      <c r="E166" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F166" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G166" s="12" t="inlineStr">
+        <is>
+          <t>Epic 장인의 인장</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="13" t="n"/>
+      <c r="B167" s="11" t="n">
+        <v>16107</v>
+      </c>
+      <c r="C167" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="D167" s="11" t="n">
+        <v>3104</v>
+      </c>
+      <c r="E167" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F167" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G167" s="12" t="inlineStr">
+        <is>
+          <t>Epic 황금 이삭석</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="13" t="n"/>
+      <c r="B168" s="11" t="n">
+        <v>16108</v>
+      </c>
+      <c r="C168" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="D168" s="11" t="n">
+        <v>3204</v>
+      </c>
+      <c r="E168" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F168" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G168" s="12" t="inlineStr">
+        <is>
+          <t>Epic 산호 진주</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="13" t="n"/>
+      <c r="B169" s="11" t="n">
+        <v>16109</v>
+      </c>
+      <c r="C169" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="D169" s="11" t="n">
+        <v>3304</v>
+      </c>
+      <c r="E169" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F169" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G169" s="12" t="inlineStr">
+        <is>
+          <t>Epic 용암 결정</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="13" t="n"/>
+      <c r="B170" s="11" t="n">
+        <v>16110</v>
+      </c>
+      <c r="C170" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="D170" s="11" t="n">
+        <v>3404</v>
+      </c>
+      <c r="E170" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F170" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G170" s="12" t="inlineStr">
+        <is>
+          <t>Epic 백년목 결정</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="13" t="n"/>
+      <c r="B171" s="11" t="n">
+        <v>16111</v>
+      </c>
+      <c r="C171" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="D171" s="11" t="n">
+        <v>3504</v>
+      </c>
+      <c r="E171" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F171" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G171" s="12" t="inlineStr">
+        <is>
+          <t>Epic 사냥꾼의 별</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="13" t="n"/>
+      <c r="B172" s="11" t="n">
+        <v>17101</v>
+      </c>
+      <c r="C172" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="D172" s="11" t="n">
+        <v>1105</v>
+      </c>
+      <c r="E172" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F172" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G172" s="12" t="inlineStr">
+        <is>
+          <t>Legendary 풍년의 괭이</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="13" t="n"/>
+      <c r="B173" s="11" t="n">
+        <v>17102</v>
+      </c>
+      <c r="C173" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="D173" s="11" t="n">
+        <v>1205</v>
+      </c>
+      <c r="E173" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F173" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G173" s="12" t="inlineStr">
+        <is>
+          <t>Legendary 용린 낚싯대</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="13" t="n"/>
+      <c r="B174" s="11" t="n">
+        <v>17103</v>
+      </c>
+      <c r="C174" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="D174" s="11" t="n">
+        <v>1305</v>
+      </c>
+      <c r="E174" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F174" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G174" s="12" t="inlineStr">
+        <is>
+          <t>Legendary 미스릴 곡괭이</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="13" t="n"/>
+      <c r="B175" s="11" t="n">
+        <v>17104</v>
+      </c>
+      <c r="C175" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="D175" s="11" t="n">
+        <v>1405</v>
+      </c>
+      <c r="E175" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F175" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G175" s="12" t="inlineStr">
+        <is>
+          <t>Legendary 서리강철 도끼</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="13" t="n"/>
+      <c r="B176" s="11" t="n">
+        <v>17105</v>
+      </c>
+      <c r="C176" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="D176" s="11" t="n">
+        <v>1505</v>
+      </c>
+      <c r="E176" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F176" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G176" s="12" t="inlineStr">
+        <is>
+          <t>Legendary 폭풍의 장궁</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="13" t="n"/>
+      <c r="B177" s="11" t="n">
+        <v>17106</v>
+      </c>
+      <c r="C177" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="D177" s="11" t="n">
+        <v>2006</v>
+      </c>
+      <c r="E177" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F177" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G177" s="12" t="inlineStr">
+        <is>
+          <t>Legendary 대장인의 훈장</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="13" t="n"/>
+      <c r="B178" s="11" t="n">
+        <v>17107</v>
+      </c>
+      <c r="C178" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="D178" s="11" t="n">
+        <v>3105</v>
+      </c>
+      <c r="E178" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F178" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G178" s="12" t="inlineStr">
+        <is>
+          <t>Legendary 대지의 심장</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="13" t="n"/>
+      <c r="B179" s="11" t="n">
+        <v>17108</v>
+      </c>
+      <c r="C179" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="D179" s="11" t="n">
+        <v>3205</v>
+      </c>
+      <c r="E179" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F179" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G179" s="12" t="inlineStr">
+        <is>
+          <t>Legendary 바다의 심장</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="13" t="n"/>
+      <c r="B180" s="11" t="n">
+        <v>17109</v>
+      </c>
+      <c r="C180" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="D180" s="11" t="n">
+        <v>3305</v>
+      </c>
+      <c r="E180" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F180" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G180" s="12" t="inlineStr">
+        <is>
+          <t>Legendary 대지핵 결정</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="13" t="n"/>
+      <c r="B181" s="11" t="n">
+        <v>17110</v>
+      </c>
+      <c r="C181" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="D181" s="11" t="n">
+        <v>3405</v>
+      </c>
+      <c r="E181" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F181" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G181" s="12" t="inlineStr">
+        <is>
+          <t>Legendary 숲의 심장</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="13" t="n"/>
+      <c r="B182" s="11" t="n">
+        <v>17111</v>
+      </c>
+      <c r="C182" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="D182" s="11" t="n">
+        <v>3505</v>
+      </c>
+      <c r="E182" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F182" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G182" s="12" t="inlineStr">
+        <is>
+          <t>Legendary 야수의 심장</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="13" t="n"/>
+      <c r="B183" s="11" t="n">
+        <v>18101</v>
+      </c>
+      <c r="C183" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="D183" s="11" t="n">
+        <v>1104</v>
+      </c>
+      <c r="E183" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F183" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G183" s="12" t="inlineStr">
+        <is>
+          <t>Epic 은빛 쟁기</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="13" t="n"/>
+      <c r="B184" s="11" t="n">
+        <v>18102</v>
+      </c>
+      <c r="C184" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="D184" s="11" t="n">
+        <v>1204</v>
+      </c>
+      <c r="E184" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F184" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G184" s="12" t="inlineStr">
+        <is>
+          <t>Epic 심해 작살</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="13" t="n"/>
+      <c r="B185" s="11" t="n">
+        <v>18103</v>
+      </c>
+      <c r="C185" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="D185" s="11" t="n">
+        <v>1304</v>
+      </c>
+      <c r="E185" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F185" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G185" s="12" t="inlineStr">
+        <is>
+          <t>Epic 흑요석 곡괭이</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="13" t="n"/>
+      <c r="B186" s="11" t="n">
+        <v>18104</v>
+      </c>
+      <c r="C186" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="D186" s="11" t="n">
+        <v>1404</v>
+      </c>
+      <c r="E186" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F186" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G186" s="12" t="inlineStr">
+        <is>
+          <t>Epic 백년목 도끼</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="13" t="n"/>
+      <c r="B187" s="11" t="n">
+        <v>18105</v>
+      </c>
+      <c r="C187" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="D187" s="11" t="n">
+        <v>1504</v>
+      </c>
+      <c r="E187" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F187" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G187" s="12" t="inlineStr">
+        <is>
+          <t>Epic 은빛 장궁</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="13" t="n"/>
+      <c r="B188" s="11" t="n">
+        <v>18106</v>
+      </c>
+      <c r="C188" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="D188" s="11" t="n">
+        <v>2005</v>
+      </c>
+      <c r="E188" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F188" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G188" s="12" t="inlineStr">
+        <is>
+          <t>Epic 장인의 인장</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="13" t="n"/>
+      <c r="B189" s="11" t="n">
+        <v>18107</v>
+      </c>
+      <c r="C189" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="D189" s="11" t="n">
+        <v>3104</v>
+      </c>
+      <c r="E189" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F189" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G189" s="12" t="inlineStr">
+        <is>
+          <t>Epic 황금 이삭석</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="13" t="n"/>
+      <c r="B190" s="11" t="n">
+        <v>18108</v>
+      </c>
+      <c r="C190" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="D190" s="11" t="n">
+        <v>3204</v>
+      </c>
+      <c r="E190" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F190" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G190" s="12" t="inlineStr">
+        <is>
+          <t>Epic 산호 진주</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="13" t="n"/>
+      <c r="B191" s="11" t="n">
+        <v>18109</v>
+      </c>
+      <c r="C191" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="D191" s="11" t="n">
+        <v>3304</v>
+      </c>
+      <c r="E191" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F191" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G191" s="12" t="inlineStr">
+        <is>
+          <t>Epic 용암 결정</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="13" t="n"/>
+      <c r="B192" s="11" t="n">
+        <v>18110</v>
+      </c>
+      <c r="C192" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="D192" s="11" t="n">
+        <v>3404</v>
+      </c>
+      <c r="E192" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F192" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G192" s="12" t="inlineStr">
+        <is>
+          <t>Epic 백년목 결정</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="13" t="n"/>
+      <c r="B193" s="11" t="n">
+        <v>18111</v>
+      </c>
+      <c r="C193" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="D193" s="11" t="n">
+        <v>3504</v>
+      </c>
+      <c r="E193" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F193" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G193" s="12" t="inlineStr">
+        <is>
+          <t>Epic 사냥꾼의 별</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="13" t="n"/>
+      <c r="B194" s="11" t="n">
+        <v>19101</v>
+      </c>
+      <c r="C194" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="D194" s="11" t="n">
+        <v>1105</v>
+      </c>
+      <c r="E194" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F194" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G194" s="12" t="inlineStr">
+        <is>
+          <t>Legendary 풍년의 괭이</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="13" t="n"/>
+      <c r="B195" s="11" t="n">
+        <v>19102</v>
+      </c>
+      <c r="C195" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="D195" s="11" t="n">
+        <v>1205</v>
+      </c>
+      <c r="E195" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F195" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G195" s="12" t="inlineStr">
+        <is>
+          <t>Legendary 용린 낚싯대</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="13" t="n"/>
+      <c r="B196" s="11" t="n">
+        <v>19103</v>
+      </c>
+      <c r="C196" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="D196" s="11" t="n">
+        <v>1305</v>
+      </c>
+      <c r="E196" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F196" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G196" s="12" t="inlineStr">
+        <is>
+          <t>Legendary 미스릴 곡괭이</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="13" t="n"/>
+      <c r="B197" s="11" t="n">
+        <v>19104</v>
+      </c>
+      <c r="C197" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="D197" s="11" t="n">
+        <v>1405</v>
+      </c>
+      <c r="E197" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F197" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G197" s="12" t="inlineStr">
+        <is>
+          <t>Legendary 서리강철 도끼</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="13" t="n"/>
+      <c r="B198" s="11" t="n">
+        <v>19105</v>
+      </c>
+      <c r="C198" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="D198" s="11" t="n">
+        <v>1505</v>
+      </c>
+      <c r="E198" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F198" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G198" s="12" t="inlineStr">
+        <is>
+          <t>Legendary 폭풍의 장궁</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="13" t="n"/>
+      <c r="B199" s="11" t="n">
+        <v>19106</v>
+      </c>
+      <c r="C199" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="D199" s="11" t="n">
+        <v>2006</v>
+      </c>
+      <c r="E199" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F199" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G199" s="12" t="inlineStr">
+        <is>
+          <t>Legendary 대장인의 훈장</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="13" t="n"/>
+      <c r="B200" s="11" t="n">
+        <v>19107</v>
+      </c>
+      <c r="C200" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="D200" s="11" t="n">
+        <v>3105</v>
+      </c>
+      <c r="E200" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F200" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G200" s="12" t="inlineStr">
+        <is>
+          <t>Legendary 대지의 심장</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="13" t="n"/>
+      <c r="B201" s="11" t="n">
+        <v>19108</v>
+      </c>
+      <c r="C201" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="D201" s="11" t="n">
+        <v>3205</v>
+      </c>
+      <c r="E201" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F201" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G201" s="12" t="inlineStr">
+        <is>
+          <t>Legendary 바다의 심장</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="13" t="n"/>
+      <c r="B202" s="11" t="n">
+        <v>19109</v>
+      </c>
+      <c r="C202" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="D202" s="11" t="n">
+        <v>3305</v>
+      </c>
+      <c r="E202" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F202" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G202" s="12" t="inlineStr">
+        <is>
+          <t>Legendary 대지핵 결정</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="13" t="n"/>
+      <c r="B203" s="11" t="n">
+        <v>19110</v>
+      </c>
+      <c r="C203" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="D203" s="11" t="n">
+        <v>3405</v>
+      </c>
+      <c r="E203" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F203" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G203" s="12" t="inlineStr">
+        <is>
+          <t>Legendary 숲의 심장</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="13" t="n"/>
+      <c r="B204" s="11" t="n">
+        <v>19111</v>
+      </c>
+      <c r="C204" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="D204" s="11" t="n">
+        <v>3505</v>
+      </c>
+      <c r="E204" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F204" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G204" s="12" t="inlineStr">
+        <is>
+          <t>Legendary 야수의 심장</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="13" t="n"/>
+      <c r="B205" s="11" t="n">
+        <v>20101</v>
+      </c>
+      <c r="C205" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="D205" s="11" t="n">
+        <v>1106</v>
+      </c>
+      <c r="E205" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F205" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G205" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 대지모의 호미</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="13" t="n"/>
+      <c r="B206" s="11" t="n">
+        <v>20102</v>
+      </c>
+      <c r="C206" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="D206" s="11" t="n">
+        <v>1206</v>
+      </c>
+      <c r="E206" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F206" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G206" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 해신의 삼지창</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="13" t="n"/>
+      <c r="B207" s="11" t="n">
+        <v>20103</v>
+      </c>
+      <c r="C207" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="D207" s="11" t="n">
+        <v>1306</v>
+      </c>
+      <c r="E207" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F207" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G207" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 산신의 곡괭이</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="13" t="n"/>
+      <c r="B208" s="11" t="n">
+        <v>20104</v>
+      </c>
+      <c r="C208" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="D208" s="11" t="n">
+        <v>1406</v>
+      </c>
+      <c r="E208" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F208" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G208" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 세계수의 도끼</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="13" t="n"/>
+      <c r="B209" s="11" t="n">
+        <v>20105</v>
+      </c>
+      <c r="C209" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="D209" s="11" t="n">
+        <v>1506</v>
+      </c>
+      <c r="E209" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F209" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G209" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 월신의 활</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="13" t="n"/>
+      <c r="B210" s="11" t="n">
+        <v>20106</v>
+      </c>
+      <c r="C210" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="D210" s="11" t="n">
+        <v>2007</v>
+      </c>
+      <c r="E210" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F210" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G210" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 창세의 고리</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="13" t="n"/>
+      <c r="B211" s="11" t="n">
+        <v>20107</v>
+      </c>
+      <c r="C211" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="D211" s="11" t="n">
+        <v>3106</v>
+      </c>
+      <c r="E211" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F211" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G211" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 풍요의 성석</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="13" t="n"/>
+      <c r="B212" s="11" t="n">
+        <v>20108</v>
+      </c>
+      <c r="C212" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="D212" s="11" t="n">
+        <v>3206</v>
+      </c>
+      <c r="E212" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F212" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G212" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 해원의 성석</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="13" t="n"/>
+      <c r="B213" s="11" t="n">
+        <v>20109</v>
+      </c>
+      <c r="C213" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="D213" s="11" t="n">
+        <v>3306</v>
+      </c>
+      <c r="E213" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F213" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G213" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 광신의 성석</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="13" t="n"/>
+      <c r="B214" s="11" t="n">
+        <v>20110</v>
+      </c>
+      <c r="C214" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="D214" s="11" t="n">
+        <v>3406</v>
+      </c>
+      <c r="E214" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F214" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G214" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 세계수 성석</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="13" t="n"/>
+      <c r="B215" s="11" t="n">
+        <v>20111</v>
+      </c>
+      <c r="C215" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="D215" s="11" t="n">
+        <v>3506</v>
+      </c>
+      <c r="E215" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F215" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G215" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 월광 성석</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="13" t="n"/>
+      <c r="B216" s="11" t="n">
+        <v>21101</v>
+      </c>
+      <c r="C216" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="D216" s="11" t="n">
+        <v>1105</v>
+      </c>
+      <c r="E216" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F216" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G216" s="12" t="inlineStr">
+        <is>
+          <t>Legendary 풍년의 괭이</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="13" t="n"/>
+      <c r="B217" s="11" t="n">
+        <v>21102</v>
+      </c>
+      <c r="C217" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="D217" s="11" t="n">
+        <v>1205</v>
+      </c>
+      <c r="E217" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F217" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G217" s="12" t="inlineStr">
+        <is>
+          <t>Legendary 용린 낚싯대</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="13" t="n"/>
+      <c r="B218" s="11" t="n">
+        <v>21103</v>
+      </c>
+      <c r="C218" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="D218" s="11" t="n">
+        <v>1305</v>
+      </c>
+      <c r="E218" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F218" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G218" s="12" t="inlineStr">
+        <is>
+          <t>Legendary 미스릴 곡괭이</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="13" t="n"/>
+      <c r="B219" s="11" t="n">
+        <v>21104</v>
+      </c>
+      <c r="C219" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="D219" s="11" t="n">
+        <v>1405</v>
+      </c>
+      <c r="E219" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F219" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G219" s="12" t="inlineStr">
+        <is>
+          <t>Legendary 서리강철 도끼</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="13" t="n"/>
+      <c r="B220" s="11" t="n">
+        <v>21105</v>
+      </c>
+      <c r="C220" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="D220" s="11" t="n">
+        <v>1505</v>
+      </c>
+      <c r="E220" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F220" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G220" s="12" t="inlineStr">
+        <is>
+          <t>Legendary 폭풍의 장궁</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="13" t="n"/>
+      <c r="B221" s="11" t="n">
+        <v>21106</v>
+      </c>
+      <c r="C221" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="D221" s="11" t="n">
+        <v>2006</v>
+      </c>
+      <c r="E221" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F221" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G221" s="12" t="inlineStr">
+        <is>
+          <t>Legendary 대장인의 훈장</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="13" t="n"/>
+      <c r="B222" s="11" t="n">
+        <v>21107</v>
+      </c>
+      <c r="C222" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="D222" s="11" t="n">
+        <v>3105</v>
+      </c>
+      <c r="E222" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F222" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G222" s="12" t="inlineStr">
+        <is>
+          <t>Legendary 대지의 심장</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="13" t="n"/>
+      <c r="B223" s="11" t="n">
+        <v>21108</v>
+      </c>
+      <c r="C223" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="D223" s="11" t="n">
+        <v>3205</v>
+      </c>
+      <c r="E223" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F223" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G223" s="12" t="inlineStr">
+        <is>
+          <t>Legendary 바다의 심장</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="13" t="n"/>
+      <c r="B224" s="11" t="n">
+        <v>21109</v>
+      </c>
+      <c r="C224" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="D224" s="11" t="n">
+        <v>3305</v>
+      </c>
+      <c r="E224" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F224" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G224" s="12" t="inlineStr">
+        <is>
+          <t>Legendary 대지핵 결정</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="13" t="n"/>
+      <c r="B225" s="11" t="n">
+        <v>21110</v>
+      </c>
+      <c r="C225" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="D225" s="11" t="n">
+        <v>3405</v>
+      </c>
+      <c r="E225" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F225" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G225" s="12" t="inlineStr">
+        <is>
+          <t>Legendary 숲의 심장</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="13" t="n"/>
+      <c r="B226" s="11" t="n">
+        <v>21111</v>
+      </c>
+      <c r="C226" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="D226" s="11" t="n">
+        <v>3505</v>
+      </c>
+      <c r="E226" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F226" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G226" s="12" t="inlineStr">
+        <is>
+          <t>Legendary 야수의 심장</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="13" t="n"/>
+      <c r="B227" s="11" t="n">
+        <v>22101</v>
+      </c>
+      <c r="C227" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="D227" s="11" t="n">
+        <v>1106</v>
+      </c>
+      <c r="E227" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F227" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G227" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 대지모의 호미</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="13" t="n"/>
+      <c r="B228" s="11" t="n">
+        <v>22102</v>
+      </c>
+      <c r="C228" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="D228" s="11" t="n">
+        <v>1206</v>
+      </c>
+      <c r="E228" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F228" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G228" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 해신의 삼지창</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="13" t="n"/>
+      <c r="B229" s="11" t="n">
+        <v>22103</v>
+      </c>
+      <c r="C229" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="D229" s="11" t="n">
+        <v>1306</v>
+      </c>
+      <c r="E229" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F229" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G229" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 산신의 곡괭이</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="13" t="n"/>
+      <c r="B230" s="11" t="n">
+        <v>22104</v>
+      </c>
+      <c r="C230" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="D230" s="11" t="n">
+        <v>1406</v>
+      </c>
+      <c r="E230" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F230" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G230" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 세계수의 도끼</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="13" t="n"/>
+      <c r="B231" s="11" t="n">
+        <v>22105</v>
+      </c>
+      <c r="C231" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="D231" s="11" t="n">
+        <v>1506</v>
+      </c>
+      <c r="E231" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F231" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G231" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 월신의 활</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="13" t="n"/>
+      <c r="B232" s="11" t="n">
+        <v>22106</v>
+      </c>
+      <c r="C232" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="D232" s="11" t="n">
+        <v>2007</v>
+      </c>
+      <c r="E232" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F232" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G232" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 창세의 고리</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="13" t="n"/>
+      <c r="B233" s="11" t="n">
+        <v>22107</v>
+      </c>
+      <c r="C233" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="D233" s="11" t="n">
+        <v>3106</v>
+      </c>
+      <c r="E233" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F233" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G233" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 풍요의 성석</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="13" t="n"/>
+      <c r="B234" s="11" t="n">
+        <v>22108</v>
+      </c>
+      <c r="C234" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="D234" s="11" t="n">
+        <v>3206</v>
+      </c>
+      <c r="E234" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F234" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G234" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 해원의 성석</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="13" t="n"/>
+      <c r="B235" s="11" t="n">
+        <v>22109</v>
+      </c>
+      <c r="C235" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="D235" s="11" t="n">
+        <v>3306</v>
+      </c>
+      <c r="E235" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F235" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G235" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 광신의 성석</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="13" t="n"/>
+      <c r="B236" s="11" t="n">
+        <v>22110</v>
+      </c>
+      <c r="C236" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="D236" s="11" t="n">
+        <v>3406</v>
+      </c>
+      <c r="E236" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F236" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G236" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 세계수 성석</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="13" t="n"/>
+      <c r="B237" s="11" t="n">
+        <v>22111</v>
+      </c>
+      <c r="C237" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="D237" s="11" t="n">
+        <v>3506</v>
+      </c>
+      <c r="E237" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F237" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G237" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 월광 성석</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="13" t="n"/>
+      <c r="B238" s="11" t="n">
+        <v>23101</v>
+      </c>
+      <c r="C238" s="11" t="n">
+        <v>23</v>
+      </c>
+      <c r="D238" s="11" t="n">
+        <v>1106</v>
+      </c>
+      <c r="E238" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F238" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G238" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 대지모의 호미</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="13" t="n"/>
+      <c r="B239" s="11" t="n">
+        <v>23102</v>
+      </c>
+      <c r="C239" s="11" t="n">
+        <v>23</v>
+      </c>
+      <c r="D239" s="11" t="n">
+        <v>1206</v>
+      </c>
+      <c r="E239" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F239" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G239" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 해신의 삼지창</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="13" t="n"/>
+      <c r="B240" s="11" t="n">
+        <v>23103</v>
+      </c>
+      <c r="C240" s="11" t="n">
+        <v>23</v>
+      </c>
+      <c r="D240" s="11" t="n">
+        <v>1306</v>
+      </c>
+      <c r="E240" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F240" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G240" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 산신의 곡괭이</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="13" t="n"/>
+      <c r="B241" s="11" t="n">
+        <v>23104</v>
+      </c>
+      <c r="C241" s="11" t="n">
+        <v>23</v>
+      </c>
+      <c r="D241" s="11" t="n">
+        <v>1406</v>
+      </c>
+      <c r="E241" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F241" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G241" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 세계수의 도끼</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="13" t="n"/>
+      <c r="B242" s="11" t="n">
+        <v>23105</v>
+      </c>
+      <c r="C242" s="11" t="n">
+        <v>23</v>
+      </c>
+      <c r="D242" s="11" t="n">
+        <v>1506</v>
+      </c>
+      <c r="E242" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F242" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G242" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 월신의 활</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="13" t="n"/>
+      <c r="B243" s="11" t="n">
+        <v>23106</v>
+      </c>
+      <c r="C243" s="11" t="n">
+        <v>23</v>
+      </c>
+      <c r="D243" s="11" t="n">
+        <v>2007</v>
+      </c>
+      <c r="E243" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F243" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G243" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 창세의 고리</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="13" t="n"/>
+      <c r="B244" s="11" t="n">
+        <v>23107</v>
+      </c>
+      <c r="C244" s="11" t="n">
+        <v>23</v>
+      </c>
+      <c r="D244" s="11" t="n">
+        <v>3106</v>
+      </c>
+      <c r="E244" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F244" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G244" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 풍요의 성석</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="13" t="n"/>
+      <c r="B245" s="11" t="n">
+        <v>23108</v>
+      </c>
+      <c r="C245" s="11" t="n">
+        <v>23</v>
+      </c>
+      <c r="D245" s="11" t="n">
+        <v>3206</v>
+      </c>
+      <c r="E245" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F245" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G245" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 해원의 성석</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="13" t="n"/>
+      <c r="B246" s="11" t="n">
+        <v>23109</v>
+      </c>
+      <c r="C246" s="11" t="n">
+        <v>23</v>
+      </c>
+      <c r="D246" s="11" t="n">
+        <v>3306</v>
+      </c>
+      <c r="E246" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F246" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G246" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 광신의 성석</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="13" t="n"/>
+      <c r="B247" s="11" t="n">
+        <v>23110</v>
+      </c>
+      <c r="C247" s="11" t="n">
+        <v>23</v>
+      </c>
+      <c r="D247" s="11" t="n">
+        <v>3406</v>
+      </c>
+      <c r="E247" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F247" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G247" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 세계수 성석</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="13" t="n"/>
+      <c r="B248" s="11" t="n">
+        <v>23111</v>
+      </c>
+      <c r="C248" s="11" t="n">
+        <v>23</v>
+      </c>
+      <c r="D248" s="11" t="n">
+        <v>3506</v>
+      </c>
+      <c r="E248" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F248" s="11" t="n">
+        <v>81</v>
+      </c>
+      <c r="G248" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 월광 성석</t>
         </is>
       </c>
     </row>
@@ -5021,7 +11049,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -5030,7 +11058,7 @@
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5255,138 +11283,690 @@
     <row r="10">
       <c r="A10" s="13" t="n"/>
       <c r="B10" s="11" t="n">
-        <v>6201</v>
+        <v>9201</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>50</v>
+        <v>135</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>100</v>
+        <v>271</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>300</v>
+        <v>3000</v>
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
-          <t>골드 50~100</t>
+          <t>골드 135~271</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="13" t="n"/>
       <c r="B11" s="11" t="n">
-        <v>6202</v>
+        <v>9202</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D11" s="11" t="n">
-        <v>100</v>
+        <v>271</v>
       </c>
       <c r="E11" s="11" t="n">
-        <v>300</v>
+        <v>677</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
-          <t>골드 100~300</t>
+          <t>골드 271~677</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="13" t="n"/>
       <c r="B12" s="11" t="n">
-        <v>7201</v>
+        <v>10201</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>300</v>
+        <v>406</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>600</v>
+        <v>813</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>300</v>
+        <v>3000</v>
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
-          <t>골드 300~600</t>
+          <t>골드 406~813</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="13" t="n"/>
       <c r="B13" s="11" t="n">
-        <v>7202</v>
+        <v>10202</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D13" s="11" t="n">
-        <v>600</v>
+        <v>813</v>
       </c>
       <c r="E13" s="11" t="n">
-        <v>1500</v>
+        <v>2032</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
-          <t>골드 600~1500</t>
+          <t>골드 813~2032</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="13" t="n"/>
       <c r="B14" s="11" t="n">
-        <v>8201</v>
+        <v>11201</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D14" s="11" t="n">
-        <v>1500</v>
+        <v>1354</v>
       </c>
       <c r="E14" s="11" t="n">
+        <v>2709</v>
+      </c>
+      <c r="F14" s="11" t="n">
         <v>3000</v>
       </c>
-      <c r="F14" s="11" t="n">
-        <v>300</v>
-      </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
-          <t>골드 1500~3000</t>
+          <t>골드 1354~2709</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="13" t="n"/>
       <c r="B15" s="11" t="n">
-        <v>8202</v>
+        <v>11202</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="D15" s="11" t="n">
+        <v>2709</v>
+      </c>
+      <c r="E15" s="11" t="n">
+        <v>6772</v>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G15" s="12" t="inlineStr">
+        <is>
+          <t>골드 2709~6772</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="n"/>
+      <c r="B16" s="11" t="n">
+        <v>12201</v>
+      </c>
+      <c r="C16" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="D16" s="11" t="n">
+        <v>406</v>
+      </c>
+      <c r="E16" s="11" t="n">
+        <v>813</v>
+      </c>
+      <c r="F16" s="11" t="n">
         <v>3000</v>
       </c>
-      <c r="E15" s="11" t="n">
-        <v>8000</v>
-      </c>
-      <c r="F15" s="11" t="n">
-        <v>100</v>
-      </c>
-      <c r="G15" s="12" t="inlineStr">
-        <is>
-          <t>골드 3000~8000</t>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>골드 406~813</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="n"/>
+      <c r="B17" s="11" t="n">
+        <v>12202</v>
+      </c>
+      <c r="C17" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="D17" s="11" t="n">
+        <v>813</v>
+      </c>
+      <c r="E17" s="11" t="n">
+        <v>2032</v>
+      </c>
+      <c r="F17" s="11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>골드 813~2032</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="n"/>
+      <c r="B18" s="11" t="n">
+        <v>13201</v>
+      </c>
+      <c r="C18" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="D18" s="11" t="n">
+        <v>1219</v>
+      </c>
+      <c r="E18" s="11" t="n">
+        <v>2438</v>
+      </c>
+      <c r="F18" s="11" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G18" s="12" t="inlineStr">
+        <is>
+          <t>골드 1219~2438</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="n"/>
+      <c r="B19" s="11" t="n">
+        <v>13202</v>
+      </c>
+      <c r="C19" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="D19" s="11" t="n">
+        <v>2438</v>
+      </c>
+      <c r="E19" s="11" t="n">
+        <v>6095</v>
+      </c>
+      <c r="F19" s="11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G19" s="12" t="inlineStr">
+        <is>
+          <t>골드 2438~6095</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="n"/>
+      <c r="B20" s="11" t="n">
+        <v>14201</v>
+      </c>
+      <c r="C20" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="D20" s="11" t="n">
+        <v>4064</v>
+      </c>
+      <c r="E20" s="11" t="n">
+        <v>8127</v>
+      </c>
+      <c r="F20" s="11" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G20" s="12" t="inlineStr">
+        <is>
+          <t>골드 4064~8127</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="n"/>
+      <c r="B21" s="11" t="n">
+        <v>14202</v>
+      </c>
+      <c r="C21" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="D21" s="11" t="n">
+        <v>8127</v>
+      </c>
+      <c r="E21" s="11" t="n">
+        <v>20318</v>
+      </c>
+      <c r="F21" s="11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G21" s="12" t="inlineStr">
+        <is>
+          <t>골드 8127~20318</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="n"/>
+      <c r="B22" s="11" t="n">
+        <v>15201</v>
+      </c>
+      <c r="C22" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="D22" s="11" t="n">
+        <v>1219</v>
+      </c>
+      <c r="E22" s="11" t="n">
+        <v>2438</v>
+      </c>
+      <c r="F22" s="11" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G22" s="12" t="inlineStr">
+        <is>
+          <t>골드 1219~2438</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="n"/>
+      <c r="B23" s="11" t="n">
+        <v>15202</v>
+      </c>
+      <c r="C23" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="D23" s="11" t="n">
+        <v>2438</v>
+      </c>
+      <c r="E23" s="11" t="n">
+        <v>6095</v>
+      </c>
+      <c r="F23" s="11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G23" s="12" t="inlineStr">
+        <is>
+          <t>골드 2438~6095</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="n"/>
+      <c r="B24" s="11" t="n">
+        <v>16201</v>
+      </c>
+      <c r="C24" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="D24" s="11" t="n">
+        <v>3657</v>
+      </c>
+      <c r="E24" s="11" t="n">
+        <v>7314</v>
+      </c>
+      <c r="F24" s="11" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G24" s="12" t="inlineStr">
+        <is>
+          <t>골드 3657~7314</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="n"/>
+      <c r="B25" s="11" t="n">
+        <v>16202</v>
+      </c>
+      <c r="C25" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="D25" s="11" t="n">
+        <v>7314</v>
+      </c>
+      <c r="E25" s="11" t="n">
+        <v>18286</v>
+      </c>
+      <c r="F25" s="11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G25" s="12" t="inlineStr">
+        <is>
+          <t>골드 7314~18286</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="13" t="n"/>
+      <c r="B26" s="11" t="n">
+        <v>17201</v>
+      </c>
+      <c r="C26" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="D26" s="11" t="n">
+        <v>12190</v>
+      </c>
+      <c r="E26" s="11" t="n">
+        <v>24381</v>
+      </c>
+      <c r="F26" s="11" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G26" s="12" t="inlineStr">
+        <is>
+          <t>골드 12190~24381</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="13" t="n"/>
+      <c r="B27" s="11" t="n">
+        <v>17202</v>
+      </c>
+      <c r="C27" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="D27" s="11" t="n">
+        <v>24381</v>
+      </c>
+      <c r="E27" s="11" t="n">
+        <v>60952</v>
+      </c>
+      <c r="F27" s="11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G27" s="12" t="inlineStr">
+        <is>
+          <t>골드 24381~60952</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="n"/>
+      <c r="B28" s="11" t="n">
+        <v>18201</v>
+      </c>
+      <c r="C28" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="D28" s="11" t="n">
+        <v>3657</v>
+      </c>
+      <c r="E28" s="11" t="n">
+        <v>7314</v>
+      </c>
+      <c r="F28" s="11" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G28" s="12" t="inlineStr">
+        <is>
+          <t>골드 3657~7314</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="13" t="n"/>
+      <c r="B29" s="11" t="n">
+        <v>18202</v>
+      </c>
+      <c r="C29" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="D29" s="11" t="n">
+        <v>7314</v>
+      </c>
+      <c r="E29" s="11" t="n">
+        <v>18286</v>
+      </c>
+      <c r="F29" s="11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G29" s="12" t="inlineStr">
+        <is>
+          <t>골드 7314~18286</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="13" t="n"/>
+      <c r="B30" s="11" t="n">
+        <v>19201</v>
+      </c>
+      <c r="C30" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="D30" s="11" t="n">
+        <v>10971</v>
+      </c>
+      <c r="E30" s="11" t="n">
+        <v>21943</v>
+      </c>
+      <c r="F30" s="11" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G30" s="12" t="inlineStr">
+        <is>
+          <t>골드 10971~21943</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="13" t="n"/>
+      <c r="B31" s="11" t="n">
+        <v>19202</v>
+      </c>
+      <c r="C31" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="D31" s="11" t="n">
+        <v>21943</v>
+      </c>
+      <c r="E31" s="11" t="n">
+        <v>54857</v>
+      </c>
+      <c r="F31" s="11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G31" s="12" t="inlineStr">
+        <is>
+          <t>골드 21943~54857</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="13" t="n"/>
+      <c r="B32" s="11" t="n">
+        <v>20201</v>
+      </c>
+      <c r="C32" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="D32" s="11" t="n">
+        <v>36572</v>
+      </c>
+      <c r="E32" s="11" t="n">
+        <v>73143</v>
+      </c>
+      <c r="F32" s="11" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G32" s="12" t="inlineStr">
+        <is>
+          <t>골드 36572~73143</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="13" t="n"/>
+      <c r="B33" s="11" t="n">
+        <v>20202</v>
+      </c>
+      <c r="C33" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="D33" s="11" t="n">
+        <v>73143</v>
+      </c>
+      <c r="E33" s="11" t="n">
+        <v>182858</v>
+      </c>
+      <c r="F33" s="11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G33" s="12" t="inlineStr">
+        <is>
+          <t>골드 73143~182858</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="13" t="n"/>
+      <c r="B34" s="11" t="n">
+        <v>21201</v>
+      </c>
+      <c r="C34" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="D34" s="11" t="n">
+        <v>10971</v>
+      </c>
+      <c r="E34" s="11" t="n">
+        <v>21943</v>
+      </c>
+      <c r="F34" s="11" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G34" s="12" t="inlineStr">
+        <is>
+          <t>골드 10971~21943</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="13" t="n"/>
+      <c r="B35" s="11" t="n">
+        <v>21202</v>
+      </c>
+      <c r="C35" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="D35" s="11" t="n">
+        <v>21943</v>
+      </c>
+      <c r="E35" s="11" t="n">
+        <v>54857</v>
+      </c>
+      <c r="F35" s="11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G35" s="12" t="inlineStr">
+        <is>
+          <t>골드 21943~54857</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="13" t="n"/>
+      <c r="B36" s="11" t="n">
+        <v>22201</v>
+      </c>
+      <c r="C36" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="D36" s="11" t="n">
+        <v>32914</v>
+      </c>
+      <c r="E36" s="11" t="n">
+        <v>65829</v>
+      </c>
+      <c r="F36" s="11" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G36" s="12" t="inlineStr">
+        <is>
+          <t>골드 32914~65829</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="13" t="n"/>
+      <c r="B37" s="11" t="n">
+        <v>22202</v>
+      </c>
+      <c r="C37" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="D37" s="11" t="n">
+        <v>65829</v>
+      </c>
+      <c r="E37" s="11" t="n">
+        <v>164572</v>
+      </c>
+      <c r="F37" s="11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G37" s="12" t="inlineStr">
+        <is>
+          <t>골드 65829~164572</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="13" t="n"/>
+      <c r="B38" s="11" t="n">
+        <v>23201</v>
+      </c>
+      <c r="C38" s="11" t="n">
+        <v>23</v>
+      </c>
+      <c r="D38" s="11" t="n">
+        <v>109714</v>
+      </c>
+      <c r="E38" s="11" t="n">
+        <v>219429</v>
+      </c>
+      <c r="F38" s="11" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G38" s="12" t="inlineStr">
+        <is>
+          <t>골드 109714~219429</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="13" t="n"/>
+      <c r="B39" s="11" t="n">
+        <v>23202</v>
+      </c>
+      <c r="C39" s="11" t="n">
+        <v>23</v>
+      </c>
+      <c r="D39" s="11" t="n">
+        <v>219429</v>
+      </c>
+      <c r="E39" s="11" t="n">
+        <v>548572</v>
+      </c>
+      <c r="F39" s="11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G39" s="12" t="inlineStr">
+        <is>
+          <t>골드 219429~548572</t>
         </is>
       </c>
     </row>

--- a/GameDesign/Excel/Gacha.xlsx
+++ b/GameDesign/Excel/Gacha.xlsx
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G130"/>
+  <dimension ref="A1:G194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -966,7 +966,7 @@
         <v>27</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>27</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>27</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
@@ -1035,7 +1035,7 @@
         <v>27</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
         <v>27</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>1</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>1</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
@@ -1127,7 +1127,7 @@
         <v>33</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
         <v>33</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>33</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>33</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
@@ -1219,7 +1219,7 @@
         <v>33</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
@@ -1242,7 +1242,7 @@
         <v>1</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
         <v>45</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
         <v>45</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G32" s="12" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>45</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>45</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
@@ -1403,7 +1403,7 @@
         <v>45</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
@@ -1426,7 +1426,7 @@
         <v>1</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="G36" s="12" t="inlineStr">
         <is>
@@ -1449,7 +1449,7 @@
         <v>1</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>27</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>27</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G40" s="12" t="inlineStr">
         <is>
@@ -1541,7 +1541,7 @@
         <v>27</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>27</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G42" s="12" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
         <v>27</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
         <v>1</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
         <v>2</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
@@ -1656,7 +1656,7 @@
         <v>33</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
@@ -1679,7 +1679,7 @@
         <v>33</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>33</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
@@ -1725,7 +1725,7 @@
         <v>33</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>33</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
@@ -1771,7 +1771,7 @@
         <v>1</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>
@@ -1840,7 +1840,7 @@
         <v>45</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G54" s="12" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v>45</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G55" s="12" t="inlineStr">
         <is>
@@ -1886,7 +1886,7 @@
         <v>45</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G56" s="12" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
         <v>45</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G57" s="12" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
         <v>45</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G58" s="12" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>1</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="G59" s="12" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         <v>2</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="G60" s="12" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>27</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G62" s="12" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>27</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G63" s="12" t="inlineStr">
         <is>
@@ -2070,7 +2070,7 @@
         <v>27</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G64" s="12" t="inlineStr">
         <is>
@@ -2093,7 +2093,7 @@
         <v>27</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G65" s="12" t="inlineStr">
         <is>
@@ -2116,7 +2116,7 @@
         <v>27</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G66" s="12" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>1</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="G67" s="12" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>3</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="G68" s="12" t="inlineStr">
         <is>
@@ -2185,7 +2185,7 @@
         <v>33</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G69" s="12" t="inlineStr">
         <is>
@@ -2208,7 +2208,7 @@
         <v>33</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G70" s="12" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>33</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G71" s="12" t="inlineStr">
         <is>
@@ -2254,7 +2254,7 @@
         <v>33</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G72" s="12" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>33</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G73" s="12" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>1</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="G74" s="12" t="inlineStr">
         <is>
@@ -2369,7 +2369,7 @@
         <v>45</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G77" s="12" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         <v>45</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G78" s="12" t="inlineStr">
         <is>
@@ -2415,7 +2415,7 @@
         <v>45</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G79" s="12" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
         <v>45</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G80" s="12" t="inlineStr">
         <is>
@@ -2461,7 +2461,7 @@
         <v>45</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G81" s="12" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>1</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="G82" s="12" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
         <v>3</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="G83" s="12" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>27</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G85" s="12" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         <v>27</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G86" s="12" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>27</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G87" s="12" t="inlineStr">
         <is>
@@ -2622,7 +2622,7 @@
         <v>27</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G88" s="12" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         <v>27</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G89" s="12" t="inlineStr">
         <is>
@@ -2668,7 +2668,7 @@
         <v>1</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="G90" s="12" t="inlineStr">
         <is>
@@ -2691,7 +2691,7 @@
         <v>4</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="G91" s="12" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>33</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G92" s="12" t="inlineStr">
         <is>
@@ -2737,7 +2737,7 @@
         <v>33</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G93" s="12" t="inlineStr">
         <is>
@@ -2760,7 +2760,7 @@
         <v>33</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G94" s="12" t="inlineStr">
         <is>
@@ -2783,7 +2783,7 @@
         <v>33</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G95" s="12" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>33</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G96" s="12" t="inlineStr">
         <is>
@@ -2829,7 +2829,7 @@
         <v>1</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="G97" s="12" t="inlineStr">
         <is>
@@ -2898,7 +2898,7 @@
         <v>45</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G100" s="12" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>45</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G101" s="12" t="inlineStr">
         <is>
@@ -2944,7 +2944,7 @@
         <v>45</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G102" s="12" t="inlineStr">
         <is>
@@ -2967,7 +2967,7 @@
         <v>45</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G103" s="12" t="inlineStr">
         <is>
@@ -2990,7 +2990,7 @@
         <v>45</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G104" s="12" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>1</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="G105" s="12" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>4</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="G106" s="12" t="inlineStr">
         <is>
@@ -3082,7 +3082,7 @@
         <v>27</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G108" s="12" t="inlineStr">
         <is>
@@ -3105,7 +3105,7 @@
         <v>27</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G109" s="12" t="inlineStr">
         <is>
@@ -3128,7 +3128,7 @@
         <v>27</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G110" s="12" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
         <v>27</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G111" s="12" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>27</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G112" s="12" t="inlineStr">
         <is>
@@ -3197,7 +3197,7 @@
         <v>1</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="G113" s="12" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>5</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="G114" s="12" t="inlineStr">
         <is>
@@ -3243,7 +3243,7 @@
         <v>33</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G115" s="12" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
         <v>33</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G116" s="12" t="inlineStr">
         <is>
@@ -3289,7 +3289,7 @@
         <v>33</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G117" s="12" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>33</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G118" s="12" t="inlineStr">
         <is>
@@ -3335,7 +3335,7 @@
         <v>33</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G119" s="12" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>1</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="G120" s="12" t="inlineStr">
         <is>
@@ -3427,7 +3427,7 @@
         <v>45</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G123" s="12" t="inlineStr">
         <is>
@@ -3450,7 +3450,7 @@
         <v>45</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G124" s="12" t="inlineStr">
         <is>
@@ -3473,7 +3473,7 @@
         <v>45</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G125" s="12" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
         <v>45</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G126" s="12" t="inlineStr">
         <is>
@@ -3519,7 +3519,7 @@
         <v>45</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="G127" s="12" t="inlineStr">
         <is>
@@ -3542,7 +3542,7 @@
         <v>1</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="G128" s="12" t="inlineStr">
         <is>
@@ -3565,7 +3565,7 @@
         <v>5</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="G129" s="12" t="inlineStr">
         <is>
@@ -3593,6 +3593,1478 @@
       <c r="G130" s="12" t="inlineStr">
         <is>
           <t>상급 인챈트 큐브 x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="13" t="n"/>
+      <c r="B131" s="11" t="n">
+        <v>9008</v>
+      </c>
+      <c r="C131" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="D131" s="11" t="n">
+        <v>100041</v>
+      </c>
+      <c r="E131" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F131" s="11" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G131" s="12" t="inlineStr">
+        <is>
+          <t>성장의 비약 (소) x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="13" t="n"/>
+      <c r="B132" s="11" t="n">
+        <v>9009</v>
+      </c>
+      <c r="C132" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="D132" s="11" t="n">
+        <v>100044</v>
+      </c>
+      <c r="E132" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F132" s="11" t="n">
+        <v>195</v>
+      </c>
+      <c r="G132" s="12" t="inlineStr">
+        <is>
+          <t>신속의 영약 x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="13" t="n"/>
+      <c r="B133" s="11" t="n">
+        <v>9010</v>
+      </c>
+      <c r="C133" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="D133" s="11" t="n">
+        <v>100045</v>
+      </c>
+      <c r="E133" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F133" s="11" t="n">
+        <v>195</v>
+      </c>
+      <c r="G133" s="12" t="inlineStr">
+        <is>
+          <t>풍요의 영약 x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="13" t="n"/>
+      <c r="B134" s="11" t="n">
+        <v>12008</v>
+      </c>
+      <c r="C134" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="D134" s="11" t="n">
+        <v>100041</v>
+      </c>
+      <c r="E134" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F134" s="11" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G134" s="12" t="inlineStr">
+        <is>
+          <t>성장의 비약 (소) x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="13" t="n"/>
+      <c r="B135" s="11" t="n">
+        <v>12009</v>
+      </c>
+      <c r="C135" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="D135" s="11" t="n">
+        <v>100044</v>
+      </c>
+      <c r="E135" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F135" s="11" t="n">
+        <v>195</v>
+      </c>
+      <c r="G135" s="12" t="inlineStr">
+        <is>
+          <t>신속의 영약 x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="13" t="n"/>
+      <c r="B136" s="11" t="n">
+        <v>12010</v>
+      </c>
+      <c r="C136" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="D136" s="11" t="n">
+        <v>100045</v>
+      </c>
+      <c r="E136" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F136" s="11" t="n">
+        <v>195</v>
+      </c>
+      <c r="G136" s="12" t="inlineStr">
+        <is>
+          <t>풍요의 영약 x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="13" t="n"/>
+      <c r="B137" s="11" t="n">
+        <v>15008</v>
+      </c>
+      <c r="C137" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="D137" s="11" t="n">
+        <v>100041</v>
+      </c>
+      <c r="E137" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F137" s="11" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G137" s="12" t="inlineStr">
+        <is>
+          <t>성장의 비약 (소) x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="13" t="n"/>
+      <c r="B138" s="11" t="n">
+        <v>15009</v>
+      </c>
+      <c r="C138" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="D138" s="11" t="n">
+        <v>100044</v>
+      </c>
+      <c r="E138" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F138" s="11" t="n">
+        <v>195</v>
+      </c>
+      <c r="G138" s="12" t="inlineStr">
+        <is>
+          <t>신속의 영약 x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="13" t="n"/>
+      <c r="B139" s="11" t="n">
+        <v>15010</v>
+      </c>
+      <c r="C139" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="D139" s="11" t="n">
+        <v>100045</v>
+      </c>
+      <c r="E139" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F139" s="11" t="n">
+        <v>195</v>
+      </c>
+      <c r="G139" s="12" t="inlineStr">
+        <is>
+          <t>풍요의 영약 x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="13" t="n"/>
+      <c r="B140" s="11" t="n">
+        <v>18008</v>
+      </c>
+      <c r="C140" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="D140" s="11" t="n">
+        <v>100041</v>
+      </c>
+      <c r="E140" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F140" s="11" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G140" s="12" t="inlineStr">
+        <is>
+          <t>성장의 비약 (소) x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="13" t="n"/>
+      <c r="B141" s="11" t="n">
+        <v>18009</v>
+      </c>
+      <c r="C141" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="D141" s="11" t="n">
+        <v>100044</v>
+      </c>
+      <c r="E141" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F141" s="11" t="n">
+        <v>195</v>
+      </c>
+      <c r="G141" s="12" t="inlineStr">
+        <is>
+          <t>신속의 영약 x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="13" t="n"/>
+      <c r="B142" s="11" t="n">
+        <v>18010</v>
+      </c>
+      <c r="C142" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="D142" s="11" t="n">
+        <v>100045</v>
+      </c>
+      <c r="E142" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F142" s="11" t="n">
+        <v>195</v>
+      </c>
+      <c r="G142" s="12" t="inlineStr">
+        <is>
+          <t>풍요의 영약 x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="13" t="n"/>
+      <c r="B143" s="11" t="n">
+        <v>21008</v>
+      </c>
+      <c r="C143" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="D143" s="11" t="n">
+        <v>100041</v>
+      </c>
+      <c r="E143" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F143" s="11" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G143" s="12" t="inlineStr">
+        <is>
+          <t>성장의 비약 (소) x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="13" t="n"/>
+      <c r="B144" s="11" t="n">
+        <v>21009</v>
+      </c>
+      <c r="C144" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="D144" s="11" t="n">
+        <v>100044</v>
+      </c>
+      <c r="E144" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F144" s="11" t="n">
+        <v>195</v>
+      </c>
+      <c r="G144" s="12" t="inlineStr">
+        <is>
+          <t>신속의 영약 x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="13" t="n"/>
+      <c r="B145" s="11" t="n">
+        <v>21010</v>
+      </c>
+      <c r="C145" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="D145" s="11" t="n">
+        <v>100045</v>
+      </c>
+      <c r="E145" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F145" s="11" t="n">
+        <v>195</v>
+      </c>
+      <c r="G145" s="12" t="inlineStr">
+        <is>
+          <t>풍요의 영약 x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="13" t="n"/>
+      <c r="B146" s="11" t="n">
+        <v>10009</v>
+      </c>
+      <c r="C146" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="D146" s="11" t="n">
+        <v>100041</v>
+      </c>
+      <c r="E146" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F146" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="G146" s="12" t="inlineStr">
+        <is>
+          <t>성장의 비약 (소) x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="13" t="n"/>
+      <c r="B147" s="11" t="n">
+        <v>10010</v>
+      </c>
+      <c r="C147" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="D147" s="11" t="n">
+        <v>100042</v>
+      </c>
+      <c r="E147" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F147" s="11" t="n">
+        <v>500</v>
+      </c>
+      <c r="G147" s="12" t="inlineStr">
+        <is>
+          <t>성장의 비약 (중) x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="13" t="n"/>
+      <c r="B148" s="11" t="n">
+        <v>10011</v>
+      </c>
+      <c r="C148" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="D148" s="11" t="n">
+        <v>100044</v>
+      </c>
+      <c r="E148" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F148" s="11" t="n">
+        <v>495</v>
+      </c>
+      <c r="G148" s="12" t="inlineStr">
+        <is>
+          <t>신속의 영약 x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="13" t="n"/>
+      <c r="B149" s="11" t="n">
+        <v>10012</v>
+      </c>
+      <c r="C149" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="D149" s="11" t="n">
+        <v>100045</v>
+      </c>
+      <c r="E149" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F149" s="11" t="n">
+        <v>495</v>
+      </c>
+      <c r="G149" s="12" t="inlineStr">
+        <is>
+          <t>풍요의 영약 x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="13" t="n"/>
+      <c r="B150" s="11" t="n">
+        <v>13009</v>
+      </c>
+      <c r="C150" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="D150" s="11" t="n">
+        <v>100041</v>
+      </c>
+      <c r="E150" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F150" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="G150" s="12" t="inlineStr">
+        <is>
+          <t>성장의 비약 (소) x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="13" t="n"/>
+      <c r="B151" s="11" t="n">
+        <v>13010</v>
+      </c>
+      <c r="C151" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="D151" s="11" t="n">
+        <v>100042</v>
+      </c>
+      <c r="E151" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F151" s="11" t="n">
+        <v>500</v>
+      </c>
+      <c r="G151" s="12" t="inlineStr">
+        <is>
+          <t>성장의 비약 (중) x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="13" t="n"/>
+      <c r="B152" s="11" t="n">
+        <v>13011</v>
+      </c>
+      <c r="C152" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="D152" s="11" t="n">
+        <v>100044</v>
+      </c>
+      <c r="E152" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F152" s="11" t="n">
+        <v>495</v>
+      </c>
+      <c r="G152" s="12" t="inlineStr">
+        <is>
+          <t>신속의 영약 x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="13" t="n"/>
+      <c r="B153" s="11" t="n">
+        <v>13012</v>
+      </c>
+      <c r="C153" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="D153" s="11" t="n">
+        <v>100045</v>
+      </c>
+      <c r="E153" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F153" s="11" t="n">
+        <v>495</v>
+      </c>
+      <c r="G153" s="12" t="inlineStr">
+        <is>
+          <t>풍요의 영약 x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="13" t="n"/>
+      <c r="B154" s="11" t="n">
+        <v>16009</v>
+      </c>
+      <c r="C154" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="D154" s="11" t="n">
+        <v>100041</v>
+      </c>
+      <c r="E154" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F154" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="G154" s="12" t="inlineStr">
+        <is>
+          <t>성장의 비약 (소) x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="13" t="n"/>
+      <c r="B155" s="11" t="n">
+        <v>16010</v>
+      </c>
+      <c r="C155" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="D155" s="11" t="n">
+        <v>100042</v>
+      </c>
+      <c r="E155" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F155" s="11" t="n">
+        <v>500</v>
+      </c>
+      <c r="G155" s="12" t="inlineStr">
+        <is>
+          <t>성장의 비약 (중) x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="13" t="n"/>
+      <c r="B156" s="11" t="n">
+        <v>16011</v>
+      </c>
+      <c r="C156" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="D156" s="11" t="n">
+        <v>100044</v>
+      </c>
+      <c r="E156" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F156" s="11" t="n">
+        <v>495</v>
+      </c>
+      <c r="G156" s="12" t="inlineStr">
+        <is>
+          <t>신속의 영약 x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="13" t="n"/>
+      <c r="B157" s="11" t="n">
+        <v>16012</v>
+      </c>
+      <c r="C157" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="D157" s="11" t="n">
+        <v>100045</v>
+      </c>
+      <c r="E157" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F157" s="11" t="n">
+        <v>495</v>
+      </c>
+      <c r="G157" s="12" t="inlineStr">
+        <is>
+          <t>풍요의 영약 x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="13" t="n"/>
+      <c r="B158" s="11" t="n">
+        <v>19009</v>
+      </c>
+      <c r="C158" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="D158" s="11" t="n">
+        <v>100041</v>
+      </c>
+      <c r="E158" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F158" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="G158" s="12" t="inlineStr">
+        <is>
+          <t>성장의 비약 (소) x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="13" t="n"/>
+      <c r="B159" s="11" t="n">
+        <v>19010</v>
+      </c>
+      <c r="C159" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="D159" s="11" t="n">
+        <v>100042</v>
+      </c>
+      <c r="E159" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F159" s="11" t="n">
+        <v>500</v>
+      </c>
+      <c r="G159" s="12" t="inlineStr">
+        <is>
+          <t>성장의 비약 (중) x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="13" t="n"/>
+      <c r="B160" s="11" t="n">
+        <v>19011</v>
+      </c>
+      <c r="C160" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="D160" s="11" t="n">
+        <v>100044</v>
+      </c>
+      <c r="E160" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F160" s="11" t="n">
+        <v>495</v>
+      </c>
+      <c r="G160" s="12" t="inlineStr">
+        <is>
+          <t>신속의 영약 x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="13" t="n"/>
+      <c r="B161" s="11" t="n">
+        <v>19012</v>
+      </c>
+      <c r="C161" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="D161" s="11" t="n">
+        <v>100045</v>
+      </c>
+      <c r="E161" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F161" s="11" t="n">
+        <v>495</v>
+      </c>
+      <c r="G161" s="12" t="inlineStr">
+        <is>
+          <t>풍요의 영약 x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="13" t="n"/>
+      <c r="B162" s="11" t="n">
+        <v>22009</v>
+      </c>
+      <c r="C162" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="D162" s="11" t="n">
+        <v>100041</v>
+      </c>
+      <c r="E162" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F162" s="11" t="n">
+        <v>800</v>
+      </c>
+      <c r="G162" s="12" t="inlineStr">
+        <is>
+          <t>성장의 비약 (소) x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="13" t="n"/>
+      <c r="B163" s="11" t="n">
+        <v>22010</v>
+      </c>
+      <c r="C163" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="D163" s="11" t="n">
+        <v>100042</v>
+      </c>
+      <c r="E163" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F163" s="11" t="n">
+        <v>500</v>
+      </c>
+      <c r="G163" s="12" t="inlineStr">
+        <is>
+          <t>성장의 비약 (중) x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="13" t="n"/>
+      <c r="B164" s="11" t="n">
+        <v>22011</v>
+      </c>
+      <c r="C164" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="D164" s="11" t="n">
+        <v>100044</v>
+      </c>
+      <c r="E164" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F164" s="11" t="n">
+        <v>495</v>
+      </c>
+      <c r="G164" s="12" t="inlineStr">
+        <is>
+          <t>신속의 영약 x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="13" t="n"/>
+      <c r="B165" s="11" t="n">
+        <v>22012</v>
+      </c>
+      <c r="C165" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="D165" s="11" t="n">
+        <v>100045</v>
+      </c>
+      <c r="E165" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F165" s="11" t="n">
+        <v>495</v>
+      </c>
+      <c r="G165" s="12" t="inlineStr">
+        <is>
+          <t>풍요의 영약 x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="13" t="n"/>
+      <c r="B166" s="11" t="n">
+        <v>11009</v>
+      </c>
+      <c r="C166" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="D166" s="11" t="n">
+        <v>100042</v>
+      </c>
+      <c r="E166" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F166" s="11" t="n">
+        <v>600</v>
+      </c>
+      <c r="G166" s="12" t="inlineStr">
+        <is>
+          <t>성장의 비약 (중) x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="13" t="n"/>
+      <c r="B167" s="11" t="n">
+        <v>11010</v>
+      </c>
+      <c r="C167" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="D167" s="11" t="n">
+        <v>100043</v>
+      </c>
+      <c r="E167" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F167" s="11" t="n">
+        <v>400</v>
+      </c>
+      <c r="G167" s="12" t="inlineStr">
+        <is>
+          <t>성장의 비약 (대) x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="13" t="n"/>
+      <c r="B168" s="11" t="n">
+        <v>11011</v>
+      </c>
+      <c r="C168" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="D168" s="11" t="n">
+        <v>100044</v>
+      </c>
+      <c r="E168" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F168" s="11" t="n">
+        <v>470</v>
+      </c>
+      <c r="G168" s="12" t="inlineStr">
+        <is>
+          <t>신속의 영약 x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="13" t="n"/>
+      <c r="B169" s="11" t="n">
+        <v>11012</v>
+      </c>
+      <c r="C169" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="D169" s="11" t="n">
+        <v>100045</v>
+      </c>
+      <c r="E169" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F169" s="11" t="n">
+        <v>470</v>
+      </c>
+      <c r="G169" s="12" t="inlineStr">
+        <is>
+          <t>풍요의 영약 x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="13" t="n"/>
+      <c r="B170" s="11" t="n">
+        <v>11013</v>
+      </c>
+      <c r="C170" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="D170" s="11" t="n">
+        <v>100046</v>
+      </c>
+      <c r="E170" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F170" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="G170" s="12" t="inlineStr">
+        <is>
+          <t>망각의 묘약 x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="13" t="n"/>
+      <c r="B171" s="11" t="n">
+        <v>14009</v>
+      </c>
+      <c r="C171" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="D171" s="11" t="n">
+        <v>100042</v>
+      </c>
+      <c r="E171" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F171" s="11" t="n">
+        <v>600</v>
+      </c>
+      <c r="G171" s="12" t="inlineStr">
+        <is>
+          <t>성장의 비약 (중) x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="13" t="n"/>
+      <c r="B172" s="11" t="n">
+        <v>14010</v>
+      </c>
+      <c r="C172" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="D172" s="11" t="n">
+        <v>100043</v>
+      </c>
+      <c r="E172" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F172" s="11" t="n">
+        <v>400</v>
+      </c>
+      <c r="G172" s="12" t="inlineStr">
+        <is>
+          <t>성장의 비약 (대) x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="13" t="n"/>
+      <c r="B173" s="11" t="n">
+        <v>14011</v>
+      </c>
+      <c r="C173" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="D173" s="11" t="n">
+        <v>100044</v>
+      </c>
+      <c r="E173" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F173" s="11" t="n">
+        <v>470</v>
+      </c>
+      <c r="G173" s="12" t="inlineStr">
+        <is>
+          <t>신속의 영약 x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="13" t="n"/>
+      <c r="B174" s="11" t="n">
+        <v>14012</v>
+      </c>
+      <c r="C174" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="D174" s="11" t="n">
+        <v>100045</v>
+      </c>
+      <c r="E174" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F174" s="11" t="n">
+        <v>470</v>
+      </c>
+      <c r="G174" s="12" t="inlineStr">
+        <is>
+          <t>풍요의 영약 x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="13" t="n"/>
+      <c r="B175" s="11" t="n">
+        <v>14013</v>
+      </c>
+      <c r="C175" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="D175" s="11" t="n">
+        <v>100046</v>
+      </c>
+      <c r="E175" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F175" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="G175" s="12" t="inlineStr">
+        <is>
+          <t>망각의 묘약 x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="13" t="n"/>
+      <c r="B176" s="11" t="n">
+        <v>17009</v>
+      </c>
+      <c r="C176" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="D176" s="11" t="n">
+        <v>100042</v>
+      </c>
+      <c r="E176" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F176" s="11" t="n">
+        <v>600</v>
+      </c>
+      <c r="G176" s="12" t="inlineStr">
+        <is>
+          <t>성장의 비약 (중) x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="13" t="n"/>
+      <c r="B177" s="11" t="n">
+        <v>17010</v>
+      </c>
+      <c r="C177" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="D177" s="11" t="n">
+        <v>100043</v>
+      </c>
+      <c r="E177" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F177" s="11" t="n">
+        <v>400</v>
+      </c>
+      <c r="G177" s="12" t="inlineStr">
+        <is>
+          <t>성장의 비약 (대) x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="13" t="n"/>
+      <c r="B178" s="11" t="n">
+        <v>17011</v>
+      </c>
+      <c r="C178" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="D178" s="11" t="n">
+        <v>100044</v>
+      </c>
+      <c r="E178" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F178" s="11" t="n">
+        <v>470</v>
+      </c>
+      <c r="G178" s="12" t="inlineStr">
+        <is>
+          <t>신속의 영약 x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="13" t="n"/>
+      <c r="B179" s="11" t="n">
+        <v>17012</v>
+      </c>
+      <c r="C179" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="D179" s="11" t="n">
+        <v>100045</v>
+      </c>
+      <c r="E179" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F179" s="11" t="n">
+        <v>470</v>
+      </c>
+      <c r="G179" s="12" t="inlineStr">
+        <is>
+          <t>풍요의 영약 x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="13" t="n"/>
+      <c r="B180" s="11" t="n">
+        <v>17013</v>
+      </c>
+      <c r="C180" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="D180" s="11" t="n">
+        <v>100046</v>
+      </c>
+      <c r="E180" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F180" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="G180" s="12" t="inlineStr">
+        <is>
+          <t>망각의 묘약 x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="13" t="n"/>
+      <c r="B181" s="11" t="n">
+        <v>20009</v>
+      </c>
+      <c r="C181" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="D181" s="11" t="n">
+        <v>100042</v>
+      </c>
+      <c r="E181" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F181" s="11" t="n">
+        <v>600</v>
+      </c>
+      <c r="G181" s="12" t="inlineStr">
+        <is>
+          <t>성장의 비약 (중) x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="13" t="n"/>
+      <c r="B182" s="11" t="n">
+        <v>20010</v>
+      </c>
+      <c r="C182" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="D182" s="11" t="n">
+        <v>100043</v>
+      </c>
+      <c r="E182" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F182" s="11" t="n">
+        <v>400</v>
+      </c>
+      <c r="G182" s="12" t="inlineStr">
+        <is>
+          <t>성장의 비약 (대) x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="13" t="n"/>
+      <c r="B183" s="11" t="n">
+        <v>20011</v>
+      </c>
+      <c r="C183" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="D183" s="11" t="n">
+        <v>100044</v>
+      </c>
+      <c r="E183" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F183" s="11" t="n">
+        <v>470</v>
+      </c>
+      <c r="G183" s="12" t="inlineStr">
+        <is>
+          <t>신속의 영약 x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="13" t="n"/>
+      <c r="B184" s="11" t="n">
+        <v>20012</v>
+      </c>
+      <c r="C184" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="D184" s="11" t="n">
+        <v>100045</v>
+      </c>
+      <c r="E184" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F184" s="11" t="n">
+        <v>470</v>
+      </c>
+      <c r="G184" s="12" t="inlineStr">
+        <is>
+          <t>풍요의 영약 x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="13" t="n"/>
+      <c r="B185" s="11" t="n">
+        <v>20013</v>
+      </c>
+      <c r="C185" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="D185" s="11" t="n">
+        <v>100046</v>
+      </c>
+      <c r="E185" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F185" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="G185" s="12" t="inlineStr">
+        <is>
+          <t>망각의 묘약 x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="13" t="n"/>
+      <c r="B186" s="11" t="n">
+        <v>23009</v>
+      </c>
+      <c r="C186" s="11" t="n">
+        <v>23</v>
+      </c>
+      <c r="D186" s="11" t="n">
+        <v>100042</v>
+      </c>
+      <c r="E186" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F186" s="11" t="n">
+        <v>600</v>
+      </c>
+      <c r="G186" s="12" t="inlineStr">
+        <is>
+          <t>성장의 비약 (중) x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="13" t="n"/>
+      <c r="B187" s="11" t="n">
+        <v>23010</v>
+      </c>
+      <c r="C187" s="11" t="n">
+        <v>23</v>
+      </c>
+      <c r="D187" s="11" t="n">
+        <v>100043</v>
+      </c>
+      <c r="E187" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F187" s="11" t="n">
+        <v>400</v>
+      </c>
+      <c r="G187" s="12" t="inlineStr">
+        <is>
+          <t>성장의 비약 (대) x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="13" t="n"/>
+      <c r="B188" s="11" t="n">
+        <v>23011</v>
+      </c>
+      <c r="C188" s="11" t="n">
+        <v>23</v>
+      </c>
+      <c r="D188" s="11" t="n">
+        <v>100044</v>
+      </c>
+      <c r="E188" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F188" s="11" t="n">
+        <v>470</v>
+      </c>
+      <c r="G188" s="12" t="inlineStr">
+        <is>
+          <t>신속의 영약 x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="13" t="n"/>
+      <c r="B189" s="11" t="n">
+        <v>23012</v>
+      </c>
+      <c r="C189" s="11" t="n">
+        <v>23</v>
+      </c>
+      <c r="D189" s="11" t="n">
+        <v>100045</v>
+      </c>
+      <c r="E189" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F189" s="11" t="n">
+        <v>470</v>
+      </c>
+      <c r="G189" s="12" t="inlineStr">
+        <is>
+          <t>풍요의 영약 x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="13" t="n"/>
+      <c r="B190" s="11" t="n">
+        <v>23013</v>
+      </c>
+      <c r="C190" s="11" t="n">
+        <v>23</v>
+      </c>
+      <c r="D190" s="11" t="n">
+        <v>100046</v>
+      </c>
+      <c r="E190" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F190" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="G190" s="12" t="inlineStr">
+        <is>
+          <t>망각의 묘약 x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="13" t="n"/>
+      <c r="B191" s="11" t="n">
+        <v>24001</v>
+      </c>
+      <c r="C191" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="D191" s="11" t="n">
+        <v>100015</v>
+      </c>
+      <c r="E191" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="F191" s="11" t="n">
+        <v>3500</v>
+      </c>
+      <c r="G191" s="12" t="inlineStr">
+        <is>
+          <t>인챈트 큐브 묶음 x5</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="13" t="n"/>
+      <c r="B192" s="11" t="n">
+        <v>24002</v>
+      </c>
+      <c r="C192" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="D192" s="11" t="n">
+        <v>100018</v>
+      </c>
+      <c r="E192" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F192" s="11" t="n">
+        <v>2500</v>
+      </c>
+      <c r="G192" s="12" t="inlineStr">
+        <is>
+          <t>상급 인챈트 큐브 묶음 x3</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="13" t="n"/>
+      <c r="B193" s="11" t="n">
+        <v>24003</v>
+      </c>
+      <c r="C193" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="D193" s="11" t="n">
+        <v>100043</v>
+      </c>
+      <c r="E193" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F193" s="11" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G193" s="12" t="inlineStr">
+        <is>
+          <t>성장의 비약 (대) 묶음 x2</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="13" t="n"/>
+      <c r="B194" s="11" t="n">
+        <v>24004</v>
+      </c>
+      <c r="C194" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="D194" s="11" t="n">
+        <v>100046</v>
+      </c>
+      <c r="E194" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F194" s="11" t="n">
+        <v>500</v>
+      </c>
+      <c r="G194" s="12" t="inlineStr">
+        <is>
+          <t>망각의 묘약 x1</t>
         </is>
       </c>
     </row>
@@ -3608,7 +5080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -3617,7 +5089,7 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="33" customWidth="1" min="7" max="7"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4357,6 +5829,33 @@
       <c r="G28" s="12" t="inlineStr">
         <is>
           <t>상자 전용 — 골드로 뽑을 수 없다</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="13" t="n"/>
+      <c r="B29" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>비밀 금고</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E29" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="12" t="inlineStr">
+        <is>
+          <t>황금 열쇠 전용 — 골드로 뽑을 수 없다</t>
         </is>
       </c>
     </row>
@@ -5307,7 +6806,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G248"/>
+  <dimension ref="A1:G270"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -11034,6 +12533,512 @@
       <c r="G248" s="12" t="inlineStr">
         <is>
           <t>Mythic 월광 성석</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="13" t="n"/>
+      <c r="B249" s="11" t="n">
+        <v>24101</v>
+      </c>
+      <c r="C249" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="D249" s="11" t="n">
+        <v>1104</v>
+      </c>
+      <c r="E249" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F249" s="11" t="n">
+        <v>69</v>
+      </c>
+      <c r="G249" s="12" t="inlineStr">
+        <is>
+          <t>Epic 은빛 쟁기</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="13" t="n"/>
+      <c r="B250" s="11" t="n">
+        <v>24102</v>
+      </c>
+      <c r="C250" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="D250" s="11" t="n">
+        <v>1204</v>
+      </c>
+      <c r="E250" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F250" s="11" t="n">
+        <v>69</v>
+      </c>
+      <c r="G250" s="12" t="inlineStr">
+        <is>
+          <t>Epic 심해 작살</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="13" t="n"/>
+      <c r="B251" s="11" t="n">
+        <v>24103</v>
+      </c>
+      <c r="C251" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="D251" s="11" t="n">
+        <v>1304</v>
+      </c>
+      <c r="E251" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F251" s="11" t="n">
+        <v>69</v>
+      </c>
+      <c r="G251" s="12" t="inlineStr">
+        <is>
+          <t>Epic 흑요석 곡괭이</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="13" t="n"/>
+      <c r="B252" s="11" t="n">
+        <v>24104</v>
+      </c>
+      <c r="C252" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="D252" s="11" t="n">
+        <v>1404</v>
+      </c>
+      <c r="E252" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F252" s="11" t="n">
+        <v>69</v>
+      </c>
+      <c r="G252" s="12" t="inlineStr">
+        <is>
+          <t>Epic 백년목 도끼</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="13" t="n"/>
+      <c r="B253" s="11" t="n">
+        <v>24105</v>
+      </c>
+      <c r="C253" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="D253" s="11" t="n">
+        <v>1504</v>
+      </c>
+      <c r="E253" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F253" s="11" t="n">
+        <v>68</v>
+      </c>
+      <c r="G253" s="12" t="inlineStr">
+        <is>
+          <t>Epic 은빛 장궁</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="13" t="n"/>
+      <c r="B254" s="11" t="n">
+        <v>24106</v>
+      </c>
+      <c r="C254" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="D254" s="11" t="n">
+        <v>2005</v>
+      </c>
+      <c r="E254" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F254" s="11" t="n">
+        <v>68</v>
+      </c>
+      <c r="G254" s="12" t="inlineStr">
+        <is>
+          <t>Epic 장인의 인장</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="13" t="n"/>
+      <c r="B255" s="11" t="n">
+        <v>24107</v>
+      </c>
+      <c r="C255" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="D255" s="11" t="n">
+        <v>3104</v>
+      </c>
+      <c r="E255" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F255" s="11" t="n">
+        <v>68</v>
+      </c>
+      <c r="G255" s="12" t="inlineStr">
+        <is>
+          <t>Epic 황금 이삭석</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="13" t="n"/>
+      <c r="B256" s="11" t="n">
+        <v>24108</v>
+      </c>
+      <c r="C256" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="D256" s="11" t="n">
+        <v>3204</v>
+      </c>
+      <c r="E256" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F256" s="11" t="n">
+        <v>68</v>
+      </c>
+      <c r="G256" s="12" t="inlineStr">
+        <is>
+          <t>Epic 산호 진주</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="13" t="n"/>
+      <c r="B257" s="11" t="n">
+        <v>24109</v>
+      </c>
+      <c r="C257" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="D257" s="11" t="n">
+        <v>3304</v>
+      </c>
+      <c r="E257" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F257" s="11" t="n">
+        <v>68</v>
+      </c>
+      <c r="G257" s="12" t="inlineStr">
+        <is>
+          <t>Epic 용암 결정</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="13" t="n"/>
+      <c r="B258" s="11" t="n">
+        <v>24110</v>
+      </c>
+      <c r="C258" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="D258" s="11" t="n">
+        <v>3404</v>
+      </c>
+      <c r="E258" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F258" s="11" t="n">
+        <v>68</v>
+      </c>
+      <c r="G258" s="12" t="inlineStr">
+        <is>
+          <t>Epic 백년목 결정</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="13" t="n"/>
+      <c r="B259" s="11" t="n">
+        <v>24111</v>
+      </c>
+      <c r="C259" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="D259" s="11" t="n">
+        <v>3504</v>
+      </c>
+      <c r="E259" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F259" s="11" t="n">
+        <v>68</v>
+      </c>
+      <c r="G259" s="12" t="inlineStr">
+        <is>
+          <t>Epic 사냥꾼의 별</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="13" t="n"/>
+      <c r="B260" s="11" t="n">
+        <v>24112</v>
+      </c>
+      <c r="C260" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="D260" s="11" t="n">
+        <v>1105</v>
+      </c>
+      <c r="E260" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F260" s="11" t="n">
+        <v>68</v>
+      </c>
+      <c r="G260" s="12" t="inlineStr">
+        <is>
+          <t>Legendary 풍년의 괭이</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="13" t="n"/>
+      <c r="B261" s="11" t="n">
+        <v>24113</v>
+      </c>
+      <c r="C261" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="D261" s="11" t="n">
+        <v>1205</v>
+      </c>
+      <c r="E261" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F261" s="11" t="n">
+        <v>68</v>
+      </c>
+      <c r="G261" s="12" t="inlineStr">
+        <is>
+          <t>Legendary 용린 낚싯대</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="13" t="n"/>
+      <c r="B262" s="11" t="n">
+        <v>24114</v>
+      </c>
+      <c r="C262" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="D262" s="11" t="n">
+        <v>1305</v>
+      </c>
+      <c r="E262" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F262" s="11" t="n">
+        <v>68</v>
+      </c>
+      <c r="G262" s="12" t="inlineStr">
+        <is>
+          <t>Legendary 미스릴 곡괭이</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="13" t="n"/>
+      <c r="B263" s="11" t="n">
+        <v>24115</v>
+      </c>
+      <c r="C263" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="D263" s="11" t="n">
+        <v>1405</v>
+      </c>
+      <c r="E263" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F263" s="11" t="n">
+        <v>68</v>
+      </c>
+      <c r="G263" s="12" t="inlineStr">
+        <is>
+          <t>Legendary 서리강철 도끼</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="13" t="n"/>
+      <c r="B264" s="11" t="n">
+        <v>24116</v>
+      </c>
+      <c r="C264" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="D264" s="11" t="n">
+        <v>1505</v>
+      </c>
+      <c r="E264" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F264" s="11" t="n">
+        <v>68</v>
+      </c>
+      <c r="G264" s="12" t="inlineStr">
+        <is>
+          <t>Legendary 폭풍의 장궁</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="13" t="n"/>
+      <c r="B265" s="11" t="n">
+        <v>24117</v>
+      </c>
+      <c r="C265" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="D265" s="11" t="n">
+        <v>2006</v>
+      </c>
+      <c r="E265" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F265" s="11" t="n">
+        <v>68</v>
+      </c>
+      <c r="G265" s="12" t="inlineStr">
+        <is>
+          <t>Legendary 대장인의 훈장</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="13" t="n"/>
+      <c r="B266" s="11" t="n">
+        <v>24118</v>
+      </c>
+      <c r="C266" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="D266" s="11" t="n">
+        <v>3105</v>
+      </c>
+      <c r="E266" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F266" s="11" t="n">
+        <v>68</v>
+      </c>
+      <c r="G266" s="12" t="inlineStr">
+        <is>
+          <t>Legendary 대지의 심장</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="13" t="n"/>
+      <c r="B267" s="11" t="n">
+        <v>24119</v>
+      </c>
+      <c r="C267" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="D267" s="11" t="n">
+        <v>3205</v>
+      </c>
+      <c r="E267" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F267" s="11" t="n">
+        <v>68</v>
+      </c>
+      <c r="G267" s="12" t="inlineStr">
+        <is>
+          <t>Legendary 바다의 심장</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="13" t="n"/>
+      <c r="B268" s="11" t="n">
+        <v>24120</v>
+      </c>
+      <c r="C268" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="D268" s="11" t="n">
+        <v>3305</v>
+      </c>
+      <c r="E268" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F268" s="11" t="n">
+        <v>68</v>
+      </c>
+      <c r="G268" s="12" t="inlineStr">
+        <is>
+          <t>Legendary 대지핵 결정</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="13" t="n"/>
+      <c r="B269" s="11" t="n">
+        <v>24121</v>
+      </c>
+      <c r="C269" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="D269" s="11" t="n">
+        <v>3405</v>
+      </c>
+      <c r="E269" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F269" s="11" t="n">
+        <v>68</v>
+      </c>
+      <c r="G269" s="12" t="inlineStr">
+        <is>
+          <t>Legendary 숲의 심장</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="13" t="n"/>
+      <c r="B270" s="11" t="n">
+        <v>24122</v>
+      </c>
+      <c r="C270" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="D270" s="11" t="n">
+        <v>3505</v>
+      </c>
+      <c r="E270" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F270" s="11" t="n">
+        <v>68</v>
+      </c>
+      <c r="G270" s="12" t="inlineStr">
+        <is>
+          <t>Legendary 야수의 심장</t>
         </is>
       </c>
     </row>
@@ -11295,7 +13300,7 @@
         <v>271</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>3000</v>
+        <v>2250</v>
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
@@ -11318,7 +13323,7 @@
         <v>677</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>1000</v>
+        <v>750</v>
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
@@ -11341,7 +13346,7 @@
         <v>813</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>3000</v>
+        <v>2250</v>
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
@@ -11364,7 +13369,7 @@
         <v>2032</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>1000</v>
+        <v>750</v>
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
@@ -11387,7 +13392,7 @@
         <v>2709</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>3000</v>
+        <v>2250</v>
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
@@ -11410,7 +13415,7 @@
         <v>6772</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>1000</v>
+        <v>750</v>
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
@@ -11433,7 +13438,7 @@
         <v>813</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>3000</v>
+        <v>2250</v>
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
@@ -11456,7 +13461,7 @@
         <v>2032</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>1000</v>
+        <v>750</v>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
@@ -11479,7 +13484,7 @@
         <v>2438</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>3000</v>
+        <v>2250</v>
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
@@ -11502,7 +13507,7 @@
         <v>6095</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>1000</v>
+        <v>750</v>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
@@ -11525,7 +13530,7 @@
         <v>8127</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>3000</v>
+        <v>2250</v>
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
@@ -11548,7 +13553,7 @@
         <v>20318</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>1000</v>
+        <v>750</v>
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
@@ -11571,7 +13576,7 @@
         <v>2438</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>3000</v>
+        <v>2250</v>
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
@@ -11594,7 +13599,7 @@
         <v>6095</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>1000</v>
+        <v>750</v>
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
@@ -11617,7 +13622,7 @@
         <v>7314</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>3000</v>
+        <v>2250</v>
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
@@ -11640,7 +13645,7 @@
         <v>18286</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>1000</v>
+        <v>750</v>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
@@ -11663,7 +13668,7 @@
         <v>24381</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>3000</v>
+        <v>2250</v>
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
@@ -11686,7 +13691,7 @@
         <v>60952</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>1000</v>
+        <v>750</v>
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
@@ -11709,7 +13714,7 @@
         <v>7314</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>3000</v>
+        <v>2250</v>
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
@@ -11732,7 +13737,7 @@
         <v>18286</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>1000</v>
+        <v>750</v>
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
@@ -11755,7 +13760,7 @@
         <v>21943</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>3000</v>
+        <v>2250</v>
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
@@ -11778,7 +13783,7 @@
         <v>54857</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>1000</v>
+        <v>750</v>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
@@ -11801,7 +13806,7 @@
         <v>73143</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>3000</v>
+        <v>2250</v>
       </c>
       <c r="G32" s="12" t="inlineStr">
         <is>
@@ -11824,7 +13829,7 @@
         <v>182858</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>1000</v>
+        <v>750</v>
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
@@ -11847,7 +13852,7 @@
         <v>21943</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>3000</v>
+        <v>2250</v>
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
@@ -11870,7 +13875,7 @@
         <v>54857</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>1000</v>
+        <v>750</v>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
@@ -11893,7 +13898,7 @@
         <v>65829</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>3000</v>
+        <v>2250</v>
       </c>
       <c r="G36" s="12" t="inlineStr">
         <is>
@@ -11916,7 +13921,7 @@
         <v>164572</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>1000</v>
+        <v>750</v>
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
@@ -11939,7 +13944,7 @@
         <v>219429</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>3000</v>
+        <v>2250</v>
       </c>
       <c r="G38" s="12" t="inlineStr">
         <is>
@@ -11962,7 +13967,7 @@
         <v>548572</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>1000</v>
+        <v>750</v>
       </c>
       <c r="G39" s="12" t="inlineStr">
         <is>

--- a/GameDesign/Excel/Gacha.xlsx
+++ b/GameDesign/Excel/Gacha.xlsx
@@ -12,6 +12,7 @@
     <sheet name="GachaCharacterTable" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="GachaEquipTable" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="GachaGoldTable" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="GachaArtifactTable" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -277,6 +278,21 @@
 </file>
 
 <file path=xl/comments/comment5.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>excel-table-creator</author>
+  </authors>
+  <commentList>
+    <comment ref="C2" authorId="0" shapeId="0">
+      <text>
+        <t>가챠 풀 ID (= GachaInfoTID)</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment6.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>excel-table-creator</author>
@@ -580,7 +596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G194"/>
+  <dimension ref="A1:G282"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -589,7 +605,7 @@
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="26" customWidth="1" min="7" max="7"/>
+    <col width="45" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5065,6 +5081,2030 @@
       <c r="G194" s="12" t="inlineStr">
         <is>
           <t>망각의 묘약 x1</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="13" t="n"/>
+      <c r="B195" s="11" t="n">
+        <v>25001</v>
+      </c>
+      <c r="C195" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="D195" s="11" t="n">
+        <v>10001</v>
+      </c>
+      <c r="E195" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="F195" s="11" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G195" s="12" t="inlineStr">
+        <is>
+          <t>자원 깨진 토기 조각 x27 (감정 · 풀 9에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="13" t="n"/>
+      <c r="B196" s="11" t="n">
+        <v>25002</v>
+      </c>
+      <c r="C196" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="D196" s="11" t="n">
+        <v>20001</v>
+      </c>
+      <c r="E196" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="F196" s="11" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G196" s="12" t="inlineStr">
+        <is>
+          <t>자원 밀 x27 (감정 · 풀 9에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="13" t="n"/>
+      <c r="B197" s="11" t="n">
+        <v>25003</v>
+      </c>
+      <c r="C197" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="D197" s="11" t="n">
+        <v>30001</v>
+      </c>
+      <c r="E197" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="F197" s="11" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G197" s="12" t="inlineStr">
+        <is>
+          <t>자원 잡목 x27 (감정 · 풀 9에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="13" t="n"/>
+      <c r="B198" s="11" t="n">
+        <v>25004</v>
+      </c>
+      <c r="C198" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="D198" s="11" t="n">
+        <v>40001</v>
+      </c>
+      <c r="E198" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="F198" s="11" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G198" s="12" t="inlineStr">
+        <is>
+          <t>자원 돌덩어리 x27 (감정 · 풀 9에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="13" t="n"/>
+      <c r="B199" s="11" t="n">
+        <v>25005</v>
+      </c>
+      <c r="C199" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="D199" s="11" t="n">
+        <v>50001</v>
+      </c>
+      <c r="E199" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="F199" s="11" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G199" s="12" t="inlineStr">
+        <is>
+          <t>자원 질긴 고기 x27 (감정 · 풀 9에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="13" t="n"/>
+      <c r="B200" s="11" t="n">
+        <v>25006</v>
+      </c>
+      <c r="C200" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="D200" s="11" t="n">
+        <v>100010</v>
+      </c>
+      <c r="E200" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F200" s="11" t="n">
+        <v>2100</v>
+      </c>
+      <c r="G200" s="12" t="inlineStr">
+        <is>
+          <t>상자 전용 낡은 보물 지도 (감정 · 풀 9에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="13" t="n"/>
+      <c r="B201" s="11" t="n">
+        <v>25007</v>
+      </c>
+      <c r="C201" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="D201" s="11" t="n">
+        <v>100015</v>
+      </c>
+      <c r="E201" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F201" s="11" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G201" s="12" t="inlineStr">
+        <is>
+          <t>인챈트 큐브 x1 (감정 · 풀 9에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="13" t="n"/>
+      <c r="B202" s="11" t="n">
+        <v>25008</v>
+      </c>
+      <c r="C202" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="D202" s="11" t="n">
+        <v>100041</v>
+      </c>
+      <c r="E202" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F202" s="11" t="n">
+        <v>20000</v>
+      </c>
+      <c r="G202" s="12" t="inlineStr">
+        <is>
+          <t>성장의 비약 (소) x1 (감정 · 풀 9에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="13" t="n"/>
+      <c r="B203" s="11" t="n">
+        <v>25009</v>
+      </c>
+      <c r="C203" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="D203" s="11" t="n">
+        <v>100044</v>
+      </c>
+      <c r="E203" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F203" s="11" t="n">
+        <v>1950</v>
+      </c>
+      <c r="G203" s="12" t="inlineStr">
+        <is>
+          <t>신속의 영약 x1 (감정 · 풀 9에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="13" t="n"/>
+      <c r="B204" s="11" t="n">
+        <v>25010</v>
+      </c>
+      <c r="C204" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="D204" s="11" t="n">
+        <v>100045</v>
+      </c>
+      <c r="E204" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F204" s="11" t="n">
+        <v>1950</v>
+      </c>
+      <c r="G204" s="12" t="inlineStr">
+        <is>
+          <t>풍요의 영약 x1 (감정 · 풀 9에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="13" t="n"/>
+      <c r="B205" s="11" t="n">
+        <v>25099</v>
+      </c>
+      <c r="C205" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="D205" s="11" t="n">
+        <v>100067</v>
+      </c>
+      <c r="E205" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F205" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="G205" s="12" t="inlineStr">
+        <is>
+          <t>Special 미감정 유물 — 약 0.02% (테스트값)</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="13" t="n"/>
+      <c r="B206" s="11" t="n">
+        <v>26001</v>
+      </c>
+      <c r="C206" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="D206" s="11" t="n">
+        <v>10012</v>
+      </c>
+      <c r="E206" s="11" t="n">
+        <v>33</v>
+      </c>
+      <c r="F206" s="11" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G206" s="12" t="inlineStr">
+        <is>
+          <t>자원 녹슨 투구 x33 (감정 · 풀 13에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="13" t="n"/>
+      <c r="B207" s="11" t="n">
+        <v>26002</v>
+      </c>
+      <c r="C207" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="D207" s="11" t="n">
+        <v>20012</v>
+      </c>
+      <c r="E207" s="11" t="n">
+        <v>33</v>
+      </c>
+      <c r="F207" s="11" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G207" s="12" t="inlineStr">
+        <is>
+          <t>자원 고구마 x33 (감정 · 풀 13에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="13" t="n"/>
+      <c r="B208" s="11" t="n">
+        <v>26003</v>
+      </c>
+      <c r="C208" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="D208" s="11" t="n">
+        <v>30012</v>
+      </c>
+      <c r="E208" s="11" t="n">
+        <v>33</v>
+      </c>
+      <c r="F208" s="11" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G208" s="12" t="inlineStr">
+        <is>
+          <t>자원 삼나무 목재 x33 (감정 · 풀 13에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="13" t="n"/>
+      <c r="B209" s="11" t="n">
+        <v>26004</v>
+      </c>
+      <c r="C209" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="D209" s="11" t="n">
+        <v>40012</v>
+      </c>
+      <c r="E209" s="11" t="n">
+        <v>33</v>
+      </c>
+      <c r="F209" s="11" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G209" s="12" t="inlineStr">
+        <is>
+          <t>자원 주석 광석 x33 (감정 · 풀 13에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="13" t="n"/>
+      <c r="B210" s="11" t="n">
+        <v>26005</v>
+      </c>
+      <c r="C210" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="D210" s="11" t="n">
+        <v>50012</v>
+      </c>
+      <c r="E210" s="11" t="n">
+        <v>33</v>
+      </c>
+      <c r="F210" s="11" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G210" s="12" t="inlineStr">
+        <is>
+          <t>자원 멧돼지 엄니 x33 (감정 · 풀 13에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="13" t="n"/>
+      <c r="B211" s="11" t="n">
+        <v>26006</v>
+      </c>
+      <c r="C211" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="D211" s="11" t="n">
+        <v>100011</v>
+      </c>
+      <c r="E211" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F211" s="11" t="n">
+        <v>2100</v>
+      </c>
+      <c r="G211" s="12" t="inlineStr">
+        <is>
+          <t>상자 전용 은빛 나침반 (감정 · 풀 13에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="13" t="n"/>
+      <c r="B212" s="11" t="n">
+        <v>26007</v>
+      </c>
+      <c r="C212" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="D212" s="11" t="n">
+        <v>100015</v>
+      </c>
+      <c r="E212" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F212" s="11" t="n">
+        <v>4000</v>
+      </c>
+      <c r="G212" s="12" t="inlineStr">
+        <is>
+          <t>인챈트 큐브 x2 (감정 · 풀 13에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="13" t="n"/>
+      <c r="B213" s="11" t="n">
+        <v>26008</v>
+      </c>
+      <c r="C213" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="D213" s="11" t="n">
+        <v>100018</v>
+      </c>
+      <c r="E213" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F213" s="11" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G213" s="12" t="inlineStr">
+        <is>
+          <t>상급 인챈트 큐브 x2 (감정 · 풀 13에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="13" t="n"/>
+      <c r="B214" s="11" t="n">
+        <v>26009</v>
+      </c>
+      <c r="C214" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="D214" s="11" t="n">
+        <v>100041</v>
+      </c>
+      <c r="E214" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F214" s="11" t="n">
+        <v>8000</v>
+      </c>
+      <c r="G214" s="12" t="inlineStr">
+        <is>
+          <t>성장의 비약 (소) x1 (감정 · 풀 13에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="13" t="n"/>
+      <c r="B215" s="11" t="n">
+        <v>26010</v>
+      </c>
+      <c r="C215" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="D215" s="11" t="n">
+        <v>100042</v>
+      </c>
+      <c r="E215" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F215" s="11" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G215" s="12" t="inlineStr">
+        <is>
+          <t>성장의 비약 (중) x1 (감정 · 풀 13에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="13" t="n"/>
+      <c r="B216" s="11" t="n">
+        <v>26011</v>
+      </c>
+      <c r="C216" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="D216" s="11" t="n">
+        <v>100044</v>
+      </c>
+      <c r="E216" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F216" s="11" t="n">
+        <v>4950</v>
+      </c>
+      <c r="G216" s="12" t="inlineStr">
+        <is>
+          <t>신속의 영약 x1 (감정 · 풀 13에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="13" t="n"/>
+      <c r="B217" s="11" t="n">
+        <v>26012</v>
+      </c>
+      <c r="C217" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="D217" s="11" t="n">
+        <v>100045</v>
+      </c>
+      <c r="E217" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F217" s="11" t="n">
+        <v>4950</v>
+      </c>
+      <c r="G217" s="12" t="inlineStr">
+        <is>
+          <t>풍요의 영약 x1 (감정 · 풀 13에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="13" t="n"/>
+      <c r="B218" s="11" t="n">
+        <v>26099</v>
+      </c>
+      <c r="C218" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="D218" s="11" t="n">
+        <v>100067</v>
+      </c>
+      <c r="E218" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F218" s="11" t="n">
+        <v>63</v>
+      </c>
+      <c r="G218" s="12" t="inlineStr">
+        <is>
+          <t>Special 미감정 유물 — 약 0.06% (테스트값)</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="13" t="n"/>
+      <c r="B219" s="11" t="n">
+        <v>27001</v>
+      </c>
+      <c r="C219" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="D219" s="11" t="n">
+        <v>10023</v>
+      </c>
+      <c r="E219" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="F219" s="11" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G219" s="12" t="inlineStr">
+        <is>
+          <t>자원 신전 촛대 x45 (감정 · 풀 17에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="13" t="n"/>
+      <c r="B220" s="11" t="n">
+        <v>27002</v>
+      </c>
+      <c r="C220" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="D220" s="11" t="n">
+        <v>20023</v>
+      </c>
+      <c r="E220" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="F220" s="11" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G220" s="12" t="inlineStr">
+        <is>
+          <t>자원 딸기 x45 (감정 · 풀 17에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="13" t="n"/>
+      <c r="B221" s="11" t="n">
+        <v>27003</v>
+      </c>
+      <c r="C221" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="D221" s="11" t="n">
+        <v>30023</v>
+      </c>
+      <c r="E221" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="F221" s="11" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G221" s="12" t="inlineStr">
+        <is>
+          <t>자원 단풍나무 목재 x45 (감정 · 풀 17에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="13" t="n"/>
+      <c r="B222" s="11" t="n">
+        <v>27004</v>
+      </c>
+      <c r="C222" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="D222" s="11" t="n">
+        <v>40023</v>
+      </c>
+      <c r="E222" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="F222" s="11" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G222" s="12" t="inlineStr">
+        <is>
+          <t>자원 미스릴 광석 x45 (감정 · 풀 17에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="13" t="n"/>
+      <c r="B223" s="11" t="n">
+        <v>27005</v>
+      </c>
+      <c r="C223" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="D223" s="11" t="n">
+        <v>50023</v>
+      </c>
+      <c r="E223" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="F223" s="11" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G223" s="12" t="inlineStr">
+        <is>
+          <t>자원 곰의 이빨 x45 (감정 · 풀 17에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="13" t="n"/>
+      <c r="B224" s="11" t="n">
+        <v>27006</v>
+      </c>
+      <c r="C224" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="D224" s="11" t="n">
+        <v>100015</v>
+      </c>
+      <c r="E224" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F224" s="11" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G224" s="12" t="inlineStr">
+        <is>
+          <t>인챈트 큐브 x3 (감정 · 풀 17에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="13" t="n"/>
+      <c r="B225" s="11" t="n">
+        <v>27007</v>
+      </c>
+      <c r="C225" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="D225" s="11" t="n">
+        <v>100018</v>
+      </c>
+      <c r="E225" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F225" s="11" t="n">
+        <v>4000</v>
+      </c>
+      <c r="G225" s="12" t="inlineStr">
+        <is>
+          <t>상급 인챈트 큐브 x3 (감정 · 풀 17에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="13" t="n"/>
+      <c r="B226" s="11" t="n">
+        <v>27008</v>
+      </c>
+      <c r="C226" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="D226" s="11" t="n">
+        <v>100042</v>
+      </c>
+      <c r="E226" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F226" s="11" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G226" s="12" t="inlineStr">
+        <is>
+          <t>성장의 비약 (중) x1 (감정 · 풀 17에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="13" t="n"/>
+      <c r="B227" s="11" t="n">
+        <v>27009</v>
+      </c>
+      <c r="C227" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="D227" s="11" t="n">
+        <v>100043</v>
+      </c>
+      <c r="E227" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F227" s="11" t="n">
+        <v>4000</v>
+      </c>
+      <c r="G227" s="12" t="inlineStr">
+        <is>
+          <t>성장의 비약 (대) x1 (감정 · 풀 17에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="13" t="n"/>
+      <c r="B228" s="11" t="n">
+        <v>27010</v>
+      </c>
+      <c r="C228" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="D228" s="11" t="n">
+        <v>100044</v>
+      </c>
+      <c r="E228" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F228" s="11" t="n">
+        <v>4700</v>
+      </c>
+      <c r="G228" s="12" t="inlineStr">
+        <is>
+          <t>신속의 영약 x1 (감정 · 풀 17에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="13" t="n"/>
+      <c r="B229" s="11" t="n">
+        <v>27011</v>
+      </c>
+      <c r="C229" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="D229" s="11" t="n">
+        <v>100045</v>
+      </c>
+      <c r="E229" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F229" s="11" t="n">
+        <v>4700</v>
+      </c>
+      <c r="G229" s="12" t="inlineStr">
+        <is>
+          <t>풍요의 영약 x1 (감정 · 풀 17에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="13" t="n"/>
+      <c r="B230" s="11" t="n">
+        <v>27012</v>
+      </c>
+      <c r="C230" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="D230" s="11" t="n">
+        <v>100046</v>
+      </c>
+      <c r="E230" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F230" s="11" t="n">
+        <v>500</v>
+      </c>
+      <c r="G230" s="12" t="inlineStr">
+        <is>
+          <t>망각의 묘약 x1 (감정 · 풀 17에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="13" t="n"/>
+      <c r="B231" s="11" t="n">
+        <v>27099</v>
+      </c>
+      <c r="C231" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="D231" s="11" t="n">
+        <v>100067</v>
+      </c>
+      <c r="E231" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F231" s="11" t="n">
+        <v>176</v>
+      </c>
+      <c r="G231" s="12" t="inlineStr">
+        <is>
+          <t>Special 미감정 유물 — 약 0.18% (테스트값)</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="13" t="n"/>
+      <c r="B232" s="11" t="n">
+        <v>28001</v>
+      </c>
+      <c r="C232" s="11" t="n">
+        <v>28</v>
+      </c>
+      <c r="D232" s="11" t="n">
+        <v>10033</v>
+      </c>
+      <c r="E232" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="F232" s="11" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G232" s="12" t="inlineStr">
+        <is>
+          <t>자원 묘실 등잔 x45 (감정 · 풀 20에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="13" t="n"/>
+      <c r="B233" s="11" t="n">
+        <v>28002</v>
+      </c>
+      <c r="C233" s="11" t="n">
+        <v>28</v>
+      </c>
+      <c r="D233" s="11" t="n">
+        <v>20033</v>
+      </c>
+      <c r="E233" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="F233" s="11" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G233" s="12" t="inlineStr">
+        <is>
+          <t>자원 커피 열매 x45 (감정 · 풀 20에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="13" t="n"/>
+      <c r="B234" s="11" t="n">
+        <v>28003</v>
+      </c>
+      <c r="C234" s="11" t="n">
+        <v>28</v>
+      </c>
+      <c r="D234" s="11" t="n">
+        <v>30033</v>
+      </c>
+      <c r="E234" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="F234" s="11" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G234" s="12" t="inlineStr">
+        <is>
+          <t>자원 자단 목재 x45 (감정 · 풀 20에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="13" t="n"/>
+      <c r="B235" s="11" t="n">
+        <v>28004</v>
+      </c>
+      <c r="C235" s="11" t="n">
+        <v>28</v>
+      </c>
+      <c r="D235" s="11" t="n">
+        <v>40033</v>
+      </c>
+      <c r="E235" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="F235" s="11" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G235" s="12" t="inlineStr">
+        <is>
+          <t>자원 오리하르콘 광석 x45 (감정 · 풀 20에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="13" t="n"/>
+      <c r="B236" s="11" t="n">
+        <v>28005</v>
+      </c>
+      <c r="C236" s="11" t="n">
+        <v>28</v>
+      </c>
+      <c r="D236" s="11" t="n">
+        <v>50033</v>
+      </c>
+      <c r="E236" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="F236" s="11" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G236" s="12" t="inlineStr">
+        <is>
+          <t>자원 서리곰 모피 x45 (감정 · 풀 20에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="13" t="n"/>
+      <c r="B237" s="11" t="n">
+        <v>28006</v>
+      </c>
+      <c r="C237" s="11" t="n">
+        <v>28</v>
+      </c>
+      <c r="D237" s="11" t="n">
+        <v>100015</v>
+      </c>
+      <c r="E237" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="F237" s="11" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G237" s="12" t="inlineStr">
+        <is>
+          <t>인챈트 큐브 x4 (감정 · 풀 20에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="13" t="n"/>
+      <c r="B238" s="11" t="n">
+        <v>28007</v>
+      </c>
+      <c r="C238" s="11" t="n">
+        <v>28</v>
+      </c>
+      <c r="D238" s="11" t="n">
+        <v>100018</v>
+      </c>
+      <c r="E238" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="F238" s="11" t="n">
+        <v>4000</v>
+      </c>
+      <c r="G238" s="12" t="inlineStr">
+        <is>
+          <t>상급 인챈트 큐브 x4 (감정 · 풀 20에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="13" t="n"/>
+      <c r="B239" s="11" t="n">
+        <v>28008</v>
+      </c>
+      <c r="C239" s="11" t="n">
+        <v>28</v>
+      </c>
+      <c r="D239" s="11" t="n">
+        <v>100042</v>
+      </c>
+      <c r="E239" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F239" s="11" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G239" s="12" t="inlineStr">
+        <is>
+          <t>성장의 비약 (중) x1 (감정 · 풀 20에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="13" t="n"/>
+      <c r="B240" s="11" t="n">
+        <v>28009</v>
+      </c>
+      <c r="C240" s="11" t="n">
+        <v>28</v>
+      </c>
+      <c r="D240" s="11" t="n">
+        <v>100043</v>
+      </c>
+      <c r="E240" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F240" s="11" t="n">
+        <v>4000</v>
+      </c>
+      <c r="G240" s="12" t="inlineStr">
+        <is>
+          <t>성장의 비약 (대) x1 (감정 · 풀 20에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="13" t="n"/>
+      <c r="B241" s="11" t="n">
+        <v>28010</v>
+      </c>
+      <c r="C241" s="11" t="n">
+        <v>28</v>
+      </c>
+      <c r="D241" s="11" t="n">
+        <v>100044</v>
+      </c>
+      <c r="E241" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F241" s="11" t="n">
+        <v>4700</v>
+      </c>
+      <c r="G241" s="12" t="inlineStr">
+        <is>
+          <t>신속의 영약 x1 (감정 · 풀 20에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="13" t="n"/>
+      <c r="B242" s="11" t="n">
+        <v>28011</v>
+      </c>
+      <c r="C242" s="11" t="n">
+        <v>28</v>
+      </c>
+      <c r="D242" s="11" t="n">
+        <v>100045</v>
+      </c>
+      <c r="E242" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F242" s="11" t="n">
+        <v>4700</v>
+      </c>
+      <c r="G242" s="12" t="inlineStr">
+        <is>
+          <t>풍요의 영약 x1 (감정 · 풀 20에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="13" t="n"/>
+      <c r="B243" s="11" t="n">
+        <v>28012</v>
+      </c>
+      <c r="C243" s="11" t="n">
+        <v>28</v>
+      </c>
+      <c r="D243" s="11" t="n">
+        <v>100046</v>
+      </c>
+      <c r="E243" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F243" s="11" t="n">
+        <v>500</v>
+      </c>
+      <c r="G243" s="12" t="inlineStr">
+        <is>
+          <t>망각의 묘약 x1 (감정 · 풀 20에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="13" t="n"/>
+      <c r="B244" s="11" t="n">
+        <v>28099</v>
+      </c>
+      <c r="C244" s="11" t="n">
+        <v>28</v>
+      </c>
+      <c r="D244" s="11" t="n">
+        <v>100067</v>
+      </c>
+      <c r="E244" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F244" s="11" t="n">
+        <v>531</v>
+      </c>
+      <c r="G244" s="12" t="inlineStr">
+        <is>
+          <t>Special 미감정 유물 — 약 0.54% (테스트값)</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="13" t="n"/>
+      <c r="B245" s="11" t="n">
+        <v>29001</v>
+      </c>
+      <c r="C245" s="11" t="n">
+        <v>29</v>
+      </c>
+      <c r="D245" s="11" t="n">
+        <v>10043</v>
+      </c>
+      <c r="E245" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="F245" s="11" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G245" s="12" t="inlineStr">
+        <is>
+          <t>자원 왕실 문서 x45 (감정 · 풀 23에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="13" t="n"/>
+      <c r="B246" s="11" t="n">
+        <v>29002</v>
+      </c>
+      <c r="C246" s="11" t="n">
+        <v>29</v>
+      </c>
+      <c r="D246" s="11" t="n">
+        <v>20043</v>
+      </c>
+      <c r="E246" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="F246" s="11" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G246" s="12" t="inlineStr">
+        <is>
+          <t>자원 영약초 x45 (감정 · 풀 23에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="13" t="n"/>
+      <c r="B247" s="11" t="n">
+        <v>29003</v>
+      </c>
+      <c r="C247" s="11" t="n">
+        <v>29</v>
+      </c>
+      <c r="D247" s="11" t="n">
+        <v>30043</v>
+      </c>
+      <c r="E247" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="F247" s="11" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G247" s="12" t="inlineStr">
+        <is>
+          <t>자원 신목 목재 x45 (감정 · 풀 23에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="13" t="n"/>
+      <c r="B248" s="11" t="n">
+        <v>29004</v>
+      </c>
+      <c r="C248" s="11" t="n">
+        <v>29</v>
+      </c>
+      <c r="D248" s="11" t="n">
+        <v>40043</v>
+      </c>
+      <c r="E248" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="F248" s="11" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G248" s="12" t="inlineStr">
+        <is>
+          <t>자원 아다만트 광석 x45 (감정 · 풀 23에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="13" t="n"/>
+      <c r="B249" s="11" t="n">
+        <v>29005</v>
+      </c>
+      <c r="C249" s="11" t="n">
+        <v>29</v>
+      </c>
+      <c r="D249" s="11" t="n">
+        <v>50043</v>
+      </c>
+      <c r="E249" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="F249" s="11" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G249" s="12" t="inlineStr">
+        <is>
+          <t>자원 흉수의 송곳니 x45 (감정 · 풀 23에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="13" t="n"/>
+      <c r="B250" s="11" t="n">
+        <v>29006</v>
+      </c>
+      <c r="C250" s="11" t="n">
+        <v>29</v>
+      </c>
+      <c r="D250" s="11" t="n">
+        <v>100015</v>
+      </c>
+      <c r="E250" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="F250" s="11" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G250" s="12" t="inlineStr">
+        <is>
+          <t>인챈트 큐브 x5 (감정 · 풀 23에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="13" t="n"/>
+      <c r="B251" s="11" t="n">
+        <v>29007</v>
+      </c>
+      <c r="C251" s="11" t="n">
+        <v>29</v>
+      </c>
+      <c r="D251" s="11" t="n">
+        <v>100018</v>
+      </c>
+      <c r="E251" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="F251" s="11" t="n">
+        <v>4000</v>
+      </c>
+      <c r="G251" s="12" t="inlineStr">
+        <is>
+          <t>상급 인챈트 큐브 x5 (감정 · 풀 23에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="13" t="n"/>
+      <c r="B252" s="11" t="n">
+        <v>29008</v>
+      </c>
+      <c r="C252" s="11" t="n">
+        <v>29</v>
+      </c>
+      <c r="D252" s="11" t="n">
+        <v>100042</v>
+      </c>
+      <c r="E252" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F252" s="11" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G252" s="12" t="inlineStr">
+        <is>
+          <t>성장의 비약 (중) x1 (감정 · 풀 23에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="13" t="n"/>
+      <c r="B253" s="11" t="n">
+        <v>29009</v>
+      </c>
+      <c r="C253" s="11" t="n">
+        <v>29</v>
+      </c>
+      <c r="D253" s="11" t="n">
+        <v>100043</v>
+      </c>
+      <c r="E253" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F253" s="11" t="n">
+        <v>4000</v>
+      </c>
+      <c r="G253" s="12" t="inlineStr">
+        <is>
+          <t>성장의 비약 (대) x1 (감정 · 풀 23에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="13" t="n"/>
+      <c r="B254" s="11" t="n">
+        <v>29010</v>
+      </c>
+      <c r="C254" s="11" t="n">
+        <v>29</v>
+      </c>
+      <c r="D254" s="11" t="n">
+        <v>100044</v>
+      </c>
+      <c r="E254" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F254" s="11" t="n">
+        <v>4700</v>
+      </c>
+      <c r="G254" s="12" t="inlineStr">
+        <is>
+          <t>신속의 영약 x1 (감정 · 풀 23에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="13" t="n"/>
+      <c r="B255" s="11" t="n">
+        <v>29011</v>
+      </c>
+      <c r="C255" s="11" t="n">
+        <v>29</v>
+      </c>
+      <c r="D255" s="11" t="n">
+        <v>100045</v>
+      </c>
+      <c r="E255" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F255" s="11" t="n">
+        <v>4700</v>
+      </c>
+      <c r="G255" s="12" t="inlineStr">
+        <is>
+          <t>풍요의 영약 x1 (감정 · 풀 23에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="13" t="n"/>
+      <c r="B256" s="11" t="n">
+        <v>29012</v>
+      </c>
+      <c r="C256" s="11" t="n">
+        <v>29</v>
+      </c>
+      <c r="D256" s="11" t="n">
+        <v>100046</v>
+      </c>
+      <c r="E256" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F256" s="11" t="n">
+        <v>500</v>
+      </c>
+      <c r="G256" s="12" t="inlineStr">
+        <is>
+          <t>망각의 묘약 x1 (감정 · 풀 23에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="13" t="n"/>
+      <c r="B257" s="11" t="n">
+        <v>29099</v>
+      </c>
+      <c r="C257" s="11" t="n">
+        <v>29</v>
+      </c>
+      <c r="D257" s="11" t="n">
+        <v>100067</v>
+      </c>
+      <c r="E257" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F257" s="11" t="n">
+        <v>1590</v>
+      </c>
+      <c r="G257" s="12" t="inlineStr">
+        <is>
+          <t>Special 미감정 유물 — 약 1.6% (테스트값)</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="13" t="n"/>
+      <c r="B258" s="11" t="n">
+        <v>30001</v>
+      </c>
+      <c r="C258" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="D258" s="11" t="n">
+        <v>10043</v>
+      </c>
+      <c r="E258" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="F258" s="11" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G258" s="12" t="inlineStr">
+        <is>
+          <t>자원 왕실 문서 x45 (감정 · 풀 23에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="13" t="n"/>
+      <c r="B259" s="11" t="n">
+        <v>30002</v>
+      </c>
+      <c r="C259" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="D259" s="11" t="n">
+        <v>20043</v>
+      </c>
+      <c r="E259" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="F259" s="11" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G259" s="12" t="inlineStr">
+        <is>
+          <t>자원 영약초 x45 (감정 · 풀 23에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="13" t="n"/>
+      <c r="B260" s="11" t="n">
+        <v>30003</v>
+      </c>
+      <c r="C260" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="D260" s="11" t="n">
+        <v>30043</v>
+      </c>
+      <c r="E260" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="F260" s="11" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G260" s="12" t="inlineStr">
+        <is>
+          <t>자원 신목 목재 x45 (감정 · 풀 23에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="13" t="n"/>
+      <c r="B261" s="11" t="n">
+        <v>30004</v>
+      </c>
+      <c r="C261" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="D261" s="11" t="n">
+        <v>40043</v>
+      </c>
+      <c r="E261" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="F261" s="11" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G261" s="12" t="inlineStr">
+        <is>
+          <t>자원 아다만트 광석 x45 (감정 · 풀 23에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="13" t="n"/>
+      <c r="B262" s="11" t="n">
+        <v>30005</v>
+      </c>
+      <c r="C262" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="D262" s="11" t="n">
+        <v>50043</v>
+      </c>
+      <c r="E262" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="F262" s="11" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G262" s="12" t="inlineStr">
+        <is>
+          <t>자원 흉수의 송곳니 x45 (감정 · 풀 23에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="13" t="n"/>
+      <c r="B263" s="11" t="n">
+        <v>30006</v>
+      </c>
+      <c r="C263" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="D263" s="11" t="n">
+        <v>100015</v>
+      </c>
+      <c r="E263" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="F263" s="11" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G263" s="12" t="inlineStr">
+        <is>
+          <t>인챈트 큐브 x5 (감정 · 풀 23에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="13" t="n"/>
+      <c r="B264" s="11" t="n">
+        <v>30007</v>
+      </c>
+      <c r="C264" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="D264" s="11" t="n">
+        <v>100018</v>
+      </c>
+      <c r="E264" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="F264" s="11" t="n">
+        <v>4000</v>
+      </c>
+      <c r="G264" s="12" t="inlineStr">
+        <is>
+          <t>상급 인챈트 큐브 x5 (감정 · 풀 23에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="13" t="n"/>
+      <c r="B265" s="11" t="n">
+        <v>30008</v>
+      </c>
+      <c r="C265" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="D265" s="11" t="n">
+        <v>100042</v>
+      </c>
+      <c r="E265" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F265" s="11" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G265" s="12" t="inlineStr">
+        <is>
+          <t>성장의 비약 (중) x1 (감정 · 풀 23에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="13" t="n"/>
+      <c r="B266" s="11" t="n">
+        <v>30009</v>
+      </c>
+      <c r="C266" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="D266" s="11" t="n">
+        <v>100043</v>
+      </c>
+      <c r="E266" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F266" s="11" t="n">
+        <v>4000</v>
+      </c>
+      <c r="G266" s="12" t="inlineStr">
+        <is>
+          <t>성장의 비약 (대) x1 (감정 · 풀 23에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="13" t="n"/>
+      <c r="B267" s="11" t="n">
+        <v>30010</v>
+      </c>
+      <c r="C267" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="D267" s="11" t="n">
+        <v>100044</v>
+      </c>
+      <c r="E267" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F267" s="11" t="n">
+        <v>4700</v>
+      </c>
+      <c r="G267" s="12" t="inlineStr">
+        <is>
+          <t>신속의 영약 x1 (감정 · 풀 23에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="13" t="n"/>
+      <c r="B268" s="11" t="n">
+        <v>30011</v>
+      </c>
+      <c r="C268" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="D268" s="11" t="n">
+        <v>100045</v>
+      </c>
+      <c r="E268" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F268" s="11" t="n">
+        <v>4700</v>
+      </c>
+      <c r="G268" s="12" t="inlineStr">
+        <is>
+          <t>풍요의 영약 x1 (감정 · 풀 23에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="13" t="n"/>
+      <c r="B269" s="11" t="n">
+        <v>30012</v>
+      </c>
+      <c r="C269" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="D269" s="11" t="n">
+        <v>100046</v>
+      </c>
+      <c r="E269" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F269" s="11" t="n">
+        <v>500</v>
+      </c>
+      <c r="G269" s="12" t="inlineStr">
+        <is>
+          <t>망각의 묘약 x1 (감정 · 풀 23에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="13" t="n"/>
+      <c r="B270" s="11" t="n">
+        <v>30099</v>
+      </c>
+      <c r="C270" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="D270" s="11" t="n">
+        <v>100067</v>
+      </c>
+      <c r="E270" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F270" s="11" t="n">
+        <v>4932</v>
+      </c>
+      <c r="G270" s="12" t="inlineStr">
+        <is>
+          <t>Special 미감정 유물 — 약 4.8% (테스트값)</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="13" t="n"/>
+      <c r="B271" s="11" t="n">
+        <v>31001</v>
+      </c>
+      <c r="C271" s="11" t="n">
+        <v>31</v>
+      </c>
+      <c r="D271" s="11" t="n">
+        <v>10043</v>
+      </c>
+      <c r="E271" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="F271" s="11" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G271" s="12" t="inlineStr">
+        <is>
+          <t>자원 왕실 문서 x45 (감정 · 풀 23에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="13" t="n"/>
+      <c r="B272" s="11" t="n">
+        <v>31002</v>
+      </c>
+      <c r="C272" s="11" t="n">
+        <v>31</v>
+      </c>
+      <c r="D272" s="11" t="n">
+        <v>20043</v>
+      </c>
+      <c r="E272" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="F272" s="11" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G272" s="12" t="inlineStr">
+        <is>
+          <t>자원 영약초 x45 (감정 · 풀 23에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="13" t="n"/>
+      <c r="B273" s="11" t="n">
+        <v>31003</v>
+      </c>
+      <c r="C273" s="11" t="n">
+        <v>31</v>
+      </c>
+      <c r="D273" s="11" t="n">
+        <v>30043</v>
+      </c>
+      <c r="E273" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="F273" s="11" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G273" s="12" t="inlineStr">
+        <is>
+          <t>자원 신목 목재 x45 (감정 · 풀 23에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="13" t="n"/>
+      <c r="B274" s="11" t="n">
+        <v>31004</v>
+      </c>
+      <c r="C274" s="11" t="n">
+        <v>31</v>
+      </c>
+      <c r="D274" s="11" t="n">
+        <v>40043</v>
+      </c>
+      <c r="E274" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="F274" s="11" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G274" s="12" t="inlineStr">
+        <is>
+          <t>자원 아다만트 광석 x45 (감정 · 풀 23에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="13" t="n"/>
+      <c r="B275" s="11" t="n">
+        <v>31005</v>
+      </c>
+      <c r="C275" s="11" t="n">
+        <v>31</v>
+      </c>
+      <c r="D275" s="11" t="n">
+        <v>50043</v>
+      </c>
+      <c r="E275" s="11" t="n">
+        <v>45</v>
+      </c>
+      <c r="F275" s="11" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G275" s="12" t="inlineStr">
+        <is>
+          <t>자원 흉수의 송곳니 x45 (감정 · 풀 23에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="13" t="n"/>
+      <c r="B276" s="11" t="n">
+        <v>31006</v>
+      </c>
+      <c r="C276" s="11" t="n">
+        <v>31</v>
+      </c>
+      <c r="D276" s="11" t="n">
+        <v>100015</v>
+      </c>
+      <c r="E276" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="F276" s="11" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G276" s="12" t="inlineStr">
+        <is>
+          <t>인챈트 큐브 x5 (감정 · 풀 23에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="13" t="n"/>
+      <c r="B277" s="11" t="n">
+        <v>31007</v>
+      </c>
+      <c r="C277" s="11" t="n">
+        <v>31</v>
+      </c>
+      <c r="D277" s="11" t="n">
+        <v>100018</v>
+      </c>
+      <c r="E277" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="F277" s="11" t="n">
+        <v>4000</v>
+      </c>
+      <c r="G277" s="12" t="inlineStr">
+        <is>
+          <t>상급 인챈트 큐브 x5 (감정 · 풀 23에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="13" t="n"/>
+      <c r="B278" s="11" t="n">
+        <v>31008</v>
+      </c>
+      <c r="C278" s="11" t="n">
+        <v>31</v>
+      </c>
+      <c r="D278" s="11" t="n">
+        <v>100042</v>
+      </c>
+      <c r="E278" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F278" s="11" t="n">
+        <v>6000</v>
+      </c>
+      <c r="G278" s="12" t="inlineStr">
+        <is>
+          <t>성장의 비약 (중) x1 (감정 · 풀 23에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="13" t="n"/>
+      <c r="B279" s="11" t="n">
+        <v>31009</v>
+      </c>
+      <c r="C279" s="11" t="n">
+        <v>31</v>
+      </c>
+      <c r="D279" s="11" t="n">
+        <v>100043</v>
+      </c>
+      <c r="E279" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F279" s="11" t="n">
+        <v>4000</v>
+      </c>
+      <c r="G279" s="12" t="inlineStr">
+        <is>
+          <t>성장의 비약 (대) x1 (감정 · 풀 23에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="13" t="n"/>
+      <c r="B280" s="11" t="n">
+        <v>31010</v>
+      </c>
+      <c r="C280" s="11" t="n">
+        <v>31</v>
+      </c>
+      <c r="D280" s="11" t="n">
+        <v>100044</v>
+      </c>
+      <c r="E280" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F280" s="11" t="n">
+        <v>4700</v>
+      </c>
+      <c r="G280" s="12" t="inlineStr">
+        <is>
+          <t>신속의 영약 x1 (감정 · 풀 23에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="13" t="n"/>
+      <c r="B281" s="11" t="n">
+        <v>31011</v>
+      </c>
+      <c r="C281" s="11" t="n">
+        <v>31</v>
+      </c>
+      <c r="D281" s="11" t="n">
+        <v>100045</v>
+      </c>
+      <c r="E281" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F281" s="11" t="n">
+        <v>4700</v>
+      </c>
+      <c r="G281" s="12" t="inlineStr">
+        <is>
+          <t>풍요의 영약 x1 (감정 · 풀 23에서)</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="13" t="n"/>
+      <c r="B282" s="11" t="n">
+        <v>31012</v>
+      </c>
+      <c r="C282" s="11" t="n">
+        <v>31</v>
+      </c>
+      <c r="D282" s="11" t="n">
+        <v>100046</v>
+      </c>
+      <c r="E282" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F282" s="11" t="n">
+        <v>500</v>
+      </c>
+      <c r="G282" s="12" t="inlineStr">
+        <is>
+          <t>망각의 묘약 x1 (감정 · 풀 23에서)</t>
         </is>
       </c>
     </row>
@@ -5080,16 +7120,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="38" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5856,6 +7896,195 @@
       <c r="G29" s="12" t="inlineStr">
         <is>
           <t>황금 열쇠 전용 — 골드로 뽑을 수 없다</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="13" t="n"/>
+      <c r="B30" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>감정 — 흙 묻은 유물</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E30" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="12" t="inlineStr">
+        <is>
+          <t>유물 감정 전용 — 골드로 뽑을 수 없다 · 비용은 ItemTable.OpenCostGold (원본 상자 풀 9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="13" t="n"/>
+      <c r="B31" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="C31" s="12" t="inlineStr">
+        <is>
+          <t>감정 — 조개 박힌 유물</t>
+        </is>
+      </c>
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="12" t="inlineStr">
+        <is>
+          <t>유물 감정 전용 — 골드로 뽑을 수 없다 · 비용은 ItemTable.OpenCostGold (원본 상자 풀 13)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="13" t="n"/>
+      <c r="B32" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="C32" s="12" t="inlineStr">
+        <is>
+          <t>감정 — 산호 엉긴 유물</t>
+        </is>
+      </c>
+      <c r="D32" s="12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E32" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="12" t="inlineStr">
+        <is>
+          <t>유물 감정 전용 — 골드로 뽑을 수 없다 · 비용은 ItemTable.OpenCostGold (원본 상자 풀 17)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="13" t="n"/>
+      <c r="B33" s="11" t="n">
+        <v>28</v>
+      </c>
+      <c r="C33" s="12" t="inlineStr">
+        <is>
+          <t>감정 — 봉인된 유물</t>
+        </is>
+      </c>
+      <c r="D33" s="12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E33" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="12" t="inlineStr">
+        <is>
+          <t>유물 감정 전용 — 골드로 뽑을 수 없다 · 비용은 ItemTable.OpenCostGold (원본 상자 풀 20)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="13" t="n"/>
+      <c r="B34" s="11" t="n">
+        <v>29</v>
+      </c>
+      <c r="C34" s="12" t="inlineStr">
+        <is>
+          <t>감정 — 황금 띠 유물</t>
+        </is>
+      </c>
+      <c r="D34" s="12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E34" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="12" t="inlineStr">
+        <is>
+          <t>유물 감정 전용 — 골드로 뽑을 수 없다 · 비용은 ItemTable.OpenCostGold (원본 상자 풀 23)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="13" t="n"/>
+      <c r="B35" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="C35" s="12" t="inlineStr">
+        <is>
+          <t>감정 — 왕의 유물</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" s="12" t="inlineStr">
+        <is>
+          <t>유물 감정 전용 — 골드로 뽑을 수 없다 · 비용은 ItemTable.OpenCostGold (원본 상자 풀 23)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="13" t="n"/>
+      <c r="B36" s="11" t="n">
+        <v>31</v>
+      </c>
+      <c r="C36" s="12" t="inlineStr">
+        <is>
+          <t>감정 — 무지개 유물</t>
+        </is>
+      </c>
+      <c r="D36" s="12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E36" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="12" t="inlineStr">
+        <is>
+          <t>유물 감정 전용 — 골드로 뽑을 수 없다 · 비용은 ItemTable.OpenCostGold (원본 상자 풀 23)</t>
         </is>
       </c>
     </row>
@@ -6806,7 +9035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G270"/>
+  <dimension ref="A1:G350"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -6815,7 +9044,7 @@
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="25" customWidth="1" min="7" max="7"/>
+    <col width="32" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13039,6 +15268,1846 @@
       <c r="G270" s="12" t="inlineStr">
         <is>
           <t>Legendary 야수의 심장</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="13" t="n"/>
+      <c r="B271" s="11" t="n">
+        <v>25101</v>
+      </c>
+      <c r="C271" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="D271" s="11" t="n">
+        <v>1001</v>
+      </c>
+      <c r="E271" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F271" s="11" t="n">
+        <v>690</v>
+      </c>
+      <c r="G271" s="12" t="inlineStr">
+        <is>
+          <t>Common 목검 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="13" t="n"/>
+      <c r="B272" s="11" t="n">
+        <v>25102</v>
+      </c>
+      <c r="C272" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="D272" s="11" t="n">
+        <v>2001</v>
+      </c>
+      <c r="E272" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F272" s="11" t="n">
+        <v>690</v>
+      </c>
+      <c r="G272" s="12" t="inlineStr">
+        <is>
+          <t>Common 구리 반지 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="13" t="n"/>
+      <c r="B273" s="11" t="n">
+        <v>25103</v>
+      </c>
+      <c r="C273" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="D273" s="11" t="n">
+        <v>3001</v>
+      </c>
+      <c r="E273" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F273" s="11" t="n">
+        <v>690</v>
+      </c>
+      <c r="G273" s="12" t="inlineStr">
+        <is>
+          <t>Common 원석 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="13" t="n"/>
+      <c r="B274" s="11" t="n">
+        <v>25104</v>
+      </c>
+      <c r="C274" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="D274" s="11" t="n">
+        <v>1101</v>
+      </c>
+      <c r="E274" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F274" s="11" t="n">
+        <v>690</v>
+      </c>
+      <c r="G274" s="12" t="inlineStr">
+        <is>
+          <t>Common 나무 호미 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="13" t="n"/>
+      <c r="B275" s="11" t="n">
+        <v>25105</v>
+      </c>
+      <c r="C275" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="D275" s="11" t="n">
+        <v>1201</v>
+      </c>
+      <c r="E275" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F275" s="11" t="n">
+        <v>690</v>
+      </c>
+      <c r="G275" s="12" t="inlineStr">
+        <is>
+          <t>Common 나무 모종삽 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="13" t="n"/>
+      <c r="B276" s="11" t="n">
+        <v>25106</v>
+      </c>
+      <c r="C276" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="D276" s="11" t="n">
+        <v>1301</v>
+      </c>
+      <c r="E276" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F276" s="11" t="n">
+        <v>690</v>
+      </c>
+      <c r="G276" s="12" t="inlineStr">
+        <is>
+          <t>Common 돌 곡괭이 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="13" t="n"/>
+      <c r="B277" s="11" t="n">
+        <v>25107</v>
+      </c>
+      <c r="C277" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="D277" s="11" t="n">
+        <v>1401</v>
+      </c>
+      <c r="E277" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F277" s="11" t="n">
+        <v>690</v>
+      </c>
+      <c r="G277" s="12" t="inlineStr">
+        <is>
+          <t>Common 손도끼 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="13" t="n"/>
+      <c r="B278" s="11" t="n">
+        <v>25108</v>
+      </c>
+      <c r="C278" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="D278" s="11" t="n">
+        <v>1501</v>
+      </c>
+      <c r="E278" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F278" s="11" t="n">
+        <v>690</v>
+      </c>
+      <c r="G278" s="12" t="inlineStr">
+        <is>
+          <t>Common 사냥용 활 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="13" t="n"/>
+      <c r="B279" s="11" t="n">
+        <v>25109</v>
+      </c>
+      <c r="C279" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="D279" s="11" t="n">
+        <v>3101</v>
+      </c>
+      <c r="E279" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F279" s="11" t="n">
+        <v>690</v>
+      </c>
+      <c r="G279" s="12" t="inlineStr">
+        <is>
+          <t>Common 풍년석 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="13" t="n"/>
+      <c r="B280" s="11" t="n">
+        <v>25110</v>
+      </c>
+      <c r="C280" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="D280" s="11" t="n">
+        <v>3201</v>
+      </c>
+      <c r="E280" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F280" s="11" t="n">
+        <v>690</v>
+      </c>
+      <c r="G280" s="12" t="inlineStr">
+        <is>
+          <t>Common 흙빛 조각석 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="13" t="n"/>
+      <c r="B281" s="11" t="n">
+        <v>25111</v>
+      </c>
+      <c r="C281" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="D281" s="11" t="n">
+        <v>3301</v>
+      </c>
+      <c r="E281" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F281" s="11" t="n">
+        <v>690</v>
+      </c>
+      <c r="G281" s="12" t="inlineStr">
+        <is>
+          <t>Common 철광석 조각 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="13" t="n"/>
+      <c r="B282" s="11" t="n">
+        <v>25112</v>
+      </c>
+      <c r="C282" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="D282" s="11" t="n">
+        <v>3401</v>
+      </c>
+      <c r="E282" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F282" s="11" t="n">
+        <v>690</v>
+      </c>
+      <c r="G282" s="12" t="inlineStr">
+        <is>
+          <t>Common 나무옹이석 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="13" t="n"/>
+      <c r="B283" s="11" t="n">
+        <v>25113</v>
+      </c>
+      <c r="C283" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="D283" s="11" t="n">
+        <v>3501</v>
+      </c>
+      <c r="E283" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F283" s="11" t="n">
+        <v>690</v>
+      </c>
+      <c r="G283" s="12" t="inlineStr">
+        <is>
+          <t>Common 짐승 이빨석 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="13" t="n"/>
+      <c r="B284" s="11" t="n">
+        <v>26101</v>
+      </c>
+      <c r="C284" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="D284" s="11" t="n">
+        <v>2002</v>
+      </c>
+      <c r="E284" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F284" s="11" t="n">
+        <v>750</v>
+      </c>
+      <c r="G284" s="12" t="inlineStr">
+        <is>
+          <t>Rare 탐험가의 목걸이 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="13" t="n"/>
+      <c r="B285" s="11" t="n">
+        <v>26102</v>
+      </c>
+      <c r="C285" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="D285" s="11" t="n">
+        <v>1103</v>
+      </c>
+      <c r="E285" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F285" s="11" t="n">
+        <v>750</v>
+      </c>
+      <c r="G285" s="12" t="inlineStr">
+        <is>
+          <t>Rare 강철 낫 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="13" t="n"/>
+      <c r="B286" s="11" t="n">
+        <v>26103</v>
+      </c>
+      <c r="C286" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="D286" s="11" t="n">
+        <v>1203</v>
+      </c>
+      <c r="E286" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F286" s="11" t="n">
+        <v>750</v>
+      </c>
+      <c r="G286" s="12" t="inlineStr">
+        <is>
+          <t>Rare 강철 삽 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="13" t="n"/>
+      <c r="B287" s="11" t="n">
+        <v>26104</v>
+      </c>
+      <c r="C287" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="D287" s="11" t="n">
+        <v>1303</v>
+      </c>
+      <c r="E287" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F287" s="11" t="n">
+        <v>750</v>
+      </c>
+      <c r="G287" s="12" t="inlineStr">
+        <is>
+          <t>Rare 강철 곡괭이 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="13" t="n"/>
+      <c r="B288" s="11" t="n">
+        <v>26105</v>
+      </c>
+      <c r="C288" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="D288" s="11" t="n">
+        <v>1403</v>
+      </c>
+      <c r="E288" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F288" s="11" t="n">
+        <v>750</v>
+      </c>
+      <c r="G288" s="12" t="inlineStr">
+        <is>
+          <t>Rare 양날 도끼 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="13" t="n"/>
+      <c r="B289" s="11" t="n">
+        <v>26106</v>
+      </c>
+      <c r="C289" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="D289" s="11" t="n">
+        <v>1503</v>
+      </c>
+      <c r="E289" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F289" s="11" t="n">
+        <v>750</v>
+      </c>
+      <c r="G289" s="12" t="inlineStr">
+        <is>
+          <t>Rare 강철 석궁 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="13" t="n"/>
+      <c r="B290" s="11" t="n">
+        <v>26107</v>
+      </c>
+      <c r="C290" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="D290" s="11" t="n">
+        <v>2004</v>
+      </c>
+      <c r="E290" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F290" s="11" t="n">
+        <v>750</v>
+      </c>
+      <c r="G290" s="12" t="inlineStr">
+        <is>
+          <t>Rare 노동자의 팔찌 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="13" t="n"/>
+      <c r="B291" s="11" t="n">
+        <v>26108</v>
+      </c>
+      <c r="C291" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="D291" s="11" t="n">
+        <v>3103</v>
+      </c>
+      <c r="E291" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F291" s="11" t="n">
+        <v>750</v>
+      </c>
+      <c r="G291" s="12" t="inlineStr">
+        <is>
+          <t>Rare 곡창의 비취 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="13" t="n"/>
+      <c r="B292" s="11" t="n">
+        <v>26109</v>
+      </c>
+      <c r="C292" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="D292" s="11" t="n">
+        <v>3203</v>
+      </c>
+      <c r="E292" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F292" s="11" t="n">
+        <v>750</v>
+      </c>
+      <c r="G292" s="12" t="inlineStr">
+        <is>
+          <t>Rare 유적의 호박 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="13" t="n"/>
+      <c r="B293" s="11" t="n">
+        <v>26110</v>
+      </c>
+      <c r="C293" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="D293" s="11" t="n">
+        <v>3303</v>
+      </c>
+      <c r="E293" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F293" s="11" t="n">
+        <v>750</v>
+      </c>
+      <c r="G293" s="12" t="inlineStr">
+        <is>
+          <t>Rare 지맥의 흑옥 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="13" t="n"/>
+      <c r="B294" s="11" t="n">
+        <v>26111</v>
+      </c>
+      <c r="C294" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="D294" s="11" t="n">
+        <v>3403</v>
+      </c>
+      <c r="E294" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F294" s="11" t="n">
+        <v>750</v>
+      </c>
+      <c r="G294" s="12" t="inlineStr">
+        <is>
+          <t>Rare 고목의 녹옥 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="13" t="n"/>
+      <c r="B295" s="11" t="n">
+        <v>26112</v>
+      </c>
+      <c r="C295" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="D295" s="11" t="n">
+        <v>3503</v>
+      </c>
+      <c r="E295" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F295" s="11" t="n">
+        <v>750</v>
+      </c>
+      <c r="G295" s="12" t="inlineStr">
+        <is>
+          <t>Rare 맹수의 홍옥 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="13" t="n"/>
+      <c r="B296" s="11" t="n">
+        <v>27101</v>
+      </c>
+      <c r="C296" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="D296" s="11" t="n">
+        <v>1105</v>
+      </c>
+      <c r="E296" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F296" s="11" t="n">
+        <v>810</v>
+      </c>
+      <c r="G296" s="12" t="inlineStr">
+        <is>
+          <t>Legendary 풍년의 괭이 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="13" t="n"/>
+      <c r="B297" s="11" t="n">
+        <v>27102</v>
+      </c>
+      <c r="C297" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="D297" s="11" t="n">
+        <v>1205</v>
+      </c>
+      <c r="E297" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F297" s="11" t="n">
+        <v>810</v>
+      </c>
+      <c r="G297" s="12" t="inlineStr">
+        <is>
+          <t>Legendary 용린 발굴삽 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="13" t="n"/>
+      <c r="B298" s="11" t="n">
+        <v>27103</v>
+      </c>
+      <c r="C298" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="D298" s="11" t="n">
+        <v>1305</v>
+      </c>
+      <c r="E298" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F298" s="11" t="n">
+        <v>810</v>
+      </c>
+      <c r="G298" s="12" t="inlineStr">
+        <is>
+          <t>Legendary 미스릴 곡괭이 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="13" t="n"/>
+      <c r="B299" s="11" t="n">
+        <v>27104</v>
+      </c>
+      <c r="C299" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="D299" s="11" t="n">
+        <v>1405</v>
+      </c>
+      <c r="E299" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F299" s="11" t="n">
+        <v>810</v>
+      </c>
+      <c r="G299" s="12" t="inlineStr">
+        <is>
+          <t>Legendary 서리강철 도끼 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="13" t="n"/>
+      <c r="B300" s="11" t="n">
+        <v>27105</v>
+      </c>
+      <c r="C300" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="D300" s="11" t="n">
+        <v>1505</v>
+      </c>
+      <c r="E300" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F300" s="11" t="n">
+        <v>810</v>
+      </c>
+      <c r="G300" s="12" t="inlineStr">
+        <is>
+          <t>Legendary 폭풍의 장궁 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" s="13" t="n"/>
+      <c r="B301" s="11" t="n">
+        <v>27106</v>
+      </c>
+      <c r="C301" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="D301" s="11" t="n">
+        <v>2006</v>
+      </c>
+      <c r="E301" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F301" s="11" t="n">
+        <v>810</v>
+      </c>
+      <c r="G301" s="12" t="inlineStr">
+        <is>
+          <t>Legendary 대장인의 훈장 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" s="13" t="n"/>
+      <c r="B302" s="11" t="n">
+        <v>27107</v>
+      </c>
+      <c r="C302" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="D302" s="11" t="n">
+        <v>3105</v>
+      </c>
+      <c r="E302" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F302" s="11" t="n">
+        <v>810</v>
+      </c>
+      <c r="G302" s="12" t="inlineStr">
+        <is>
+          <t>Legendary 대지의 심장 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" s="13" t="n"/>
+      <c r="B303" s="11" t="n">
+        <v>27108</v>
+      </c>
+      <c r="C303" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="D303" s="11" t="n">
+        <v>3205</v>
+      </c>
+      <c r="E303" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F303" s="11" t="n">
+        <v>810</v>
+      </c>
+      <c r="G303" s="12" t="inlineStr">
+        <is>
+          <t>Legendary 왕도의 심장 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" s="13" t="n"/>
+      <c r="B304" s="11" t="n">
+        <v>27109</v>
+      </c>
+      <c r="C304" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="D304" s="11" t="n">
+        <v>3305</v>
+      </c>
+      <c r="E304" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F304" s="11" t="n">
+        <v>810</v>
+      </c>
+      <c r="G304" s="12" t="inlineStr">
+        <is>
+          <t>Legendary 대지핵 결정 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" s="13" t="n"/>
+      <c r="B305" s="11" t="n">
+        <v>27110</v>
+      </c>
+      <c r="C305" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="D305" s="11" t="n">
+        <v>3405</v>
+      </c>
+      <c r="E305" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F305" s="11" t="n">
+        <v>810</v>
+      </c>
+      <c r="G305" s="12" t="inlineStr">
+        <is>
+          <t>Legendary 숲의 심장 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" s="13" t="n"/>
+      <c r="B306" s="11" t="n">
+        <v>27111</v>
+      </c>
+      <c r="C306" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="D306" s="11" t="n">
+        <v>3505</v>
+      </c>
+      <c r="E306" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F306" s="11" t="n">
+        <v>810</v>
+      </c>
+      <c r="G306" s="12" t="inlineStr">
+        <is>
+          <t>Legendary 야수의 심장 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" s="13" t="n"/>
+      <c r="B307" s="11" t="n">
+        <v>28101</v>
+      </c>
+      <c r="C307" s="11" t="n">
+        <v>28</v>
+      </c>
+      <c r="D307" s="11" t="n">
+        <v>1106</v>
+      </c>
+      <c r="E307" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F307" s="11" t="n">
+        <v>810</v>
+      </c>
+      <c r="G307" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 대지모의 호미 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" s="13" t="n"/>
+      <c r="B308" s="11" t="n">
+        <v>28102</v>
+      </c>
+      <c r="C308" s="11" t="n">
+        <v>28</v>
+      </c>
+      <c r="D308" s="11" t="n">
+        <v>1206</v>
+      </c>
+      <c r="E308" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F308" s="11" t="n">
+        <v>810</v>
+      </c>
+      <c r="G308" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 태초의 발굴삽 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" s="13" t="n"/>
+      <c r="B309" s="11" t="n">
+        <v>28103</v>
+      </c>
+      <c r="C309" s="11" t="n">
+        <v>28</v>
+      </c>
+      <c r="D309" s="11" t="n">
+        <v>1306</v>
+      </c>
+      <c r="E309" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F309" s="11" t="n">
+        <v>810</v>
+      </c>
+      <c r="G309" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 산신의 곡괭이 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" s="13" t="n"/>
+      <c r="B310" s="11" t="n">
+        <v>28104</v>
+      </c>
+      <c r="C310" s="11" t="n">
+        <v>28</v>
+      </c>
+      <c r="D310" s="11" t="n">
+        <v>1406</v>
+      </c>
+      <c r="E310" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F310" s="11" t="n">
+        <v>810</v>
+      </c>
+      <c r="G310" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 세계수의 도끼 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" s="13" t="n"/>
+      <c r="B311" s="11" t="n">
+        <v>28105</v>
+      </c>
+      <c r="C311" s="11" t="n">
+        <v>28</v>
+      </c>
+      <c r="D311" s="11" t="n">
+        <v>1506</v>
+      </c>
+      <c r="E311" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F311" s="11" t="n">
+        <v>810</v>
+      </c>
+      <c r="G311" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 월신의 활 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" s="13" t="n"/>
+      <c r="B312" s="11" t="n">
+        <v>28106</v>
+      </c>
+      <c r="C312" s="11" t="n">
+        <v>28</v>
+      </c>
+      <c r="D312" s="11" t="n">
+        <v>2007</v>
+      </c>
+      <c r="E312" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F312" s="11" t="n">
+        <v>810</v>
+      </c>
+      <c r="G312" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 창세의 고리 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" s="13" t="n"/>
+      <c r="B313" s="11" t="n">
+        <v>28107</v>
+      </c>
+      <c r="C313" s="11" t="n">
+        <v>28</v>
+      </c>
+      <c r="D313" s="11" t="n">
+        <v>3106</v>
+      </c>
+      <c r="E313" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F313" s="11" t="n">
+        <v>810</v>
+      </c>
+      <c r="G313" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 풍요의 성석 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="13" t="n"/>
+      <c r="B314" s="11" t="n">
+        <v>28108</v>
+      </c>
+      <c r="C314" s="11" t="n">
+        <v>28</v>
+      </c>
+      <c r="D314" s="11" t="n">
+        <v>3206</v>
+      </c>
+      <c r="E314" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F314" s="11" t="n">
+        <v>810</v>
+      </c>
+      <c r="G314" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 태고의 성석 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" s="13" t="n"/>
+      <c r="B315" s="11" t="n">
+        <v>28109</v>
+      </c>
+      <c r="C315" s="11" t="n">
+        <v>28</v>
+      </c>
+      <c r="D315" s="11" t="n">
+        <v>3306</v>
+      </c>
+      <c r="E315" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F315" s="11" t="n">
+        <v>810</v>
+      </c>
+      <c r="G315" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 광신의 성석 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="13" t="n"/>
+      <c r="B316" s="11" t="n">
+        <v>28110</v>
+      </c>
+      <c r="C316" s="11" t="n">
+        <v>28</v>
+      </c>
+      <c r="D316" s="11" t="n">
+        <v>3406</v>
+      </c>
+      <c r="E316" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F316" s="11" t="n">
+        <v>810</v>
+      </c>
+      <c r="G316" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 세계수 성석 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" s="13" t="n"/>
+      <c r="B317" s="11" t="n">
+        <v>28111</v>
+      </c>
+      <c r="C317" s="11" t="n">
+        <v>28</v>
+      </c>
+      <c r="D317" s="11" t="n">
+        <v>3506</v>
+      </c>
+      <c r="E317" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F317" s="11" t="n">
+        <v>810</v>
+      </c>
+      <c r="G317" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 월광 성석 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" s="13" t="n"/>
+      <c r="B318" s="11" t="n">
+        <v>29101</v>
+      </c>
+      <c r="C318" s="11" t="n">
+        <v>29</v>
+      </c>
+      <c r="D318" s="11" t="n">
+        <v>1106</v>
+      </c>
+      <c r="E318" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F318" s="11" t="n">
+        <v>810</v>
+      </c>
+      <c r="G318" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 대지모의 호미 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" s="13" t="n"/>
+      <c r="B319" s="11" t="n">
+        <v>29102</v>
+      </c>
+      <c r="C319" s="11" t="n">
+        <v>29</v>
+      </c>
+      <c r="D319" s="11" t="n">
+        <v>1206</v>
+      </c>
+      <c r="E319" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F319" s="11" t="n">
+        <v>810</v>
+      </c>
+      <c r="G319" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 태초의 발굴삽 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" s="13" t="n"/>
+      <c r="B320" s="11" t="n">
+        <v>29103</v>
+      </c>
+      <c r="C320" s="11" t="n">
+        <v>29</v>
+      </c>
+      <c r="D320" s="11" t="n">
+        <v>1306</v>
+      </c>
+      <c r="E320" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F320" s="11" t="n">
+        <v>810</v>
+      </c>
+      <c r="G320" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 산신의 곡괭이 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" s="13" t="n"/>
+      <c r="B321" s="11" t="n">
+        <v>29104</v>
+      </c>
+      <c r="C321" s="11" t="n">
+        <v>29</v>
+      </c>
+      <c r="D321" s="11" t="n">
+        <v>1406</v>
+      </c>
+      <c r="E321" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F321" s="11" t="n">
+        <v>810</v>
+      </c>
+      <c r="G321" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 세계수의 도끼 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="13" t="n"/>
+      <c r="B322" s="11" t="n">
+        <v>29105</v>
+      </c>
+      <c r="C322" s="11" t="n">
+        <v>29</v>
+      </c>
+      <c r="D322" s="11" t="n">
+        <v>1506</v>
+      </c>
+      <c r="E322" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F322" s="11" t="n">
+        <v>810</v>
+      </c>
+      <c r="G322" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 월신의 활 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" s="13" t="n"/>
+      <c r="B323" s="11" t="n">
+        <v>29106</v>
+      </c>
+      <c r="C323" s="11" t="n">
+        <v>29</v>
+      </c>
+      <c r="D323" s="11" t="n">
+        <v>2007</v>
+      </c>
+      <c r="E323" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F323" s="11" t="n">
+        <v>810</v>
+      </c>
+      <c r="G323" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 창세의 고리 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" s="13" t="n"/>
+      <c r="B324" s="11" t="n">
+        <v>29107</v>
+      </c>
+      <c r="C324" s="11" t="n">
+        <v>29</v>
+      </c>
+      <c r="D324" s="11" t="n">
+        <v>3106</v>
+      </c>
+      <c r="E324" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F324" s="11" t="n">
+        <v>810</v>
+      </c>
+      <c r="G324" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 풍요의 성석 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="13" t="n"/>
+      <c r="B325" s="11" t="n">
+        <v>29108</v>
+      </c>
+      <c r="C325" s="11" t="n">
+        <v>29</v>
+      </c>
+      <c r="D325" s="11" t="n">
+        <v>3206</v>
+      </c>
+      <c r="E325" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F325" s="11" t="n">
+        <v>810</v>
+      </c>
+      <c r="G325" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 태고의 성석 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" s="13" t="n"/>
+      <c r="B326" s="11" t="n">
+        <v>29109</v>
+      </c>
+      <c r="C326" s="11" t="n">
+        <v>29</v>
+      </c>
+      <c r="D326" s="11" t="n">
+        <v>3306</v>
+      </c>
+      <c r="E326" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F326" s="11" t="n">
+        <v>810</v>
+      </c>
+      <c r="G326" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 광신의 성석 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="13" t="n"/>
+      <c r="B327" s="11" t="n">
+        <v>29110</v>
+      </c>
+      <c r="C327" s="11" t="n">
+        <v>29</v>
+      </c>
+      <c r="D327" s="11" t="n">
+        <v>3406</v>
+      </c>
+      <c r="E327" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F327" s="11" t="n">
+        <v>810</v>
+      </c>
+      <c r="G327" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 세계수 성석 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="13" t="n"/>
+      <c r="B328" s="11" t="n">
+        <v>29111</v>
+      </c>
+      <c r="C328" s="11" t="n">
+        <v>29</v>
+      </c>
+      <c r="D328" s="11" t="n">
+        <v>3506</v>
+      </c>
+      <c r="E328" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F328" s="11" t="n">
+        <v>810</v>
+      </c>
+      <c r="G328" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 월광 성석 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="13" t="n"/>
+      <c r="B329" s="11" t="n">
+        <v>30101</v>
+      </c>
+      <c r="C329" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="D329" s="11" t="n">
+        <v>1106</v>
+      </c>
+      <c r="E329" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F329" s="11" t="n">
+        <v>810</v>
+      </c>
+      <c r="G329" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 대지모의 호미 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="13" t="n"/>
+      <c r="B330" s="11" t="n">
+        <v>30102</v>
+      </c>
+      <c r="C330" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="D330" s="11" t="n">
+        <v>1206</v>
+      </c>
+      <c r="E330" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F330" s="11" t="n">
+        <v>810</v>
+      </c>
+      <c r="G330" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 태초의 발굴삽 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="13" t="n"/>
+      <c r="B331" s="11" t="n">
+        <v>30103</v>
+      </c>
+      <c r="C331" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="D331" s="11" t="n">
+        <v>1306</v>
+      </c>
+      <c r="E331" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F331" s="11" t="n">
+        <v>810</v>
+      </c>
+      <c r="G331" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 산신의 곡괭이 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="13" t="n"/>
+      <c r="B332" s="11" t="n">
+        <v>30104</v>
+      </c>
+      <c r="C332" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="D332" s="11" t="n">
+        <v>1406</v>
+      </c>
+      <c r="E332" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F332" s="11" t="n">
+        <v>810</v>
+      </c>
+      <c r="G332" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 세계수의 도끼 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="13" t="n"/>
+      <c r="B333" s="11" t="n">
+        <v>30105</v>
+      </c>
+      <c r="C333" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="D333" s="11" t="n">
+        <v>1506</v>
+      </c>
+      <c r="E333" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F333" s="11" t="n">
+        <v>810</v>
+      </c>
+      <c r="G333" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 월신의 활 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="13" t="n"/>
+      <c r="B334" s="11" t="n">
+        <v>30106</v>
+      </c>
+      <c r="C334" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="D334" s="11" t="n">
+        <v>2007</v>
+      </c>
+      <c r="E334" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F334" s="11" t="n">
+        <v>810</v>
+      </c>
+      <c r="G334" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 창세의 고리 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="13" t="n"/>
+      <c r="B335" s="11" t="n">
+        <v>30107</v>
+      </c>
+      <c r="C335" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="D335" s="11" t="n">
+        <v>3106</v>
+      </c>
+      <c r="E335" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F335" s="11" t="n">
+        <v>810</v>
+      </c>
+      <c r="G335" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 풍요의 성석 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" s="13" t="n"/>
+      <c r="B336" s="11" t="n">
+        <v>30108</v>
+      </c>
+      <c r="C336" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="D336" s="11" t="n">
+        <v>3206</v>
+      </c>
+      <c r="E336" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F336" s="11" t="n">
+        <v>810</v>
+      </c>
+      <c r="G336" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 태고의 성석 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="13" t="n"/>
+      <c r="B337" s="11" t="n">
+        <v>30109</v>
+      </c>
+      <c r="C337" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="D337" s="11" t="n">
+        <v>3306</v>
+      </c>
+      <c r="E337" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F337" s="11" t="n">
+        <v>810</v>
+      </c>
+      <c r="G337" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 광신의 성석 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="13" t="n"/>
+      <c r="B338" s="11" t="n">
+        <v>30110</v>
+      </c>
+      <c r="C338" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="D338" s="11" t="n">
+        <v>3406</v>
+      </c>
+      <c r="E338" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F338" s="11" t="n">
+        <v>810</v>
+      </c>
+      <c r="G338" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 세계수 성석 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="13" t="n"/>
+      <c r="B339" s="11" t="n">
+        <v>30111</v>
+      </c>
+      <c r="C339" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="D339" s="11" t="n">
+        <v>3506</v>
+      </c>
+      <c r="E339" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F339" s="11" t="n">
+        <v>810</v>
+      </c>
+      <c r="G339" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 월광 성석 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="13" t="n"/>
+      <c r="B340" s="11" t="n">
+        <v>31101</v>
+      </c>
+      <c r="C340" s="11" t="n">
+        <v>31</v>
+      </c>
+      <c r="D340" s="11" t="n">
+        <v>1106</v>
+      </c>
+      <c r="E340" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F340" s="11" t="n">
+        <v>810</v>
+      </c>
+      <c r="G340" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 대지모의 호미 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="13" t="n"/>
+      <c r="B341" s="11" t="n">
+        <v>31102</v>
+      </c>
+      <c r="C341" s="11" t="n">
+        <v>31</v>
+      </c>
+      <c r="D341" s="11" t="n">
+        <v>1206</v>
+      </c>
+      <c r="E341" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F341" s="11" t="n">
+        <v>810</v>
+      </c>
+      <c r="G341" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 태초의 발굴삽 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="13" t="n"/>
+      <c r="B342" s="11" t="n">
+        <v>31103</v>
+      </c>
+      <c r="C342" s="11" t="n">
+        <v>31</v>
+      </c>
+      <c r="D342" s="11" t="n">
+        <v>1306</v>
+      </c>
+      <c r="E342" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F342" s="11" t="n">
+        <v>810</v>
+      </c>
+      <c r="G342" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 산신의 곡괭이 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="13" t="n"/>
+      <c r="B343" s="11" t="n">
+        <v>31104</v>
+      </c>
+      <c r="C343" s="11" t="n">
+        <v>31</v>
+      </c>
+      <c r="D343" s="11" t="n">
+        <v>1406</v>
+      </c>
+      <c r="E343" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F343" s="11" t="n">
+        <v>810</v>
+      </c>
+      <c r="G343" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 세계수의 도끼 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="13" t="n"/>
+      <c r="B344" s="11" t="n">
+        <v>31105</v>
+      </c>
+      <c r="C344" s="11" t="n">
+        <v>31</v>
+      </c>
+      <c r="D344" s="11" t="n">
+        <v>1506</v>
+      </c>
+      <c r="E344" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F344" s="11" t="n">
+        <v>810</v>
+      </c>
+      <c r="G344" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 월신의 활 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" s="13" t="n"/>
+      <c r="B345" s="11" t="n">
+        <v>31106</v>
+      </c>
+      <c r="C345" s="11" t="n">
+        <v>31</v>
+      </c>
+      <c r="D345" s="11" t="n">
+        <v>2007</v>
+      </c>
+      <c r="E345" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F345" s="11" t="n">
+        <v>810</v>
+      </c>
+      <c r="G345" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 창세의 고리 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="13" t="n"/>
+      <c r="B346" s="11" t="n">
+        <v>31107</v>
+      </c>
+      <c r="C346" s="11" t="n">
+        <v>31</v>
+      </c>
+      <c r="D346" s="11" t="n">
+        <v>3106</v>
+      </c>
+      <c r="E346" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F346" s="11" t="n">
+        <v>810</v>
+      </c>
+      <c r="G346" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 풍요의 성석 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="13" t="n"/>
+      <c r="B347" s="11" t="n">
+        <v>31108</v>
+      </c>
+      <c r="C347" s="11" t="n">
+        <v>31</v>
+      </c>
+      <c r="D347" s="11" t="n">
+        <v>3206</v>
+      </c>
+      <c r="E347" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F347" s="11" t="n">
+        <v>810</v>
+      </c>
+      <c r="G347" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 태고의 성석 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="13" t="n"/>
+      <c r="B348" s="11" t="n">
+        <v>31109</v>
+      </c>
+      <c r="C348" s="11" t="n">
+        <v>31</v>
+      </c>
+      <c r="D348" s="11" t="n">
+        <v>3306</v>
+      </c>
+      <c r="E348" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F348" s="11" t="n">
+        <v>810</v>
+      </c>
+      <c r="G348" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 광신의 성석 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="13" t="n"/>
+      <c r="B349" s="11" t="n">
+        <v>31110</v>
+      </c>
+      <c r="C349" s="11" t="n">
+        <v>31</v>
+      </c>
+      <c r="D349" s="11" t="n">
+        <v>3406</v>
+      </c>
+      <c r="E349" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F349" s="11" t="n">
+        <v>810</v>
+      </c>
+      <c r="G349" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 세계수 성석 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" s="13" t="n"/>
+      <c r="B350" s="11" t="n">
+        <v>31111</v>
+      </c>
+      <c r="C350" s="11" t="n">
+        <v>31</v>
+      </c>
+      <c r="D350" s="11" t="n">
+        <v>3506</v>
+      </c>
+      <c r="E350" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F350" s="11" t="n">
+        <v>810</v>
+      </c>
+      <c r="G350" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 월광 성석 (감정)</t>
         </is>
       </c>
     </row>
@@ -13054,7 +17123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -13063,7 +17132,7 @@
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -13975,6 +18044,1079 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" s="13" t="n"/>
+      <c r="B40" s="11" t="n">
+        <v>25201</v>
+      </c>
+      <c r="C40" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="D40" s="11" t="n">
+        <v>135</v>
+      </c>
+      <c r="E40" s="11" t="n">
+        <v>271</v>
+      </c>
+      <c r="F40" s="11" t="n">
+        <v>22500</v>
+      </c>
+      <c r="G40" s="12" t="inlineStr">
+        <is>
+          <t>골드 135~271 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="13" t="n"/>
+      <c r="B41" s="11" t="n">
+        <v>25202</v>
+      </c>
+      <c r="C41" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="D41" s="11" t="n">
+        <v>271</v>
+      </c>
+      <c r="E41" s="11" t="n">
+        <v>677</v>
+      </c>
+      <c r="F41" s="11" t="n">
+        <v>7500</v>
+      </c>
+      <c r="G41" s="12" t="inlineStr">
+        <is>
+          <t>골드 271~677 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="13" t="n"/>
+      <c r="B42" s="11" t="n">
+        <v>26201</v>
+      </c>
+      <c r="C42" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="D42" s="11" t="n">
+        <v>1219</v>
+      </c>
+      <c r="E42" s="11" t="n">
+        <v>2438</v>
+      </c>
+      <c r="F42" s="11" t="n">
+        <v>22500</v>
+      </c>
+      <c r="G42" s="12" t="inlineStr">
+        <is>
+          <t>골드 1219~2438 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="13" t="n"/>
+      <c r="B43" s="11" t="n">
+        <v>26202</v>
+      </c>
+      <c r="C43" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="D43" s="11" t="n">
+        <v>2438</v>
+      </c>
+      <c r="E43" s="11" t="n">
+        <v>6095</v>
+      </c>
+      <c r="F43" s="11" t="n">
+        <v>7500</v>
+      </c>
+      <c r="G43" s="12" t="inlineStr">
+        <is>
+          <t>골드 2438~6095 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="13" t="n"/>
+      <c r="B44" s="11" t="n">
+        <v>27201</v>
+      </c>
+      <c r="C44" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="D44" s="11" t="n">
+        <v>12190</v>
+      </c>
+      <c r="E44" s="11" t="n">
+        <v>24381</v>
+      </c>
+      <c r="F44" s="11" t="n">
+        <v>22500</v>
+      </c>
+      <c r="G44" s="12" t="inlineStr">
+        <is>
+          <t>골드 12190~24381 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="13" t="n"/>
+      <c r="B45" s="11" t="n">
+        <v>27202</v>
+      </c>
+      <c r="C45" s="11" t="n">
+        <v>27</v>
+      </c>
+      <c r="D45" s="11" t="n">
+        <v>24381</v>
+      </c>
+      <c r="E45" s="11" t="n">
+        <v>60952</v>
+      </c>
+      <c r="F45" s="11" t="n">
+        <v>7500</v>
+      </c>
+      <c r="G45" s="12" t="inlineStr">
+        <is>
+          <t>골드 24381~60952 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="13" t="n"/>
+      <c r="B46" s="11" t="n">
+        <v>28201</v>
+      </c>
+      <c r="C46" s="11" t="n">
+        <v>28</v>
+      </c>
+      <c r="D46" s="11" t="n">
+        <v>36572</v>
+      </c>
+      <c r="E46" s="11" t="n">
+        <v>73143</v>
+      </c>
+      <c r="F46" s="11" t="n">
+        <v>22500</v>
+      </c>
+      <c r="G46" s="12" t="inlineStr">
+        <is>
+          <t>골드 36572~73143 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="13" t="n"/>
+      <c r="B47" s="11" t="n">
+        <v>28202</v>
+      </c>
+      <c r="C47" s="11" t="n">
+        <v>28</v>
+      </c>
+      <c r="D47" s="11" t="n">
+        <v>73143</v>
+      </c>
+      <c r="E47" s="11" t="n">
+        <v>182858</v>
+      </c>
+      <c r="F47" s="11" t="n">
+        <v>7500</v>
+      </c>
+      <c r="G47" s="12" t="inlineStr">
+        <is>
+          <t>골드 73143~182858 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="13" t="n"/>
+      <c r="B48" s="11" t="n">
+        <v>29201</v>
+      </c>
+      <c r="C48" s="11" t="n">
+        <v>29</v>
+      </c>
+      <c r="D48" s="11" t="n">
+        <v>109714</v>
+      </c>
+      <c r="E48" s="11" t="n">
+        <v>219429</v>
+      </c>
+      <c r="F48" s="11" t="n">
+        <v>22500</v>
+      </c>
+      <c r="G48" s="12" t="inlineStr">
+        <is>
+          <t>골드 109714~219429 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="13" t="n"/>
+      <c r="B49" s="11" t="n">
+        <v>29202</v>
+      </c>
+      <c r="C49" s="11" t="n">
+        <v>29</v>
+      </c>
+      <c r="D49" s="11" t="n">
+        <v>219429</v>
+      </c>
+      <c r="E49" s="11" t="n">
+        <v>548572</v>
+      </c>
+      <c r="F49" s="11" t="n">
+        <v>7500</v>
+      </c>
+      <c r="G49" s="12" t="inlineStr">
+        <is>
+          <t>골드 219429~548572 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="13" t="n"/>
+      <c r="B50" s="11" t="n">
+        <v>30201</v>
+      </c>
+      <c r="C50" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="D50" s="11" t="n">
+        <v>219428</v>
+      </c>
+      <c r="E50" s="11" t="n">
+        <v>438858</v>
+      </c>
+      <c r="F50" s="11" t="n">
+        <v>22500</v>
+      </c>
+      <c r="G50" s="12" t="inlineStr">
+        <is>
+          <t>골드 219428~438858 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="13" t="n"/>
+      <c r="B51" s="11" t="n">
+        <v>30202</v>
+      </c>
+      <c r="C51" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="D51" s="11" t="n">
+        <v>438858</v>
+      </c>
+      <c r="E51" s="11" t="n">
+        <v>1097144</v>
+      </c>
+      <c r="F51" s="11" t="n">
+        <v>7500</v>
+      </c>
+      <c r="G51" s="12" t="inlineStr">
+        <is>
+          <t>골드 438858~1097144 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="13" t="n"/>
+      <c r="B52" s="11" t="n">
+        <v>31201</v>
+      </c>
+      <c r="C52" s="11" t="n">
+        <v>31</v>
+      </c>
+      <c r="D52" s="11" t="n">
+        <v>329142</v>
+      </c>
+      <c r="E52" s="11" t="n">
+        <v>658287</v>
+      </c>
+      <c r="F52" s="11" t="n">
+        <v>22500</v>
+      </c>
+      <c r="G52" s="12" t="inlineStr">
+        <is>
+          <t>골드 329142~658287 (감정)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="13" t="n"/>
+      <c r="B53" s="11" t="n">
+        <v>31202</v>
+      </c>
+      <c r="C53" s="11" t="n">
+        <v>31</v>
+      </c>
+      <c r="D53" s="11" t="n">
+        <v>658287</v>
+      </c>
+      <c r="E53" s="11" t="n">
+        <v>1645716</v>
+      </c>
+      <c r="F53" s="11" t="n">
+        <v>7500</v>
+      </c>
+      <c r="G53" s="12" t="inlineStr">
+        <is>
+          <t>골드 658287~1645716 (감정)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="41" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="13" t="n"/>
+      <c r="B1" s="13" t="n"/>
+      <c r="C1" s="13" t="n"/>
+      <c r="D1" s="13" t="n"/>
+      <c r="E1" s="13" t="n"/>
+      <c r="F1" s="13" t="n"/>
+      <c r="G1" s="13" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="14" t="inlineStr">
+        <is>
+          <t>//</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>아티팩트 가챠 TID</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>가챠 풀 ID</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>아티팩트 TID</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>지급 수량</t>
+        </is>
+      </c>
+      <c r="F2" s="8" t="inlineStr">
+        <is>
+          <t>확률가중치</t>
+        </is>
+      </c>
+      <c r="G2" s="8" t="inlineStr">
+        <is>
+          <t>메모</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="inlineStr">
+        <is>
+          <t>C&amp;S</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="G3" s="9" t="inlineStr">
+        <is>
+          <t>a</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F4" s="9" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="G4" s="9" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>Min</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="n"/>
+      <c r="C5" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="9" t="n"/>
+      <c r="E5" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="9" t="n"/>
+      <c r="G5" s="9" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>Max</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="n"/>
+      <c r="C6" s="9" t="n"/>
+      <c r="D6" s="9" t="n"/>
+      <c r="E6" s="9" t="n"/>
+      <c r="F6" s="9" t="n"/>
+      <c r="G6" s="9" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>Default(Null)</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="n"/>
+      <c r="C7" s="9" t="n"/>
+      <c r="D7" s="9" t="n"/>
+      <c r="E7" s="9" t="n"/>
+      <c r="F7" s="9" t="n"/>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>""</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>Ref</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="n"/>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>GachaInfoTable.GachaInfoTID</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>ArtifactTable.ArtifactTID</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="n"/>
+      <c r="F8" s="9" t="n"/>
+      <c r="G8" s="9" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="n"/>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>GachaArtifactTID</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>GachaId</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>ArtifactTID</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="n"/>
+      <c r="B10" s="11" t="n">
+        <v>25301</v>
+      </c>
+      <c r="C10" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="D10" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="11" t="n">
+        <v>438</v>
+      </c>
+      <c r="G10" s="12" t="inlineStr">
+        <is>
+          <t>일반 아티팩트 No.001 어부의 낡은 부적</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="n"/>
+      <c r="B11" s="11" t="n">
+        <v>25302</v>
+      </c>
+      <c r="C11" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="D11" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E11" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" s="11" t="n">
+        <v>438</v>
+      </c>
+      <c r="G11" s="12" t="inlineStr">
+        <is>
+          <t>일반 아티팩트 No.002 깨진 토기 빗</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="n"/>
+      <c r="B12" s="11" t="n">
+        <v>25303</v>
+      </c>
+      <c r="C12" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="D12" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="11" t="n">
+        <v>438</v>
+      </c>
+      <c r="G12" s="12" t="inlineStr">
+        <is>
+          <t>일반 아티팩트 No.003 녹슨 쇠못</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="n"/>
+      <c r="B13" s="11" t="n">
+        <v>25304</v>
+      </c>
+      <c r="C13" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="D13" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="E13" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="11" t="n">
+        <v>438</v>
+      </c>
+      <c r="G13" s="12" t="inlineStr">
+        <is>
+          <t>일반 아티팩트 No.004 조개 단추</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="n"/>
+      <c r="B14" s="11" t="n">
+        <v>25305</v>
+      </c>
+      <c r="C14" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="D14" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E14" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F14" s="11" t="n">
+        <v>438</v>
+      </c>
+      <c r="G14" s="12" t="inlineStr">
+        <is>
+          <t>일반 아티팩트 No.005 낡은 동전</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="n"/>
+      <c r="B15" s="11" t="n">
+        <v>25306</v>
+      </c>
+      <c r="C15" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="D15" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="E15" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>438</v>
+      </c>
+      <c r="G15" s="12" t="inlineStr">
+        <is>
+          <t>일반 아티팩트 No.006 닳은 숫돌</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="n"/>
+      <c r="B16" s="11" t="n">
+        <v>25307</v>
+      </c>
+      <c r="C16" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="D16" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="E16" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="11" t="n">
+        <v>438</v>
+      </c>
+      <c r="G16" s="12" t="inlineStr">
+        <is>
+          <t>일반 아티팩트 No.007 흙 구슬</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="n"/>
+      <c r="B17" s="11" t="n">
+        <v>25308</v>
+      </c>
+      <c r="C17" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="D17" s="11" t="n">
+        <v>8</v>
+      </c>
+      <c r="E17" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="11" t="n">
+        <v>438</v>
+      </c>
+      <c r="G17" s="12" t="inlineStr">
+        <is>
+          <t>일반 아티팩트 No.008 돌 화살촉</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="n"/>
+      <c r="B18" s="11" t="n">
+        <v>25309</v>
+      </c>
+      <c r="C18" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="D18" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="E18" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="11" t="n">
+        <v>438</v>
+      </c>
+      <c r="G18" s="12" t="inlineStr">
+        <is>
+          <t>일반 아티팩트 No.009 짚신 조각</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="n"/>
+      <c r="B19" s="11" t="n">
+        <v>25310</v>
+      </c>
+      <c r="C19" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="D19" s="11" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" s="11" t="n">
+        <v>438</v>
+      </c>
+      <c r="G19" s="12" t="inlineStr">
+        <is>
+          <t>일반 아티팩트 No.010 녹슨 열쇠</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="n"/>
+      <c r="B20" s="11" t="n">
+        <v>25311</v>
+      </c>
+      <c r="C20" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="D20" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="E20" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F20" s="11" t="n">
+        <v>438</v>
+      </c>
+      <c r="G20" s="12" t="inlineStr">
+        <is>
+          <t>일반 아티팩트 No.011 나무 빗</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="n"/>
+      <c r="B21" s="11" t="n">
+        <v>25312</v>
+      </c>
+      <c r="C21" s="11" t="n">
+        <v>25</v>
+      </c>
+      <c r="D21" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="E21" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="11" t="n">
+        <v>438</v>
+      </c>
+      <c r="G21" s="12" t="inlineStr">
+        <is>
+          <t>일반 아티팩트 No.012 작은 돌 인형</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="n"/>
+      <c r="B22" s="11" t="n">
+        <v>26301</v>
+      </c>
+      <c r="C22" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="D22" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="E22" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F22" s="11" t="n">
+        <v>526</v>
+      </c>
+      <c r="G22" s="12" t="inlineStr">
+        <is>
+          <t>고급 아티팩트 No.013 조개 껍데기 목걸이</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="n"/>
+      <c r="B23" s="11" t="n">
+        <v>26302</v>
+      </c>
+      <c r="C23" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="D23" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="E23" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="11" t="n">
+        <v>526</v>
+      </c>
+      <c r="G23" s="12" t="inlineStr">
+        <is>
+          <t>고급 아티팩트 No.014 토기 술잔</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="n"/>
+      <c r="B24" s="11" t="n">
+        <v>26303</v>
+      </c>
+      <c r="C24" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="D24" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="E24" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F24" s="11" t="n">
+        <v>526</v>
+      </c>
+      <c r="G24" s="12" t="inlineStr">
+        <is>
+          <t>고급 아티팩트 No.015 뼈 바늘</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="n"/>
+      <c r="B25" s="11" t="n">
+        <v>26304</v>
+      </c>
+      <c r="C25" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="D25" s="11" t="n">
+        <v>16</v>
+      </c>
+      <c r="E25" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F25" s="11" t="n">
+        <v>526</v>
+      </c>
+      <c r="G25" s="12" t="inlineStr">
+        <is>
+          <t>고급 아티팩트 No.016 조약돌 팔찌</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="13" t="n"/>
+      <c r="B26" s="11" t="n">
+        <v>26305</v>
+      </c>
+      <c r="C26" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="D26" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="E26" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F26" s="11" t="n">
+        <v>526</v>
+      </c>
+      <c r="G26" s="12" t="inlineStr">
+        <is>
+          <t>고급 아티팩트 No.017 그물추</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="13" t="n"/>
+      <c r="B27" s="11" t="n">
+        <v>26306</v>
+      </c>
+      <c r="C27" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="D27" s="11" t="n">
+        <v>18</v>
+      </c>
+      <c r="E27" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F27" s="11" t="n">
+        <v>526</v>
+      </c>
+      <c r="G27" s="12" t="inlineStr">
+        <is>
+          <t>고급 아티팩트 No.018 갈대 피리</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="13" t="n"/>
+      <c r="B28" s="11" t="n">
+        <v>26307</v>
+      </c>
+      <c r="C28" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="D28" s="11" t="n">
+        <v>19</v>
+      </c>
+      <c r="E28" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="11" t="n">
+        <v>526</v>
+      </c>
+      <c r="G28" s="12" t="inlineStr">
+        <is>
+          <t>고급 아티팩트 No.019 모래시계 조각</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="13" t="n"/>
+      <c r="B29" s="11" t="n">
+        <v>26308</v>
+      </c>
+      <c r="C29" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="D29" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="E29" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F29" s="11" t="n">
+        <v>526</v>
+      </c>
+      <c r="G29" s="12" t="inlineStr">
+        <is>
+          <t>고급 아티팩트 No.020 나무 가면</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="13" t="n"/>
+      <c r="B30" s="11" t="n">
+        <v>26309</v>
+      </c>
+      <c r="C30" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="D30" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="E30" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" s="11" t="n">
+        <v>526</v>
+      </c>
+      <c r="G30" s="12" t="inlineStr">
+        <is>
+          <t>고급 아티팩트 No.021 흙 인형</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="13" t="n"/>
+      <c r="B31" s="11" t="n">
+        <v>26310</v>
+      </c>
+      <c r="C31" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="D31" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="E31" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F31" s="11" t="n">
+        <v>526</v>
+      </c>
+      <c r="G31" s="12" t="inlineStr">
+        <is>
+          <t>고급 아티팩트 No.022 돌 도끼</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>

--- a/GameDesign/Excel/Gacha.xlsx
+++ b/GameDesign/Excel/Gacha.xlsx
@@ -591,7 +591,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -7110,12 +7110,12 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+  <legacyDrawing r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -7228,7 +7228,7 @@
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>lstring</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
@@ -8090,12 +8090,12 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+  <legacyDrawing r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -9025,12 +9025,12 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+  <legacyDrawing r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -17113,12 +17113,12 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+  <legacyDrawing r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -18368,12 +18368,12 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+  <legacyDrawing r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -19119,6 +19119,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+  <legacyDrawing r:id="anysvml"/>
 </worksheet>
 </file>
--- a/GameDesign/Excel/Gacha.xlsx
+++ b/GameDesign/Excel/Gacha.xlsx
@@ -591,7 +591,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -7110,17 +7110,17 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing r:id="anysvml"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -8088,19 +8088,127 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="13" t="n"/>
+      <c r="B37" s="11" t="n">
+        <v>32</v>
+      </c>
+      <c r="C37" s="12" t="inlineStr">
+        <is>
+          <t>캐릭터 뽑기권 A</t>
+        </is>
+      </c>
+      <c r="D37" s="12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="12" t="inlineStr">
+        <is>
+          <t>뽑기권 전용 — 골드로 뽑을 수 없다 · 희귀 이하 (아이템 100071)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="13" t="n"/>
+      <c r="B38" s="11" t="n">
+        <v>33</v>
+      </c>
+      <c r="C38" s="12" t="inlineStr">
+        <is>
+          <t>캐릭터 뽑기권 B</t>
+        </is>
+      </c>
+      <c r="D38" s="12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E38" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="12" t="inlineStr">
+        <is>
+          <t>뽑기권 전용 — 골드로 뽑을 수 없다 · 영웅 이하 (아이템 100072)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="13" t="n"/>
+      <c r="B39" s="11" t="n">
+        <v>34</v>
+      </c>
+      <c r="C39" s="12" t="inlineStr">
+        <is>
+          <t>캐릭터 뽑기권 C</t>
+        </is>
+      </c>
+      <c r="D39" s="12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="12" t="inlineStr">
+        <is>
+          <t>뽑기권 전용 — 골드로 뽑을 수 없다 · 전설 이하 (아이템 100073)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="13" t="n"/>
+      <c r="B40" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="C40" s="12" t="inlineStr">
+        <is>
+          <t>캐릭터 뽑기권 D</t>
+        </is>
+      </c>
+      <c r="D40" s="12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="E40" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G40" s="12" t="inlineStr">
+        <is>
+          <t>뽑기권 전용 — 골드로 뽑을 수 없다 · 신화 이하 (아이템 100074)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing r:id="anysvml"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -8109,7 +8217,7 @@
     <col width="29" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9023,14 +9131,2452 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" s="13" t="n"/>
+      <c r="B40" s="11" t="n">
+        <v>32001</v>
+      </c>
+      <c r="C40" s="11" t="n">
+        <v>32</v>
+      </c>
+      <c r="D40" s="11" t="n">
+        <v>1001</v>
+      </c>
+      <c r="E40" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" s="11" t="n">
+        <v>7700</v>
+      </c>
+      <c r="G40" s="12" t="inlineStr">
+        <is>
+          <t>Common 떠돌이 전사 (뽑기권 A)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="13" t="n"/>
+      <c r="B41" s="11" t="n">
+        <v>32002</v>
+      </c>
+      <c r="C41" s="11" t="n">
+        <v>32</v>
+      </c>
+      <c r="D41" s="11" t="n">
+        <v>1007</v>
+      </c>
+      <c r="E41" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" s="11" t="n">
+        <v>7700</v>
+      </c>
+      <c r="G41" s="12" t="inlineStr">
+        <is>
+          <t>Common 들쥐 (뽑기권 A)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="13" t="n"/>
+      <c r="B42" s="11" t="n">
+        <v>32003</v>
+      </c>
+      <c r="C42" s="11" t="n">
+        <v>32</v>
+      </c>
+      <c r="D42" s="11" t="n">
+        <v>1008</v>
+      </c>
+      <c r="E42" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F42" s="11" t="n">
+        <v>7700</v>
+      </c>
+      <c r="G42" s="12" t="inlineStr">
+        <is>
+          <t>Common 물방개미 (뽑기권 A)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="13" t="n"/>
+      <c r="B43" s="11" t="n">
+        <v>32004</v>
+      </c>
+      <c r="C43" s="11" t="n">
+        <v>32</v>
+      </c>
+      <c r="D43" s="11" t="n">
+        <v>1009</v>
+      </c>
+      <c r="E43" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F43" s="11" t="n">
+        <v>7700</v>
+      </c>
+      <c r="G43" s="12" t="inlineStr">
+        <is>
+          <t>Common 동굴 박쥐 (뽑기권 A)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="13" t="n"/>
+      <c r="B44" s="11" t="n">
+        <v>32005</v>
+      </c>
+      <c r="C44" s="11" t="n">
+        <v>32</v>
+      </c>
+      <c r="D44" s="11" t="n">
+        <v>1010</v>
+      </c>
+      <c r="E44" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F44" s="11" t="n">
+        <v>7700</v>
+      </c>
+      <c r="G44" s="12" t="inlineStr">
+        <is>
+          <t>Common 톱니쥐 (뽑기권 A)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="13" t="n"/>
+      <c r="B45" s="11" t="n">
+        <v>32006</v>
+      </c>
+      <c r="C45" s="11" t="n">
+        <v>32</v>
+      </c>
+      <c r="D45" s="11" t="n">
+        <v>1011</v>
+      </c>
+      <c r="E45" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" s="11" t="n">
+        <v>7700</v>
+      </c>
+      <c r="G45" s="12" t="inlineStr">
+        <is>
+          <t>Common 흡혈 박쥐 (뽑기권 A)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="13" t="n"/>
+      <c r="B46" s="11" t="n">
+        <v>32007</v>
+      </c>
+      <c r="C46" s="11" t="n">
+        <v>32</v>
+      </c>
+      <c r="D46" s="11" t="n">
+        <v>1002</v>
+      </c>
+      <c r="E46" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F46" s="11" t="n">
+        <v>3885</v>
+      </c>
+      <c r="G46" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon 숲 슬라임 (뽑기권 A)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="13" t="n"/>
+      <c r="B47" s="11" t="n">
+        <v>32008</v>
+      </c>
+      <c r="C47" s="11" t="n">
+        <v>32</v>
+      </c>
+      <c r="D47" s="11" t="n">
+        <v>1003</v>
+      </c>
+      <c r="E47" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" s="11" t="n">
+        <v>3885</v>
+      </c>
+      <c r="G47" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon 뿔쥐 (뽑기권 A)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="13" t="n"/>
+      <c r="B48" s="11" t="n">
+        <v>32009</v>
+      </c>
+      <c r="C48" s="11" t="n">
+        <v>32</v>
+      </c>
+      <c r="D48" s="11" t="n">
+        <v>1004</v>
+      </c>
+      <c r="E48" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F48" s="11" t="n">
+        <v>3885</v>
+      </c>
+      <c r="G48" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon 가시 슬라임 (뽑기권 A)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="13" t="n"/>
+      <c r="B49" s="11" t="n">
+        <v>32010</v>
+      </c>
+      <c r="C49" s="11" t="n">
+        <v>32</v>
+      </c>
+      <c r="D49" s="11" t="n">
+        <v>1005</v>
+      </c>
+      <c r="E49" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F49" s="11" t="n">
+        <v>3885</v>
+      </c>
+      <c r="G49" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon 방랑 기사 (뽑기권 A)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="13" t="n"/>
+      <c r="B50" s="11" t="n">
+        <v>32011</v>
+      </c>
+      <c r="C50" s="11" t="n">
+        <v>32</v>
+      </c>
+      <c r="D50" s="11" t="n">
+        <v>1006</v>
+      </c>
+      <c r="E50" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F50" s="11" t="n">
+        <v>3885</v>
+      </c>
+      <c r="G50" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon 날개 눈알 (뽑기권 A)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="13" t="n"/>
+      <c r="B51" s="11" t="n">
+        <v>32012</v>
+      </c>
+      <c r="C51" s="11" t="n">
+        <v>32</v>
+      </c>
+      <c r="D51" s="11" t="n">
+        <v>1012</v>
+      </c>
+      <c r="E51" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F51" s="11" t="n">
+        <v>3885</v>
+      </c>
+      <c r="G51" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon 망령 마법사 (뽑기권 A)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="13" t="n"/>
+      <c r="B52" s="11" t="n">
+        <v>32013</v>
+      </c>
+      <c r="C52" s="11" t="n">
+        <v>32</v>
+      </c>
+      <c r="D52" s="11" t="n">
+        <v>1013</v>
+      </c>
+      <c r="E52" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F52" s="11" t="n">
+        <v>3885</v>
+      </c>
+      <c r="G52" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon 화염 마법사 (뽑기권 A)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="13" t="n"/>
+      <c r="B53" s="11" t="n">
+        <v>32014</v>
+      </c>
+      <c r="C53" s="11" t="n">
+        <v>32</v>
+      </c>
+      <c r="D53" s="11" t="n">
+        <v>1014</v>
+      </c>
+      <c r="E53" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F53" s="11" t="n">
+        <v>3885</v>
+      </c>
+      <c r="G53" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon 솔방울곰 (뽑기권 A)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="13" t="n"/>
+      <c r="B54" s="11" t="n">
+        <v>32015</v>
+      </c>
+      <c r="C54" s="11" t="n">
+        <v>32</v>
+      </c>
+      <c r="D54" s="11" t="n">
+        <v>1015</v>
+      </c>
+      <c r="E54" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F54" s="11" t="n">
+        <v>960</v>
+      </c>
+      <c r="G54" s="12" t="inlineStr">
+        <is>
+          <t>Rare 미믹 (뽑기권 A)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="13" t="n"/>
+      <c r="B55" s="11" t="n">
+        <v>32016</v>
+      </c>
+      <c r="C55" s="11" t="n">
+        <v>32</v>
+      </c>
+      <c r="D55" s="11" t="n">
+        <v>1016</v>
+      </c>
+      <c r="E55" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F55" s="11" t="n">
+        <v>960</v>
+      </c>
+      <c r="G55" s="12" t="inlineStr">
+        <is>
+          <t>Rare 버섯 인간 (뽑기권 A)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="13" t="n"/>
+      <c r="B56" s="11" t="n">
+        <v>32017</v>
+      </c>
+      <c r="C56" s="11" t="n">
+        <v>32</v>
+      </c>
+      <c r="D56" s="11" t="n">
+        <v>1017</v>
+      </c>
+      <c r="E56" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F56" s="11" t="n">
+        <v>960</v>
+      </c>
+      <c r="G56" s="12" t="inlineStr">
+        <is>
+          <t>Rare 고블린 (뽑기권 A)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="13" t="n"/>
+      <c r="B57" s="11" t="n">
+        <v>32018</v>
+      </c>
+      <c r="C57" s="11" t="n">
+        <v>32</v>
+      </c>
+      <c r="D57" s="11" t="n">
+        <v>1018</v>
+      </c>
+      <c r="E57" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F57" s="11" t="n">
+        <v>960</v>
+      </c>
+      <c r="G57" s="12" t="inlineStr">
+        <is>
+          <t>Rare 은빛 기사 (뽑기권 A)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="13" t="n"/>
+      <c r="B58" s="11" t="n">
+        <v>32019</v>
+      </c>
+      <c r="C58" s="11" t="n">
+        <v>32</v>
+      </c>
+      <c r="D58" s="11" t="n">
+        <v>1019</v>
+      </c>
+      <c r="E58" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F58" s="11" t="n">
+        <v>960</v>
+      </c>
+      <c r="G58" s="12" t="inlineStr">
+        <is>
+          <t>Rare 그림자 마법사 (뽑기권 A)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="13" t="n"/>
+      <c r="B59" s="11" t="n">
+        <v>32020</v>
+      </c>
+      <c r="C59" s="11" t="n">
+        <v>32</v>
+      </c>
+      <c r="D59" s="11" t="n">
+        <v>1020</v>
+      </c>
+      <c r="E59" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F59" s="11" t="n">
+        <v>960</v>
+      </c>
+      <c r="G59" s="12" t="inlineStr">
+        <is>
+          <t>Rare 무예가 (뽑기권 A)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="13" t="n"/>
+      <c r="B60" s="11" t="n">
+        <v>32021</v>
+      </c>
+      <c r="C60" s="11" t="n">
+        <v>32</v>
+      </c>
+      <c r="D60" s="11" t="n">
+        <v>1021</v>
+      </c>
+      <c r="E60" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F60" s="11" t="n">
+        <v>960</v>
+      </c>
+      <c r="G60" s="12" t="inlineStr">
+        <is>
+          <t>Rare 해골 병사 (뽑기권 A)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="13" t="n"/>
+      <c r="B61" s="11" t="n">
+        <v>33001</v>
+      </c>
+      <c r="C61" s="11" t="n">
+        <v>33</v>
+      </c>
+      <c r="D61" s="11" t="n">
+        <v>1001</v>
+      </c>
+      <c r="E61" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F61" s="11" t="n">
+        <v>4480</v>
+      </c>
+      <c r="G61" s="12" t="inlineStr">
+        <is>
+          <t>Common 떠돌이 전사 (뽑기권 B)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="13" t="n"/>
+      <c r="B62" s="11" t="n">
+        <v>33002</v>
+      </c>
+      <c r="C62" s="11" t="n">
+        <v>33</v>
+      </c>
+      <c r="D62" s="11" t="n">
+        <v>1007</v>
+      </c>
+      <c r="E62" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F62" s="11" t="n">
+        <v>4480</v>
+      </c>
+      <c r="G62" s="12" t="inlineStr">
+        <is>
+          <t>Common 들쥐 (뽑기권 B)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="13" t="n"/>
+      <c r="B63" s="11" t="n">
+        <v>33003</v>
+      </c>
+      <c r="C63" s="11" t="n">
+        <v>33</v>
+      </c>
+      <c r="D63" s="11" t="n">
+        <v>1008</v>
+      </c>
+      <c r="E63" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F63" s="11" t="n">
+        <v>4480</v>
+      </c>
+      <c r="G63" s="12" t="inlineStr">
+        <is>
+          <t>Common 물방개미 (뽑기권 B)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="13" t="n"/>
+      <c r="B64" s="11" t="n">
+        <v>33004</v>
+      </c>
+      <c r="C64" s="11" t="n">
+        <v>33</v>
+      </c>
+      <c r="D64" s="11" t="n">
+        <v>1009</v>
+      </c>
+      <c r="E64" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F64" s="11" t="n">
+        <v>4480</v>
+      </c>
+      <c r="G64" s="12" t="inlineStr">
+        <is>
+          <t>Common 동굴 박쥐 (뽑기권 B)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="13" t="n"/>
+      <c r="B65" s="11" t="n">
+        <v>33005</v>
+      </c>
+      <c r="C65" s="11" t="n">
+        <v>33</v>
+      </c>
+      <c r="D65" s="11" t="n">
+        <v>1010</v>
+      </c>
+      <c r="E65" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F65" s="11" t="n">
+        <v>4480</v>
+      </c>
+      <c r="G65" s="12" t="inlineStr">
+        <is>
+          <t>Common 톱니쥐 (뽑기권 B)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="13" t="n"/>
+      <c r="B66" s="11" t="n">
+        <v>33006</v>
+      </c>
+      <c r="C66" s="11" t="n">
+        <v>33</v>
+      </c>
+      <c r="D66" s="11" t="n">
+        <v>1011</v>
+      </c>
+      <c r="E66" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F66" s="11" t="n">
+        <v>4480</v>
+      </c>
+      <c r="G66" s="12" t="inlineStr">
+        <is>
+          <t>Common 흡혈 박쥐 (뽑기권 B)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="13" t="n"/>
+      <c r="B67" s="11" t="n">
+        <v>33007</v>
+      </c>
+      <c r="C67" s="11" t="n">
+        <v>33</v>
+      </c>
+      <c r="D67" s="11" t="n">
+        <v>1002</v>
+      </c>
+      <c r="E67" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F67" s="11" t="n">
+        <v>3990</v>
+      </c>
+      <c r="G67" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon 숲 슬라임 (뽑기권 B)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="13" t="n"/>
+      <c r="B68" s="11" t="n">
+        <v>33008</v>
+      </c>
+      <c r="C68" s="11" t="n">
+        <v>33</v>
+      </c>
+      <c r="D68" s="11" t="n">
+        <v>1003</v>
+      </c>
+      <c r="E68" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F68" s="11" t="n">
+        <v>3990</v>
+      </c>
+      <c r="G68" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon 뿔쥐 (뽑기권 B)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="13" t="n"/>
+      <c r="B69" s="11" t="n">
+        <v>33009</v>
+      </c>
+      <c r="C69" s="11" t="n">
+        <v>33</v>
+      </c>
+      <c r="D69" s="11" t="n">
+        <v>1004</v>
+      </c>
+      <c r="E69" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F69" s="11" t="n">
+        <v>3990</v>
+      </c>
+      <c r="G69" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon 가시 슬라임 (뽑기권 B)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="13" t="n"/>
+      <c r="B70" s="11" t="n">
+        <v>33010</v>
+      </c>
+      <c r="C70" s="11" t="n">
+        <v>33</v>
+      </c>
+      <c r="D70" s="11" t="n">
+        <v>1005</v>
+      </c>
+      <c r="E70" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F70" s="11" t="n">
+        <v>3990</v>
+      </c>
+      <c r="G70" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon 방랑 기사 (뽑기권 B)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="13" t="n"/>
+      <c r="B71" s="11" t="n">
+        <v>33011</v>
+      </c>
+      <c r="C71" s="11" t="n">
+        <v>33</v>
+      </c>
+      <c r="D71" s="11" t="n">
+        <v>1006</v>
+      </c>
+      <c r="E71" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F71" s="11" t="n">
+        <v>3990</v>
+      </c>
+      <c r="G71" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon 날개 눈알 (뽑기권 B)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="13" t="n"/>
+      <c r="B72" s="11" t="n">
+        <v>33012</v>
+      </c>
+      <c r="C72" s="11" t="n">
+        <v>33</v>
+      </c>
+      <c r="D72" s="11" t="n">
+        <v>1012</v>
+      </c>
+      <c r="E72" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F72" s="11" t="n">
+        <v>3990</v>
+      </c>
+      <c r="G72" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon 망령 마법사 (뽑기권 B)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="13" t="n"/>
+      <c r="B73" s="11" t="n">
+        <v>33013</v>
+      </c>
+      <c r="C73" s="11" t="n">
+        <v>33</v>
+      </c>
+      <c r="D73" s="11" t="n">
+        <v>1013</v>
+      </c>
+      <c r="E73" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F73" s="11" t="n">
+        <v>3990</v>
+      </c>
+      <c r="G73" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon 화염 마법사 (뽑기권 B)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="13" t="n"/>
+      <c r="B74" s="11" t="n">
+        <v>33014</v>
+      </c>
+      <c r="C74" s="11" t="n">
+        <v>33</v>
+      </c>
+      <c r="D74" s="11" t="n">
+        <v>1014</v>
+      </c>
+      <c r="E74" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F74" s="11" t="n">
+        <v>3990</v>
+      </c>
+      <c r="G74" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon 솔방울곰 (뽑기권 B)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="13" t="n"/>
+      <c r="B75" s="11" t="n">
+        <v>33015</v>
+      </c>
+      <c r="C75" s="11" t="n">
+        <v>33</v>
+      </c>
+      <c r="D75" s="11" t="n">
+        <v>1015</v>
+      </c>
+      <c r="E75" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F75" s="11" t="n">
+        <v>3120</v>
+      </c>
+      <c r="G75" s="12" t="inlineStr">
+        <is>
+          <t>Rare 미믹 (뽑기권 B)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="13" t="n"/>
+      <c r="B76" s="11" t="n">
+        <v>33016</v>
+      </c>
+      <c r="C76" s="11" t="n">
+        <v>33</v>
+      </c>
+      <c r="D76" s="11" t="n">
+        <v>1016</v>
+      </c>
+      <c r="E76" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F76" s="11" t="n">
+        <v>3120</v>
+      </c>
+      <c r="G76" s="12" t="inlineStr">
+        <is>
+          <t>Rare 버섯 인간 (뽑기권 B)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="13" t="n"/>
+      <c r="B77" s="11" t="n">
+        <v>33017</v>
+      </c>
+      <c r="C77" s="11" t="n">
+        <v>33</v>
+      </c>
+      <c r="D77" s="11" t="n">
+        <v>1017</v>
+      </c>
+      <c r="E77" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F77" s="11" t="n">
+        <v>3120</v>
+      </c>
+      <c r="G77" s="12" t="inlineStr">
+        <is>
+          <t>Rare 고블린 (뽑기권 B)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="13" t="n"/>
+      <c r="B78" s="11" t="n">
+        <v>33018</v>
+      </c>
+      <c r="C78" s="11" t="n">
+        <v>33</v>
+      </c>
+      <c r="D78" s="11" t="n">
+        <v>1018</v>
+      </c>
+      <c r="E78" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F78" s="11" t="n">
+        <v>3120</v>
+      </c>
+      <c r="G78" s="12" t="inlineStr">
+        <is>
+          <t>Rare 은빛 기사 (뽑기권 B)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="13" t="n"/>
+      <c r="B79" s="11" t="n">
+        <v>33019</v>
+      </c>
+      <c r="C79" s="11" t="n">
+        <v>33</v>
+      </c>
+      <c r="D79" s="11" t="n">
+        <v>1019</v>
+      </c>
+      <c r="E79" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F79" s="11" t="n">
+        <v>3120</v>
+      </c>
+      <c r="G79" s="12" t="inlineStr">
+        <is>
+          <t>Rare 그림자 마법사 (뽑기권 B)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="13" t="n"/>
+      <c r="B80" s="11" t="n">
+        <v>33020</v>
+      </c>
+      <c r="C80" s="11" t="n">
+        <v>33</v>
+      </c>
+      <c r="D80" s="11" t="n">
+        <v>1020</v>
+      </c>
+      <c r="E80" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F80" s="11" t="n">
+        <v>3120</v>
+      </c>
+      <c r="G80" s="12" t="inlineStr">
+        <is>
+          <t>Rare 무예가 (뽑기권 B)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="13" t="n"/>
+      <c r="B81" s="11" t="n">
+        <v>33021</v>
+      </c>
+      <c r="C81" s="11" t="n">
+        <v>33</v>
+      </c>
+      <c r="D81" s="11" t="n">
+        <v>1021</v>
+      </c>
+      <c r="E81" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F81" s="11" t="n">
+        <v>3120</v>
+      </c>
+      <c r="G81" s="12" t="inlineStr">
+        <is>
+          <t>Rare 해골 병사 (뽑기권 B)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="13" t="n"/>
+      <c r="B82" s="11" t="n">
+        <v>33022</v>
+      </c>
+      <c r="C82" s="11" t="n">
+        <v>33</v>
+      </c>
+      <c r="D82" s="11" t="n">
+        <v>1022</v>
+      </c>
+      <c r="E82" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F82" s="11" t="n">
+        <v>672</v>
+      </c>
+      <c r="G82" s="12" t="inlineStr">
+        <is>
+          <t>Epic 바위 골렘 (뽑기권 B)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="13" t="n"/>
+      <c r="B83" s="11" t="n">
+        <v>33023</v>
+      </c>
+      <c r="C83" s="11" t="n">
+        <v>33</v>
+      </c>
+      <c r="D83" s="11" t="n">
+        <v>1023</v>
+      </c>
+      <c r="E83" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F83" s="11" t="n">
+        <v>672</v>
+      </c>
+      <c r="G83" s="12" t="inlineStr">
+        <is>
+          <t>Epic 붉은 집게게 (뽑기권 B)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="13" t="n"/>
+      <c r="B84" s="11" t="n">
+        <v>33024</v>
+      </c>
+      <c r="C84" s="11" t="n">
+        <v>33</v>
+      </c>
+      <c r="D84" s="11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="E84" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F84" s="11" t="n">
+        <v>672</v>
+      </c>
+      <c r="G84" s="12" t="inlineStr">
+        <is>
+          <t>Epic 대검 전사 (뽑기권 B)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="13" t="n"/>
+      <c r="B85" s="11" t="n">
+        <v>33025</v>
+      </c>
+      <c r="C85" s="11" t="n">
+        <v>33</v>
+      </c>
+      <c r="D85" s="11" t="n">
+        <v>1025</v>
+      </c>
+      <c r="E85" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F85" s="11" t="n">
+        <v>672</v>
+      </c>
+      <c r="G85" s="12" t="inlineStr">
+        <is>
+          <t>Epic 검왕 (뽑기권 B)</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="13" t="n"/>
+      <c r="B86" s="11" t="n">
+        <v>33026</v>
+      </c>
+      <c r="C86" s="11" t="n">
+        <v>33</v>
+      </c>
+      <c r="D86" s="11" t="n">
+        <v>1026</v>
+      </c>
+      <c r="E86" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F86" s="11" t="n">
+        <v>672</v>
+      </c>
+      <c r="G86" s="12" t="inlineStr">
+        <is>
+          <t>Epic 영웅 기사 (뽑기권 B)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="13" t="n"/>
+      <c r="B87" s="11" t="n">
+        <v>34001</v>
+      </c>
+      <c r="C87" s="11" t="n">
+        <v>34</v>
+      </c>
+      <c r="D87" s="11" t="n">
+        <v>1001</v>
+      </c>
+      <c r="E87" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F87" s="11" t="n">
+        <v>3080</v>
+      </c>
+      <c r="G87" s="12" t="inlineStr">
+        <is>
+          <t>Common 떠돌이 전사 (뽑기권 C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="13" t="n"/>
+      <c r="B88" s="11" t="n">
+        <v>34002</v>
+      </c>
+      <c r="C88" s="11" t="n">
+        <v>34</v>
+      </c>
+      <c r="D88" s="11" t="n">
+        <v>1007</v>
+      </c>
+      <c r="E88" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F88" s="11" t="n">
+        <v>3080</v>
+      </c>
+      <c r="G88" s="12" t="inlineStr">
+        <is>
+          <t>Common 들쥐 (뽑기권 C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="13" t="n"/>
+      <c r="B89" s="11" t="n">
+        <v>34003</v>
+      </c>
+      <c r="C89" s="11" t="n">
+        <v>34</v>
+      </c>
+      <c r="D89" s="11" t="n">
+        <v>1008</v>
+      </c>
+      <c r="E89" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F89" s="11" t="n">
+        <v>3080</v>
+      </c>
+      <c r="G89" s="12" t="inlineStr">
+        <is>
+          <t>Common 물방개미 (뽑기권 C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="13" t="n"/>
+      <c r="B90" s="11" t="n">
+        <v>34004</v>
+      </c>
+      <c r="C90" s="11" t="n">
+        <v>34</v>
+      </c>
+      <c r="D90" s="11" t="n">
+        <v>1009</v>
+      </c>
+      <c r="E90" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F90" s="11" t="n">
+        <v>3080</v>
+      </c>
+      <c r="G90" s="12" t="inlineStr">
+        <is>
+          <t>Common 동굴 박쥐 (뽑기권 C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="13" t="n"/>
+      <c r="B91" s="11" t="n">
+        <v>34005</v>
+      </c>
+      <c r="C91" s="11" t="n">
+        <v>34</v>
+      </c>
+      <c r="D91" s="11" t="n">
+        <v>1010</v>
+      </c>
+      <c r="E91" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F91" s="11" t="n">
+        <v>3080</v>
+      </c>
+      <c r="G91" s="12" t="inlineStr">
+        <is>
+          <t>Common 톱니쥐 (뽑기권 C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="13" t="n"/>
+      <c r="B92" s="11" t="n">
+        <v>34006</v>
+      </c>
+      <c r="C92" s="11" t="n">
+        <v>34</v>
+      </c>
+      <c r="D92" s="11" t="n">
+        <v>1011</v>
+      </c>
+      <c r="E92" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F92" s="11" t="n">
+        <v>3080</v>
+      </c>
+      <c r="G92" s="12" t="inlineStr">
+        <is>
+          <t>Common 흡혈 박쥐 (뽑기권 C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="13" t="n"/>
+      <c r="B93" s="11" t="n">
+        <v>34007</v>
+      </c>
+      <c r="C93" s="11" t="n">
+        <v>34</v>
+      </c>
+      <c r="D93" s="11" t="n">
+        <v>1002</v>
+      </c>
+      <c r="E93" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F93" s="11" t="n">
+        <v>3360</v>
+      </c>
+      <c r="G93" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon 숲 슬라임 (뽑기권 C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="13" t="n"/>
+      <c r="B94" s="11" t="n">
+        <v>34008</v>
+      </c>
+      <c r="C94" s="11" t="n">
+        <v>34</v>
+      </c>
+      <c r="D94" s="11" t="n">
+        <v>1003</v>
+      </c>
+      <c r="E94" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F94" s="11" t="n">
+        <v>3360</v>
+      </c>
+      <c r="G94" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon 뿔쥐 (뽑기권 C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="13" t="n"/>
+      <c r="B95" s="11" t="n">
+        <v>34009</v>
+      </c>
+      <c r="C95" s="11" t="n">
+        <v>34</v>
+      </c>
+      <c r="D95" s="11" t="n">
+        <v>1004</v>
+      </c>
+      <c r="E95" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F95" s="11" t="n">
+        <v>3360</v>
+      </c>
+      <c r="G95" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon 가시 슬라임 (뽑기권 C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="13" t="n"/>
+      <c r="B96" s="11" t="n">
+        <v>34010</v>
+      </c>
+      <c r="C96" s="11" t="n">
+        <v>34</v>
+      </c>
+      <c r="D96" s="11" t="n">
+        <v>1005</v>
+      </c>
+      <c r="E96" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F96" s="11" t="n">
+        <v>3360</v>
+      </c>
+      <c r="G96" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon 방랑 기사 (뽑기권 C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="13" t="n"/>
+      <c r="B97" s="11" t="n">
+        <v>34011</v>
+      </c>
+      <c r="C97" s="11" t="n">
+        <v>34</v>
+      </c>
+      <c r="D97" s="11" t="n">
+        <v>1006</v>
+      </c>
+      <c r="E97" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F97" s="11" t="n">
+        <v>3360</v>
+      </c>
+      <c r="G97" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon 날개 눈알 (뽑기권 C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="13" t="n"/>
+      <c r="B98" s="11" t="n">
+        <v>34012</v>
+      </c>
+      <c r="C98" s="11" t="n">
+        <v>34</v>
+      </c>
+      <c r="D98" s="11" t="n">
+        <v>1012</v>
+      </c>
+      <c r="E98" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F98" s="11" t="n">
+        <v>3360</v>
+      </c>
+      <c r="G98" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon 망령 마법사 (뽑기권 C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="13" t="n"/>
+      <c r="B99" s="11" t="n">
+        <v>34013</v>
+      </c>
+      <c r="C99" s="11" t="n">
+        <v>34</v>
+      </c>
+      <c r="D99" s="11" t="n">
+        <v>1013</v>
+      </c>
+      <c r="E99" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F99" s="11" t="n">
+        <v>3360</v>
+      </c>
+      <c r="G99" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon 화염 마법사 (뽑기권 C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="13" t="n"/>
+      <c r="B100" s="11" t="n">
+        <v>34014</v>
+      </c>
+      <c r="C100" s="11" t="n">
+        <v>34</v>
+      </c>
+      <c r="D100" s="11" t="n">
+        <v>1014</v>
+      </c>
+      <c r="E100" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F100" s="11" t="n">
+        <v>3360</v>
+      </c>
+      <c r="G100" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon 솔방울곰 (뽑기권 C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="13" t="n"/>
+      <c r="B101" s="11" t="n">
+        <v>34015</v>
+      </c>
+      <c r="C101" s="11" t="n">
+        <v>34</v>
+      </c>
+      <c r="D101" s="11" t="n">
+        <v>1015</v>
+      </c>
+      <c r="E101" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F101" s="11" t="n">
+        <v>3600</v>
+      </c>
+      <c r="G101" s="12" t="inlineStr">
+        <is>
+          <t>Rare 미믹 (뽑기권 C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="13" t="n"/>
+      <c r="B102" s="11" t="n">
+        <v>34016</v>
+      </c>
+      <c r="C102" s="11" t="n">
+        <v>34</v>
+      </c>
+      <c r="D102" s="11" t="n">
+        <v>1016</v>
+      </c>
+      <c r="E102" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F102" s="11" t="n">
+        <v>3600</v>
+      </c>
+      <c r="G102" s="12" t="inlineStr">
+        <is>
+          <t>Rare 버섯 인간 (뽑기권 C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="13" t="n"/>
+      <c r="B103" s="11" t="n">
+        <v>34017</v>
+      </c>
+      <c r="C103" s="11" t="n">
+        <v>34</v>
+      </c>
+      <c r="D103" s="11" t="n">
+        <v>1017</v>
+      </c>
+      <c r="E103" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F103" s="11" t="n">
+        <v>3600</v>
+      </c>
+      <c r="G103" s="12" t="inlineStr">
+        <is>
+          <t>Rare 고블린 (뽑기권 C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="13" t="n"/>
+      <c r="B104" s="11" t="n">
+        <v>34018</v>
+      </c>
+      <c r="C104" s="11" t="n">
+        <v>34</v>
+      </c>
+      <c r="D104" s="11" t="n">
+        <v>1018</v>
+      </c>
+      <c r="E104" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F104" s="11" t="n">
+        <v>3600</v>
+      </c>
+      <c r="G104" s="12" t="inlineStr">
+        <is>
+          <t>Rare 은빛 기사 (뽑기권 C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="13" t="n"/>
+      <c r="B105" s="11" t="n">
+        <v>34019</v>
+      </c>
+      <c r="C105" s="11" t="n">
+        <v>34</v>
+      </c>
+      <c r="D105" s="11" t="n">
+        <v>1019</v>
+      </c>
+      <c r="E105" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F105" s="11" t="n">
+        <v>3600</v>
+      </c>
+      <c r="G105" s="12" t="inlineStr">
+        <is>
+          <t>Rare 그림자 마법사 (뽑기권 C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="13" t="n"/>
+      <c r="B106" s="11" t="n">
+        <v>34020</v>
+      </c>
+      <c r="C106" s="11" t="n">
+        <v>34</v>
+      </c>
+      <c r="D106" s="11" t="n">
+        <v>1020</v>
+      </c>
+      <c r="E106" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F106" s="11" t="n">
+        <v>3600</v>
+      </c>
+      <c r="G106" s="12" t="inlineStr">
+        <is>
+          <t>Rare 무예가 (뽑기권 C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="13" t="n"/>
+      <c r="B107" s="11" t="n">
+        <v>34021</v>
+      </c>
+      <c r="C107" s="11" t="n">
+        <v>34</v>
+      </c>
+      <c r="D107" s="11" t="n">
+        <v>1021</v>
+      </c>
+      <c r="E107" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F107" s="11" t="n">
+        <v>3600</v>
+      </c>
+      <c r="G107" s="12" t="inlineStr">
+        <is>
+          <t>Rare 해골 병사 (뽑기권 C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="13" t="n"/>
+      <c r="B108" s="11" t="n">
+        <v>34022</v>
+      </c>
+      <c r="C108" s="11" t="n">
+        <v>34</v>
+      </c>
+      <c r="D108" s="11" t="n">
+        <v>1022</v>
+      </c>
+      <c r="E108" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F108" s="11" t="n">
+        <v>2352</v>
+      </c>
+      <c r="G108" s="12" t="inlineStr">
+        <is>
+          <t>Epic 바위 골렘 (뽑기권 C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="13" t="n"/>
+      <c r="B109" s="11" t="n">
+        <v>34023</v>
+      </c>
+      <c r="C109" s="11" t="n">
+        <v>34</v>
+      </c>
+      <c r="D109" s="11" t="n">
+        <v>1023</v>
+      </c>
+      <c r="E109" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F109" s="11" t="n">
+        <v>2352</v>
+      </c>
+      <c r="G109" s="12" t="inlineStr">
+        <is>
+          <t>Epic 붉은 집게게 (뽑기권 C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="13" t="n"/>
+      <c r="B110" s="11" t="n">
+        <v>34024</v>
+      </c>
+      <c r="C110" s="11" t="n">
+        <v>34</v>
+      </c>
+      <c r="D110" s="11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="E110" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F110" s="11" t="n">
+        <v>2352</v>
+      </c>
+      <c r="G110" s="12" t="inlineStr">
+        <is>
+          <t>Epic 대검 전사 (뽑기권 C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="13" t="n"/>
+      <c r="B111" s="11" t="n">
+        <v>34025</v>
+      </c>
+      <c r="C111" s="11" t="n">
+        <v>34</v>
+      </c>
+      <c r="D111" s="11" t="n">
+        <v>1025</v>
+      </c>
+      <c r="E111" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F111" s="11" t="n">
+        <v>2352</v>
+      </c>
+      <c r="G111" s="12" t="inlineStr">
+        <is>
+          <t>Epic 검왕 (뽑기권 C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="13" t="n"/>
+      <c r="B112" s="11" t="n">
+        <v>34026</v>
+      </c>
+      <c r="C112" s="11" t="n">
+        <v>34</v>
+      </c>
+      <c r="D112" s="11" t="n">
+        <v>1026</v>
+      </c>
+      <c r="E112" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F112" s="11" t="n">
+        <v>2352</v>
+      </c>
+      <c r="G112" s="12" t="inlineStr">
+        <is>
+          <t>Epic 영웅 기사 (뽑기권 C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="13" t="n"/>
+      <c r="B113" s="11" t="n">
+        <v>34027</v>
+      </c>
+      <c r="C113" s="11" t="n">
+        <v>34</v>
+      </c>
+      <c r="D113" s="11" t="n">
+        <v>1027</v>
+      </c>
+      <c r="E113" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F113" s="11" t="n">
+        <v>560</v>
+      </c>
+      <c r="G113" s="12" t="inlineStr">
+        <is>
+          <t>Legendary 죽음의 사신 (뽑기권 C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="13" t="n"/>
+      <c r="B114" s="11" t="n">
+        <v>34028</v>
+      </c>
+      <c r="C114" s="11" t="n">
+        <v>34</v>
+      </c>
+      <c r="D114" s="11" t="n">
+        <v>1028</v>
+      </c>
+      <c r="E114" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F114" s="11" t="n">
+        <v>560</v>
+      </c>
+      <c r="G114" s="12" t="inlineStr">
+        <is>
+          <t>Legendary 흑기사 (뽑기권 C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="13" t="n"/>
+      <c r="B115" s="11" t="n">
+        <v>34029</v>
+      </c>
+      <c r="C115" s="11" t="n">
+        <v>34</v>
+      </c>
+      <c r="D115" s="11" t="n">
+        <v>1029</v>
+      </c>
+      <c r="E115" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F115" s="11" t="n">
+        <v>560</v>
+      </c>
+      <c r="G115" s="12" t="inlineStr">
+        <is>
+          <t>Legendary 흑요석골렘 (뽑기권 C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="13" t="n"/>
+      <c r="B116" s="11" t="n">
+        <v>35001</v>
+      </c>
+      <c r="C116" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="D116" s="11" t="n">
+        <v>1001</v>
+      </c>
+      <c r="E116" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F116" s="11" t="n">
+        <v>2240</v>
+      </c>
+      <c r="G116" s="12" t="inlineStr">
+        <is>
+          <t>Common 떠돌이 전사 (뽑기권 D)</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="13" t="n"/>
+      <c r="B117" s="11" t="n">
+        <v>35002</v>
+      </c>
+      <c r="C117" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="D117" s="11" t="n">
+        <v>1007</v>
+      </c>
+      <c r="E117" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F117" s="11" t="n">
+        <v>2240</v>
+      </c>
+      <c r="G117" s="12" t="inlineStr">
+        <is>
+          <t>Common 들쥐 (뽑기권 D)</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="13" t="n"/>
+      <c r="B118" s="11" t="n">
+        <v>35003</v>
+      </c>
+      <c r="C118" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="D118" s="11" t="n">
+        <v>1008</v>
+      </c>
+      <c r="E118" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F118" s="11" t="n">
+        <v>2240</v>
+      </c>
+      <c r="G118" s="12" t="inlineStr">
+        <is>
+          <t>Common 물방개미 (뽑기권 D)</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="13" t="n"/>
+      <c r="B119" s="11" t="n">
+        <v>35004</v>
+      </c>
+      <c r="C119" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="D119" s="11" t="n">
+        <v>1009</v>
+      </c>
+      <c r="E119" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F119" s="11" t="n">
+        <v>2240</v>
+      </c>
+      <c r="G119" s="12" t="inlineStr">
+        <is>
+          <t>Common 동굴 박쥐 (뽑기권 D)</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="13" t="n"/>
+      <c r="B120" s="11" t="n">
+        <v>35005</v>
+      </c>
+      <c r="C120" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="D120" s="11" t="n">
+        <v>1010</v>
+      </c>
+      <c r="E120" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F120" s="11" t="n">
+        <v>2240</v>
+      </c>
+      <c r="G120" s="12" t="inlineStr">
+        <is>
+          <t>Common 톱니쥐 (뽑기권 D)</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="13" t="n"/>
+      <c r="B121" s="11" t="n">
+        <v>35006</v>
+      </c>
+      <c r="C121" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="D121" s="11" t="n">
+        <v>1011</v>
+      </c>
+      <c r="E121" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F121" s="11" t="n">
+        <v>2240</v>
+      </c>
+      <c r="G121" s="12" t="inlineStr">
+        <is>
+          <t>Common 흡혈 박쥐 (뽑기권 D)</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="13" t="n"/>
+      <c r="B122" s="11" t="n">
+        <v>35007</v>
+      </c>
+      <c r="C122" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="D122" s="11" t="n">
+        <v>1002</v>
+      </c>
+      <c r="E122" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F122" s="11" t="n">
+        <v>2835</v>
+      </c>
+      <c r="G122" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon 숲 슬라임 (뽑기권 D)</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="13" t="n"/>
+      <c r="B123" s="11" t="n">
+        <v>35008</v>
+      </c>
+      <c r="C123" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="D123" s="11" t="n">
+        <v>1003</v>
+      </c>
+      <c r="E123" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F123" s="11" t="n">
+        <v>2835</v>
+      </c>
+      <c r="G123" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon 뿔쥐 (뽑기권 D)</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="13" t="n"/>
+      <c r="B124" s="11" t="n">
+        <v>35009</v>
+      </c>
+      <c r="C124" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="D124" s="11" t="n">
+        <v>1004</v>
+      </c>
+      <c r="E124" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F124" s="11" t="n">
+        <v>2835</v>
+      </c>
+      <c r="G124" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon 가시 슬라임 (뽑기권 D)</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="13" t="n"/>
+      <c r="B125" s="11" t="n">
+        <v>35010</v>
+      </c>
+      <c r="C125" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="D125" s="11" t="n">
+        <v>1005</v>
+      </c>
+      <c r="E125" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F125" s="11" t="n">
+        <v>2835</v>
+      </c>
+      <c r="G125" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon 방랑 기사 (뽑기권 D)</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="13" t="n"/>
+      <c r="B126" s="11" t="n">
+        <v>35011</v>
+      </c>
+      <c r="C126" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="D126" s="11" t="n">
+        <v>1006</v>
+      </c>
+      <c r="E126" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F126" s="11" t="n">
+        <v>2835</v>
+      </c>
+      <c r="G126" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon 날개 눈알 (뽑기권 D)</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="13" t="n"/>
+      <c r="B127" s="11" t="n">
+        <v>35012</v>
+      </c>
+      <c r="C127" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="D127" s="11" t="n">
+        <v>1012</v>
+      </c>
+      <c r="E127" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F127" s="11" t="n">
+        <v>2835</v>
+      </c>
+      <c r="G127" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon 망령 마법사 (뽑기권 D)</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="13" t="n"/>
+      <c r="B128" s="11" t="n">
+        <v>35013</v>
+      </c>
+      <c r="C128" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="D128" s="11" t="n">
+        <v>1013</v>
+      </c>
+      <c r="E128" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F128" s="11" t="n">
+        <v>2835</v>
+      </c>
+      <c r="G128" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon 화염 마법사 (뽑기권 D)</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="13" t="n"/>
+      <c r="B129" s="11" t="n">
+        <v>35014</v>
+      </c>
+      <c r="C129" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="D129" s="11" t="n">
+        <v>1014</v>
+      </c>
+      <c r="E129" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F129" s="11" t="n">
+        <v>2835</v>
+      </c>
+      <c r="G129" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon 솔방울곰 (뽑기권 D)</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="13" t="n"/>
+      <c r="B130" s="11" t="n">
+        <v>35015</v>
+      </c>
+      <c r="C130" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="D130" s="11" t="n">
+        <v>1015</v>
+      </c>
+      <c r="E130" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F130" s="11" t="n">
+        <v>3720</v>
+      </c>
+      <c r="G130" s="12" t="inlineStr">
+        <is>
+          <t>Rare 미믹 (뽑기권 D)</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="13" t="n"/>
+      <c r="B131" s="11" t="n">
+        <v>35016</v>
+      </c>
+      <c r="C131" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="D131" s="11" t="n">
+        <v>1016</v>
+      </c>
+      <c r="E131" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F131" s="11" t="n">
+        <v>3720</v>
+      </c>
+      <c r="G131" s="12" t="inlineStr">
+        <is>
+          <t>Rare 버섯 인간 (뽑기권 D)</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="13" t="n"/>
+      <c r="B132" s="11" t="n">
+        <v>35017</v>
+      </c>
+      <c r="C132" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="D132" s="11" t="n">
+        <v>1017</v>
+      </c>
+      <c r="E132" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F132" s="11" t="n">
+        <v>3720</v>
+      </c>
+      <c r="G132" s="12" t="inlineStr">
+        <is>
+          <t>Rare 고블린 (뽑기권 D)</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="13" t="n"/>
+      <c r="B133" s="11" t="n">
+        <v>35018</v>
+      </c>
+      <c r="C133" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="D133" s="11" t="n">
+        <v>1018</v>
+      </c>
+      <c r="E133" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F133" s="11" t="n">
+        <v>3720</v>
+      </c>
+      <c r="G133" s="12" t="inlineStr">
+        <is>
+          <t>Rare 은빛 기사 (뽑기권 D)</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="13" t="n"/>
+      <c r="B134" s="11" t="n">
+        <v>35019</v>
+      </c>
+      <c r="C134" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="D134" s="11" t="n">
+        <v>1019</v>
+      </c>
+      <c r="E134" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F134" s="11" t="n">
+        <v>3720</v>
+      </c>
+      <c r="G134" s="12" t="inlineStr">
+        <is>
+          <t>Rare 그림자 마법사 (뽑기권 D)</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="13" t="n"/>
+      <c r="B135" s="11" t="n">
+        <v>35020</v>
+      </c>
+      <c r="C135" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="D135" s="11" t="n">
+        <v>1020</v>
+      </c>
+      <c r="E135" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F135" s="11" t="n">
+        <v>3720</v>
+      </c>
+      <c r="G135" s="12" t="inlineStr">
+        <is>
+          <t>Rare 무예가 (뽑기권 D)</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="13" t="n"/>
+      <c r="B136" s="11" t="n">
+        <v>35021</v>
+      </c>
+      <c r="C136" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="D136" s="11" t="n">
+        <v>1021</v>
+      </c>
+      <c r="E136" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F136" s="11" t="n">
+        <v>3720</v>
+      </c>
+      <c r="G136" s="12" t="inlineStr">
+        <is>
+          <t>Rare 해골 병사 (뽑기권 D)</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="13" t="n"/>
+      <c r="B137" s="11" t="n">
+        <v>35022</v>
+      </c>
+      <c r="C137" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="D137" s="11" t="n">
+        <v>1022</v>
+      </c>
+      <c r="E137" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F137" s="11" t="n">
+        <v>3024</v>
+      </c>
+      <c r="G137" s="12" t="inlineStr">
+        <is>
+          <t>Epic 바위 골렘 (뽑기권 D)</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="13" t="n"/>
+      <c r="B138" s="11" t="n">
+        <v>35023</v>
+      </c>
+      <c r="C138" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="D138" s="11" t="n">
+        <v>1023</v>
+      </c>
+      <c r="E138" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F138" s="11" t="n">
+        <v>3024</v>
+      </c>
+      <c r="G138" s="12" t="inlineStr">
+        <is>
+          <t>Epic 붉은 집게게 (뽑기권 D)</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="13" t="n"/>
+      <c r="B139" s="11" t="n">
+        <v>35024</v>
+      </c>
+      <c r="C139" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="D139" s="11" t="n">
+        <v>1024</v>
+      </c>
+      <c r="E139" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F139" s="11" t="n">
+        <v>3024</v>
+      </c>
+      <c r="G139" s="12" t="inlineStr">
+        <is>
+          <t>Epic 대검 전사 (뽑기권 D)</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="13" t="n"/>
+      <c r="B140" s="11" t="n">
+        <v>35025</v>
+      </c>
+      <c r="C140" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="D140" s="11" t="n">
+        <v>1025</v>
+      </c>
+      <c r="E140" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F140" s="11" t="n">
+        <v>3024</v>
+      </c>
+      <c r="G140" s="12" t="inlineStr">
+        <is>
+          <t>Epic 검왕 (뽑기권 D)</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="13" t="n"/>
+      <c r="B141" s="11" t="n">
+        <v>35026</v>
+      </c>
+      <c r="C141" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="D141" s="11" t="n">
+        <v>1026</v>
+      </c>
+      <c r="E141" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F141" s="11" t="n">
+        <v>3024</v>
+      </c>
+      <c r="G141" s="12" t="inlineStr">
+        <is>
+          <t>Epic 영웅 기사 (뽑기권 D)</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="13" t="n"/>
+      <c r="B142" s="11" t="n">
+        <v>35027</v>
+      </c>
+      <c r="C142" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="D142" s="11" t="n">
+        <v>1027</v>
+      </c>
+      <c r="E142" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F142" s="11" t="n">
+        <v>2100</v>
+      </c>
+      <c r="G142" s="12" t="inlineStr">
+        <is>
+          <t>Legendary 죽음의 사신 (뽑기권 D)</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="13" t="n"/>
+      <c r="B143" s="11" t="n">
+        <v>35028</v>
+      </c>
+      <c r="C143" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="D143" s="11" t="n">
+        <v>1028</v>
+      </c>
+      <c r="E143" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F143" s="11" t="n">
+        <v>2100</v>
+      </c>
+      <c r="G143" s="12" t="inlineStr">
+        <is>
+          <t>Legendary 흑기사 (뽑기권 D)</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="13" t="n"/>
+      <c r="B144" s="11" t="n">
+        <v>35029</v>
+      </c>
+      <c r="C144" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="D144" s="11" t="n">
+        <v>1029</v>
+      </c>
+      <c r="E144" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F144" s="11" t="n">
+        <v>2100</v>
+      </c>
+      <c r="G144" s="12" t="inlineStr">
+        <is>
+          <t>Legendary 흑요석골렘 (뽑기권 D)</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="13" t="n"/>
+      <c r="B145" s="11" t="n">
+        <v>35030</v>
+      </c>
+      <c r="C145" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="D145" s="11" t="n">
+        <v>1030</v>
+      </c>
+      <c r="E145" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F145" s="11" t="n">
+        <v>420</v>
+      </c>
+      <c r="G145" s="12" t="inlineStr">
+        <is>
+          <t>Mythic 질풍 검호 (뽑기권 D)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing r:id="anysvml"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -17113,12 +19659,12 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing r:id="anysvml"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -18368,12 +20914,12 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing r:id="anysvml"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -19119,6 +21665,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing r:id="anysvml"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
--- a/GameDesign/Excel/Gacha.xlsx
+++ b/GameDesign/Excel/Gacha.xlsx
@@ -591,7 +591,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -7110,12 +7110,12 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+  <legacyDrawing r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -7371,18 +7371,18 @@
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>None</t>
         </is>
       </c>
       <c r="E10" s="11" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
-          <t>캐릭터 풀 30종</t>
+          <t>캐릭터 풀 30종 — 닫음: 캐릭터는 상점 뽑기권으로(T-184)</t>
         </is>
       </c>
     </row>
@@ -8198,12 +8198,12 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+  <legacyDrawing r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -11571,12 +11571,12 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+  <legacyDrawing r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -19659,12 +19659,12 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+  <legacyDrawing r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -20914,12 +20914,12 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+  <legacyDrawing r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -21665,6 +21665,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+  <legacyDrawing r:id="anysvml"/>
 </worksheet>
 </file>
--- a/GameDesign/Excel/Gacha.xlsx
+++ b/GameDesign/Excel/Gacha.xlsx
@@ -591,7 +591,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -7110,12 +7110,12 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing r:id="anysvml"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -8198,17 +8198,17 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing r:id="anysvml"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G145"/>
+  <dimension ref="A1:G149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -9617,36 +9617,36 @@
     <row r="61">
       <c r="A61" s="13" t="n"/>
       <c r="B61" s="11" t="n">
-        <v>33001</v>
+        <v>32031</v>
       </c>
       <c r="C61" s="11" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D61" s="11" t="n">
-        <v>1001</v>
+        <v>1031</v>
       </c>
       <c r="E61" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>4480</v>
+        <v>3885</v>
       </c>
       <c r="G61" s="12" t="inlineStr">
         <is>
-          <t>Common 떠돌이 전사 (뽑기권 B)</t>
+          <t>Uncommon 숙련 채굴꾼 (뽑기권 A)</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="13" t="n"/>
       <c r="B62" s="11" t="n">
-        <v>33002</v>
+        <v>33001</v>
       </c>
       <c r="C62" s="11" t="n">
         <v>33</v>
       </c>
       <c r="D62" s="11" t="n">
-        <v>1007</v>
+        <v>1001</v>
       </c>
       <c r="E62" s="11" t="n">
         <v>1</v>
@@ -9656,20 +9656,20 @@
       </c>
       <c r="G62" s="12" t="inlineStr">
         <is>
-          <t>Common 들쥐 (뽑기권 B)</t>
+          <t>Common 떠돌이 전사 (뽑기권 B)</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="13" t="n"/>
       <c r="B63" s="11" t="n">
-        <v>33003</v>
+        <v>33002</v>
       </c>
       <c r="C63" s="11" t="n">
         <v>33</v>
       </c>
       <c r="D63" s="11" t="n">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="E63" s="11" t="n">
         <v>1</v>
@@ -9679,20 +9679,20 @@
       </c>
       <c r="G63" s="12" t="inlineStr">
         <is>
-          <t>Common 물방개미 (뽑기권 B)</t>
+          <t>Common 들쥐 (뽑기권 B)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="13" t="n"/>
       <c r="B64" s="11" t="n">
-        <v>33004</v>
+        <v>33003</v>
       </c>
       <c r="C64" s="11" t="n">
         <v>33</v>
       </c>
       <c r="D64" s="11" t="n">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="E64" s="11" t="n">
         <v>1</v>
@@ -9702,20 +9702,20 @@
       </c>
       <c r="G64" s="12" t="inlineStr">
         <is>
-          <t>Common 동굴 박쥐 (뽑기권 B)</t>
+          <t>Common 물방개미 (뽑기권 B)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="13" t="n"/>
       <c r="B65" s="11" t="n">
-        <v>33005</v>
+        <v>33004</v>
       </c>
       <c r="C65" s="11" t="n">
         <v>33</v>
       </c>
       <c r="D65" s="11" t="n">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="E65" s="11" t="n">
         <v>1</v>
@@ -9725,20 +9725,20 @@
       </c>
       <c r="G65" s="12" t="inlineStr">
         <is>
-          <t>Common 톱니쥐 (뽑기권 B)</t>
+          <t>Common 동굴 박쥐 (뽑기권 B)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="13" t="n"/>
       <c r="B66" s="11" t="n">
-        <v>33006</v>
+        <v>33005</v>
       </c>
       <c r="C66" s="11" t="n">
         <v>33</v>
       </c>
       <c r="D66" s="11" t="n">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="E66" s="11" t="n">
         <v>1</v>
@@ -9748,43 +9748,43 @@
       </c>
       <c r="G66" s="12" t="inlineStr">
         <is>
-          <t>Common 흡혈 박쥐 (뽑기권 B)</t>
+          <t>Common 톱니쥐 (뽑기권 B)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="13" t="n"/>
       <c r="B67" s="11" t="n">
-        <v>33007</v>
+        <v>33006</v>
       </c>
       <c r="C67" s="11" t="n">
         <v>33</v>
       </c>
       <c r="D67" s="11" t="n">
-        <v>1002</v>
+        <v>1011</v>
       </c>
       <c r="E67" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>3990</v>
+        <v>4480</v>
       </c>
       <c r="G67" s="12" t="inlineStr">
         <is>
-          <t>Uncommon 숲 슬라임 (뽑기권 B)</t>
+          <t>Common 흡혈 박쥐 (뽑기권 B)</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="13" t="n"/>
       <c r="B68" s="11" t="n">
-        <v>33008</v>
+        <v>33007</v>
       </c>
       <c r="C68" s="11" t="n">
         <v>33</v>
       </c>
       <c r="D68" s="11" t="n">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="E68" s="11" t="n">
         <v>1</v>
@@ -9794,20 +9794,20 @@
       </c>
       <c r="G68" s="12" t="inlineStr">
         <is>
-          <t>Uncommon 뿔쥐 (뽑기권 B)</t>
+          <t>Uncommon 숲 슬라임 (뽑기권 B)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="13" t="n"/>
       <c r="B69" s="11" t="n">
-        <v>33009</v>
+        <v>33008</v>
       </c>
       <c r="C69" s="11" t="n">
         <v>33</v>
       </c>
       <c r="D69" s="11" t="n">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="E69" s="11" t="n">
         <v>1</v>
@@ -9817,20 +9817,20 @@
       </c>
       <c r="G69" s="12" t="inlineStr">
         <is>
-          <t>Uncommon 가시 슬라임 (뽑기권 B)</t>
+          <t>Uncommon 뿔쥐 (뽑기권 B)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="13" t="n"/>
       <c r="B70" s="11" t="n">
-        <v>33010</v>
+        <v>33009</v>
       </c>
       <c r="C70" s="11" t="n">
         <v>33</v>
       </c>
       <c r="D70" s="11" t="n">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="E70" s="11" t="n">
         <v>1</v>
@@ -9840,20 +9840,20 @@
       </c>
       <c r="G70" s="12" t="inlineStr">
         <is>
-          <t>Uncommon 방랑 기사 (뽑기권 B)</t>
+          <t>Uncommon 가시 슬라임 (뽑기권 B)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="13" t="n"/>
       <c r="B71" s="11" t="n">
-        <v>33011</v>
+        <v>33010</v>
       </c>
       <c r="C71" s="11" t="n">
         <v>33</v>
       </c>
       <c r="D71" s="11" t="n">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="E71" s="11" t="n">
         <v>1</v>
@@ -9863,20 +9863,20 @@
       </c>
       <c r="G71" s="12" t="inlineStr">
         <is>
-          <t>Uncommon 날개 눈알 (뽑기권 B)</t>
+          <t>Uncommon 방랑 기사 (뽑기권 B)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="13" t="n"/>
       <c r="B72" s="11" t="n">
-        <v>33012</v>
+        <v>33011</v>
       </c>
       <c r="C72" s="11" t="n">
         <v>33</v>
       </c>
       <c r="D72" s="11" t="n">
-        <v>1012</v>
+        <v>1006</v>
       </c>
       <c r="E72" s="11" t="n">
         <v>1</v>
@@ -9886,20 +9886,20 @@
       </c>
       <c r="G72" s="12" t="inlineStr">
         <is>
-          <t>Uncommon 망령 마법사 (뽑기권 B)</t>
+          <t>Uncommon 날개 눈알 (뽑기권 B)</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="13" t="n"/>
       <c r="B73" s="11" t="n">
-        <v>33013</v>
+        <v>33012</v>
       </c>
       <c r="C73" s="11" t="n">
         <v>33</v>
       </c>
       <c r="D73" s="11" t="n">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="E73" s="11" t="n">
         <v>1</v>
@@ -9909,20 +9909,20 @@
       </c>
       <c r="G73" s="12" t="inlineStr">
         <is>
-          <t>Uncommon 화염 마법사 (뽑기권 B)</t>
+          <t>Uncommon 망령 마법사 (뽑기권 B)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="13" t="n"/>
       <c r="B74" s="11" t="n">
-        <v>33014</v>
+        <v>33013</v>
       </c>
       <c r="C74" s="11" t="n">
         <v>33</v>
       </c>
       <c r="D74" s="11" t="n">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="E74" s="11" t="n">
         <v>1</v>
@@ -9932,43 +9932,43 @@
       </c>
       <c r="G74" s="12" t="inlineStr">
         <is>
-          <t>Uncommon 솔방울곰 (뽑기권 B)</t>
+          <t>Uncommon 화염 마법사 (뽑기권 B)</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="13" t="n"/>
       <c r="B75" s="11" t="n">
-        <v>33015</v>
+        <v>33014</v>
       </c>
       <c r="C75" s="11" t="n">
         <v>33</v>
       </c>
       <c r="D75" s="11" t="n">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="E75" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>3120</v>
+        <v>3990</v>
       </c>
       <c r="G75" s="12" t="inlineStr">
         <is>
-          <t>Rare 미믹 (뽑기권 B)</t>
+          <t>Uncommon 솔방울곰 (뽑기권 B)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="13" t="n"/>
       <c r="B76" s="11" t="n">
-        <v>33016</v>
+        <v>33015</v>
       </c>
       <c r="C76" s="11" t="n">
         <v>33</v>
       </c>
       <c r="D76" s="11" t="n">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="E76" s="11" t="n">
         <v>1</v>
@@ -9978,20 +9978,20 @@
       </c>
       <c r="G76" s="12" t="inlineStr">
         <is>
-          <t>Rare 버섯 인간 (뽑기권 B)</t>
+          <t>Rare 미믹 (뽑기권 B)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="13" t="n"/>
       <c r="B77" s="11" t="n">
-        <v>33017</v>
+        <v>33016</v>
       </c>
       <c r="C77" s="11" t="n">
         <v>33</v>
       </c>
       <c r="D77" s="11" t="n">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="E77" s="11" t="n">
         <v>1</v>
@@ -10001,20 +10001,20 @@
       </c>
       <c r="G77" s="12" t="inlineStr">
         <is>
-          <t>Rare 고블린 (뽑기권 B)</t>
+          <t>Rare 버섯 인간 (뽑기권 B)</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="13" t="n"/>
       <c r="B78" s="11" t="n">
-        <v>33018</v>
+        <v>33017</v>
       </c>
       <c r="C78" s="11" t="n">
         <v>33</v>
       </c>
       <c r="D78" s="11" t="n">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="E78" s="11" t="n">
         <v>1</v>
@@ -10024,20 +10024,20 @@
       </c>
       <c r="G78" s="12" t="inlineStr">
         <is>
-          <t>Rare 은빛 기사 (뽑기권 B)</t>
+          <t>Rare 고블린 (뽑기권 B)</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="13" t="n"/>
       <c r="B79" s="11" t="n">
-        <v>33019</v>
+        <v>33018</v>
       </c>
       <c r="C79" s="11" t="n">
         <v>33</v>
       </c>
       <c r="D79" s="11" t="n">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="E79" s="11" t="n">
         <v>1</v>
@@ -10047,20 +10047,20 @@
       </c>
       <c r="G79" s="12" t="inlineStr">
         <is>
-          <t>Rare 그림자 마법사 (뽑기권 B)</t>
+          <t>Rare 은빛 기사 (뽑기권 B)</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="13" t="n"/>
       <c r="B80" s="11" t="n">
-        <v>33020</v>
+        <v>33019</v>
       </c>
       <c r="C80" s="11" t="n">
         <v>33</v>
       </c>
       <c r="D80" s="11" t="n">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="E80" s="11" t="n">
         <v>1</v>
@@ -10070,20 +10070,20 @@
       </c>
       <c r="G80" s="12" t="inlineStr">
         <is>
-          <t>Rare 무예가 (뽑기권 B)</t>
+          <t>Rare 그림자 마법사 (뽑기권 B)</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="13" t="n"/>
       <c r="B81" s="11" t="n">
-        <v>33021</v>
+        <v>33020</v>
       </c>
       <c r="C81" s="11" t="n">
         <v>33</v>
       </c>
       <c r="D81" s="11" t="n">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="E81" s="11" t="n">
         <v>1</v>
@@ -10093,43 +10093,43 @@
       </c>
       <c r="G81" s="12" t="inlineStr">
         <is>
-          <t>Rare 해골 병사 (뽑기권 B)</t>
+          <t>Rare 무예가 (뽑기권 B)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="13" t="n"/>
       <c r="B82" s="11" t="n">
-        <v>33022</v>
+        <v>33021</v>
       </c>
       <c r="C82" s="11" t="n">
         <v>33</v>
       </c>
       <c r="D82" s="11" t="n">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="E82" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>672</v>
+        <v>3120</v>
       </c>
       <c r="G82" s="12" t="inlineStr">
         <is>
-          <t>Epic 바위 골렘 (뽑기권 B)</t>
+          <t>Rare 해골 병사 (뽑기권 B)</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="13" t="n"/>
       <c r="B83" s="11" t="n">
-        <v>33023</v>
+        <v>33022</v>
       </c>
       <c r="C83" s="11" t="n">
         <v>33</v>
       </c>
       <c r="D83" s="11" t="n">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="E83" s="11" t="n">
         <v>1</v>
@@ -10139,20 +10139,20 @@
       </c>
       <c r="G83" s="12" t="inlineStr">
         <is>
-          <t>Epic 붉은 집게게 (뽑기권 B)</t>
+          <t>Epic 바위 골렘 (뽑기권 B)</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="13" t="n"/>
       <c r="B84" s="11" t="n">
-        <v>33024</v>
+        <v>33023</v>
       </c>
       <c r="C84" s="11" t="n">
         <v>33</v>
       </c>
       <c r="D84" s="11" t="n">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="E84" s="11" t="n">
         <v>1</v>
@@ -10162,20 +10162,20 @@
       </c>
       <c r="G84" s="12" t="inlineStr">
         <is>
-          <t>Epic 대검 전사 (뽑기권 B)</t>
+          <t>Epic 붉은 집게게 (뽑기권 B)</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="13" t="n"/>
       <c r="B85" s="11" t="n">
-        <v>33025</v>
+        <v>33024</v>
       </c>
       <c r="C85" s="11" t="n">
         <v>33</v>
       </c>
       <c r="D85" s="11" t="n">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="E85" s="11" t="n">
         <v>1</v>
@@ -10185,20 +10185,20 @@
       </c>
       <c r="G85" s="12" t="inlineStr">
         <is>
-          <t>Epic 검왕 (뽑기권 B)</t>
+          <t>Epic 대검 전사 (뽑기권 B)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="13" t="n"/>
       <c r="B86" s="11" t="n">
-        <v>33026</v>
+        <v>33025</v>
       </c>
       <c r="C86" s="11" t="n">
         <v>33</v>
       </c>
       <c r="D86" s="11" t="n">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="E86" s="11" t="n">
         <v>1</v>
@@ -10208,66 +10208,66 @@
       </c>
       <c r="G86" s="12" t="inlineStr">
         <is>
-          <t>Epic 영웅 기사 (뽑기권 B)</t>
+          <t>Epic 검왕 (뽑기권 B)</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="13" t="n"/>
       <c r="B87" s="11" t="n">
-        <v>34001</v>
+        <v>33026</v>
       </c>
       <c r="C87" s="11" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D87" s="11" t="n">
-        <v>1001</v>
+        <v>1026</v>
       </c>
       <c r="E87" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>3080</v>
+        <v>672</v>
       </c>
       <c r="G87" s="12" t="inlineStr">
         <is>
-          <t>Common 떠돌이 전사 (뽑기권 C)</t>
+          <t>Epic 영웅 기사 (뽑기권 B)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="13" t="n"/>
       <c r="B88" s="11" t="n">
-        <v>34002</v>
+        <v>33031</v>
       </c>
       <c r="C88" s="11" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D88" s="11" t="n">
-        <v>1007</v>
+        <v>1031</v>
       </c>
       <c r="E88" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>3080</v>
+        <v>3990</v>
       </c>
       <c r="G88" s="12" t="inlineStr">
         <is>
-          <t>Common 들쥐 (뽑기권 C)</t>
+          <t>Uncommon 숙련 채굴꾼 (뽑기권 B)</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="13" t="n"/>
       <c r="B89" s="11" t="n">
-        <v>34003</v>
+        <v>34001</v>
       </c>
       <c r="C89" s="11" t="n">
         <v>34</v>
       </c>
       <c r="D89" s="11" t="n">
-        <v>1008</v>
+        <v>1001</v>
       </c>
       <c r="E89" s="11" t="n">
         <v>1</v>
@@ -10277,20 +10277,20 @@
       </c>
       <c r="G89" s="12" t="inlineStr">
         <is>
-          <t>Common 물방개미 (뽑기권 C)</t>
+          <t>Common 떠돌이 전사 (뽑기권 C)</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="13" t="n"/>
       <c r="B90" s="11" t="n">
-        <v>34004</v>
+        <v>34002</v>
       </c>
       <c r="C90" s="11" t="n">
         <v>34</v>
       </c>
       <c r="D90" s="11" t="n">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="E90" s="11" t="n">
         <v>1</v>
@@ -10300,20 +10300,20 @@
       </c>
       <c r="G90" s="12" t="inlineStr">
         <is>
-          <t>Common 동굴 박쥐 (뽑기권 C)</t>
+          <t>Common 들쥐 (뽑기권 C)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="13" t="n"/>
       <c r="B91" s="11" t="n">
-        <v>34005</v>
+        <v>34003</v>
       </c>
       <c r="C91" s="11" t="n">
         <v>34</v>
       </c>
       <c r="D91" s="11" t="n">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="E91" s="11" t="n">
         <v>1</v>
@@ -10323,20 +10323,20 @@
       </c>
       <c r="G91" s="12" t="inlineStr">
         <is>
-          <t>Common 톱니쥐 (뽑기권 C)</t>
+          <t>Common 물방개미 (뽑기권 C)</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="13" t="n"/>
       <c r="B92" s="11" t="n">
-        <v>34006</v>
+        <v>34004</v>
       </c>
       <c r="C92" s="11" t="n">
         <v>34</v>
       </c>
       <c r="D92" s="11" t="n">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="E92" s="11" t="n">
         <v>1</v>
@@ -10346,66 +10346,66 @@
       </c>
       <c r="G92" s="12" t="inlineStr">
         <is>
-          <t>Common 흡혈 박쥐 (뽑기권 C)</t>
+          <t>Common 동굴 박쥐 (뽑기권 C)</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="13" t="n"/>
       <c r="B93" s="11" t="n">
-        <v>34007</v>
+        <v>34005</v>
       </c>
       <c r="C93" s="11" t="n">
         <v>34</v>
       </c>
       <c r="D93" s="11" t="n">
-        <v>1002</v>
+        <v>1010</v>
       </c>
       <c r="E93" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>3360</v>
+        <v>3080</v>
       </c>
       <c r="G93" s="12" t="inlineStr">
         <is>
-          <t>Uncommon 숲 슬라임 (뽑기권 C)</t>
+          <t>Common 톱니쥐 (뽑기권 C)</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="13" t="n"/>
       <c r="B94" s="11" t="n">
-        <v>34008</v>
+        <v>34006</v>
       </c>
       <c r="C94" s="11" t="n">
         <v>34</v>
       </c>
       <c r="D94" s="11" t="n">
-        <v>1003</v>
+        <v>1011</v>
       </c>
       <c r="E94" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>3360</v>
+        <v>3080</v>
       </c>
       <c r="G94" s="12" t="inlineStr">
         <is>
-          <t>Uncommon 뿔쥐 (뽑기권 C)</t>
+          <t>Common 흡혈 박쥐 (뽑기권 C)</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="13" t="n"/>
       <c r="B95" s="11" t="n">
-        <v>34009</v>
+        <v>34007</v>
       </c>
       <c r="C95" s="11" t="n">
         <v>34</v>
       </c>
       <c r="D95" s="11" t="n">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="E95" s="11" t="n">
         <v>1</v>
@@ -10415,20 +10415,20 @@
       </c>
       <c r="G95" s="12" t="inlineStr">
         <is>
-          <t>Uncommon 가시 슬라임 (뽑기권 C)</t>
+          <t>Uncommon 숲 슬라임 (뽑기권 C)</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="13" t="n"/>
       <c r="B96" s="11" t="n">
-        <v>34010</v>
+        <v>34008</v>
       </c>
       <c r="C96" s="11" t="n">
         <v>34</v>
       </c>
       <c r="D96" s="11" t="n">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="E96" s="11" t="n">
         <v>1</v>
@@ -10438,20 +10438,20 @@
       </c>
       <c r="G96" s="12" t="inlineStr">
         <is>
-          <t>Uncommon 방랑 기사 (뽑기권 C)</t>
+          <t>Uncommon 뿔쥐 (뽑기권 C)</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="13" t="n"/>
       <c r="B97" s="11" t="n">
-        <v>34011</v>
+        <v>34009</v>
       </c>
       <c r="C97" s="11" t="n">
         <v>34</v>
       </c>
       <c r="D97" s="11" t="n">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="E97" s="11" t="n">
         <v>1</v>
@@ -10461,20 +10461,20 @@
       </c>
       <c r="G97" s="12" t="inlineStr">
         <is>
-          <t>Uncommon 날개 눈알 (뽑기권 C)</t>
+          <t>Uncommon 가시 슬라임 (뽑기권 C)</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="13" t="n"/>
       <c r="B98" s="11" t="n">
-        <v>34012</v>
+        <v>34010</v>
       </c>
       <c r="C98" s="11" t="n">
         <v>34</v>
       </c>
       <c r="D98" s="11" t="n">
-        <v>1012</v>
+        <v>1005</v>
       </c>
       <c r="E98" s="11" t="n">
         <v>1</v>
@@ -10484,20 +10484,20 @@
       </c>
       <c r="G98" s="12" t="inlineStr">
         <is>
-          <t>Uncommon 망령 마법사 (뽑기권 C)</t>
+          <t>Uncommon 방랑 기사 (뽑기권 C)</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="13" t="n"/>
       <c r="B99" s="11" t="n">
-        <v>34013</v>
+        <v>34011</v>
       </c>
       <c r="C99" s="11" t="n">
         <v>34</v>
       </c>
       <c r="D99" s="11" t="n">
-        <v>1013</v>
+        <v>1006</v>
       </c>
       <c r="E99" s="11" t="n">
         <v>1</v>
@@ -10507,20 +10507,20 @@
       </c>
       <c r="G99" s="12" t="inlineStr">
         <is>
-          <t>Uncommon 화염 마법사 (뽑기권 C)</t>
+          <t>Uncommon 날개 눈알 (뽑기권 C)</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="13" t="n"/>
       <c r="B100" s="11" t="n">
-        <v>34014</v>
+        <v>34012</v>
       </c>
       <c r="C100" s="11" t="n">
         <v>34</v>
       </c>
       <c r="D100" s="11" t="n">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="E100" s="11" t="n">
         <v>1</v>
@@ -10530,66 +10530,66 @@
       </c>
       <c r="G100" s="12" t="inlineStr">
         <is>
-          <t>Uncommon 솔방울곰 (뽑기권 C)</t>
+          <t>Uncommon 망령 마법사 (뽑기권 C)</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="13" t="n"/>
       <c r="B101" s="11" t="n">
-        <v>34015</v>
+        <v>34013</v>
       </c>
       <c r="C101" s="11" t="n">
         <v>34</v>
       </c>
       <c r="D101" s="11" t="n">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="E101" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>3600</v>
+        <v>3360</v>
       </c>
       <c r="G101" s="12" t="inlineStr">
         <is>
-          <t>Rare 미믹 (뽑기권 C)</t>
+          <t>Uncommon 화염 마법사 (뽑기권 C)</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="13" t="n"/>
       <c r="B102" s="11" t="n">
-        <v>34016</v>
+        <v>34014</v>
       </c>
       <c r="C102" s="11" t="n">
         <v>34</v>
       </c>
       <c r="D102" s="11" t="n">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="E102" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>3600</v>
+        <v>3360</v>
       </c>
       <c r="G102" s="12" t="inlineStr">
         <is>
-          <t>Rare 버섯 인간 (뽑기권 C)</t>
+          <t>Uncommon 솔방울곰 (뽑기권 C)</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="13" t="n"/>
       <c r="B103" s="11" t="n">
-        <v>34017</v>
+        <v>34015</v>
       </c>
       <c r="C103" s="11" t="n">
         <v>34</v>
       </c>
       <c r="D103" s="11" t="n">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="E103" s="11" t="n">
         <v>1</v>
@@ -10599,20 +10599,20 @@
       </c>
       <c r="G103" s="12" t="inlineStr">
         <is>
-          <t>Rare 고블린 (뽑기권 C)</t>
+          <t>Rare 미믹 (뽑기권 C)</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="13" t="n"/>
       <c r="B104" s="11" t="n">
-        <v>34018</v>
+        <v>34016</v>
       </c>
       <c r="C104" s="11" t="n">
         <v>34</v>
       </c>
       <c r="D104" s="11" t="n">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="E104" s="11" t="n">
         <v>1</v>
@@ -10622,20 +10622,20 @@
       </c>
       <c r="G104" s="12" t="inlineStr">
         <is>
-          <t>Rare 은빛 기사 (뽑기권 C)</t>
+          <t>Rare 버섯 인간 (뽑기권 C)</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="13" t="n"/>
       <c r="B105" s="11" t="n">
-        <v>34019</v>
+        <v>34017</v>
       </c>
       <c r="C105" s="11" t="n">
         <v>34</v>
       </c>
       <c r="D105" s="11" t="n">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="E105" s="11" t="n">
         <v>1</v>
@@ -10645,20 +10645,20 @@
       </c>
       <c r="G105" s="12" t="inlineStr">
         <is>
-          <t>Rare 그림자 마법사 (뽑기권 C)</t>
+          <t>Rare 고블린 (뽑기권 C)</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="13" t="n"/>
       <c r="B106" s="11" t="n">
-        <v>34020</v>
+        <v>34018</v>
       </c>
       <c r="C106" s="11" t="n">
         <v>34</v>
       </c>
       <c r="D106" s="11" t="n">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="E106" s="11" t="n">
         <v>1</v>
@@ -10668,20 +10668,20 @@
       </c>
       <c r="G106" s="12" t="inlineStr">
         <is>
-          <t>Rare 무예가 (뽑기권 C)</t>
+          <t>Rare 은빛 기사 (뽑기권 C)</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="13" t="n"/>
       <c r="B107" s="11" t="n">
-        <v>34021</v>
+        <v>34019</v>
       </c>
       <c r="C107" s="11" t="n">
         <v>34</v>
       </c>
       <c r="D107" s="11" t="n">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="E107" s="11" t="n">
         <v>1</v>
@@ -10691,66 +10691,66 @@
       </c>
       <c r="G107" s="12" t="inlineStr">
         <is>
-          <t>Rare 해골 병사 (뽑기권 C)</t>
+          <t>Rare 그림자 마법사 (뽑기권 C)</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="13" t="n"/>
       <c r="B108" s="11" t="n">
-        <v>34022</v>
+        <v>34020</v>
       </c>
       <c r="C108" s="11" t="n">
         <v>34</v>
       </c>
       <c r="D108" s="11" t="n">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="E108" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>2352</v>
+        <v>3600</v>
       </c>
       <c r="G108" s="12" t="inlineStr">
         <is>
-          <t>Epic 바위 골렘 (뽑기권 C)</t>
+          <t>Rare 무예가 (뽑기권 C)</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="13" t="n"/>
       <c r="B109" s="11" t="n">
-        <v>34023</v>
+        <v>34021</v>
       </c>
       <c r="C109" s="11" t="n">
         <v>34</v>
       </c>
       <c r="D109" s="11" t="n">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="E109" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>2352</v>
+        <v>3600</v>
       </c>
       <c r="G109" s="12" t="inlineStr">
         <is>
-          <t>Epic 붉은 집게게 (뽑기권 C)</t>
+          <t>Rare 해골 병사 (뽑기권 C)</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="13" t="n"/>
       <c r="B110" s="11" t="n">
-        <v>34024</v>
+        <v>34022</v>
       </c>
       <c r="C110" s="11" t="n">
         <v>34</v>
       </c>
       <c r="D110" s="11" t="n">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="E110" s="11" t="n">
         <v>1</v>
@@ -10760,20 +10760,20 @@
       </c>
       <c r="G110" s="12" t="inlineStr">
         <is>
-          <t>Epic 대검 전사 (뽑기권 C)</t>
+          <t>Epic 바위 골렘 (뽑기권 C)</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="13" t="n"/>
       <c r="B111" s="11" t="n">
-        <v>34025</v>
+        <v>34023</v>
       </c>
       <c r="C111" s="11" t="n">
         <v>34</v>
       </c>
       <c r="D111" s="11" t="n">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="E111" s="11" t="n">
         <v>1</v>
@@ -10783,20 +10783,20 @@
       </c>
       <c r="G111" s="12" t="inlineStr">
         <is>
-          <t>Epic 검왕 (뽑기권 C)</t>
+          <t>Epic 붉은 집게게 (뽑기권 C)</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="13" t="n"/>
       <c r="B112" s="11" t="n">
-        <v>34026</v>
+        <v>34024</v>
       </c>
       <c r="C112" s="11" t="n">
         <v>34</v>
       </c>
       <c r="D112" s="11" t="n">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="E112" s="11" t="n">
         <v>1</v>
@@ -10806,66 +10806,66 @@
       </c>
       <c r="G112" s="12" t="inlineStr">
         <is>
-          <t>Epic 영웅 기사 (뽑기권 C)</t>
+          <t>Epic 대검 전사 (뽑기권 C)</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="13" t="n"/>
       <c r="B113" s="11" t="n">
-        <v>34027</v>
+        <v>34025</v>
       </c>
       <c r="C113" s="11" t="n">
         <v>34</v>
       </c>
       <c r="D113" s="11" t="n">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="E113" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>560</v>
+        <v>2352</v>
       </c>
       <c r="G113" s="12" t="inlineStr">
         <is>
-          <t>Legendary 죽음의 사신 (뽑기권 C)</t>
+          <t>Epic 검왕 (뽑기권 C)</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="13" t="n"/>
       <c r="B114" s="11" t="n">
-        <v>34028</v>
+        <v>34026</v>
       </c>
       <c r="C114" s="11" t="n">
         <v>34</v>
       </c>
       <c r="D114" s="11" t="n">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="E114" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>560</v>
+        <v>2352</v>
       </c>
       <c r="G114" s="12" t="inlineStr">
         <is>
-          <t>Legendary 흑기사 (뽑기권 C)</t>
+          <t>Epic 영웅 기사 (뽑기권 C)</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="13" t="n"/>
       <c r="B115" s="11" t="n">
-        <v>34029</v>
+        <v>34027</v>
       </c>
       <c r="C115" s="11" t="n">
         <v>34</v>
       </c>
       <c r="D115" s="11" t="n">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="E115" s="11" t="n">
         <v>1</v>
@@ -10875,89 +10875,89 @@
       </c>
       <c r="G115" s="12" t="inlineStr">
         <is>
-          <t>Legendary 흑요석골렘 (뽑기권 C)</t>
+          <t>Legendary 죽음의 사신 (뽑기권 C)</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="13" t="n"/>
       <c r="B116" s="11" t="n">
-        <v>35001</v>
+        <v>34028</v>
       </c>
       <c r="C116" s="11" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D116" s="11" t="n">
-        <v>1001</v>
+        <v>1028</v>
       </c>
       <c r="E116" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>2240</v>
+        <v>560</v>
       </c>
       <c r="G116" s="12" t="inlineStr">
         <is>
-          <t>Common 떠돌이 전사 (뽑기권 D)</t>
+          <t>Legendary 흑기사 (뽑기권 C)</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="13" t="n"/>
       <c r="B117" s="11" t="n">
-        <v>35002</v>
+        <v>34029</v>
       </c>
       <c r="C117" s="11" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D117" s="11" t="n">
-        <v>1007</v>
+        <v>1029</v>
       </c>
       <c r="E117" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>2240</v>
+        <v>560</v>
       </c>
       <c r="G117" s="12" t="inlineStr">
         <is>
-          <t>Common 들쥐 (뽑기권 D)</t>
+          <t>Legendary 흑요석골렘 (뽑기권 C)</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="13" t="n"/>
       <c r="B118" s="11" t="n">
-        <v>35003</v>
+        <v>34031</v>
       </c>
       <c r="C118" s="11" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D118" s="11" t="n">
-        <v>1008</v>
+        <v>1031</v>
       </c>
       <c r="E118" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>2240</v>
+        <v>3360</v>
       </c>
       <c r="G118" s="12" t="inlineStr">
         <is>
-          <t>Common 물방개미 (뽑기권 D)</t>
+          <t>Uncommon 숙련 채굴꾼 (뽑기권 C)</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="13" t="n"/>
       <c r="B119" s="11" t="n">
-        <v>35004</v>
+        <v>35001</v>
       </c>
       <c r="C119" s="11" t="n">
         <v>35</v>
       </c>
       <c r="D119" s="11" t="n">
-        <v>1009</v>
+        <v>1001</v>
       </c>
       <c r="E119" s="11" t="n">
         <v>1</v>
@@ -10967,20 +10967,20 @@
       </c>
       <c r="G119" s="12" t="inlineStr">
         <is>
-          <t>Common 동굴 박쥐 (뽑기권 D)</t>
+          <t>Common 떠돌이 전사 (뽑기권 D)</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="13" t="n"/>
       <c r="B120" s="11" t="n">
-        <v>35005</v>
+        <v>35002</v>
       </c>
       <c r="C120" s="11" t="n">
         <v>35</v>
       </c>
       <c r="D120" s="11" t="n">
-        <v>1010</v>
+        <v>1007</v>
       </c>
       <c r="E120" s="11" t="n">
         <v>1</v>
@@ -10990,20 +10990,20 @@
       </c>
       <c r="G120" s="12" t="inlineStr">
         <is>
-          <t>Common 톱니쥐 (뽑기권 D)</t>
+          <t>Common 들쥐 (뽑기권 D)</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="13" t="n"/>
       <c r="B121" s="11" t="n">
-        <v>35006</v>
+        <v>35003</v>
       </c>
       <c r="C121" s="11" t="n">
         <v>35</v>
       </c>
       <c r="D121" s="11" t="n">
-        <v>1011</v>
+        <v>1008</v>
       </c>
       <c r="E121" s="11" t="n">
         <v>1</v>
@@ -11013,89 +11013,89 @@
       </c>
       <c r="G121" s="12" t="inlineStr">
         <is>
-          <t>Common 흡혈 박쥐 (뽑기권 D)</t>
+          <t>Common 물방개미 (뽑기권 D)</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="13" t="n"/>
       <c r="B122" s="11" t="n">
-        <v>35007</v>
+        <v>35004</v>
       </c>
       <c r="C122" s="11" t="n">
         <v>35</v>
       </c>
       <c r="D122" s="11" t="n">
-        <v>1002</v>
+        <v>1009</v>
       </c>
       <c r="E122" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>2835</v>
+        <v>2240</v>
       </c>
       <c r="G122" s="12" t="inlineStr">
         <is>
-          <t>Uncommon 숲 슬라임 (뽑기권 D)</t>
+          <t>Common 동굴 박쥐 (뽑기권 D)</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="13" t="n"/>
       <c r="B123" s="11" t="n">
-        <v>35008</v>
+        <v>35005</v>
       </c>
       <c r="C123" s="11" t="n">
         <v>35</v>
       </c>
       <c r="D123" s="11" t="n">
-        <v>1003</v>
+        <v>1010</v>
       </c>
       <c r="E123" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>2835</v>
+        <v>2240</v>
       </c>
       <c r="G123" s="12" t="inlineStr">
         <is>
-          <t>Uncommon 뿔쥐 (뽑기권 D)</t>
+          <t>Common 톱니쥐 (뽑기권 D)</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="13" t="n"/>
       <c r="B124" s="11" t="n">
-        <v>35009</v>
+        <v>35006</v>
       </c>
       <c r="C124" s="11" t="n">
         <v>35</v>
       </c>
       <c r="D124" s="11" t="n">
-        <v>1004</v>
+        <v>1011</v>
       </c>
       <c r="E124" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>2835</v>
+        <v>2240</v>
       </c>
       <c r="G124" s="12" t="inlineStr">
         <is>
-          <t>Uncommon 가시 슬라임 (뽑기권 D)</t>
+          <t>Common 흡혈 박쥐 (뽑기권 D)</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="13" t="n"/>
       <c r="B125" s="11" t="n">
-        <v>35010</v>
+        <v>35007</v>
       </c>
       <c r="C125" s="11" t="n">
         <v>35</v>
       </c>
       <c r="D125" s="11" t="n">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="E125" s="11" t="n">
         <v>1</v>
@@ -11105,20 +11105,20 @@
       </c>
       <c r="G125" s="12" t="inlineStr">
         <is>
-          <t>Uncommon 방랑 기사 (뽑기권 D)</t>
+          <t>Uncommon 숲 슬라임 (뽑기권 D)</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="13" t="n"/>
       <c r="B126" s="11" t="n">
-        <v>35011</v>
+        <v>35008</v>
       </c>
       <c r="C126" s="11" t="n">
         <v>35</v>
       </c>
       <c r="D126" s="11" t="n">
-        <v>1006</v>
+        <v>1003</v>
       </c>
       <c r="E126" s="11" t="n">
         <v>1</v>
@@ -11128,20 +11128,20 @@
       </c>
       <c r="G126" s="12" t="inlineStr">
         <is>
-          <t>Uncommon 날개 눈알 (뽑기권 D)</t>
+          <t>Uncommon 뿔쥐 (뽑기권 D)</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="13" t="n"/>
       <c r="B127" s="11" t="n">
-        <v>35012</v>
+        <v>35009</v>
       </c>
       <c r="C127" s="11" t="n">
         <v>35</v>
       </c>
       <c r="D127" s="11" t="n">
-        <v>1012</v>
+        <v>1004</v>
       </c>
       <c r="E127" s="11" t="n">
         <v>1</v>
@@ -11151,20 +11151,20 @@
       </c>
       <c r="G127" s="12" t="inlineStr">
         <is>
-          <t>Uncommon 망령 마법사 (뽑기권 D)</t>
+          <t>Uncommon 가시 슬라임 (뽑기권 D)</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="13" t="n"/>
       <c r="B128" s="11" t="n">
-        <v>35013</v>
+        <v>35010</v>
       </c>
       <c r="C128" s="11" t="n">
         <v>35</v>
       </c>
       <c r="D128" s="11" t="n">
-        <v>1013</v>
+        <v>1005</v>
       </c>
       <c r="E128" s="11" t="n">
         <v>1</v>
@@ -11174,20 +11174,20 @@
       </c>
       <c r="G128" s="12" t="inlineStr">
         <is>
-          <t>Uncommon 화염 마법사 (뽑기권 D)</t>
+          <t>Uncommon 방랑 기사 (뽑기권 D)</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="13" t="n"/>
       <c r="B129" s="11" t="n">
-        <v>35014</v>
+        <v>35011</v>
       </c>
       <c r="C129" s="11" t="n">
         <v>35</v>
       </c>
       <c r="D129" s="11" t="n">
-        <v>1014</v>
+        <v>1006</v>
       </c>
       <c r="E129" s="11" t="n">
         <v>1</v>
@@ -11197,89 +11197,89 @@
       </c>
       <c r="G129" s="12" t="inlineStr">
         <is>
-          <t>Uncommon 솔방울곰 (뽑기권 D)</t>
+          <t>Uncommon 날개 눈알 (뽑기권 D)</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="13" t="n"/>
       <c r="B130" s="11" t="n">
-        <v>35015</v>
+        <v>35012</v>
       </c>
       <c r="C130" s="11" t="n">
         <v>35</v>
       </c>
       <c r="D130" s="11" t="n">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="E130" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>3720</v>
+        <v>2835</v>
       </c>
       <c r="G130" s="12" t="inlineStr">
         <is>
-          <t>Rare 미믹 (뽑기권 D)</t>
+          <t>Uncommon 망령 마법사 (뽑기권 D)</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="13" t="n"/>
       <c r="B131" s="11" t="n">
-        <v>35016</v>
+        <v>35013</v>
       </c>
       <c r="C131" s="11" t="n">
         <v>35</v>
       </c>
       <c r="D131" s="11" t="n">
-        <v>1016</v>
+        <v>1013</v>
       </c>
       <c r="E131" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>3720</v>
+        <v>2835</v>
       </c>
       <c r="G131" s="12" t="inlineStr">
         <is>
-          <t>Rare 버섯 인간 (뽑기권 D)</t>
+          <t>Uncommon 화염 마법사 (뽑기권 D)</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="13" t="n"/>
       <c r="B132" s="11" t="n">
-        <v>35017</v>
+        <v>35014</v>
       </c>
       <c r="C132" s="11" t="n">
         <v>35</v>
       </c>
       <c r="D132" s="11" t="n">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="E132" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>3720</v>
+        <v>2835</v>
       </c>
       <c r="G132" s="12" t="inlineStr">
         <is>
-          <t>Rare 고블린 (뽑기권 D)</t>
+          <t>Uncommon 솔방울곰 (뽑기권 D)</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="13" t="n"/>
       <c r="B133" s="11" t="n">
-        <v>35018</v>
+        <v>35015</v>
       </c>
       <c r="C133" s="11" t="n">
         <v>35</v>
       </c>
       <c r="D133" s="11" t="n">
-        <v>1018</v>
+        <v>1015</v>
       </c>
       <c r="E133" s="11" t="n">
         <v>1</v>
@@ -11289,20 +11289,20 @@
       </c>
       <c r="G133" s="12" t="inlineStr">
         <is>
-          <t>Rare 은빛 기사 (뽑기권 D)</t>
+          <t>Rare 미믹 (뽑기권 D)</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="13" t="n"/>
       <c r="B134" s="11" t="n">
-        <v>35019</v>
+        <v>35016</v>
       </c>
       <c r="C134" s="11" t="n">
         <v>35</v>
       </c>
       <c r="D134" s="11" t="n">
-        <v>1019</v>
+        <v>1016</v>
       </c>
       <c r="E134" s="11" t="n">
         <v>1</v>
@@ -11312,20 +11312,20 @@
       </c>
       <c r="G134" s="12" t="inlineStr">
         <is>
-          <t>Rare 그림자 마법사 (뽑기권 D)</t>
+          <t>Rare 버섯 인간 (뽑기권 D)</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="13" t="n"/>
       <c r="B135" s="11" t="n">
-        <v>35020</v>
+        <v>35017</v>
       </c>
       <c r="C135" s="11" t="n">
         <v>35</v>
       </c>
       <c r="D135" s="11" t="n">
-        <v>1020</v>
+        <v>1017</v>
       </c>
       <c r="E135" s="11" t="n">
         <v>1</v>
@@ -11335,20 +11335,20 @@
       </c>
       <c r="G135" s="12" t="inlineStr">
         <is>
-          <t>Rare 무예가 (뽑기권 D)</t>
+          <t>Rare 고블린 (뽑기권 D)</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="13" t="n"/>
       <c r="B136" s="11" t="n">
-        <v>35021</v>
+        <v>35018</v>
       </c>
       <c r="C136" s="11" t="n">
         <v>35</v>
       </c>
       <c r="D136" s="11" t="n">
-        <v>1021</v>
+        <v>1018</v>
       </c>
       <c r="E136" s="11" t="n">
         <v>1</v>
@@ -11358,89 +11358,89 @@
       </c>
       <c r="G136" s="12" t="inlineStr">
         <is>
-          <t>Rare 해골 병사 (뽑기권 D)</t>
+          <t>Rare 은빛 기사 (뽑기권 D)</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="13" t="n"/>
       <c r="B137" s="11" t="n">
-        <v>35022</v>
+        <v>35019</v>
       </c>
       <c r="C137" s="11" t="n">
         <v>35</v>
       </c>
       <c r="D137" s="11" t="n">
-        <v>1022</v>
+        <v>1019</v>
       </c>
       <c r="E137" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>3024</v>
+        <v>3720</v>
       </c>
       <c r="G137" s="12" t="inlineStr">
         <is>
-          <t>Epic 바위 골렘 (뽑기권 D)</t>
+          <t>Rare 그림자 마법사 (뽑기권 D)</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="13" t="n"/>
       <c r="B138" s="11" t="n">
-        <v>35023</v>
+        <v>35020</v>
       </c>
       <c r="C138" s="11" t="n">
         <v>35</v>
       </c>
       <c r="D138" s="11" t="n">
-        <v>1023</v>
+        <v>1020</v>
       </c>
       <c r="E138" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>3024</v>
+        <v>3720</v>
       </c>
       <c r="G138" s="12" t="inlineStr">
         <is>
-          <t>Epic 붉은 집게게 (뽑기권 D)</t>
+          <t>Rare 무예가 (뽑기권 D)</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="13" t="n"/>
       <c r="B139" s="11" t="n">
-        <v>35024</v>
+        <v>35021</v>
       </c>
       <c r="C139" s="11" t="n">
         <v>35</v>
       </c>
       <c r="D139" s="11" t="n">
-        <v>1024</v>
+        <v>1021</v>
       </c>
       <c r="E139" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>3024</v>
+        <v>3720</v>
       </c>
       <c r="G139" s="12" t="inlineStr">
         <is>
-          <t>Epic 대검 전사 (뽑기권 D)</t>
+          <t>Rare 해골 병사 (뽑기권 D)</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="13" t="n"/>
       <c r="B140" s="11" t="n">
-        <v>35025</v>
+        <v>35022</v>
       </c>
       <c r="C140" s="11" t="n">
         <v>35</v>
       </c>
       <c r="D140" s="11" t="n">
-        <v>1025</v>
+        <v>1022</v>
       </c>
       <c r="E140" s="11" t="n">
         <v>1</v>
@@ -11450,20 +11450,20 @@
       </c>
       <c r="G140" s="12" t="inlineStr">
         <is>
-          <t>Epic 검왕 (뽑기권 D)</t>
+          <t>Epic 바위 골렘 (뽑기권 D)</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="13" t="n"/>
       <c r="B141" s="11" t="n">
-        <v>35026</v>
+        <v>35023</v>
       </c>
       <c r="C141" s="11" t="n">
         <v>35</v>
       </c>
       <c r="D141" s="11" t="n">
-        <v>1026</v>
+        <v>1023</v>
       </c>
       <c r="E141" s="11" t="n">
         <v>1</v>
@@ -11473,110 +11473,202 @@
       </c>
       <c r="G141" s="12" t="inlineStr">
         <is>
-          <t>Epic 영웅 기사 (뽑기권 D)</t>
+          <t>Epic 붉은 집게게 (뽑기권 D)</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="13" t="n"/>
       <c r="B142" s="11" t="n">
-        <v>35027</v>
+        <v>35024</v>
       </c>
       <c r="C142" s="11" t="n">
         <v>35</v>
       </c>
       <c r="D142" s="11" t="n">
-        <v>1027</v>
+        <v>1024</v>
       </c>
       <c r="E142" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>2100</v>
+        <v>3024</v>
       </c>
       <c r="G142" s="12" t="inlineStr">
         <is>
-          <t>Legendary 죽음의 사신 (뽑기권 D)</t>
+          <t>Epic 대검 전사 (뽑기권 D)</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="13" t="n"/>
       <c r="B143" s="11" t="n">
-        <v>35028</v>
+        <v>35025</v>
       </c>
       <c r="C143" s="11" t="n">
         <v>35</v>
       </c>
       <c r="D143" s="11" t="n">
-        <v>1028</v>
+        <v>1025</v>
       </c>
       <c r="E143" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>2100</v>
+        <v>3024</v>
       </c>
       <c r="G143" s="12" t="inlineStr">
         <is>
-          <t>Legendary 흑기사 (뽑기권 D)</t>
+          <t>Epic 검왕 (뽑기권 D)</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="13" t="n"/>
       <c r="B144" s="11" t="n">
-        <v>35029</v>
+        <v>35026</v>
       </c>
       <c r="C144" s="11" t="n">
         <v>35</v>
       </c>
       <c r="D144" s="11" t="n">
-        <v>1029</v>
+        <v>1026</v>
       </c>
       <c r="E144" s="11" t="n">
         <v>1</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>2100</v>
+        <v>3024</v>
       </c>
       <c r="G144" s="12" t="inlineStr">
         <is>
-          <t>Legendary 흑요석골렘 (뽑기권 D)</t>
+          <t>Epic 영웅 기사 (뽑기권 D)</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="13" t="n"/>
       <c r="B145" s="11" t="n">
-        <v>35030</v>
+        <v>35027</v>
       </c>
       <c r="C145" s="11" t="n">
         <v>35</v>
       </c>
       <c r="D145" s="11" t="n">
+        <v>1027</v>
+      </c>
+      <c r="E145" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F145" s="11" t="n">
+        <v>2100</v>
+      </c>
+      <c r="G145" s="12" t="inlineStr">
+        <is>
+          <t>Legendary 죽음의 사신 (뽑기권 D)</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="13" t="n"/>
+      <c r="B146" s="11" t="n">
+        <v>35028</v>
+      </c>
+      <c r="C146" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="D146" s="11" t="n">
+        <v>1028</v>
+      </c>
+      <c r="E146" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F146" s="11" t="n">
+        <v>2100</v>
+      </c>
+      <c r="G146" s="12" t="inlineStr">
+        <is>
+          <t>Legendary 흑기사 (뽑기권 D)</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="13" t="n"/>
+      <c r="B147" s="11" t="n">
+        <v>35029</v>
+      </c>
+      <c r="C147" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="D147" s="11" t="n">
+        <v>1029</v>
+      </c>
+      <c r="E147" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F147" s="11" t="n">
+        <v>2100</v>
+      </c>
+      <c r="G147" s="12" t="inlineStr">
+        <is>
+          <t>Legendary 흑요석골렘 (뽑기권 D)</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="13" t="n"/>
+      <c r="B148" s="11" t="n">
+        <v>35030</v>
+      </c>
+      <c r="C148" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="D148" s="11" t="n">
         <v>1030</v>
       </c>
-      <c r="E145" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F145" s="11" t="n">
+      <c r="E148" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F148" s="11" t="n">
         <v>420</v>
       </c>
-      <c r="G145" s="12" t="inlineStr">
+      <c r="G148" s="12" t="inlineStr">
         <is>
           <t>Mythic 질풍 검호 (뽑기권 D)</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="13" t="n"/>
+      <c r="B149" s="11" t="n">
+        <v>35031</v>
+      </c>
+      <c r="C149" s="11" t="n">
+        <v>35</v>
+      </c>
+      <c r="D149" s="11" t="n">
+        <v>1031</v>
+      </c>
+      <c r="E149" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F149" s="11" t="n">
+        <v>2835</v>
+      </c>
+      <c r="G149" s="12" t="inlineStr">
+        <is>
+          <t>Uncommon 숙련 채굴꾼 (뽑기권 D)</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing r:id="anysvml"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -19659,12 +19751,12 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing r:id="anysvml"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -20914,12 +21006,12 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing r:id="anysvml"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
@@ -21665,6 +21757,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing r:id="anysvml"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>